--- a/audit_report_ALL_TEAM_23_Sep_2026.xlsx
+++ b/audit_report_ALL_TEAM_23_Sep_2026.xlsx
@@ -483,7 +483,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AW5"/>
+  <dimension ref="A1:AW6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="23" customWidth="1" min="1" max="1"/>
@@ -494,12 +494,12 @@
     <col width="17" customWidth="1" min="6" max="6"/>
     <col width="18" customWidth="1" min="7" max="7"/>
     <col width="40" customWidth="1" min="8" max="8"/>
-    <col width="13" customWidth="1" min="9" max="9"/>
+    <col width="16" customWidth="1" min="9" max="9"/>
     <col width="16" customWidth="1" min="10" max="10"/>
-    <col width="24" customWidth="1" min="11" max="11"/>
+    <col width="29" customWidth="1" min="11" max="11"/>
     <col width="12" customWidth="1" min="12" max="12"/>
     <col width="14" customWidth="1" min="13" max="13"/>
-    <col width="24" customWidth="1" min="14" max="14"/>
+    <col width="29" customWidth="1" min="14" max="14"/>
     <col width="13" customWidth="1" min="15" max="15"/>
     <col width="27" customWidth="1" min="16" max="16"/>
     <col width="19" customWidth="1" min="17" max="17"/>
@@ -851,10 +851,8 @@
           <t>Rashmi Tuladhar</t>
         </is>
       </c>
-      <c r="O2" s="3" t="inlineStr">
-        <is>
-          <t>9841724979</t>
-        </is>
+      <c r="O2" s="3" t="n">
+        <v>9841724979</v>
       </c>
       <c r="P2" s="3" t="inlineStr">
         <is>
@@ -869,10 +867,8 @@
       </c>
       <c r="S2" s="3" t="inlineStr"/>
       <c r="T2" s="3" t="inlineStr"/>
-      <c r="U2" s="3" t="inlineStr">
-        <is>
-          <t>9841724979</t>
-        </is>
+      <c r="U2" s="3" t="n">
+        <v>9841724979</v>
       </c>
       <c r="V2" s="3" t="inlineStr">
         <is>
@@ -889,10 +885,8 @@
           <t>Active</t>
         </is>
       </c>
-      <c r="Y2" s="3" t="inlineStr">
-        <is>
-          <t>27.70945</t>
-        </is>
+      <c r="Y2" s="3" t="n">
+        <v>27.70945</v>
       </c>
       <c r="Z2" s="3" t="inlineStr">
         <is>
@@ -944,25 +938,21 @@
           <t>Ajit Shrestha</t>
         </is>
       </c>
-      <c r="AN2" s="3" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
+      <c r="AN2" s="3" t="n">
+        <v>4</v>
       </c>
       <c r="AO2" s="3" t="inlineStr">
         <is>
           <t>3,5</t>
         </is>
       </c>
-      <c r="AP2" s="3" t="inlineStr">
-        <is>
-          <t>85.31289</t>
-        </is>
+      <c r="AP2" s="3" t="n">
+        <v>85.31289</v>
       </c>
       <c r="AQ2" s="3" t="inlineStr"/>
       <c r="AR2" s="3" t="inlineStr">
         <is>
-          <t>Case : WiFi 6  has been updated by Ajit Shrestha</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="AS2" s="3" t="inlineStr">
@@ -1058,10 +1048,8 @@
           <t>Bijay Carlos Rana</t>
         </is>
       </c>
-      <c r="O3" s="3" t="inlineStr">
-        <is>
-          <t>9818574527</t>
-        </is>
+      <c r="O3" s="3" t="n">
+        <v>9818574527</v>
       </c>
       <c r="P3" s="3" t="inlineStr">
         <is>
@@ -1076,10 +1064,8 @@
       </c>
       <c r="S3" s="3" t="inlineStr"/>
       <c r="T3" s="3" t="inlineStr"/>
-      <c r="U3" s="3" t="inlineStr">
-        <is>
-          <t>9818574527</t>
-        </is>
+      <c r="U3" s="3" t="n">
+        <v>9818574527</v>
       </c>
       <c r="V3" s="3" t="inlineStr">
         <is>
@@ -1096,10 +1082,8 @@
           <t>Active</t>
         </is>
       </c>
-      <c r="Y3" s="3" t="inlineStr">
-        <is>
-          <t>27.65568</t>
-        </is>
+      <c r="Y3" s="3" t="n">
+        <v>27.65568</v>
       </c>
       <c r="Z3" s="3" t="inlineStr">
         <is>
@@ -1155,25 +1139,21 @@
           <t>Rajesh Maharjan</t>
         </is>
       </c>
-      <c r="AN3" s="3" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
+      <c r="AN3" s="3" t="n">
+        <v>6</v>
       </c>
       <c r="AO3" s="3" t="inlineStr">
         <is>
           <t>CDB114</t>
         </is>
       </c>
-      <c r="AP3" s="3" t="inlineStr">
-        <is>
-          <t>85.30695</t>
-        </is>
+      <c r="AP3" s="3" t="n">
+        <v>85.30695</v>
       </c>
       <c r="AQ3" s="3" t="inlineStr"/>
       <c r="AR3" s="3" t="inlineStr">
         <is>
-          <t>Case : WIFI 6  has been updated by Rajesh Maharjan</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="AS3" s="3" t="inlineStr">
@@ -1269,10 +1249,8 @@
           <t>Krishna Prasad Paudel</t>
         </is>
       </c>
-      <c r="O4" s="3" t="inlineStr">
-        <is>
-          <t>9849481434</t>
-        </is>
+      <c r="O4" s="3" t="n">
+        <v>9849481434</v>
       </c>
       <c r="P4" s="3" t="inlineStr">
         <is>
@@ -1287,10 +1265,8 @@
       </c>
       <c r="S4" s="3" t="inlineStr"/>
       <c r="T4" s="3" t="inlineStr"/>
-      <c r="U4" s="3" t="inlineStr">
-        <is>
-          <t>9849481434</t>
-        </is>
+      <c r="U4" s="3" t="n">
+        <v>9849481434</v>
       </c>
       <c r="V4" s="3" t="inlineStr">
         <is>
@@ -1307,10 +1283,8 @@
           <t>Active</t>
         </is>
       </c>
-      <c r="Y4" s="3" t="inlineStr">
-        <is>
-          <t>27.67106</t>
-        </is>
+      <c r="Y4" s="3" t="n">
+        <v>27.67106</v>
       </c>
       <c r="Z4" s="3" t="inlineStr">
         <is>
@@ -1362,25 +1336,21 @@
           <t>Shashikant Chaudhary</t>
         </is>
       </c>
-      <c r="AN4" s="3" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
+      <c r="AN4" s="3" t="n">
+        <v>6</v>
       </c>
       <c r="AO4" s="3" t="inlineStr">
         <is>
           <t>CDB626</t>
         </is>
       </c>
-      <c r="AP4" s="3" t="inlineStr">
-        <is>
-          <t>85.33733</t>
-        </is>
+      <c r="AP4" s="3" t="n">
+        <v>85.33732999999999</v>
       </c>
       <c r="AQ4" s="3" t="inlineStr"/>
       <c r="AR4" s="3" t="inlineStr">
         <is>
-          <t>Case : SLOW ISSUE   has been updated by Shashikant Chaudhary</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="AS4" s="3" t="inlineStr">
@@ -1476,10 +1446,8 @@
           <t>Kirti Kiran Joshi</t>
         </is>
       </c>
-      <c r="O5" s="3" t="inlineStr">
-        <is>
-          <t>9741673311</t>
-        </is>
+      <c r="O5" s="3" t="n">
+        <v>9741673311</v>
       </c>
       <c r="P5" s="3" t="inlineStr">
         <is>
@@ -1494,10 +1462,8 @@
       </c>
       <c r="S5" s="3" t="inlineStr"/>
       <c r="T5" s="3" t="inlineStr"/>
-      <c r="U5" s="3" t="inlineStr">
-        <is>
-          <t>9841229694</t>
-        </is>
+      <c r="U5" s="3" t="n">
+        <v>9841229694</v>
       </c>
       <c r="V5" s="3" t="inlineStr">
         <is>
@@ -1514,10 +1480,8 @@
           <t>Active</t>
         </is>
       </c>
-      <c r="Y5" s="3" t="inlineStr">
-        <is>
-          <t>27.68406</t>
-        </is>
+      <c r="Y5" s="3" t="n">
+        <v>27.68406</v>
       </c>
       <c r="Z5" s="3" t="inlineStr">
         <is>
@@ -1569,48 +1533,255 @@
           <t>Shashikant Chaudhary</t>
         </is>
       </c>
-      <c r="AN5" s="3" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
+      <c r="AN5" s="3" t="n">
+        <v>4</v>
       </c>
       <c r="AO5" s="3" t="inlineStr">
         <is>
           <t>2,12</t>
         </is>
       </c>
-      <c r="AP5" s="3" t="inlineStr">
-        <is>
-          <t>85.32381</t>
-        </is>
+      <c r="AP5" s="3" t="n">
+        <v>85.32380999999999</v>
       </c>
       <c r="AQ5" s="3" t="inlineStr"/>
       <c r="AR5" s="3" t="inlineStr">
         <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="AS5" s="3" t="inlineStr">
+        <is>
+          <t>56m</t>
+        </is>
+      </c>
+      <c r="AT5" s="3" t="inlineStr">
+        <is>
+          <t>1h 8m</t>
+        </is>
+      </c>
+      <c r="AU5" s="3" t="inlineStr">
+        <is>
+          <t>Other / In Progress (On Hold)</t>
+        </is>
+      </c>
+      <c r="AV5" s="3" t="inlineStr">
+        <is>
           <t>Case : wifi 6  has been updated by Shashikant Chaudhary</t>
         </is>
       </c>
-      <c r="AS5" s="3" t="inlineStr">
-        <is>
-          <t>56m</t>
-        </is>
-      </c>
-      <c r="AT5" s="3" t="inlineStr">
-        <is>
-          <t>1h 8m</t>
-        </is>
-      </c>
-      <c r="AU5" s="3" t="inlineStr">
-        <is>
-          <t>Other / In Progress (On Hold)</t>
-        </is>
-      </c>
-      <c r="AV5" s="3" t="inlineStr">
-        <is>
-          <t>Case : wifi 6  has been updated by Shashikant Chaudhary</t>
-        </is>
-      </c>
       <c r="AW5" s="3" t="inlineStr">
+        <is>
+          <t>WiFi 6 Upgrade</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="3" t="inlineStr">
+        <is>
+          <t>Sabin Giri</t>
+        </is>
+      </c>
+      <c r="B6" s="3" t="inlineStr">
+        <is>
+          <t>23 Sep 2026 12:31 PM</t>
+        </is>
+      </c>
+      <c r="C6" s="3" t="inlineStr">
+        <is>
+          <t>WGnmUJF06LTlUriJ5DeDBQ==</t>
+        </is>
+      </c>
+      <c r="D6" s="3" t="inlineStr">
+        <is>
+          <t>Sabin Giri</t>
+        </is>
+      </c>
+      <c r="E6" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F6" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G6" s="3" t="inlineStr"/>
+      <c r="H6" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi 6 router  has been updated by Sabin Giri</t>
+        </is>
+      </c>
+      <c r="I6" s="3" t="inlineStr">
+        <is>
+          <t>wifi 6 router</t>
+        </is>
+      </c>
+      <c r="J6" s="3" t="inlineStr">
+        <is>
+          <t>TKT1343394</t>
+        </is>
+      </c>
+      <c r="K6" s="3" t="inlineStr">
+        <is>
+          <t>Kaizen Business consultant</t>
+        </is>
+      </c>
+      <c r="L6" s="3" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="M6" s="3" t="inlineStr">
+        <is>
+          <t>Phone</t>
+        </is>
+      </c>
+      <c r="N6" s="3" t="inlineStr">
+        <is>
+          <t>Kaizen Business consultant</t>
+        </is>
+      </c>
+      <c r="O6" s="3" t="inlineStr">
+        <is>
+          <t>9861779555</t>
+        </is>
+      </c>
+      <c r="P6" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="Q6" s="3" t="inlineStr"/>
+      <c r="R6" s="3" t="inlineStr">
+        <is>
+          <t>23 Sep 2026 12:31:18 PM</t>
+        </is>
+      </c>
+      <c r="S6" s="3" t="inlineStr"/>
+      <c r="T6" s="3" t="inlineStr"/>
+      <c r="U6" s="3" t="inlineStr">
+        <is>
+          <t>9861779555</t>
+        </is>
+      </c>
+      <c r="V6" s="3" t="inlineStr">
+        <is>
+          <t>23 Sep 2026 09:53:33 AM</t>
+        </is>
+      </c>
+      <c r="W6" s="3" t="inlineStr">
+        <is>
+          <t>23 Sep 2026 12:31:18 PM</t>
+        </is>
+      </c>
+      <c r="X6" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Y6" s="3" t="inlineStr">
+        <is>
+          <t>27.72821</t>
+        </is>
+      </c>
+      <c r="Z6" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="AA6" s="3" t="inlineStr">
+        <is>
+          <t>Layer 1-User</t>
+        </is>
+      </c>
+      <c r="AB6" s="3" t="inlineStr">
+        <is>
+          <t>L1  Support</t>
+        </is>
+      </c>
+      <c r="AC6" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="AD6" s="3" t="inlineStr"/>
+      <c r="AE6" s="3" t="inlineStr">
+        <is>
+          <t>Bhakta Marg Kiran Chowk,, Bagmati, Central, Nepal</t>
+        </is>
+      </c>
+      <c r="AF6" s="3" t="inlineStr">
+        <is>
+          <t>info.kbcnepal@gmail.com</t>
+        </is>
+      </c>
+      <c r="AG6" s="3" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="AH6" s="3" t="inlineStr"/>
+      <c r="AI6" s="3" t="inlineStr">
+        <is>
+          <t>02:31 hour</t>
+        </is>
+      </c>
+      <c r="AJ6" s="3" t="inlineStr"/>
+      <c r="AK6" s="3" t="inlineStr"/>
+      <c r="AL6" s="3" t="inlineStr">
+        <is>
+          <t>Nisha Joshi</t>
+        </is>
+      </c>
+      <c r="AM6" s="3" t="inlineStr">
+        <is>
+          <t>Sabin Giri</t>
+        </is>
+      </c>
+      <c r="AN6" s="3" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AO6" s="3" t="inlineStr">
+        <is>
+          <t>4,12</t>
+        </is>
+      </c>
+      <c r="AP6" s="3" t="inlineStr">
+        <is>
+          <t>85.32427</t>
+        </is>
+      </c>
+      <c r="AQ6" s="3" t="inlineStr"/>
+      <c r="AR6" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi 6 router  has been updated by Sabin Giri</t>
+        </is>
+      </c>
+      <c r="AS6" s="3" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="AT6" s="3" t="inlineStr">
+        <is>
+          <t>2h 37m</t>
+        </is>
+      </c>
+      <c r="AU6" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Completed)</t>
+        </is>
+      </c>
+      <c r="AV6" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi 6 router  has been updated by Sabin Giri</t>
+        </is>
+      </c>
+      <c r="AW6" s="3" t="inlineStr">
         <is>
           <t>WiFi 6 Upgrade</t>
         </is>
@@ -1627,7 +1798,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M20"/>
+  <dimension ref="A1:M21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="45" customWidth="1" min="1" max="1"/>
@@ -1664,7 +1835,7 @@
         </is>
       </c>
       <c r="B2" s="3" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="3">
@@ -1674,7 +1845,7 @@
         </is>
       </c>
       <c r="B3" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="4">
@@ -1685,7 +1856,7 @@
       </c>
       <c r="B4" s="3" t="inlineStr">
         <is>
-          <t>25.0%</t>
+          <t>40.0%</t>
         </is>
       </c>
     </row>
@@ -1709,7 +1880,7 @@
       </c>
       <c r="B6" s="3" t="inlineStr">
         <is>
-          <t>20h 46m</t>
+          <t>11h 42m</t>
         </is>
       </c>
     </row>
@@ -1750,14 +1921,14 @@
         </is>
       </c>
       <c r="B10" s="3" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C10" s="3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D10" s="3" t="inlineStr">
         <is>
-          <t>33.3%</t>
+          <t>50.0%</t>
         </is>
       </c>
     </row>
@@ -1826,14 +1997,14 @@
         </is>
       </c>
       <c r="C15" s="5" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D15" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E15" s="5" t="inlineStr">
         <is>
-          <t>33.3%</t>
+          <t>50.0%</t>
         </is>
       </c>
     </row>
@@ -1968,14 +2139,14 @@
       </c>
       <c r="G20" s="3" t="inlineStr">
         <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="H20" s="3" t="inlineStr">
+        <is>
           <t>Case : WIFI 6  has been updated by Rajesh Maharjan</t>
         </is>
       </c>
-      <c r="H20" s="3" t="inlineStr">
-        <is>
-          <t>Case : WIFI 6  has been updated by Rajesh Maharjan</t>
-        </is>
-      </c>
       <c r="I20" s="3" t="inlineStr">
         <is>
           <t>23 Sep 2026 11:16:05 AM</t>
@@ -1999,6 +2170,73 @@
       <c r="M20" s="3" t="inlineStr">
         <is>
           <t>20h 46m</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="5" t="inlineStr">
+        <is>
+          <t>TKT1343394</t>
+        </is>
+      </c>
+      <c r="B21" s="5" t="inlineStr">
+        <is>
+          <t>Kaizen Business consultant</t>
+        </is>
+      </c>
+      <c r="C21" s="5" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="D21" s="5" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="E21" s="5" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="F21" s="5" t="inlineStr">
+        <is>
+          <t>Completed (Completed)</t>
+        </is>
+      </c>
+      <c r="G21" s="5" t="inlineStr">
+        <is>
+          <t>Case : wifi 6 router  has been updated by Sabin Giri</t>
+        </is>
+      </c>
+      <c r="H21" s="5" t="inlineStr">
+        <is>
+          <t>Case : wifi 6 router  has been updated by Sabin Giri</t>
+        </is>
+      </c>
+      <c r="I21" s="5" t="inlineStr">
+        <is>
+          <t>23 Sep 2026 12:31:18 PM</t>
+        </is>
+      </c>
+      <c r="J21" s="5" t="inlineStr">
+        <is>
+          <t>23 Sep 2026 09:53:33 AM</t>
+        </is>
+      </c>
+      <c r="K21" s="5" t="inlineStr">
+        <is>
+          <t>23 Sep 2026 12:31:18 PM</t>
+        </is>
+      </c>
+      <c r="L21" s="5" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="M21" s="5" t="inlineStr">
+        <is>
+          <t>2h 37m</t>
         </is>
       </c>
     </row>

--- a/audit_report_ALL_TEAM_23_Sep_2026.xlsx
+++ b/audit_report_ALL_TEAM_23_Sep_2026.xlsx
@@ -483,7 +483,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AW6"/>
+  <dimension ref="A1:AW7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="23" customWidth="1" min="1" max="1"/>
@@ -512,12 +512,12 @@
     <col width="29" customWidth="1" min="24" max="24"/>
     <col width="11" customWidth="1" min="25" max="25"/>
     <col width="27" customWidth="1" min="26" max="26"/>
-    <col width="15" customWidth="1" min="27" max="27"/>
+    <col width="19" customWidth="1" min="27" max="27"/>
     <col width="17" customWidth="1" min="28" max="28"/>
     <col width="11" customWidth="1" min="29" max="29"/>
     <col width="10" customWidth="1" min="30" max="30"/>
     <col width="40" customWidth="1" min="31" max="31"/>
-    <col width="29" customWidth="1" min="32" max="32"/>
+    <col width="33" customWidth="1" min="32" max="32"/>
     <col width="29" customWidth="1" min="33" max="33"/>
     <col width="18" customWidth="1" min="34" max="34"/>
     <col width="13" customWidth="1" min="35" max="35"/>
@@ -1643,10 +1643,8 @@
           <t>Kaizen Business consultant</t>
         </is>
       </c>
-      <c r="O6" s="3" t="inlineStr">
-        <is>
-          <t>9861779555</t>
-        </is>
+      <c r="O6" s="3" t="n">
+        <v>9861779555</v>
       </c>
       <c r="P6" s="3" t="inlineStr">
         <is>
@@ -1661,10 +1659,8 @@
       </c>
       <c r="S6" s="3" t="inlineStr"/>
       <c r="T6" s="3" t="inlineStr"/>
-      <c r="U6" s="3" t="inlineStr">
-        <is>
-          <t>9861779555</t>
-        </is>
+      <c r="U6" s="3" t="n">
+        <v>9861779555</v>
       </c>
       <c r="V6" s="3" t="inlineStr">
         <is>
@@ -1681,10 +1677,8 @@
           <t>Active</t>
         </is>
       </c>
-      <c r="Y6" s="3" t="inlineStr">
-        <is>
-          <t>27.72821</t>
-        </is>
+      <c r="Y6" s="3" t="n">
+        <v>27.72821</v>
       </c>
       <c r="Z6" s="3" t="inlineStr">
         <is>
@@ -1740,48 +1734,259 @@
           <t>Sabin Giri</t>
         </is>
       </c>
-      <c r="AN6" s="3" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
+      <c r="AN6" s="3" t="n">
+        <v>4</v>
       </c>
       <c r="AO6" s="3" t="inlineStr">
         <is>
           <t>4,12</t>
         </is>
       </c>
-      <c r="AP6" s="3" t="inlineStr">
-        <is>
-          <t>85.32427</t>
-        </is>
+      <c r="AP6" s="3" t="n">
+        <v>85.32427</v>
       </c>
       <c r="AQ6" s="3" t="inlineStr"/>
       <c r="AR6" s="3" t="inlineStr">
         <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="AS6" s="3" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="AT6" s="3" t="inlineStr">
+        <is>
+          <t>2h 37m</t>
+        </is>
+      </c>
+      <c r="AU6" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Completed)</t>
+        </is>
+      </c>
+      <c r="AV6" s="3" t="inlineStr">
+        <is>
           <t>Case : wifi 6 router  has been updated by Sabin Giri</t>
         </is>
       </c>
-      <c r="AS6" s="3" t="inlineStr">
+      <c r="AW6" s="3" t="inlineStr">
+        <is>
+          <t>WiFi 6 Upgrade</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="3" t="inlineStr">
+        <is>
+          <t>Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="B7" s="3" t="inlineStr">
+        <is>
+          <t>23 Sep 2026 12:37 PM</t>
+        </is>
+      </c>
+      <c r="C7" s="3" t="inlineStr">
+        <is>
+          <t>w7A8I7MXNVw6IhJoudC/TknnOVKMobUO</t>
+        </is>
+      </c>
+      <c r="D7" s="3" t="inlineStr">
+        <is>
+          <t>Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="E7" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F7" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G7" s="3" t="inlineStr"/>
+      <c r="H7" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi 6  has been updated by Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="I7" s="3" t="inlineStr">
+        <is>
+          <t>wifi 6</t>
+        </is>
+      </c>
+      <c r="J7" s="3" t="inlineStr">
+        <is>
+          <t>TKT1343122</t>
+        </is>
+      </c>
+      <c r="K7" s="3" t="inlineStr">
+        <is>
+          <t>Rajesh Shahi</t>
+        </is>
+      </c>
+      <c r="L7" s="3" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="M7" s="3" t="inlineStr">
+        <is>
+          <t>Phone</t>
+        </is>
+      </c>
+      <c r="N7" s="3" t="inlineStr">
+        <is>
+          <t>Rajesh Shahi</t>
+        </is>
+      </c>
+      <c r="O7" s="3" t="inlineStr">
+        <is>
+          <t>9848052440</t>
+        </is>
+      </c>
+      <c r="P7" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="Q7" s="3" t="inlineStr"/>
+      <c r="R7" s="3" t="inlineStr">
+        <is>
+          <t>23 Sep 2026 12:37:13 PM</t>
+        </is>
+      </c>
+      <c r="S7" s="3" t="inlineStr"/>
+      <c r="T7" s="3" t="inlineStr"/>
+      <c r="U7" s="3" t="inlineStr">
+        <is>
+          <t>9848052440</t>
+        </is>
+      </c>
+      <c r="V7" s="3" t="inlineStr">
+        <is>
+          <t>22 Sep 2026 09:56:18 PM</t>
+        </is>
+      </c>
+      <c r="W7" s="3" t="inlineStr">
+        <is>
+          <t>23 Sep 2026 12:37:13 PM</t>
+        </is>
+      </c>
+      <c r="X7" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Y7" s="3" t="inlineStr">
+        <is>
+          <t>27.69193</t>
+        </is>
+      </c>
+      <c r="Z7" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="AA7" s="3" t="inlineStr">
+        <is>
+          <t>Layer 2-CG Group</t>
+        </is>
+      </c>
+      <c r="AB7" s="3" t="inlineStr">
+        <is>
+          <t>L1  Support</t>
+        </is>
+      </c>
+      <c r="AC7" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="AD7" s="3" t="inlineStr"/>
+      <c r="AE7" s="3" t="inlineStr">
+        <is>
+          <t>Near Butwal Power Co. Ltd., Ganga Devi Marga, Kathmanduutsal, Next To Hungry munk, Kathmandu, Centra</t>
+        </is>
+      </c>
+      <c r="AF7" s="3" t="inlineStr">
+        <is>
+          <t>rajeshshahithakuree1@gmail.com</t>
+        </is>
+      </c>
+      <c r="AG7" s="3" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="AH7" s="3" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AI7" s="3" t="inlineStr">
+        <is>
+          <t>02:37 hour</t>
+        </is>
+      </c>
+      <c r="AJ7" s="3" t="inlineStr"/>
+      <c r="AK7" s="3" t="inlineStr"/>
+      <c r="AL7" s="3" t="inlineStr">
+        <is>
+          <t>Aakash Shah</t>
+        </is>
+      </c>
+      <c r="AM7" s="3" t="inlineStr">
+        <is>
+          <t>Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="AN7" s="3" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AO7" s="3" t="inlineStr">
+        <is>
+          <t>CDB497</t>
+        </is>
+      </c>
+      <c r="AP7" s="3" t="inlineStr">
+        <is>
+          <t>85.34813</t>
+        </is>
+      </c>
+      <c r="AQ7" s="3" t="inlineStr"/>
+      <c r="AR7" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi 6  has been updated by Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="AS7" s="3" t="inlineStr">
         <is>
           <t>0m</t>
         </is>
       </c>
-      <c r="AT6" s="3" t="inlineStr">
-        <is>
-          <t>2h 37m</t>
-        </is>
-      </c>
-      <c r="AU6" s="3" t="inlineStr">
+      <c r="AT7" s="3" t="inlineStr">
+        <is>
+          <t>14h 40m</t>
+        </is>
+      </c>
+      <c r="AU7" s="3" t="inlineStr">
         <is>
           <t>Completed (Completed)</t>
         </is>
       </c>
-      <c r="AV6" s="3" t="inlineStr">
-        <is>
-          <t>Case : wifi 6 router  has been updated by Sabin Giri</t>
-        </is>
-      </c>
-      <c r="AW6" s="3" t="inlineStr">
+      <c r="AV7" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi 6  has been updated by Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="AW7" s="3" t="inlineStr">
         <is>
           <t>WiFi 6 Upgrade</t>
         </is>
@@ -1798,7 +2003,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M21"/>
+  <dimension ref="A1:M22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="45" customWidth="1" min="1" max="1"/>
@@ -1835,7 +2040,7 @@
         </is>
       </c>
       <c r="B2" s="3" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="3">
@@ -1845,7 +2050,7 @@
         </is>
       </c>
       <c r="B3" s="5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="4">
@@ -1856,7 +2061,7 @@
       </c>
       <c r="B4" s="3" t="inlineStr">
         <is>
-          <t>40.0%</t>
+          <t>50.0%</t>
         </is>
       </c>
     </row>
@@ -1880,7 +2085,7 @@
       </c>
       <c r="B6" s="3" t="inlineStr">
         <is>
-          <t>11h 42m</t>
+          <t>12h 41m</t>
         </is>
       </c>
     </row>
@@ -1921,14 +2126,14 @@
         </is>
       </c>
       <c r="B10" s="3" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C10" s="3" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D10" s="3" t="inlineStr">
         <is>
-          <t>50.0%</t>
+          <t>60.0%</t>
         </is>
       </c>
     </row>
@@ -1997,14 +2202,14 @@
         </is>
       </c>
       <c r="C15" s="5" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D15" s="5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E15" s="5" t="inlineStr">
         <is>
-          <t>50.0%</t>
+          <t>60.0%</t>
         </is>
       </c>
     </row>
@@ -2206,14 +2411,14 @@
       </c>
       <c r="G21" s="5" t="inlineStr">
         <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="H21" s="5" t="inlineStr">
+        <is>
           <t>Case : wifi 6 router  has been updated by Sabin Giri</t>
         </is>
       </c>
-      <c r="H21" s="5" t="inlineStr">
-        <is>
-          <t>Case : wifi 6 router  has been updated by Sabin Giri</t>
-        </is>
-      </c>
       <c r="I21" s="5" t="inlineStr">
         <is>
           <t>23 Sep 2026 12:31:18 PM</t>
@@ -2237,6 +2442,73 @@
       <c r="M21" s="5" t="inlineStr">
         <is>
           <t>2h 37m</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="3" t="inlineStr">
+        <is>
+          <t>TKT1343122</t>
+        </is>
+      </c>
+      <c r="B22" s="3" t="inlineStr">
+        <is>
+          <t>Rajesh Shahi</t>
+        </is>
+      </c>
+      <c r="C22" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="D22" s="3" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="E22" s="3" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="F22" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Completed)</t>
+        </is>
+      </c>
+      <c r="G22" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi 6  has been updated by Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="H22" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi 6  has been updated by Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="I22" s="3" t="inlineStr">
+        <is>
+          <t>23 Sep 2026 12:37:13 PM</t>
+        </is>
+      </c>
+      <c r="J22" s="3" t="inlineStr">
+        <is>
+          <t>22 Sep 2026 09:56:18 PM</t>
+        </is>
+      </c>
+      <c r="K22" s="3" t="inlineStr">
+        <is>
+          <t>23 Sep 2026 12:37:13 PM</t>
+        </is>
+      </c>
+      <c r="L22" s="3" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="M22" s="3" t="inlineStr">
+        <is>
+          <t>14h 40m</t>
         </is>
       </c>
     </row>

--- a/audit_report_ALL_TEAM_23_Sep_2026.xlsx
+++ b/audit_report_ALL_TEAM_23_Sep_2026.xlsx
@@ -483,7 +483,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AW7"/>
+  <dimension ref="A1:AW9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="23" customWidth="1" min="1" max="1"/>
@@ -494,7 +494,7 @@
     <col width="17" customWidth="1" min="6" max="6"/>
     <col width="18" customWidth="1" min="7" max="7"/>
     <col width="40" customWidth="1" min="8" max="8"/>
-    <col width="16" customWidth="1" min="9" max="9"/>
+    <col width="19" customWidth="1" min="9" max="9"/>
     <col width="16" customWidth="1" min="10" max="10"/>
     <col width="29" customWidth="1" min="11" max="11"/>
     <col width="12" customWidth="1" min="12" max="12"/>
@@ -506,7 +506,7 @@
     <col width="26" customWidth="1" min="18" max="18"/>
     <col width="37" customWidth="1" min="19" max="19"/>
     <col width="37" customWidth="1" min="20" max="20"/>
-    <col width="13" customWidth="1" min="21" max="21"/>
+    <col width="14" customWidth="1" min="21" max="21"/>
     <col width="26" customWidth="1" min="22" max="22"/>
     <col width="26" customWidth="1" min="23" max="23"/>
     <col width="29" customWidth="1" min="24" max="24"/>
@@ -1844,10 +1844,8 @@
           <t>Rajesh Shahi</t>
         </is>
       </c>
-      <c r="O7" s="3" t="inlineStr">
-        <is>
-          <t>9848052440</t>
-        </is>
+      <c r="O7" s="3" t="n">
+        <v>9848052440</v>
       </c>
       <c r="P7" s="3" t="inlineStr">
         <is>
@@ -1862,10 +1860,8 @@
       </c>
       <c r="S7" s="3" t="inlineStr"/>
       <c r="T7" s="3" t="inlineStr"/>
-      <c r="U7" s="3" t="inlineStr">
-        <is>
-          <t>9848052440</t>
-        </is>
+      <c r="U7" s="3" t="n">
+        <v>9848052440</v>
       </c>
       <c r="V7" s="3" t="inlineStr">
         <is>
@@ -1882,10 +1878,8 @@
           <t>Active</t>
         </is>
       </c>
-      <c r="Y7" s="3" t="inlineStr">
-        <is>
-          <t>27.69193</t>
-        </is>
+      <c r="Y7" s="3" t="n">
+        <v>27.69193</v>
       </c>
       <c r="Z7" s="3" t="inlineStr">
         <is>
@@ -1923,10 +1917,8 @@
           <t>Router Upgrade  Wi-Fi 6</t>
         </is>
       </c>
-      <c r="AH7" s="3" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
+      <c r="AH7" s="3" t="n">
+        <v>2</v>
       </c>
       <c r="AI7" s="3" t="inlineStr">
         <is>
@@ -1945,50 +1937,468 @@
           <t>Shashikant Chaudhary</t>
         </is>
       </c>
-      <c r="AN7" s="3" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
+      <c r="AN7" s="3" t="n">
+        <v>6</v>
       </c>
       <c r="AO7" s="3" t="inlineStr">
         <is>
           <t>CDB497</t>
         </is>
       </c>
-      <c r="AP7" s="3" t="inlineStr">
-        <is>
-          <t>85.34813</t>
-        </is>
+      <c r="AP7" s="3" t="n">
+        <v>85.34813</v>
       </c>
       <c r="AQ7" s="3" t="inlineStr"/>
       <c r="AR7" s="3" t="inlineStr">
         <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="AS7" s="3" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="AT7" s="3" t="inlineStr">
+        <is>
+          <t>14h 40m</t>
+        </is>
+      </c>
+      <c r="AU7" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Completed)</t>
+        </is>
+      </c>
+      <c r="AV7" s="3" t="inlineStr">
+        <is>
           <t>Case : wifi 6  has been updated by Shashikant Chaudhary</t>
         </is>
       </c>
-      <c r="AS7" s="3" t="inlineStr">
+      <c r="AW7" s="3" t="inlineStr">
+        <is>
+          <t>WiFi 6 Upgrade</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="3" t="inlineStr">
+        <is>
+          <t>Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="B8" s="3" t="inlineStr">
+        <is>
+          <t>23 Sep 2026 12:59 PM</t>
+        </is>
+      </c>
+      <c r="C8" s="3" t="inlineStr">
+        <is>
+          <t>w7A8I7MXNVw6IhJoudC/TknnOVKMobUO</t>
+        </is>
+      </c>
+      <c r="D8" s="3" t="inlineStr">
+        <is>
+          <t>Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="E8" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F8" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G8" s="3" t="inlineStr"/>
+      <c r="H8" s="3" t="inlineStr">
+        <is>
+          <t>Case : router change  has been updated by Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="I8" s="3" t="inlineStr">
+        <is>
+          <t>router change</t>
+        </is>
+      </c>
+      <c r="J8" s="3" t="inlineStr">
+        <is>
+          <t>TKT1343670</t>
+        </is>
+      </c>
+      <c r="K8" s="3" t="inlineStr">
+        <is>
+          <t>Suman Shah</t>
+        </is>
+      </c>
+      <c r="L8" s="3" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="M8" s="3" t="inlineStr">
+        <is>
+          <t>Phone</t>
+        </is>
+      </c>
+      <c r="N8" s="3" t="inlineStr">
+        <is>
+          <t>Suman Shah</t>
+        </is>
+      </c>
+      <c r="O8" s="3" t="inlineStr">
+        <is>
+          <t>9851097693</t>
+        </is>
+      </c>
+      <c r="P8" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="Q8" s="3" t="inlineStr"/>
+      <c r="R8" s="3" t="inlineStr">
+        <is>
+          <t>23 Sep 2026 12:59:40 PM</t>
+        </is>
+      </c>
+      <c r="S8" s="3" t="inlineStr"/>
+      <c r="T8" s="3" t="inlineStr"/>
+      <c r="U8" s="3" t="inlineStr">
+        <is>
+          <t>9840588889</t>
+        </is>
+      </c>
+      <c r="V8" s="3" t="inlineStr">
+        <is>
+          <t>23 Sep 2026 12:23:42 PM</t>
+        </is>
+      </c>
+      <c r="W8" s="3" t="inlineStr">
+        <is>
+          <t>23 Sep 2026 12:59:40 PM</t>
+        </is>
+      </c>
+      <c r="X8" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Y8" s="3" t="inlineStr">
+        <is>
+          <t>27.67363</t>
+        </is>
+      </c>
+      <c r="Z8" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="AA8" s="3" t="inlineStr">
+        <is>
+          <t>Layer 1-User</t>
+        </is>
+      </c>
+      <c r="AB8" s="3" t="inlineStr">
+        <is>
+          <t>L1  Support</t>
+        </is>
+      </c>
+      <c r="AC8" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="AD8" s="3" t="inlineStr"/>
+      <c r="AE8" s="3" t="inlineStr">
+        <is>
+          <t>Near Unique Nepal Academy, Bagmati, Central, Nepal</t>
+        </is>
+      </c>
+      <c r="AF8" s="3" t="inlineStr">
+        <is>
+          <t>workcgnet@gmail.com</t>
+        </is>
+      </c>
+      <c r="AG8" s="3" t="inlineStr">
+        <is>
+          <t>Router Upgrade Dual Band</t>
+        </is>
+      </c>
+      <c r="AH8" s="3" t="inlineStr"/>
+      <c r="AI8" s="3" t="inlineStr">
+        <is>
+          <t>00:36 hour</t>
+        </is>
+      </c>
+      <c r="AJ8" s="3" t="inlineStr"/>
+      <c r="AK8" s="3" t="inlineStr"/>
+      <c r="AL8" s="3" t="inlineStr">
+        <is>
+          <t>Sabina K.C</t>
+        </is>
+      </c>
+      <c r="AM8" s="3" t="inlineStr">
+        <is>
+          <t>Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="AN8" s="3" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AO8" s="3" t="inlineStr">
+        <is>
+          <t>L41-5</t>
+        </is>
+      </c>
+      <c r="AP8" s="3" t="inlineStr">
+        <is>
+          <t>85.35691</t>
+        </is>
+      </c>
+      <c r="AQ8" s="3" t="inlineStr"/>
+      <c r="AR8" s="3" t="inlineStr">
+        <is>
+          <t>Case : router change  has been updated by Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="AS8" s="3" t="inlineStr">
         <is>
           <t>0m</t>
         </is>
       </c>
-      <c r="AT7" s="3" t="inlineStr">
-        <is>
-          <t>14h 40m</t>
-        </is>
-      </c>
-      <c r="AU7" s="3" t="inlineStr">
+      <c r="AT8" s="3" t="inlineStr">
+        <is>
+          <t>35m</t>
+        </is>
+      </c>
+      <c r="AU8" s="3" t="inlineStr">
         <is>
           <t>Completed (Completed)</t>
         </is>
       </c>
-      <c r="AV7" s="3" t="inlineStr">
-        <is>
-          <t>Case : wifi 6  has been updated by Shashikant Chaudhary</t>
-        </is>
-      </c>
-      <c r="AW7" s="3" t="inlineStr">
-        <is>
-          <t>WiFi 6 Upgrade</t>
+      <c r="AV8" s="3" t="inlineStr">
+        <is>
+          <t>Case : router change  has been updated by Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="AW8" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="3" t="inlineStr">
+        <is>
+          <t>Ajit Shrestha</t>
+        </is>
+      </c>
+      <c r="B9" s="3" t="inlineStr">
+        <is>
+          <t>23 Sep 2026 12:57 PM</t>
+        </is>
+      </c>
+      <c r="C9" s="3" t="inlineStr">
+        <is>
+          <t>KK1e4rFHODw22QGqrKXwiw==</t>
+        </is>
+      </c>
+      <c r="D9" s="3" t="inlineStr">
+        <is>
+          <t>Ajit Shrestha</t>
+        </is>
+      </c>
+      <c r="E9" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F9" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G9" s="3" t="inlineStr"/>
+      <c r="H9" s="3" t="inlineStr">
+        <is>
+          <t>Case : CONFINGURE ISSUE  has been updated by Ajit Shrestha</t>
+        </is>
+      </c>
+      <c r="I9" s="3" t="inlineStr">
+        <is>
+          <t>CONFINGURE ISSUE</t>
+        </is>
+      </c>
+      <c r="J9" s="3" t="inlineStr">
+        <is>
+          <t>TKT1342524</t>
+        </is>
+      </c>
+      <c r="K9" s="3" t="inlineStr">
+        <is>
+          <t>Nakul Bhandari</t>
+        </is>
+      </c>
+      <c r="L9" s="3" t="inlineStr">
+        <is>
+          <t>Closed</t>
+        </is>
+      </c>
+      <c r="M9" s="3" t="inlineStr">
+        <is>
+          <t>Phone</t>
+        </is>
+      </c>
+      <c r="N9" s="3" t="inlineStr">
+        <is>
+          <t>Nakul Bhandari</t>
+        </is>
+      </c>
+      <c r="O9" s="3" t="inlineStr">
+        <is>
+          <t>9841438557</t>
+        </is>
+      </c>
+      <c r="P9" s="3" t="inlineStr">
+        <is>
+          <t>No Internet Connection</t>
+        </is>
+      </c>
+      <c r="Q9" s="3" t="inlineStr"/>
+      <c r="R9" s="3" t="inlineStr">
+        <is>
+          <t>22 Sep 2026 02:52:24 PM</t>
+        </is>
+      </c>
+      <c r="S9" s="3" t="inlineStr"/>
+      <c r="T9" s="3" t="inlineStr"/>
+      <c r="U9" s="3" t="inlineStr">
+        <is>
+          <t>9841438557N</t>
+        </is>
+      </c>
+      <c r="V9" s="3" t="inlineStr">
+        <is>
+          <t>22 Sep 2026 02:35:30 PM</t>
+        </is>
+      </c>
+      <c r="W9" s="3" t="inlineStr">
+        <is>
+          <t>23 Sep 2026 12:57:31 PM</t>
+        </is>
+      </c>
+      <c r="X9" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Y9" s="3" t="inlineStr">
+        <is>
+          <t>27.7197</t>
+        </is>
+      </c>
+      <c r="Z9" s="3" t="inlineStr">
+        <is>
+          <t>No Internet Connection</t>
+        </is>
+      </c>
+      <c r="AA9" s="3" t="inlineStr">
+        <is>
+          <t>Layer 1-</t>
+        </is>
+      </c>
+      <c r="AB9" s="3" t="inlineStr">
+        <is>
+          <t>Laxman Koirala</t>
+        </is>
+      </c>
+      <c r="AC9" s="3" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="AD9" s="3" t="inlineStr"/>
+      <c r="AE9" s="3" t="inlineStr">
+        <is>
+          <t>Dathu Sadak Way To Prime Collage From Geetanjali Chock, ???????? 44600 near Patanjali Store, Bagmati</t>
+        </is>
+      </c>
+      <c r="AF9" s="3" t="inlineStr">
+        <is>
+          <t>hwtravels@gmail.com</t>
+        </is>
+      </c>
+      <c r="AG9" s="3" t="inlineStr">
+        <is>
+          <t>Configuration Issue</t>
+        </is>
+      </c>
+      <c r="AH9" s="3" t="inlineStr"/>
+      <c r="AI9" s="3" t="inlineStr">
+        <is>
+          <t>08:22 hour</t>
+        </is>
+      </c>
+      <c r="AJ9" s="3" t="inlineStr"/>
+      <c r="AK9" s="3" t="inlineStr"/>
+      <c r="AL9" s="3" t="inlineStr">
+        <is>
+          <t>Sanam Sadar</t>
+        </is>
+      </c>
+      <c r="AM9" s="3" t="inlineStr">
+        <is>
+          <t>Ajit Shrestha</t>
+        </is>
+      </c>
+      <c r="AN9" s="3" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AO9" s="3" t="inlineStr">
+        <is>
+          <t>CDB216</t>
+        </is>
+      </c>
+      <c r="AP9" s="3" t="inlineStr">
+        <is>
+          <t>85.3044</t>
+        </is>
+      </c>
+      <c r="AQ9" s="3" t="inlineStr"/>
+      <c r="AR9" s="3" t="inlineStr">
+        <is>
+          <t>Case : CONFINGURE ISSUE  has been updated by Ajit Shrestha</t>
+        </is>
+      </c>
+      <c r="AS9" s="3" t="inlineStr">
+        <is>
+          <t>22h 5m</t>
+        </is>
+      </c>
+      <c r="AT9" s="3" t="inlineStr">
+        <is>
+          <t>22h 22m</t>
+        </is>
+      </c>
+      <c r="AU9" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Closed)</t>
+        </is>
+      </c>
+      <c r="AV9" s="3" t="inlineStr">
+        <is>
+          <t>Case : CONFINGURE ISSUE  has been updated by Ajit Shrestha</t>
+        </is>
+      </c>
+      <c r="AW9" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
         </is>
       </c>
     </row>
@@ -2003,7 +2413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M22"/>
+  <dimension ref="A1:M27"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="45" customWidth="1" min="1" max="1"/>
@@ -2040,7 +2450,7 @@
         </is>
       </c>
       <c r="B2" s="3" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
     </row>
     <row r="3">
@@ -2050,7 +2460,7 @@
         </is>
       </c>
       <c r="B3" s="5" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
     </row>
     <row r="4">
@@ -2061,7 +2471,7 @@
       </c>
       <c r="B4" s="3" t="inlineStr">
         <is>
-          <t>50.0%</t>
+          <t>62.5%</t>
         </is>
       </c>
     </row>
@@ -2073,7 +2483,7 @@
       </c>
       <c r="B5" s="5" t="inlineStr">
         <is>
-          <t>0m</t>
+          <t>4h 25m</t>
         </is>
       </c>
     </row>
@@ -2085,7 +2495,7 @@
       </c>
       <c r="B6" s="3" t="inlineStr">
         <is>
-          <t>12h 41m</t>
+          <t>12h 12m</t>
         </is>
       </c>
     </row>
@@ -2126,389 +2536,587 @@
         </is>
       </c>
       <c r="B10" s="3" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C10" s="3" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D10" s="3" t="inlineStr">
         <is>
-          <t>60.0%</t>
+          <t>66.7%</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="5" t="inlineStr">
         <is>
-          <t>Slow Internet Connection</t>
+          <t>No Internet Connection</t>
         </is>
       </c>
       <c r="B11" s="5" t="n">
         <v>1</v>
       </c>
       <c r="C11" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="D11" s="5" t="inlineStr">
+        <is>
+          <t>100.0%</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="3" t="inlineStr">
+        <is>
+          <t>Slow Internet Connection</t>
+        </is>
+      </c>
+      <c r="B12" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="C12" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="D11" s="5" t="inlineStr">
+      <c r="D12" s="3" t="inlineStr">
         <is>
           <t>0.0%</t>
         </is>
       </c>
     </row>
-    <row r="12"/>
-    <row r="13">
-      <c r="A13" s="6" t="inlineStr">
+    <row r="13"/>
+    <row r="14">
+      <c r="A14" s="6" t="inlineStr">
         <is>
           <t>Total Tickets Breakdown by Category &amp; Sub Category</t>
         </is>
       </c>
     </row>
-    <row r="14">
-      <c r="A14" s="4" t="inlineStr">
+    <row r="15">
+      <c r="A15" s="4" t="inlineStr">
         <is>
           <t>Category</t>
         </is>
       </c>
-      <c r="B14" s="4" t="inlineStr">
+      <c r="B15" s="4" t="inlineStr">
         <is>
           <t>Sub Category</t>
         </is>
       </c>
-      <c r="C14" s="4" t="inlineStr">
+      <c r="C15" s="4" t="inlineStr">
         <is>
           <t>Total Scraped Tickets</t>
         </is>
       </c>
-      <c r="D14" s="4" t="inlineStr">
+      <c r="D15" s="4" t="inlineStr">
         <is>
           <t>Solved / Handled Count</t>
         </is>
       </c>
-      <c r="E14" s="4" t="inlineStr">
+      <c r="E15" s="4" t="inlineStr">
         <is>
           <t>Solution Rate %</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="5" t="inlineStr">
-        <is>
-          <t>General / Other Issues</t>
-        </is>
-      </c>
-      <c r="B15" s="5" t="inlineStr">
-        <is>
-          <t>Router Upgrade  Wi-Fi 6</t>
-        </is>
-      </c>
-      <c r="C15" s="5" t="n">
-        <v>5</v>
-      </c>
-      <c r="D15" s="5" t="n">
-        <v>3</v>
-      </c>
-      <c r="E15" s="5" t="inlineStr">
-        <is>
-          <t>60.0%</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="3" t="inlineStr">
         <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="B16" s="3" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="C16" s="3" t="n">
+        <v>5</v>
+      </c>
+      <c r="D16" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="E16" s="3" t="inlineStr">
+        <is>
+          <t>60.0%</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="5" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="B17" s="5" t="inlineStr">
+        <is>
+          <t>Router Upgrade Dual Band</t>
+        </is>
+      </c>
+      <c r="C17" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="D17" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="E17" s="5" t="inlineStr">
+        <is>
+          <t>100.0%</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="3" t="inlineStr">
+        <is>
+          <t>No Internet Connection</t>
+        </is>
+      </c>
+      <c r="B18" s="3" t="inlineStr">
+        <is>
+          <t>Configuration Issue</t>
+        </is>
+      </c>
+      <c r="C18" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="D18" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="E18" s="3" t="inlineStr">
+        <is>
+          <t>100.0%</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="5" t="inlineStr">
+        <is>
           <t>Slow Internet Connection</t>
         </is>
       </c>
-      <c r="B16" s="3" t="inlineStr">
+      <c r="B19" s="5" t="inlineStr">
         <is>
           <t>Video content is Buffering</t>
         </is>
       </c>
-      <c r="C16" s="3" t="n">
+      <c r="C19" s="5" t="n">
         <v>1</v>
       </c>
-      <c r="D16" s="3" t="n">
+      <c r="D19" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="E16" s="3" t="inlineStr">
+      <c r="E19" s="5" t="inlineStr">
         <is>
           <t>0.0%</t>
         </is>
       </c>
     </row>
-    <row r="17"/>
-    <row r="18">
-      <c r="A18" s="6" t="inlineStr">
+    <row r="20"/>
+    <row r="21">
+      <c r="A21" s="6" t="inlineStr">
         <is>
           <t>Detailed Solved / Handled Tickets List</t>
         </is>
       </c>
     </row>
-    <row r="19">
-      <c r="A19" s="4" t="inlineStr">
+    <row r="22">
+      <c r="A22" s="4" t="inlineStr">
         <is>
           <t>Ticket Number</t>
         </is>
       </c>
-      <c r="B19" s="4" t="inlineStr">
+      <c r="B22" s="4" t="inlineStr">
         <is>
           <t>Account Name</t>
         </is>
       </c>
-      <c r="C19" s="4" t="inlineStr">
+      <c r="C22" s="4" t="inlineStr">
         <is>
           <t>Category</t>
         </is>
       </c>
-      <c r="D19" s="4" t="inlineStr">
+      <c r="D22" s="4" t="inlineStr">
         <is>
           <t>Sub Category</t>
         </is>
       </c>
-      <c r="E19" s="4" t="inlineStr">
+      <c r="E22" s="4" t="inlineStr">
         <is>
           <t>Status</t>
         </is>
       </c>
-      <c r="F19" s="4" t="inlineStr">
+      <c r="F22" s="4" t="inlineStr">
         <is>
           <t>Resolution Type</t>
         </is>
       </c>
-      <c r="G19" s="4" t="inlineStr">
+      <c r="G22" s="4" t="inlineStr">
         <is>
           <t>Employee Remark / Solution Note</t>
         </is>
       </c>
-      <c r="H19" s="4" t="inlineStr">
+      <c r="H22" s="4" t="inlineStr">
         <is>
           <t>Action / Transfer Remark</t>
         </is>
       </c>
-      <c r="I19" s="4" t="inlineStr">
+      <c r="I22" s="4" t="inlineStr">
         <is>
           <t>Assigned Date</t>
         </is>
       </c>
-      <c r="J19" s="4" t="inlineStr">
+      <c r="J22" s="4" t="inlineStr">
         <is>
           <t>Created Date</t>
         </is>
       </c>
-      <c r="K19" s="4" t="inlineStr">
+      <c r="K22" s="4" t="inlineStr">
         <is>
           <t>Last Modified Date</t>
         </is>
       </c>
-      <c r="L19" s="4" t="inlineStr">
+      <c r="L22" s="4" t="inlineStr">
         <is>
           <t>Resolution Time (From Assigned)</t>
         </is>
       </c>
-      <c r="M19" s="4" t="inlineStr">
+      <c r="M22" s="4" t="inlineStr">
         <is>
           <t>Resolution Time (From Created)</t>
         </is>
       </c>
     </row>
-    <row r="20">
-      <c r="A20" s="3" t="inlineStr">
+    <row r="23">
+      <c r="A23" s="5" t="inlineStr">
         <is>
           <t>TKT1342514</t>
         </is>
       </c>
-      <c r="B20" s="3" t="inlineStr">
+      <c r="B23" s="5" t="inlineStr">
         <is>
           <t>Bijay Carlos Rana</t>
         </is>
       </c>
-      <c r="C20" s="3" t="inlineStr">
+      <c r="C23" s="5" t="inlineStr">
         <is>
           <t>General / Other Issues</t>
         </is>
       </c>
-      <c r="D20" s="3" t="inlineStr">
+      <c r="D23" s="5" t="inlineStr">
         <is>
           <t>Router Upgrade  Wi-Fi 6</t>
         </is>
       </c>
-      <c r="E20" s="3" t="inlineStr">
+      <c r="E23" s="5" t="inlineStr">
         <is>
           <t>Completed</t>
         </is>
       </c>
-      <c r="F20" s="3" t="inlineStr">
+      <c r="F23" s="5" t="inlineStr">
         <is>
           <t>Completed (Completed)</t>
         </is>
       </c>
-      <c r="G20" s="3" t="inlineStr">
+      <c r="G23" s="5" t="inlineStr">
         <is>
           <t>nan</t>
         </is>
       </c>
-      <c r="H20" s="3" t="inlineStr">
+      <c r="H23" s="5" t="inlineStr">
         <is>
           <t>Case : WIFI 6  has been updated by Rajesh Maharjan</t>
         </is>
       </c>
-      <c r="I20" s="3" t="inlineStr">
+      <c r="I23" s="5" t="inlineStr">
         <is>
           <t>23 Sep 2026 11:16:05 AM</t>
         </is>
       </c>
-      <c r="J20" s="3" t="inlineStr">
+      <c r="J23" s="5" t="inlineStr">
         <is>
           <t>22 Sep 2026 02:29:16 PM</t>
         </is>
       </c>
-      <c r="K20" s="3" t="inlineStr">
+      <c r="K23" s="5" t="inlineStr">
         <is>
           <t>23 Sep 2026 11:16:05 AM</t>
         </is>
       </c>
-      <c r="L20" s="3" t="inlineStr">
+      <c r="L23" s="5" t="inlineStr">
         <is>
           <t>0m</t>
         </is>
       </c>
-      <c r="M20" s="3" t="inlineStr">
+      <c r="M23" s="5" t="inlineStr">
         <is>
           <t>20h 46m</t>
         </is>
       </c>
     </row>
-    <row r="21">
-      <c r="A21" s="5" t="inlineStr">
+    <row r="24">
+      <c r="A24" s="3" t="inlineStr">
         <is>
           <t>TKT1343394</t>
         </is>
       </c>
-      <c r="B21" s="5" t="inlineStr">
+      <c r="B24" s="3" t="inlineStr">
         <is>
           <t>Kaizen Business consultant</t>
         </is>
       </c>
-      <c r="C21" s="5" t="inlineStr">
+      <c r="C24" s="3" t="inlineStr">
         <is>
           <t>General / Other Issues</t>
         </is>
       </c>
-      <c r="D21" s="5" t="inlineStr">
+      <c r="D24" s="3" t="inlineStr">
         <is>
           <t>Router Upgrade  Wi-Fi 6</t>
         </is>
       </c>
-      <c r="E21" s="5" t="inlineStr">
+      <c r="E24" s="3" t="inlineStr">
         <is>
           <t>Completed</t>
         </is>
       </c>
-      <c r="F21" s="5" t="inlineStr">
+      <c r="F24" s="3" t="inlineStr">
         <is>
           <t>Completed (Completed)</t>
         </is>
       </c>
-      <c r="G21" s="5" t="inlineStr">
+      <c r="G24" s="3" t="inlineStr">
         <is>
           <t>nan</t>
         </is>
       </c>
-      <c r="H21" s="5" t="inlineStr">
+      <c r="H24" s="3" t="inlineStr">
         <is>
           <t>Case : wifi 6 router  has been updated by Sabin Giri</t>
         </is>
       </c>
-      <c r="I21" s="5" t="inlineStr">
+      <c r="I24" s="3" t="inlineStr">
         <is>
           <t>23 Sep 2026 12:31:18 PM</t>
         </is>
       </c>
-      <c r="J21" s="5" t="inlineStr">
+      <c r="J24" s="3" t="inlineStr">
         <is>
           <t>23 Sep 2026 09:53:33 AM</t>
         </is>
       </c>
-      <c r="K21" s="5" t="inlineStr">
+      <c r="K24" s="3" t="inlineStr">
         <is>
           <t>23 Sep 2026 12:31:18 PM</t>
         </is>
       </c>
-      <c r="L21" s="5" t="inlineStr">
+      <c r="L24" s="3" t="inlineStr">
         <is>
           <t>0m</t>
         </is>
       </c>
-      <c r="M21" s="5" t="inlineStr">
+      <c r="M24" s="3" t="inlineStr">
         <is>
           <t>2h 37m</t>
         </is>
       </c>
     </row>
-    <row r="22">
-      <c r="A22" s="3" t="inlineStr">
+    <row r="25">
+      <c r="A25" s="5" t="inlineStr">
         <is>
           <t>TKT1343122</t>
         </is>
       </c>
-      <c r="B22" s="3" t="inlineStr">
+      <c r="B25" s="5" t="inlineStr">
         <is>
           <t>Rajesh Shahi</t>
         </is>
       </c>
-      <c r="C22" s="3" t="inlineStr">
+      <c r="C25" s="5" t="inlineStr">
         <is>
           <t>General / Other Issues</t>
         </is>
       </c>
-      <c r="D22" s="3" t="inlineStr">
+      <c r="D25" s="5" t="inlineStr">
         <is>
           <t>Router Upgrade  Wi-Fi 6</t>
         </is>
       </c>
-      <c r="E22" s="3" t="inlineStr">
+      <c r="E25" s="5" t="inlineStr">
         <is>
           <t>Completed</t>
         </is>
       </c>
-      <c r="F22" s="3" t="inlineStr">
+      <c r="F25" s="5" t="inlineStr">
         <is>
           <t>Completed (Completed)</t>
         </is>
       </c>
-      <c r="G22" s="3" t="inlineStr">
+      <c r="G25" s="5" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="H25" s="5" t="inlineStr">
         <is>
           <t>Case : wifi 6  has been updated by Shashikant Chaudhary</t>
         </is>
       </c>
-      <c r="H22" s="3" t="inlineStr">
-        <is>
-          <t>Case : wifi 6  has been updated by Shashikant Chaudhary</t>
-        </is>
-      </c>
-      <c r="I22" s="3" t="inlineStr">
+      <c r="I25" s="5" t="inlineStr">
         <is>
           <t>23 Sep 2026 12:37:13 PM</t>
         </is>
       </c>
-      <c r="J22" s="3" t="inlineStr">
+      <c r="J25" s="5" t="inlineStr">
         <is>
           <t>22 Sep 2026 09:56:18 PM</t>
         </is>
       </c>
-      <c r="K22" s="3" t="inlineStr">
+      <c r="K25" s="5" t="inlineStr">
         <is>
           <t>23 Sep 2026 12:37:13 PM</t>
         </is>
       </c>
-      <c r="L22" s="3" t="inlineStr">
+      <c r="L25" s="5" t="inlineStr">
         <is>
           <t>0m</t>
         </is>
       </c>
-      <c r="M22" s="3" t="inlineStr">
+      <c r="M25" s="5" t="inlineStr">
         <is>
           <t>14h 40m</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="3" t="inlineStr">
+        <is>
+          <t>TKT1343670</t>
+        </is>
+      </c>
+      <c r="B26" s="3" t="inlineStr">
+        <is>
+          <t>Suman Shah</t>
+        </is>
+      </c>
+      <c r="C26" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="D26" s="3" t="inlineStr">
+        <is>
+          <t>Router Upgrade Dual Band</t>
+        </is>
+      </c>
+      <c r="E26" s="3" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="F26" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Completed)</t>
+        </is>
+      </c>
+      <c r="G26" s="3" t="inlineStr">
+        <is>
+          <t>Case : router change  has been updated by Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="H26" s="3" t="inlineStr">
+        <is>
+          <t>Case : router change  has been updated by Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="I26" s="3" t="inlineStr">
+        <is>
+          <t>23 Sep 2026 12:59:40 PM</t>
+        </is>
+      </c>
+      <c r="J26" s="3" t="inlineStr">
+        <is>
+          <t>23 Sep 2026 12:23:42 PM</t>
+        </is>
+      </c>
+      <c r="K26" s="3" t="inlineStr">
+        <is>
+          <t>23 Sep 2026 12:59:40 PM</t>
+        </is>
+      </c>
+      <c r="L26" s="3" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="M26" s="3" t="inlineStr">
+        <is>
+          <t>35m</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="5" t="inlineStr">
+        <is>
+          <t>TKT1342524</t>
+        </is>
+      </c>
+      <c r="B27" s="5" t="inlineStr">
+        <is>
+          <t>Nakul Bhandari</t>
+        </is>
+      </c>
+      <c r="C27" s="5" t="inlineStr">
+        <is>
+          <t>No Internet Connection</t>
+        </is>
+      </c>
+      <c r="D27" s="5" t="inlineStr">
+        <is>
+          <t>Configuration Issue</t>
+        </is>
+      </c>
+      <c r="E27" s="5" t="inlineStr">
+        <is>
+          <t>Closed</t>
+        </is>
+      </c>
+      <c r="F27" s="5" t="inlineStr">
+        <is>
+          <t>Completed (Closed)</t>
+        </is>
+      </c>
+      <c r="G27" s="5" t="inlineStr">
+        <is>
+          <t>Case : CONFINGURE ISSUE  has been updated by Ajit Shrestha</t>
+        </is>
+      </c>
+      <c r="H27" s="5" t="inlineStr">
+        <is>
+          <t>Case : CONFINGURE ISSUE  has been updated by Ajit Shrestha</t>
+        </is>
+      </c>
+      <c r="I27" s="5" t="inlineStr">
+        <is>
+          <t>22 Sep 2026 02:52:24 PM</t>
+        </is>
+      </c>
+      <c r="J27" s="5" t="inlineStr">
+        <is>
+          <t>22 Sep 2026 02:35:30 PM</t>
+        </is>
+      </c>
+      <c r="K27" s="5" t="inlineStr">
+        <is>
+          <t>23 Sep 2026 12:57:31 PM</t>
+        </is>
+      </c>
+      <c r="L27" s="5" t="inlineStr">
+        <is>
+          <t>22h 5m</t>
+        </is>
+      </c>
+      <c r="M27" s="5" t="inlineStr">
+        <is>
+          <t>22h 22m</t>
         </is>
       </c>
     </row>

--- a/audit_report_ALL_TEAM_23_Sep_2026.xlsx
+++ b/audit_report_ALL_TEAM_23_Sep_2026.xlsx
@@ -483,7 +483,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AW9"/>
+  <dimension ref="A1:AW10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="23" customWidth="1" min="1" max="1"/>
@@ -494,7 +494,7 @@
     <col width="17" customWidth="1" min="6" max="6"/>
     <col width="18" customWidth="1" min="7" max="7"/>
     <col width="40" customWidth="1" min="8" max="8"/>
-    <col width="19" customWidth="1" min="9" max="9"/>
+    <col width="27" customWidth="1" min="9" max="9"/>
     <col width="16" customWidth="1" min="10" max="10"/>
     <col width="29" customWidth="1" min="11" max="11"/>
     <col width="12" customWidth="1" min="12" max="12"/>
@@ -2047,10 +2047,8 @@
           <t>Suman Shah</t>
         </is>
       </c>
-      <c r="O8" s="3" t="inlineStr">
-        <is>
-          <t>9851097693</t>
-        </is>
+      <c r="O8" s="3" t="n">
+        <v>9851097693</v>
       </c>
       <c r="P8" s="3" t="inlineStr">
         <is>
@@ -2085,10 +2083,8 @@
           <t>Active</t>
         </is>
       </c>
-      <c r="Y8" s="3" t="inlineStr">
-        <is>
-          <t>27.67363</t>
-        </is>
+      <c r="Y8" s="3" t="n">
+        <v>27.67363</v>
       </c>
       <c r="Z8" s="3" t="inlineStr">
         <is>
@@ -2144,25 +2140,21 @@
           <t>Shashikant Chaudhary</t>
         </is>
       </c>
-      <c r="AN8" s="3" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
+      <c r="AN8" s="3" t="n">
+        <v>6</v>
       </c>
       <c r="AO8" s="3" t="inlineStr">
         <is>
           <t>L41-5</t>
         </is>
       </c>
-      <c r="AP8" s="3" t="inlineStr">
-        <is>
-          <t>85.35691</t>
-        </is>
+      <c r="AP8" s="3" t="n">
+        <v>85.35691</v>
       </c>
       <c r="AQ8" s="3" t="inlineStr"/>
       <c r="AR8" s="3" t="inlineStr">
         <is>
-          <t>Case : router change  has been updated by Shashikant Chaudhary</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="AS8" s="3" t="inlineStr">
@@ -2258,10 +2250,8 @@
           <t>Nakul Bhandari</t>
         </is>
       </c>
-      <c r="O9" s="3" t="inlineStr">
-        <is>
-          <t>9841438557</t>
-        </is>
+      <c r="O9" s="3" t="n">
+        <v>9841438557</v>
       </c>
       <c r="P9" s="3" t="inlineStr">
         <is>
@@ -2296,10 +2286,8 @@
           <t>Active</t>
         </is>
       </c>
-      <c r="Y9" s="3" t="inlineStr">
-        <is>
-          <t>27.7197</t>
-        </is>
+      <c r="Y9" s="3" t="n">
+        <v>27.7197</v>
       </c>
       <c r="Z9" s="3" t="inlineStr">
         <is>
@@ -2355,50 +2343,249 @@
           <t>Ajit Shrestha</t>
         </is>
       </c>
-      <c r="AN9" s="3" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
+      <c r="AN9" s="3" t="n">
+        <v>6</v>
       </c>
       <c r="AO9" s="3" t="inlineStr">
         <is>
           <t>CDB216</t>
         </is>
       </c>
-      <c r="AP9" s="3" t="inlineStr">
-        <is>
-          <t>85.3044</t>
-        </is>
+      <c r="AP9" s="3" t="n">
+        <v>85.3044</v>
       </c>
       <c r="AQ9" s="3" t="inlineStr"/>
       <c r="AR9" s="3" t="inlineStr">
         <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="AS9" s="3" t="inlineStr">
+        <is>
+          <t>22h 5m</t>
+        </is>
+      </c>
+      <c r="AT9" s="3" t="inlineStr">
+        <is>
+          <t>22h 22m</t>
+        </is>
+      </c>
+      <c r="AU9" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Closed)</t>
+        </is>
+      </c>
+      <c r="AV9" s="3" t="inlineStr">
+        <is>
           <t>Case : CONFINGURE ISSUE  has been updated by Ajit Shrestha</t>
         </is>
       </c>
-      <c r="AS9" s="3" t="inlineStr">
-        <is>
-          <t>22h 5m</t>
-        </is>
-      </c>
-      <c r="AT9" s="3" t="inlineStr">
-        <is>
-          <t>22h 22m</t>
-        </is>
-      </c>
-      <c r="AU9" s="3" t="inlineStr">
-        <is>
-          <t>Completed (Closed)</t>
-        </is>
-      </c>
-      <c r="AV9" s="3" t="inlineStr">
-        <is>
-          <t>Case : CONFINGURE ISSUE  has been updated by Ajit Shrestha</t>
-        </is>
-      </c>
       <c r="AW9" s="3" t="inlineStr">
         <is>
           <t>General / Other Issues</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="3" t="inlineStr">
+        <is>
+          <t>Sabin Giri</t>
+        </is>
+      </c>
+      <c r="B10" s="3" t="inlineStr">
+        <is>
+          <t>23 Sep 2026 1:01 PM</t>
+        </is>
+      </c>
+      <c r="C10" s="3" t="inlineStr">
+        <is>
+          <t>WGnmUJF06LTlUriJ5DeDBQ==</t>
+        </is>
+      </c>
+      <c r="D10" s="3" t="inlineStr">
+        <is>
+          <t>Sabin Giri</t>
+        </is>
+      </c>
+      <c r="E10" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F10" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G10" s="3" t="inlineStr"/>
+      <c r="H10" s="3" t="inlineStr">
+        <is>
+          <t>Case : For upgradation to wifi6   has been updated by Sabin Giri</t>
+        </is>
+      </c>
+      <c r="I10" s="3" t="inlineStr">
+        <is>
+          <t>For upgradation to wifi6</t>
+        </is>
+      </c>
+      <c r="J10" s="3" t="inlineStr">
+        <is>
+          <t>TKT1342923</t>
+        </is>
+      </c>
+      <c r="K10" s="3" t="inlineStr">
+        <is>
+          <t>Maan maya poon</t>
+        </is>
+      </c>
+      <c r="L10" s="3" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="M10" s="3" t="inlineStr">
+        <is>
+          <t>Phone</t>
+        </is>
+      </c>
+      <c r="N10" s="3" t="inlineStr">
+        <is>
+          <t>Maan maya poon</t>
+        </is>
+      </c>
+      <c r="O10" s="3" t="inlineStr">
+        <is>
+          <t>9841732687</t>
+        </is>
+      </c>
+      <c r="P10" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="Q10" s="3" t="inlineStr"/>
+      <c r="R10" s="3" t="inlineStr">
+        <is>
+          <t>23 Sep 2026 01:01:06 PM</t>
+        </is>
+      </c>
+      <c r="S10" s="3" t="inlineStr"/>
+      <c r="T10" s="3" t="inlineStr"/>
+      <c r="U10" s="3" t="inlineStr">
+        <is>
+          <t>9869608121</t>
+        </is>
+      </c>
+      <c r="V10" s="3" t="inlineStr">
+        <is>
+          <t>22 Sep 2026 06:58:31 PM</t>
+        </is>
+      </c>
+      <c r="W10" s="3" t="inlineStr">
+        <is>
+          <t>23 Sep 2026 01:01:06 PM</t>
+        </is>
+      </c>
+      <c r="X10" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Y10" s="3" t="inlineStr"/>
+      <c r="Z10" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="AA10" s="3" t="inlineStr">
+        <is>
+          <t>Layer 2-CG Group</t>
+        </is>
+      </c>
+      <c r="AB10" s="3" t="inlineStr">
+        <is>
+          <t>L1  Support</t>
+        </is>
+      </c>
+      <c r="AC10" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="AD10" s="3" t="inlineStr"/>
+      <c r="AE10" s="3" t="inlineStr">
+        <is>
+          <t>Near Ganeshthan - Housing development P8P8+W48 Gongbu Road Tokha 44600, Bagmati, Central, Nepal</t>
+        </is>
+      </c>
+      <c r="AF10" s="3" t="inlineStr"/>
+      <c r="AG10" s="3" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="AH10" s="3" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AI10" s="3" t="inlineStr">
+        <is>
+          <t>04:03 hour</t>
+        </is>
+      </c>
+      <c r="AJ10" s="3" t="inlineStr"/>
+      <c r="AK10" s="3" t="inlineStr"/>
+      <c r="AL10" s="3" t="inlineStr">
+        <is>
+          <t>Pradeep Yadav</t>
+        </is>
+      </c>
+      <c r="AM10" s="3" t="inlineStr">
+        <is>
+          <t>Sabin Giri</t>
+        </is>
+      </c>
+      <c r="AN10" s="3" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AO10" s="3" t="inlineStr">
+        <is>
+          <t>L41-1</t>
+        </is>
+      </c>
+      <c r="AP10" s="3" t="inlineStr"/>
+      <c r="AQ10" s="3" t="inlineStr"/>
+      <c r="AR10" s="3" t="inlineStr">
+        <is>
+          <t>Case : For upgradation to wifi6   has been updated by Sabin Giri</t>
+        </is>
+      </c>
+      <c r="AS10" s="3" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="AT10" s="3" t="inlineStr">
+        <is>
+          <t>18h 2m</t>
+        </is>
+      </c>
+      <c r="AU10" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Completed)</t>
+        </is>
+      </c>
+      <c r="AV10" s="3" t="inlineStr">
+        <is>
+          <t>Case : For upgradation to wifi6   has been updated by Sabin Giri</t>
+        </is>
+      </c>
+      <c r="AW10" s="3" t="inlineStr">
+        <is>
+          <t>WiFi 6 Upgrade</t>
         </is>
       </c>
     </row>
@@ -2413,7 +2600,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M27"/>
+  <dimension ref="A1:M28"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="45" customWidth="1" min="1" max="1"/>
@@ -2450,7 +2637,7 @@
         </is>
       </c>
       <c r="B2" s="3" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="3">
@@ -2460,7 +2647,7 @@
         </is>
       </c>
       <c r="B3" s="5" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="4">
@@ -2471,7 +2658,7 @@
       </c>
       <c r="B4" s="3" t="inlineStr">
         <is>
-          <t>62.5%</t>
+          <t>66.7%</t>
         </is>
       </c>
     </row>
@@ -2483,7 +2670,7 @@
       </c>
       <c r="B5" s="5" t="inlineStr">
         <is>
-          <t>4h 25m</t>
+          <t>3h 40m</t>
         </is>
       </c>
     </row>
@@ -2495,7 +2682,7 @@
       </c>
       <c r="B6" s="3" t="inlineStr">
         <is>
-          <t>12h 12m</t>
+          <t>13h 11m</t>
         </is>
       </c>
     </row>
@@ -2536,14 +2723,14 @@
         </is>
       </c>
       <c r="B10" s="3" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C10" s="3" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D10" s="3" t="inlineStr">
         <is>
-          <t>66.7%</t>
+          <t>71.4%</t>
         </is>
       </c>
     </row>
@@ -2630,14 +2817,14 @@
         </is>
       </c>
       <c r="C16" s="3" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D16" s="3" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E16" s="3" t="inlineStr">
         <is>
-          <t>60.0%</t>
+          <t>66.7%</t>
         </is>
       </c>
     </row>
@@ -3019,7 +3206,7 @@
       </c>
       <c r="G26" s="3" t="inlineStr">
         <is>
-          <t>Case : router change  has been updated by Shashikant Chaudhary</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="H26" s="3" t="inlineStr">
@@ -3086,14 +3273,14 @@
       </c>
       <c r="G27" s="5" t="inlineStr">
         <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="H27" s="5" t="inlineStr">
+        <is>
           <t>Case : CONFINGURE ISSUE  has been updated by Ajit Shrestha</t>
         </is>
       </c>
-      <c r="H27" s="5" t="inlineStr">
-        <is>
-          <t>Case : CONFINGURE ISSUE  has been updated by Ajit Shrestha</t>
-        </is>
-      </c>
       <c r="I27" s="5" t="inlineStr">
         <is>
           <t>22 Sep 2026 02:52:24 PM</t>
@@ -3117,6 +3304,73 @@
       <c r="M27" s="5" t="inlineStr">
         <is>
           <t>22h 22m</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="3" t="inlineStr">
+        <is>
+          <t>TKT1342923</t>
+        </is>
+      </c>
+      <c r="B28" s="3" t="inlineStr">
+        <is>
+          <t>Maan maya poon</t>
+        </is>
+      </c>
+      <c r="C28" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="D28" s="3" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="E28" s="3" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="F28" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Completed)</t>
+        </is>
+      </c>
+      <c r="G28" s="3" t="inlineStr">
+        <is>
+          <t>Case : For upgradation to wifi6   has been updated by Sabin Giri</t>
+        </is>
+      </c>
+      <c r="H28" s="3" t="inlineStr">
+        <is>
+          <t>Case : For upgradation to wifi6   has been updated by Sabin Giri</t>
+        </is>
+      </c>
+      <c r="I28" s="3" t="inlineStr">
+        <is>
+          <t>23 Sep 2026 01:01:06 PM</t>
+        </is>
+      </c>
+      <c r="J28" s="3" t="inlineStr">
+        <is>
+          <t>22 Sep 2026 06:58:31 PM</t>
+        </is>
+      </c>
+      <c r="K28" s="3" t="inlineStr">
+        <is>
+          <t>23 Sep 2026 01:01:06 PM</t>
+        </is>
+      </c>
+      <c r="L28" s="3" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="M28" s="3" t="inlineStr">
+        <is>
+          <t>18h 2m</t>
         </is>
       </c>
     </row>

--- a/audit_report_ALL_TEAM_23_Sep_2026.xlsx
+++ b/audit_report_ALL_TEAM_23_Sep_2026.xlsx
@@ -529,7 +529,7 @@
     <col width="27" customWidth="1" min="41" max="41"/>
     <col width="12" customWidth="1" min="42" max="42"/>
     <col width="17" customWidth="1" min="43" max="43"/>
-    <col width="40" customWidth="1" min="44" max="44"/>
+    <col width="34" customWidth="1" min="44" max="44"/>
     <col width="34" customWidth="1" min="45" max="45"/>
     <col width="33" customWidth="1" min="46" max="46"/>
     <col width="32" customWidth="1" min="47" max="47"/>
@@ -2453,10 +2453,8 @@
           <t>Maan maya poon</t>
         </is>
       </c>
-      <c r="O10" s="3" t="inlineStr">
-        <is>
-          <t>9841732687</t>
-        </is>
+      <c r="O10" s="3" t="n">
+        <v>9841732687</v>
       </c>
       <c r="P10" s="3" t="inlineStr">
         <is>
@@ -2524,10 +2522,8 @@
           <t>Router Upgrade  Wi-Fi 6</t>
         </is>
       </c>
-      <c r="AH10" s="3" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
+      <c r="AH10" s="3" t="n">
+        <v>2</v>
       </c>
       <c r="AI10" s="3" t="inlineStr">
         <is>
@@ -2546,10 +2542,8 @@
           <t>Sabin Giri</t>
         </is>
       </c>
-      <c r="AN10" s="3" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
+      <c r="AN10" s="3" t="n">
+        <v>6</v>
       </c>
       <c r="AO10" s="3" t="inlineStr">
         <is>
@@ -2560,7 +2554,7 @@
       <c r="AQ10" s="3" t="inlineStr"/>
       <c r="AR10" s="3" t="inlineStr">
         <is>
-          <t>Case : For upgradation to wifi6   has been updated by Sabin Giri</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="AS10" s="3" t="inlineStr">
@@ -2609,7 +2603,7 @@
     <col width="28" customWidth="1" min="4" max="4"/>
     <col width="19" customWidth="1" min="5" max="5"/>
     <col width="25" customWidth="1" min="6" max="6"/>
-    <col width="45" customWidth="1" min="7" max="7"/>
+    <col width="35" customWidth="1" min="7" max="7"/>
     <col width="45" customWidth="1" min="8" max="8"/>
     <col width="27" customWidth="1" min="9" max="9"/>
     <col width="27" customWidth="1" min="10" max="10"/>
@@ -3340,7 +3334,7 @@
       </c>
       <c r="G28" s="3" t="inlineStr">
         <is>
-          <t>Case : For upgradation to wifi6   has been updated by Sabin Giri</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="H28" s="3" t="inlineStr">

--- a/audit_report_ALL_TEAM_23_Sep_2026.xlsx
+++ b/audit_report_ALL_TEAM_23_Sep_2026.xlsx
@@ -483,7 +483,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AW10"/>
+  <dimension ref="A1:AW13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="23" customWidth="1" min="1" max="1"/>
@@ -501,7 +501,7 @@
     <col width="14" customWidth="1" min="13" max="13"/>
     <col width="29" customWidth="1" min="14" max="14"/>
     <col width="13" customWidth="1" min="15" max="15"/>
-    <col width="27" customWidth="1" min="16" max="16"/>
+    <col width="32" customWidth="1" min="16" max="16"/>
     <col width="19" customWidth="1" min="17" max="17"/>
     <col width="26" customWidth="1" min="18" max="18"/>
     <col width="37" customWidth="1" min="19" max="19"/>
@@ -511,13 +511,13 @@
     <col width="26" customWidth="1" min="23" max="23"/>
     <col width="29" customWidth="1" min="24" max="24"/>
     <col width="11" customWidth="1" min="25" max="25"/>
-    <col width="27" customWidth="1" min="26" max="26"/>
+    <col width="32" customWidth="1" min="26" max="26"/>
     <col width="19" customWidth="1" min="27" max="27"/>
     <col width="17" customWidth="1" min="28" max="28"/>
     <col width="11" customWidth="1" min="29" max="29"/>
     <col width="10" customWidth="1" min="30" max="30"/>
     <col width="40" customWidth="1" min="31" max="31"/>
-    <col width="33" customWidth="1" min="32" max="32"/>
+    <col width="34" customWidth="1" min="32" max="32"/>
     <col width="29" customWidth="1" min="33" max="33"/>
     <col width="18" customWidth="1" min="34" max="34"/>
     <col width="13" customWidth="1" min="35" max="35"/>
@@ -529,7 +529,7 @@
     <col width="27" customWidth="1" min="41" max="41"/>
     <col width="12" customWidth="1" min="42" max="42"/>
     <col width="17" customWidth="1" min="43" max="43"/>
-    <col width="34" customWidth="1" min="44" max="44"/>
+    <col width="40" customWidth="1" min="44" max="44"/>
     <col width="34" customWidth="1" min="45" max="45"/>
     <col width="33" customWidth="1" min="46" max="46"/>
     <col width="32" customWidth="1" min="47" max="47"/>
@@ -2578,6 +2578,639 @@
         </is>
       </c>
       <c r="AW10" s="3" t="inlineStr">
+        <is>
+          <t>WiFi 6 Upgrade</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="3" t="inlineStr">
+        <is>
+          <t>Sabin Giri</t>
+        </is>
+      </c>
+      <c r="B11" s="3" t="inlineStr">
+        <is>
+          <t>23 Sep 2026 1:17 PM</t>
+        </is>
+      </c>
+      <c r="C11" s="3" t="inlineStr">
+        <is>
+          <t>WGnmUJF06LTlUriJ5DeDBQ==</t>
+        </is>
+      </c>
+      <c r="D11" s="3" t="inlineStr">
+        <is>
+          <t>Sabin Giri</t>
+        </is>
+      </c>
+      <c r="E11" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F11" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G11" s="3" t="inlineStr"/>
+      <c r="H11" s="3" t="inlineStr">
+        <is>
+          <t>Case : Wifi 6  has been updated by Sabin Giri</t>
+        </is>
+      </c>
+      <c r="I11" s="3" t="inlineStr">
+        <is>
+          <t>Wifi 6</t>
+        </is>
+      </c>
+      <c r="J11" s="3" t="inlineStr">
+        <is>
+          <t>TKT1343451</t>
+        </is>
+      </c>
+      <c r="K11" s="3" t="inlineStr">
+        <is>
+          <t>Sabin Maharjan</t>
+        </is>
+      </c>
+      <c r="L11" s="3" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="M11" s="3" t="inlineStr">
+        <is>
+          <t>Phone</t>
+        </is>
+      </c>
+      <c r="N11" s="3" t="inlineStr">
+        <is>
+          <t>Sabin Maharjan</t>
+        </is>
+      </c>
+      <c r="O11" s="3" t="inlineStr">
+        <is>
+          <t>9843366470</t>
+        </is>
+      </c>
+      <c r="P11" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="Q11" s="3" t="inlineStr"/>
+      <c r="R11" s="3" t="inlineStr">
+        <is>
+          <t>23 Sep 2026 01:17:39 PM</t>
+        </is>
+      </c>
+      <c r="S11" s="3" t="inlineStr"/>
+      <c r="T11" s="3" t="inlineStr"/>
+      <c r="U11" s="3" t="inlineStr">
+        <is>
+          <t>9843366470</t>
+        </is>
+      </c>
+      <c r="V11" s="3" t="inlineStr">
+        <is>
+          <t>23 Sep 2026 10:26:34 AM</t>
+        </is>
+      </c>
+      <c r="W11" s="3" t="inlineStr">
+        <is>
+          <t>23 Sep 2026 01:17:39 PM</t>
+        </is>
+      </c>
+      <c r="X11" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Y11" s="3" t="inlineStr">
+        <is>
+          <t>27.74905</t>
+        </is>
+      </c>
+      <c r="Z11" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="AA11" s="3" t="inlineStr">
+        <is>
+          <t>Layer 1-User</t>
+        </is>
+      </c>
+      <c r="AB11" s="3" t="inlineStr">
+        <is>
+          <t>L1  Support</t>
+        </is>
+      </c>
+      <c r="AC11" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="AD11" s="3" t="inlineStr"/>
+      <c r="AE11" s="3" t="inlineStr">
+        <is>
+          <t>Himalayan Valley English Boarding School,Baniyatar Rd 11, Tokha, , ,</t>
+        </is>
+      </c>
+      <c r="AF11" s="3" t="inlineStr">
+        <is>
+          <t>sanjimaharjan0@gmail.com</t>
+        </is>
+      </c>
+      <c r="AG11" s="3" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="AH11" s="3" t="inlineStr"/>
+      <c r="AI11" s="3" t="inlineStr">
+        <is>
+          <t>02:51 hour</t>
+        </is>
+      </c>
+      <c r="AJ11" s="3" t="inlineStr"/>
+      <c r="AK11" s="3" t="inlineStr"/>
+      <c r="AL11" s="3" t="inlineStr">
+        <is>
+          <t>Sandesh Ghale</t>
+        </is>
+      </c>
+      <c r="AM11" s="3" t="inlineStr">
+        <is>
+          <t>Sabin Giri</t>
+        </is>
+      </c>
+      <c r="AN11" s="3" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AO11" s="3" t="inlineStr">
+        <is>
+          <t>L39-7</t>
+        </is>
+      </c>
+      <c r="AP11" s="3" t="inlineStr">
+        <is>
+          <t>85.31771</t>
+        </is>
+      </c>
+      <c r="AQ11" s="3" t="inlineStr"/>
+      <c r="AR11" s="3" t="inlineStr">
+        <is>
+          <t>Case : Wifi 6  has been updated by Sabin Giri</t>
+        </is>
+      </c>
+      <c r="AS11" s="3" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="AT11" s="3" t="inlineStr">
+        <is>
+          <t>2h 51m</t>
+        </is>
+      </c>
+      <c r="AU11" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Completed)</t>
+        </is>
+      </c>
+      <c r="AV11" s="3" t="inlineStr">
+        <is>
+          <t>Case : Wifi 6  has been updated by Sabin Giri</t>
+        </is>
+      </c>
+      <c r="AW11" s="3" t="inlineStr">
+        <is>
+          <t>WiFi 6 Upgrade</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="3" t="inlineStr">
+        <is>
+          <t>Ajit Shrestha</t>
+        </is>
+      </c>
+      <c r="B12" s="3" t="inlineStr">
+        <is>
+          <t>23 Sep 2026 1:16 PM</t>
+        </is>
+      </c>
+      <c r="C12" s="3" t="inlineStr">
+        <is>
+          <t>KK1e4rFHODw22QGqrKXwiw==</t>
+        </is>
+      </c>
+      <c r="D12" s="3" t="inlineStr">
+        <is>
+          <t>Ajit Shrestha</t>
+        </is>
+      </c>
+      <c r="E12" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F12" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G12" s="3" t="inlineStr"/>
+      <c r="H12" s="3" t="inlineStr">
+        <is>
+          <t>Case : IP TV not Working   has been updated by Ajit Shrestha</t>
+        </is>
+      </c>
+      <c r="I12" s="3" t="inlineStr">
+        <is>
+          <t>IP TV not Working</t>
+        </is>
+      </c>
+      <c r="J12" s="3" t="inlineStr">
+        <is>
+          <t>TKT1343062</t>
+        </is>
+      </c>
+      <c r="K12" s="3" t="inlineStr">
+        <is>
+          <t>Sabin Magar</t>
+        </is>
+      </c>
+      <c r="L12" s="3" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="M12" s="3" t="inlineStr">
+        <is>
+          <t>Self Care</t>
+        </is>
+      </c>
+      <c r="N12" s="3" t="inlineStr">
+        <is>
+          <t>Sabin Magar</t>
+        </is>
+      </c>
+      <c r="O12" s="3" t="inlineStr">
+        <is>
+          <t>9813664152</t>
+        </is>
+      </c>
+      <c r="P12" s="3" t="inlineStr">
+        <is>
+          <t>Hardware Damage / Malfunction</t>
+        </is>
+      </c>
+      <c r="Q12" s="3" t="inlineStr"/>
+      <c r="R12" s="3" t="inlineStr">
+        <is>
+          <t>23 Sep 2026 01:16:47 PM</t>
+        </is>
+      </c>
+      <c r="S12" s="3" t="inlineStr"/>
+      <c r="T12" s="3" t="inlineStr"/>
+      <c r="U12" s="3" t="inlineStr">
+        <is>
+          <t>9813664152</t>
+        </is>
+      </c>
+      <c r="V12" s="3" t="inlineStr">
+        <is>
+          <t>22 Sep 2026 08:56:52 PM</t>
+        </is>
+      </c>
+      <c r="W12" s="3" t="inlineStr">
+        <is>
+          <t>23 Sep 2026 01:16:47 PM</t>
+        </is>
+      </c>
+      <c r="X12" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Y12" s="3" t="inlineStr">
+        <is>
+          <t>27.70515</t>
+        </is>
+      </c>
+      <c r="Z12" s="3" t="inlineStr">
+        <is>
+          <t>Hardware Damage / Malfunction</t>
+        </is>
+      </c>
+      <c r="AA12" s="3" t="inlineStr">
+        <is>
+          <t>Layer 1-User</t>
+        </is>
+      </c>
+      <c r="AB12" s="3" t="inlineStr">
+        <is>
+          <t>L1  Support</t>
+        </is>
+      </c>
+      <c r="AC12" s="3" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="AD12" s="3" t="inlineStr">
+        <is>
+          <t>Problem</t>
+        </is>
+      </c>
+      <c r="AE12" s="3" t="inlineStr">
+        <is>
+          <t>P842+3W9, ???????: ?????, Kathmandu 44600 near Paropakar Furniture, Bagmati, Central, Nepal</t>
+        </is>
+      </c>
+      <c r="AF12" s="3" t="inlineStr">
+        <is>
+          <t>sabinmagar4152@gmail.com</t>
+        </is>
+      </c>
+      <c r="AG12" s="3" t="inlineStr">
+        <is>
+          <t>IPTV STB box Damage Issue</t>
+        </is>
+      </c>
+      <c r="AH12" s="3" t="inlineStr"/>
+      <c r="AI12" s="3" t="inlineStr">
+        <is>
+          <t>03:16 hour</t>
+        </is>
+      </c>
+      <c r="AJ12" s="3" t="inlineStr"/>
+      <c r="AK12" s="3" t="inlineStr"/>
+      <c r="AL12" s="3" t="inlineStr"/>
+      <c r="AM12" s="3" t="inlineStr">
+        <is>
+          <t>Ajit Shrestha</t>
+        </is>
+      </c>
+      <c r="AN12" s="3" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AO12" s="3" t="inlineStr">
+        <is>
+          <t>4,11</t>
+        </is>
+      </c>
+      <c r="AP12" s="3" t="inlineStr">
+        <is>
+          <t>85.302205</t>
+        </is>
+      </c>
+      <c r="AQ12" s="3" t="inlineStr"/>
+      <c r="AR12" s="3" t="inlineStr">
+        <is>
+          <t>Case : IP TV not Working   has been updated by Ajit Shrestha</t>
+        </is>
+      </c>
+      <c r="AS12" s="3" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="AT12" s="3" t="inlineStr">
+        <is>
+          <t>16h 19m</t>
+        </is>
+      </c>
+      <c r="AU12" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Completed)</t>
+        </is>
+      </c>
+      <c r="AV12" s="3" t="inlineStr">
+        <is>
+          <t>Case : IP TV not Working   has been updated by Ajit Shrestha</t>
+        </is>
+      </c>
+      <c r="AW12" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="3" t="inlineStr">
+        <is>
+          <t>Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="B13" s="3" t="inlineStr">
+        <is>
+          <t>23 Sep 2026 1:22 PM</t>
+        </is>
+      </c>
+      <c r="C13" s="3" t="inlineStr">
+        <is>
+          <t>Zg1bIUI+iSmQ1fi360NaxA==</t>
+        </is>
+      </c>
+      <c r="D13" s="3" t="inlineStr">
+        <is>
+          <t>Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="E13" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F13" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G13" s="3" t="inlineStr"/>
+      <c r="H13" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi 6  has been updated by Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="I13" s="3" t="inlineStr">
+        <is>
+          <t>wifi 6</t>
+        </is>
+      </c>
+      <c r="J13" s="3" t="inlineStr">
+        <is>
+          <t>TKT1341347</t>
+        </is>
+      </c>
+      <c r="K13" s="3" t="inlineStr">
+        <is>
+          <t>Siddhartha Model School</t>
+        </is>
+      </c>
+      <c r="L13" s="3" t="inlineStr">
+        <is>
+          <t>Closed</t>
+        </is>
+      </c>
+      <c r="M13" s="3" t="inlineStr">
+        <is>
+          <t>Phone</t>
+        </is>
+      </c>
+      <c r="N13" s="3" t="inlineStr">
+        <is>
+          <t>Siddhartha Model School</t>
+        </is>
+      </c>
+      <c r="O13" s="3" t="inlineStr">
+        <is>
+          <t>9849893921</t>
+        </is>
+      </c>
+      <c r="P13" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="Q13" s="3" t="inlineStr"/>
+      <c r="R13" s="3" t="inlineStr">
+        <is>
+          <t>21 Sep 2026 01:35:47 PM</t>
+        </is>
+      </c>
+      <c r="S13" s="3" t="inlineStr"/>
+      <c r="T13" s="3" t="inlineStr"/>
+      <c r="U13" s="3" t="inlineStr">
+        <is>
+          <t>9851039654</t>
+        </is>
+      </c>
+      <c r="V13" s="3" t="inlineStr">
+        <is>
+          <t>21 Sep 2026 01:35:47 PM</t>
+        </is>
+      </c>
+      <c r="W13" s="3" t="inlineStr">
+        <is>
+          <t>23 Sep 2026 01:22:44 PM</t>
+        </is>
+      </c>
+      <c r="X13" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Y13" s="3" t="inlineStr">
+        <is>
+          <t>27.74454</t>
+        </is>
+      </c>
+      <c r="Z13" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="AA13" s="3" t="inlineStr">
+        <is>
+          <t>Layer 1-</t>
+        </is>
+      </c>
+      <c r="AB13" s="3" t="inlineStr">
+        <is>
+          <t>Laxman Koirala</t>
+        </is>
+      </c>
+      <c r="AC13" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="AD13" s="3" t="inlineStr"/>
+      <c r="AE13" s="3" t="inlineStr">
+        <is>
+          <t>sesmati naya basti word-8 Tarakeshwar near  behind Gramin Adarsha Multiple College, Bagmati, Central</t>
+        </is>
+      </c>
+      <c r="AF13" s="3" t="inlineStr">
+        <is>
+          <t>Schoolsiddharthamodel@gmail.com</t>
+        </is>
+      </c>
+      <c r="AG13" s="3" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="AH13" s="3" t="inlineStr"/>
+      <c r="AI13" s="3" t="inlineStr">
+        <is>
+          <t>19:47 hour</t>
+        </is>
+      </c>
+      <c r="AJ13" s="3" t="inlineStr"/>
+      <c r="AK13" s="3" t="inlineStr"/>
+      <c r="AL13" s="3" t="inlineStr">
+        <is>
+          <t>Monika Chaudhary</t>
+        </is>
+      </c>
+      <c r="AM13" s="3" t="inlineStr">
+        <is>
+          <t>Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="AN13" s="3" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AO13" s="3" t="inlineStr">
+        <is>
+          <t>L21-8</t>
+        </is>
+      </c>
+      <c r="AP13" s="3" t="inlineStr">
+        <is>
+          <t>85.3016</t>
+        </is>
+      </c>
+      <c r="AQ13" s="3" t="inlineStr"/>
+      <c r="AR13" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi 6  has been updated by Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="AS13" s="3" t="inlineStr">
+        <is>
+          <t>1d 23h 46m</t>
+        </is>
+      </c>
+      <c r="AT13" s="3" t="inlineStr">
+        <is>
+          <t>1d 23h 46m</t>
+        </is>
+      </c>
+      <c r="AU13" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Closed)</t>
+        </is>
+      </c>
+      <c r="AV13" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi 6  has been updated by Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="AW13" s="3" t="inlineStr">
         <is>
           <t>WiFi 6 Upgrade</t>
         </is>
@@ -2594,16 +3227,16 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M28"/>
+  <dimension ref="A1:M33"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="45" customWidth="1" min="1" max="1"/>
     <col width="30" customWidth="1" min="2" max="2"/>
-    <col width="26" customWidth="1" min="3" max="3"/>
-    <col width="28" customWidth="1" min="4" max="4"/>
+    <col width="33" customWidth="1" min="3" max="3"/>
+    <col width="29" customWidth="1" min="4" max="4"/>
     <col width="19" customWidth="1" min="5" max="5"/>
     <col width="25" customWidth="1" min="6" max="6"/>
-    <col width="35" customWidth="1" min="7" max="7"/>
+    <col width="45" customWidth="1" min="7" max="7"/>
     <col width="45" customWidth="1" min="8" max="8"/>
     <col width="27" customWidth="1" min="9" max="9"/>
     <col width="27" customWidth="1" min="10" max="10"/>
@@ -2631,7 +3264,7 @@
         </is>
       </c>
       <c r="B2" s="3" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
     </row>
     <row r="3">
@@ -2641,7 +3274,7 @@
         </is>
       </c>
       <c r="B3" s="5" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
     </row>
     <row r="4">
@@ -2652,7 +3285,7 @@
       </c>
       <c r="B4" s="3" t="inlineStr">
         <is>
-          <t>66.7%</t>
+          <t>75.0%</t>
         </is>
       </c>
     </row>
@@ -2664,7 +3297,7 @@
       </c>
       <c r="B5" s="5" t="inlineStr">
         <is>
-          <t>3h 40m</t>
+          <t>7h 45m</t>
         </is>
       </c>
     </row>
@@ -2676,7 +3309,7 @@
       </c>
       <c r="B6" s="3" t="inlineStr">
         <is>
-          <t>13h 11m</t>
+          <t>16h 13m</t>
         </is>
       </c>
     </row>
@@ -2717,21 +3350,21 @@
         </is>
       </c>
       <c r="B10" s="3" t="n">
+        <v>9</v>
+      </c>
+      <c r="C10" s="3" t="n">
         <v>7</v>
       </c>
-      <c r="C10" s="3" t="n">
-        <v>5</v>
-      </c>
       <c r="D10" s="3" t="inlineStr">
         <is>
-          <t>71.4%</t>
+          <t>77.8%</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="5" t="inlineStr">
         <is>
-          <t>No Internet Connection</t>
+          <t>Hardware Damage / Malfunction</t>
         </is>
       </c>
       <c r="B11" s="5" t="n">
@@ -2749,76 +3382,71 @@
     <row r="12">
       <c r="A12" s="3" t="inlineStr">
         <is>
-          <t>Slow Internet Connection</t>
+          <t>No Internet Connection</t>
         </is>
       </c>
       <c r="B12" s="3" t="n">
         <v>1</v>
       </c>
       <c r="C12" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="D12" s="3" t="inlineStr">
+        <is>
+          <t>100.0%</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="5" t="inlineStr">
+        <is>
+          <t>Slow Internet Connection</t>
+        </is>
+      </c>
+      <c r="B13" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="C13" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="D12" s="3" t="inlineStr">
+      <c r="D13" s="5" t="inlineStr">
         <is>
           <t>0.0%</t>
         </is>
       </c>
     </row>
-    <row r="13"/>
-    <row r="14">
-      <c r="A14" s="6" t="inlineStr">
+    <row r="14"/>
+    <row r="15">
+      <c r="A15" s="6" t="inlineStr">
         <is>
           <t>Total Tickets Breakdown by Category &amp; Sub Category</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="4" t="inlineStr">
-        <is>
-          <t>Category</t>
-        </is>
-      </c>
-      <c r="B15" s="4" t="inlineStr">
-        <is>
-          <t>Sub Category</t>
-        </is>
-      </c>
-      <c r="C15" s="4" t="inlineStr">
-        <is>
-          <t>Total Scraped Tickets</t>
-        </is>
-      </c>
-      <c r="D15" s="4" t="inlineStr">
-        <is>
-          <t>Solved / Handled Count</t>
-        </is>
-      </c>
-      <c r="E15" s="4" t="inlineStr">
-        <is>
-          <t>Solution Rate %</t>
         </is>
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="3" t="inlineStr">
-        <is>
-          <t>General / Other Issues</t>
-        </is>
-      </c>
-      <c r="B16" s="3" t="inlineStr">
-        <is>
-          <t>Router Upgrade  Wi-Fi 6</t>
-        </is>
-      </c>
-      <c r="C16" s="3" t="n">
-        <v>6</v>
-      </c>
-      <c r="D16" s="3" t="n">
-        <v>4</v>
-      </c>
-      <c r="E16" s="3" t="inlineStr">
-        <is>
-          <t>66.7%</t>
+      <c r="A16" s="4" t="inlineStr">
+        <is>
+          <t>Category</t>
+        </is>
+      </c>
+      <c r="B16" s="4" t="inlineStr">
+        <is>
+          <t>Sub Category</t>
+        </is>
+      </c>
+      <c r="C16" s="4" t="inlineStr">
+        <is>
+          <t>Total Scraped Tickets</t>
+        </is>
+      </c>
+      <c r="D16" s="4" t="inlineStr">
+        <is>
+          <t>Solved / Handled Count</t>
+        </is>
+      </c>
+      <c r="E16" s="4" t="inlineStr">
+        <is>
+          <t>Solution Rate %</t>
         </is>
       </c>
     </row>
@@ -2830,30 +3458,30 @@
       </c>
       <c r="B17" s="5" t="inlineStr">
         <is>
-          <t>Router Upgrade Dual Band</t>
+          <t>Router Upgrade  Wi-Fi 6</t>
         </is>
       </c>
       <c r="C17" s="5" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="D17" s="5" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="E17" s="5" t="inlineStr">
         <is>
-          <t>100.0%</t>
+          <t>75.0%</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="3" t="inlineStr">
         <is>
-          <t>No Internet Connection</t>
+          <t>General / Other Issues</t>
         </is>
       </c>
       <c r="B18" s="3" t="inlineStr">
         <is>
-          <t>Configuration Issue</t>
+          <t>Router Upgrade Dual Band</t>
         </is>
       </c>
       <c r="C18" s="3" t="n">
@@ -2871,244 +3499,156 @@
     <row r="19">
       <c r="A19" s="5" t="inlineStr">
         <is>
-          <t>Slow Internet Connection</t>
+          <t>Hardware Damage / Malfunction</t>
         </is>
       </c>
       <c r="B19" s="5" t="inlineStr">
         <is>
-          <t>Video content is Buffering</t>
+          <t>IPTV STB box Damage Issue</t>
         </is>
       </c>
       <c r="C19" s="5" t="n">
         <v>1</v>
       </c>
       <c r="D19" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="E19" s="5" t="inlineStr">
+        <is>
+          <t>100.0%</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="3" t="inlineStr">
+        <is>
+          <t>No Internet Connection</t>
+        </is>
+      </c>
+      <c r="B20" s="3" t="inlineStr">
+        <is>
+          <t>Configuration Issue</t>
+        </is>
+      </c>
+      <c r="C20" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="D20" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="E20" s="3" t="inlineStr">
+        <is>
+          <t>100.0%</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="5" t="inlineStr">
+        <is>
+          <t>Slow Internet Connection</t>
+        </is>
+      </c>
+      <c r="B21" s="5" t="inlineStr">
+        <is>
+          <t>Video content is Buffering</t>
+        </is>
+      </c>
+      <c r="C21" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="D21" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="E19" s="5" t="inlineStr">
+      <c r="E21" s="5" t="inlineStr">
         <is>
           <t>0.0%</t>
         </is>
       </c>
     </row>
-    <row r="20"/>
-    <row r="21">
-      <c r="A21" s="6" t="inlineStr">
+    <row r="22"/>
+    <row r="23">
+      <c r="A23" s="6" t="inlineStr">
         <is>
           <t>Detailed Solved / Handled Tickets List</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" s="4" t="inlineStr">
-        <is>
-          <t>Ticket Number</t>
-        </is>
-      </c>
-      <c r="B22" s="4" t="inlineStr">
-        <is>
-          <t>Account Name</t>
-        </is>
-      </c>
-      <c r="C22" s="4" t="inlineStr">
-        <is>
-          <t>Category</t>
-        </is>
-      </c>
-      <c r="D22" s="4" t="inlineStr">
-        <is>
-          <t>Sub Category</t>
-        </is>
-      </c>
-      <c r="E22" s="4" t="inlineStr">
-        <is>
-          <t>Status</t>
-        </is>
-      </c>
-      <c r="F22" s="4" t="inlineStr">
-        <is>
-          <t>Resolution Type</t>
-        </is>
-      </c>
-      <c r="G22" s="4" t="inlineStr">
-        <is>
-          <t>Employee Remark / Solution Note</t>
-        </is>
-      </c>
-      <c r="H22" s="4" t="inlineStr">
-        <is>
-          <t>Action / Transfer Remark</t>
-        </is>
-      </c>
-      <c r="I22" s="4" t="inlineStr">
-        <is>
-          <t>Assigned Date</t>
-        </is>
-      </c>
-      <c r="J22" s="4" t="inlineStr">
-        <is>
-          <t>Created Date</t>
-        </is>
-      </c>
-      <c r="K22" s="4" t="inlineStr">
-        <is>
-          <t>Last Modified Date</t>
-        </is>
-      </c>
-      <c r="L22" s="4" t="inlineStr">
-        <is>
-          <t>Resolution Time (From Assigned)</t>
-        </is>
-      </c>
-      <c r="M22" s="4" t="inlineStr">
-        <is>
-          <t>Resolution Time (From Created)</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" s="5" t="inlineStr">
-        <is>
-          <t>TKT1342514</t>
-        </is>
-      </c>
-      <c r="B23" s="5" t="inlineStr">
-        <is>
-          <t>Bijay Carlos Rana</t>
-        </is>
-      </c>
-      <c r="C23" s="5" t="inlineStr">
-        <is>
-          <t>General / Other Issues</t>
-        </is>
-      </c>
-      <c r="D23" s="5" t="inlineStr">
-        <is>
-          <t>Router Upgrade  Wi-Fi 6</t>
-        </is>
-      </c>
-      <c r="E23" s="5" t="inlineStr">
-        <is>
-          <t>Completed</t>
-        </is>
-      </c>
-      <c r="F23" s="5" t="inlineStr">
-        <is>
-          <t>Completed (Completed)</t>
-        </is>
-      </c>
-      <c r="G23" s="5" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
-      <c r="H23" s="5" t="inlineStr">
-        <is>
-          <t>Case : WIFI 6  has been updated by Rajesh Maharjan</t>
-        </is>
-      </c>
-      <c r="I23" s="5" t="inlineStr">
-        <is>
-          <t>23 Sep 2026 11:16:05 AM</t>
-        </is>
-      </c>
-      <c r="J23" s="5" t="inlineStr">
-        <is>
-          <t>22 Sep 2026 02:29:16 PM</t>
-        </is>
-      </c>
-      <c r="K23" s="5" t="inlineStr">
-        <is>
-          <t>23 Sep 2026 11:16:05 AM</t>
-        </is>
-      </c>
-      <c r="L23" s="5" t="inlineStr">
-        <is>
-          <t>0m</t>
-        </is>
-      </c>
-      <c r="M23" s="5" t="inlineStr">
-        <is>
-          <t>20h 46m</t>
         </is>
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="3" t="inlineStr">
-        <is>
-          <t>TKT1343394</t>
-        </is>
-      </c>
-      <c r="B24" s="3" t="inlineStr">
-        <is>
-          <t>Kaizen Business consultant</t>
-        </is>
-      </c>
-      <c r="C24" s="3" t="inlineStr">
-        <is>
-          <t>General / Other Issues</t>
-        </is>
-      </c>
-      <c r="D24" s="3" t="inlineStr">
-        <is>
-          <t>Router Upgrade  Wi-Fi 6</t>
-        </is>
-      </c>
-      <c r="E24" s="3" t="inlineStr">
-        <is>
-          <t>Completed</t>
-        </is>
-      </c>
-      <c r="F24" s="3" t="inlineStr">
-        <is>
-          <t>Completed (Completed)</t>
-        </is>
-      </c>
-      <c r="G24" s="3" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
-      <c r="H24" s="3" t="inlineStr">
-        <is>
-          <t>Case : wifi 6 router  has been updated by Sabin Giri</t>
-        </is>
-      </c>
-      <c r="I24" s="3" t="inlineStr">
-        <is>
-          <t>23 Sep 2026 12:31:18 PM</t>
-        </is>
-      </c>
-      <c r="J24" s="3" t="inlineStr">
-        <is>
-          <t>23 Sep 2026 09:53:33 AM</t>
-        </is>
-      </c>
-      <c r="K24" s="3" t="inlineStr">
-        <is>
-          <t>23 Sep 2026 12:31:18 PM</t>
-        </is>
-      </c>
-      <c r="L24" s="3" t="inlineStr">
-        <is>
-          <t>0m</t>
-        </is>
-      </c>
-      <c r="M24" s="3" t="inlineStr">
-        <is>
-          <t>2h 37m</t>
+      <c r="A24" s="4" t="inlineStr">
+        <is>
+          <t>Ticket Number</t>
+        </is>
+      </c>
+      <c r="B24" s="4" t="inlineStr">
+        <is>
+          <t>Account Name</t>
+        </is>
+      </c>
+      <c r="C24" s="4" t="inlineStr">
+        <is>
+          <t>Category</t>
+        </is>
+      </c>
+      <c r="D24" s="4" t="inlineStr">
+        <is>
+          <t>Sub Category</t>
+        </is>
+      </c>
+      <c r="E24" s="4" t="inlineStr">
+        <is>
+          <t>Status</t>
+        </is>
+      </c>
+      <c r="F24" s="4" t="inlineStr">
+        <is>
+          <t>Resolution Type</t>
+        </is>
+      </c>
+      <c r="G24" s="4" t="inlineStr">
+        <is>
+          <t>Employee Remark / Solution Note</t>
+        </is>
+      </c>
+      <c r="H24" s="4" t="inlineStr">
+        <is>
+          <t>Action / Transfer Remark</t>
+        </is>
+      </c>
+      <c r="I24" s="4" t="inlineStr">
+        <is>
+          <t>Assigned Date</t>
+        </is>
+      </c>
+      <c r="J24" s="4" t="inlineStr">
+        <is>
+          <t>Created Date</t>
+        </is>
+      </c>
+      <c r="K24" s="4" t="inlineStr">
+        <is>
+          <t>Last Modified Date</t>
+        </is>
+      </c>
+      <c r="L24" s="4" t="inlineStr">
+        <is>
+          <t>Resolution Time (From Assigned)</t>
+        </is>
+      </c>
+      <c r="M24" s="4" t="inlineStr">
+        <is>
+          <t>Resolution Time (From Created)</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="5" t="inlineStr">
         <is>
-          <t>TKT1343122</t>
+          <t>TKT1342514</t>
         </is>
       </c>
       <c r="B25" s="5" t="inlineStr">
         <is>
-          <t>Rajesh Shahi</t>
+          <t>Bijay Carlos Rana</t>
         </is>
       </c>
       <c r="C25" s="5" t="inlineStr">
@@ -3138,22 +3678,22 @@
       </c>
       <c r="H25" s="5" t="inlineStr">
         <is>
-          <t>Case : wifi 6  has been updated by Shashikant Chaudhary</t>
+          <t>Case : WIFI 6  has been updated by Rajesh Maharjan</t>
         </is>
       </c>
       <c r="I25" s="5" t="inlineStr">
         <is>
-          <t>23 Sep 2026 12:37:13 PM</t>
+          <t>23 Sep 2026 11:16:05 AM</t>
         </is>
       </c>
       <c r="J25" s="5" t="inlineStr">
         <is>
-          <t>22 Sep 2026 09:56:18 PM</t>
+          <t>22 Sep 2026 02:29:16 PM</t>
         </is>
       </c>
       <c r="K25" s="5" t="inlineStr">
         <is>
-          <t>23 Sep 2026 12:37:13 PM</t>
+          <t>23 Sep 2026 11:16:05 AM</t>
         </is>
       </c>
       <c r="L25" s="5" t="inlineStr">
@@ -3163,19 +3703,19 @@
       </c>
       <c r="M25" s="5" t="inlineStr">
         <is>
-          <t>14h 40m</t>
+          <t>20h 46m</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="3" t="inlineStr">
         <is>
-          <t>TKT1343670</t>
+          <t>TKT1343394</t>
         </is>
       </c>
       <c r="B26" s="3" t="inlineStr">
         <is>
-          <t>Suman Shah</t>
+          <t>Kaizen Business consultant</t>
         </is>
       </c>
       <c r="C26" s="3" t="inlineStr">
@@ -3185,7 +3725,7 @@
       </c>
       <c r="D26" s="3" t="inlineStr">
         <is>
-          <t>Router Upgrade Dual Band</t>
+          <t>Router Upgrade  Wi-Fi 6</t>
         </is>
       </c>
       <c r="E26" s="3" t="inlineStr">
@@ -3205,22 +3745,22 @@
       </c>
       <c r="H26" s="3" t="inlineStr">
         <is>
-          <t>Case : router change  has been updated by Shashikant Chaudhary</t>
+          <t>Case : wifi 6 router  has been updated by Sabin Giri</t>
         </is>
       </c>
       <c r="I26" s="3" t="inlineStr">
         <is>
-          <t>23 Sep 2026 12:59:40 PM</t>
+          <t>23 Sep 2026 12:31:18 PM</t>
         </is>
       </c>
       <c r="J26" s="3" t="inlineStr">
         <is>
-          <t>23 Sep 2026 12:23:42 PM</t>
+          <t>23 Sep 2026 09:53:33 AM</t>
         </is>
       </c>
       <c r="K26" s="3" t="inlineStr">
         <is>
-          <t>23 Sep 2026 12:59:40 PM</t>
+          <t>23 Sep 2026 12:31:18 PM</t>
         </is>
       </c>
       <c r="L26" s="3" t="inlineStr">
@@ -3230,39 +3770,39 @@
       </c>
       <c r="M26" s="3" t="inlineStr">
         <is>
-          <t>35m</t>
+          <t>2h 37m</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="5" t="inlineStr">
         <is>
-          <t>TKT1342524</t>
+          <t>TKT1343122</t>
         </is>
       </c>
       <c r="B27" s="5" t="inlineStr">
         <is>
-          <t>Nakul Bhandari</t>
+          <t>Rajesh Shahi</t>
         </is>
       </c>
       <c r="C27" s="5" t="inlineStr">
         <is>
-          <t>No Internet Connection</t>
+          <t>General / Other Issues</t>
         </is>
       </c>
       <c r="D27" s="5" t="inlineStr">
         <is>
-          <t>Configuration Issue</t>
+          <t>Router Upgrade  Wi-Fi 6</t>
         </is>
       </c>
       <c r="E27" s="5" t="inlineStr">
         <is>
-          <t>Closed</t>
+          <t>Completed</t>
         </is>
       </c>
       <c r="F27" s="5" t="inlineStr">
         <is>
-          <t>Completed (Closed)</t>
+          <t>Completed (Completed)</t>
         </is>
       </c>
       <c r="G27" s="5" t="inlineStr">
@@ -3272,99 +3812,434 @@
       </c>
       <c r="H27" s="5" t="inlineStr">
         <is>
-          <t>Case : CONFINGURE ISSUE  has been updated by Ajit Shrestha</t>
+          <t>Case : wifi 6  has been updated by Shashikant Chaudhary</t>
         </is>
       </c>
       <c r="I27" s="5" t="inlineStr">
         <is>
-          <t>22 Sep 2026 02:52:24 PM</t>
+          <t>23 Sep 2026 12:37:13 PM</t>
         </is>
       </c>
       <c r="J27" s="5" t="inlineStr">
         <is>
-          <t>22 Sep 2026 02:35:30 PM</t>
+          <t>22 Sep 2026 09:56:18 PM</t>
         </is>
       </c>
       <c r="K27" s="5" t="inlineStr">
         <is>
-          <t>23 Sep 2026 12:57:31 PM</t>
+          <t>23 Sep 2026 12:37:13 PM</t>
         </is>
       </c>
       <c r="L27" s="5" t="inlineStr">
         <is>
-          <t>22h 5m</t>
+          <t>0m</t>
         </is>
       </c>
       <c r="M27" s="5" t="inlineStr">
         <is>
-          <t>22h 22m</t>
+          <t>14h 40m</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="3" t="inlineStr">
         <is>
+          <t>TKT1343670</t>
+        </is>
+      </c>
+      <c r="B28" s="3" t="inlineStr">
+        <is>
+          <t>Suman Shah</t>
+        </is>
+      </c>
+      <c r="C28" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="D28" s="3" t="inlineStr">
+        <is>
+          <t>Router Upgrade Dual Band</t>
+        </is>
+      </c>
+      <c r="E28" s="3" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="F28" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Completed)</t>
+        </is>
+      </c>
+      <c r="G28" s="3" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="H28" s="3" t="inlineStr">
+        <is>
+          <t>Case : router change  has been updated by Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="I28" s="3" t="inlineStr">
+        <is>
+          <t>23 Sep 2026 12:59:40 PM</t>
+        </is>
+      </c>
+      <c r="J28" s="3" t="inlineStr">
+        <is>
+          <t>23 Sep 2026 12:23:42 PM</t>
+        </is>
+      </c>
+      <c r="K28" s="3" t="inlineStr">
+        <is>
+          <t>23 Sep 2026 12:59:40 PM</t>
+        </is>
+      </c>
+      <c r="L28" s="3" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="M28" s="3" t="inlineStr">
+        <is>
+          <t>35m</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="5" t="inlineStr">
+        <is>
+          <t>TKT1342524</t>
+        </is>
+      </c>
+      <c r="B29" s="5" t="inlineStr">
+        <is>
+          <t>Nakul Bhandari</t>
+        </is>
+      </c>
+      <c r="C29" s="5" t="inlineStr">
+        <is>
+          <t>No Internet Connection</t>
+        </is>
+      </c>
+      <c r="D29" s="5" t="inlineStr">
+        <is>
+          <t>Configuration Issue</t>
+        </is>
+      </c>
+      <c r="E29" s="5" t="inlineStr">
+        <is>
+          <t>Closed</t>
+        </is>
+      </c>
+      <c r="F29" s="5" t="inlineStr">
+        <is>
+          <t>Completed (Closed)</t>
+        </is>
+      </c>
+      <c r="G29" s="5" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="H29" s="5" t="inlineStr">
+        <is>
+          <t>Case : CONFINGURE ISSUE  has been updated by Ajit Shrestha</t>
+        </is>
+      </c>
+      <c r="I29" s="5" t="inlineStr">
+        <is>
+          <t>22 Sep 2026 02:52:24 PM</t>
+        </is>
+      </c>
+      <c r="J29" s="5" t="inlineStr">
+        <is>
+          <t>22 Sep 2026 02:35:30 PM</t>
+        </is>
+      </c>
+      <c r="K29" s="5" t="inlineStr">
+        <is>
+          <t>23 Sep 2026 12:57:31 PM</t>
+        </is>
+      </c>
+      <c r="L29" s="5" t="inlineStr">
+        <is>
+          <t>22h 5m</t>
+        </is>
+      </c>
+      <c r="M29" s="5" t="inlineStr">
+        <is>
+          <t>22h 22m</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="3" t="inlineStr">
+        <is>
           <t>TKT1342923</t>
         </is>
       </c>
-      <c r="B28" s="3" t="inlineStr">
+      <c r="B30" s="3" t="inlineStr">
         <is>
           <t>Maan maya poon</t>
         </is>
       </c>
-      <c r="C28" s="3" t="inlineStr">
+      <c r="C30" s="3" t="inlineStr">
         <is>
           <t>General / Other Issues</t>
         </is>
       </c>
-      <c r="D28" s="3" t="inlineStr">
+      <c r="D30" s="3" t="inlineStr">
         <is>
           <t>Router Upgrade  Wi-Fi 6</t>
         </is>
       </c>
-      <c r="E28" s="3" t="inlineStr">
+      <c r="E30" s="3" t="inlineStr">
         <is>
           <t>Completed</t>
         </is>
       </c>
-      <c r="F28" s="3" t="inlineStr">
+      <c r="F30" s="3" t="inlineStr">
         <is>
           <t>Completed (Completed)</t>
         </is>
       </c>
-      <c r="G28" s="3" t="inlineStr">
+      <c r="G30" s="3" t="inlineStr">
         <is>
           <t>nan</t>
         </is>
       </c>
-      <c r="H28" s="3" t="inlineStr">
+      <c r="H30" s="3" t="inlineStr">
         <is>
           <t>Case : For upgradation to wifi6   has been updated by Sabin Giri</t>
         </is>
       </c>
-      <c r="I28" s="3" t="inlineStr">
+      <c r="I30" s="3" t="inlineStr">
         <is>
           <t>23 Sep 2026 01:01:06 PM</t>
         </is>
       </c>
-      <c r="J28" s="3" t="inlineStr">
+      <c r="J30" s="3" t="inlineStr">
         <is>
           <t>22 Sep 2026 06:58:31 PM</t>
         </is>
       </c>
-      <c r="K28" s="3" t="inlineStr">
+      <c r="K30" s="3" t="inlineStr">
         <is>
           <t>23 Sep 2026 01:01:06 PM</t>
         </is>
       </c>
-      <c r="L28" s="3" t="inlineStr">
+      <c r="L30" s="3" t="inlineStr">
         <is>
           <t>0m</t>
         </is>
       </c>
-      <c r="M28" s="3" t="inlineStr">
+      <c r="M30" s="3" t="inlineStr">
         <is>
           <t>18h 2m</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="5" t="inlineStr">
+        <is>
+          <t>TKT1343451</t>
+        </is>
+      </c>
+      <c r="B31" s="5" t="inlineStr">
+        <is>
+          <t>Sabin Maharjan</t>
+        </is>
+      </c>
+      <c r="C31" s="5" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="D31" s="5" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="E31" s="5" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="F31" s="5" t="inlineStr">
+        <is>
+          <t>Completed (Completed)</t>
+        </is>
+      </c>
+      <c r="G31" s="5" t="inlineStr">
+        <is>
+          <t>Case : Wifi 6  has been updated by Sabin Giri</t>
+        </is>
+      </c>
+      <c r="H31" s="5" t="inlineStr">
+        <is>
+          <t>Case : Wifi 6  has been updated by Sabin Giri</t>
+        </is>
+      </c>
+      <c r="I31" s="5" t="inlineStr">
+        <is>
+          <t>23 Sep 2026 01:17:39 PM</t>
+        </is>
+      </c>
+      <c r="J31" s="5" t="inlineStr">
+        <is>
+          <t>23 Sep 2026 10:26:34 AM</t>
+        </is>
+      </c>
+      <c r="K31" s="5" t="inlineStr">
+        <is>
+          <t>23 Sep 2026 01:17:39 PM</t>
+        </is>
+      </c>
+      <c r="L31" s="5" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="M31" s="5" t="inlineStr">
+        <is>
+          <t>2h 51m</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="3" t="inlineStr">
+        <is>
+          <t>TKT1343062</t>
+        </is>
+      </c>
+      <c r="B32" s="3" t="inlineStr">
+        <is>
+          <t>Sabin Magar</t>
+        </is>
+      </c>
+      <c r="C32" s="3" t="inlineStr">
+        <is>
+          <t>Hardware Damage / Malfunction</t>
+        </is>
+      </c>
+      <c r="D32" s="3" t="inlineStr">
+        <is>
+          <t>IPTV STB box Damage Issue</t>
+        </is>
+      </c>
+      <c r="E32" s="3" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="F32" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Completed)</t>
+        </is>
+      </c>
+      <c r="G32" s="3" t="inlineStr">
+        <is>
+          <t>Case : IP TV not Working   has been updated by Ajit Shrestha</t>
+        </is>
+      </c>
+      <c r="H32" s="3" t="inlineStr">
+        <is>
+          <t>Case : IP TV not Working   has been updated by Ajit Shrestha</t>
+        </is>
+      </c>
+      <c r="I32" s="3" t="inlineStr">
+        <is>
+          <t>23 Sep 2026 01:16:47 PM</t>
+        </is>
+      </c>
+      <c r="J32" s="3" t="inlineStr">
+        <is>
+          <t>22 Sep 2026 08:56:52 PM</t>
+        </is>
+      </c>
+      <c r="K32" s="3" t="inlineStr">
+        <is>
+          <t>23 Sep 2026 01:16:47 PM</t>
+        </is>
+      </c>
+      <c r="L32" s="3" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="M32" s="3" t="inlineStr">
+        <is>
+          <t>16h 19m</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="5" t="inlineStr">
+        <is>
+          <t>TKT1341347</t>
+        </is>
+      </c>
+      <c r="B33" s="5" t="inlineStr">
+        <is>
+          <t>Siddhartha Model School</t>
+        </is>
+      </c>
+      <c r="C33" s="5" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="D33" s="5" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="E33" s="5" t="inlineStr">
+        <is>
+          <t>Closed</t>
+        </is>
+      </c>
+      <c r="F33" s="5" t="inlineStr">
+        <is>
+          <t>Completed (Closed)</t>
+        </is>
+      </c>
+      <c r="G33" s="5" t="inlineStr">
+        <is>
+          <t>Case : wifi 6  has been updated by Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="H33" s="5" t="inlineStr">
+        <is>
+          <t>Case : wifi 6  has been updated by Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="I33" s="5" t="inlineStr">
+        <is>
+          <t>21 Sep 2026 01:35:47 PM</t>
+        </is>
+      </c>
+      <c r="J33" s="5" t="inlineStr">
+        <is>
+          <t>21 Sep 2026 01:35:47 PM</t>
+        </is>
+      </c>
+      <c r="K33" s="5" t="inlineStr">
+        <is>
+          <t>23 Sep 2026 01:22:44 PM</t>
+        </is>
+      </c>
+      <c r="L33" s="5" t="inlineStr">
+        <is>
+          <t>1d 23h 46m</t>
+        </is>
+      </c>
+      <c r="M33" s="5" t="inlineStr">
+        <is>
+          <t>1d 23h 46m</t>
         </is>
       </c>
     </row>

--- a/audit_report_ALL_TEAM_23_Sep_2026.xlsx
+++ b/audit_report_ALL_TEAM_23_Sep_2026.xlsx
@@ -529,7 +529,7 @@
     <col width="27" customWidth="1" min="41" max="41"/>
     <col width="12" customWidth="1" min="42" max="42"/>
     <col width="17" customWidth="1" min="43" max="43"/>
-    <col width="40" customWidth="1" min="44" max="44"/>
+    <col width="34" customWidth="1" min="44" max="44"/>
     <col width="34" customWidth="1" min="45" max="45"/>
     <col width="33" customWidth="1" min="46" max="46"/>
     <col width="32" customWidth="1" min="47" max="47"/>
@@ -2650,10 +2650,8 @@
           <t>Sabin Maharjan</t>
         </is>
       </c>
-      <c r="O11" s="3" t="inlineStr">
-        <is>
-          <t>9843366470</t>
-        </is>
+      <c r="O11" s="3" t="n">
+        <v>9843366470</v>
       </c>
       <c r="P11" s="3" t="inlineStr">
         <is>
@@ -2688,10 +2686,8 @@
           <t>Active</t>
         </is>
       </c>
-      <c r="Y11" s="3" t="inlineStr">
-        <is>
-          <t>27.74905</t>
-        </is>
+      <c r="Y11" s="3" t="n">
+        <v>27.74905</v>
       </c>
       <c r="Z11" s="3" t="inlineStr">
         <is>
@@ -2747,25 +2743,21 @@
           <t>Sabin Giri</t>
         </is>
       </c>
-      <c r="AN11" s="3" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
+      <c r="AN11" s="3" t="n">
+        <v>6</v>
       </c>
       <c r="AO11" s="3" t="inlineStr">
         <is>
           <t>L39-7</t>
         </is>
       </c>
-      <c r="AP11" s="3" t="inlineStr">
-        <is>
-          <t>85.31771</t>
-        </is>
+      <c r="AP11" s="3" t="n">
+        <v>85.31771000000001</v>
       </c>
       <c r="AQ11" s="3" t="inlineStr"/>
       <c r="AR11" s="3" t="inlineStr">
         <is>
-          <t>Case : Wifi 6  has been updated by Sabin Giri</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="AS11" s="3" t="inlineStr">
@@ -2861,10 +2853,8 @@
           <t>Sabin Magar</t>
         </is>
       </c>
-      <c r="O12" s="3" t="inlineStr">
-        <is>
-          <t>9813664152</t>
-        </is>
+      <c r="O12" s="3" t="n">
+        <v>9813664152</v>
       </c>
       <c r="P12" s="3" t="inlineStr">
         <is>
@@ -2899,10 +2889,8 @@
           <t>Active</t>
         </is>
       </c>
-      <c r="Y12" s="3" t="inlineStr">
-        <is>
-          <t>27.70515</t>
-        </is>
+      <c r="Y12" s="3" t="n">
+        <v>27.70515</v>
       </c>
       <c r="Z12" s="3" t="inlineStr">
         <is>
@@ -2958,25 +2946,21 @@
           <t>Ajit Shrestha</t>
         </is>
       </c>
-      <c r="AN12" s="3" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
+      <c r="AN12" s="3" t="n">
+        <v>4</v>
       </c>
       <c r="AO12" s="3" t="inlineStr">
         <is>
           <t>4,11</t>
         </is>
       </c>
-      <c r="AP12" s="3" t="inlineStr">
-        <is>
-          <t>85.302205</t>
-        </is>
+      <c r="AP12" s="3" t="n">
+        <v>85.302205</v>
       </c>
       <c r="AQ12" s="3" t="inlineStr"/>
       <c r="AR12" s="3" t="inlineStr">
         <is>
-          <t>Case : IP TV not Working   has been updated by Ajit Shrestha</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="AS12" s="3" t="inlineStr">
@@ -3072,10 +3056,8 @@
           <t>Siddhartha Model School</t>
         </is>
       </c>
-      <c r="O13" s="3" t="inlineStr">
-        <is>
-          <t>9849893921</t>
-        </is>
+      <c r="O13" s="3" t="n">
+        <v>9849893921</v>
       </c>
       <c r="P13" s="3" t="inlineStr">
         <is>
@@ -3110,10 +3092,8 @@
           <t>Active</t>
         </is>
       </c>
-      <c r="Y13" s="3" t="inlineStr">
-        <is>
-          <t>27.74454</t>
-        </is>
+      <c r="Y13" s="3" t="n">
+        <v>27.74454</v>
       </c>
       <c r="Z13" s="3" t="inlineStr">
         <is>
@@ -3169,25 +3149,21 @@
           <t>Sunil Chaudhary</t>
         </is>
       </c>
-      <c r="AN13" s="3" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
+      <c r="AN13" s="3" t="n">
+        <v>6</v>
       </c>
       <c r="AO13" s="3" t="inlineStr">
         <is>
           <t>L21-8</t>
         </is>
       </c>
-      <c r="AP13" s="3" t="inlineStr">
-        <is>
-          <t>85.3016</t>
-        </is>
+      <c r="AP13" s="3" t="n">
+        <v>85.30159999999999</v>
       </c>
       <c r="AQ13" s="3" t="inlineStr"/>
       <c r="AR13" s="3" t="inlineStr">
         <is>
-          <t>Case : wifi 6  has been updated by Sunil Chaudhary</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="AS13" s="3" t="inlineStr">
@@ -3236,7 +3212,7 @@
     <col width="29" customWidth="1" min="4" max="4"/>
     <col width="19" customWidth="1" min="5" max="5"/>
     <col width="25" customWidth="1" min="6" max="6"/>
-    <col width="45" customWidth="1" min="7" max="7"/>
+    <col width="35" customWidth="1" min="7" max="7"/>
     <col width="45" customWidth="1" min="8" max="8"/>
     <col width="27" customWidth="1" min="9" max="9"/>
     <col width="27" customWidth="1" min="10" max="10"/>
@@ -4075,7 +4051,7 @@
       </c>
       <c r="G31" s="5" t="inlineStr">
         <is>
-          <t>Case : Wifi 6  has been updated by Sabin Giri</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="H31" s="5" t="inlineStr">
@@ -4142,7 +4118,7 @@
       </c>
       <c r="G32" s="3" t="inlineStr">
         <is>
-          <t>Case : IP TV not Working   has been updated by Ajit Shrestha</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="H32" s="3" t="inlineStr">
@@ -4209,7 +4185,7 @@
       </c>
       <c r="G33" s="5" t="inlineStr">
         <is>
-          <t>Case : wifi 6  has been updated by Sunil Chaudhary</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="H33" s="5" t="inlineStr">

--- a/audit_report_ALL_TEAM_23_Sep_2026.xlsx
+++ b/audit_report_ALL_TEAM_23_Sep_2026.xlsx
@@ -483,7 +483,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AW13"/>
+  <dimension ref="A1:AW16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="23" customWidth="1" min="1" max="1"/>
@@ -506,7 +506,7 @@
     <col width="26" customWidth="1" min="18" max="18"/>
     <col width="37" customWidth="1" min="19" max="19"/>
     <col width="37" customWidth="1" min="20" max="20"/>
-    <col width="14" customWidth="1" min="21" max="21"/>
+    <col width="16" customWidth="1" min="21" max="21"/>
     <col width="26" customWidth="1" min="22" max="22"/>
     <col width="26" customWidth="1" min="23" max="23"/>
     <col width="29" customWidth="1" min="24" max="24"/>
@@ -529,7 +529,7 @@
     <col width="27" customWidth="1" min="41" max="41"/>
     <col width="12" customWidth="1" min="42" max="42"/>
     <col width="17" customWidth="1" min="43" max="43"/>
-    <col width="34" customWidth="1" min="44" max="44"/>
+    <col width="40" customWidth="1" min="44" max="44"/>
     <col width="34" customWidth="1" min="45" max="45"/>
     <col width="33" customWidth="1" min="46" max="46"/>
     <col width="32" customWidth="1" min="47" max="47"/>
@@ -3187,6 +3187,623 @@
         </is>
       </c>
       <c r="AW13" s="3" t="inlineStr">
+        <is>
+          <t>WiFi 6 Upgrade</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="3" t="inlineStr">
+        <is>
+          <t>Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="B14" s="3" t="inlineStr">
+        <is>
+          <t>23 Sep 2026 1:48 PM</t>
+        </is>
+      </c>
+      <c r="C14" s="3" t="inlineStr">
+        <is>
+          <t>w7A8I7MXNVw6IhJoudC/TknnOVKMobUO</t>
+        </is>
+      </c>
+      <c r="D14" s="3" t="inlineStr">
+        <is>
+          <t>Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="E14" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F14" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G14" s="3" t="inlineStr"/>
+      <c r="H14" s="3" t="inlineStr">
+        <is>
+          <t>Case : Wifi 6  has been updated by Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="I14" s="3" t="inlineStr">
+        <is>
+          <t>Wifi 6</t>
+        </is>
+      </c>
+      <c r="J14" s="3" t="inlineStr">
+        <is>
+          <t>TKT1342867</t>
+        </is>
+      </c>
+      <c r="K14" s="3" t="inlineStr">
+        <is>
+          <t>Punit Kumar Barnawal</t>
+        </is>
+      </c>
+      <c r="L14" s="3" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="M14" s="3" t="inlineStr">
+        <is>
+          <t>Phone</t>
+        </is>
+      </c>
+      <c r="N14" s="3" t="inlineStr">
+        <is>
+          <t>Punit Kumar Barnawal</t>
+        </is>
+      </c>
+      <c r="O14" s="3" t="inlineStr">
+        <is>
+          <t>9845947695</t>
+        </is>
+      </c>
+      <c r="P14" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="Q14" s="3" t="inlineStr"/>
+      <c r="R14" s="3" t="inlineStr">
+        <is>
+          <t>23 Sep 2026 01:48:42 PM</t>
+        </is>
+      </c>
+      <c r="S14" s="3" t="inlineStr"/>
+      <c r="T14" s="3" t="inlineStr"/>
+      <c r="U14" s="3" t="inlineStr">
+        <is>
+          <t>9845947695</t>
+        </is>
+      </c>
+      <c r="V14" s="3" t="inlineStr">
+        <is>
+          <t>22 Sep 2026 06:02:29 PM</t>
+        </is>
+      </c>
+      <c r="W14" s="3" t="inlineStr">
+        <is>
+          <t>23 Sep 2026 01:48:42 PM</t>
+        </is>
+      </c>
+      <c r="X14" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Y14" s="3" t="inlineStr">
+        <is>
+          <t>27.68099</t>
+        </is>
+      </c>
+      <c r="Z14" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="AA14" s="3" t="inlineStr">
+        <is>
+          <t>Layer 1-User</t>
+        </is>
+      </c>
+      <c r="AB14" s="3" t="inlineStr">
+        <is>
+          <t>L1  Support</t>
+        </is>
+      </c>
+      <c r="AC14" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="AD14" s="3" t="inlineStr"/>
+      <c r="AE14" s="3" t="inlineStr">
+        <is>
+          <t>Matribhumi School Madhyapur Thimi 44600, Bagmati, Central, Nepal</t>
+        </is>
+      </c>
+      <c r="AF14" s="3" t="inlineStr"/>
+      <c r="AG14" s="3" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="AH14" s="3" t="inlineStr"/>
+      <c r="AI14" s="3" t="inlineStr">
+        <is>
+          <t>05:46 hour</t>
+        </is>
+      </c>
+      <c r="AJ14" s="3" t="inlineStr"/>
+      <c r="AK14" s="3" t="inlineStr"/>
+      <c r="AL14" s="3" t="inlineStr">
+        <is>
+          <t>Sameer Thapa</t>
+        </is>
+      </c>
+      <c r="AM14" s="3" t="inlineStr">
+        <is>
+          <t>Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="AN14" s="3" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AO14" s="3" t="inlineStr">
+        <is>
+          <t>4,13</t>
+        </is>
+      </c>
+      <c r="AP14" s="3" t="inlineStr">
+        <is>
+          <t>85.3673</t>
+        </is>
+      </c>
+      <c r="AQ14" s="3" t="inlineStr"/>
+      <c r="AR14" s="3" t="inlineStr">
+        <is>
+          <t>Case : Wifi 6  has been updated by Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="AS14" s="3" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="AT14" s="3" t="inlineStr">
+        <is>
+          <t>19h 46m</t>
+        </is>
+      </c>
+      <c r="AU14" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Completed)</t>
+        </is>
+      </c>
+      <c r="AV14" s="3" t="inlineStr">
+        <is>
+          <t>Case : Wifi 6  has been updated by Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="AW14" s="3" t="inlineStr">
+        <is>
+          <t>WiFi 6 Upgrade</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="3" t="inlineStr">
+        <is>
+          <t>Rajesh Maharjan</t>
+        </is>
+      </c>
+      <c r="B15" s="3" t="inlineStr">
+        <is>
+          <t>23 Sep 2026 1:51 PM</t>
+        </is>
+      </c>
+      <c r="C15" s="3" t="inlineStr">
+        <is>
+          <t>/Oi+2zlne73U37ZA62PktA==</t>
+        </is>
+      </c>
+      <c r="D15" s="3" t="inlineStr">
+        <is>
+          <t>Rajesh Maharjan</t>
+        </is>
+      </c>
+      <c r="E15" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F15" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G15" s="3" t="inlineStr"/>
+      <c r="H15" s="3" t="inlineStr">
+        <is>
+          <t>Case : 5g not working   has been updated by Rajesh Maharjan</t>
+        </is>
+      </c>
+      <c r="I15" s="3" t="inlineStr">
+        <is>
+          <t>5g not working</t>
+        </is>
+      </c>
+      <c r="J15" s="3" t="inlineStr">
+        <is>
+          <t>TKT1343135</t>
+        </is>
+      </c>
+      <c r="K15" s="3" t="inlineStr">
+        <is>
+          <t>Ashish Shahbadi</t>
+        </is>
+      </c>
+      <c r="L15" s="3" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="M15" s="3" t="inlineStr">
+        <is>
+          <t>Phone</t>
+        </is>
+      </c>
+      <c r="N15" s="3" t="inlineStr">
+        <is>
+          <t>Ashish Shahbadi</t>
+        </is>
+      </c>
+      <c r="O15" s="3" t="inlineStr">
+        <is>
+          <t>9845424784</t>
+        </is>
+      </c>
+      <c r="P15" s="3" t="inlineStr">
+        <is>
+          <t>Hardware Damage / Malfunction</t>
+        </is>
+      </c>
+      <c r="Q15" s="3" t="inlineStr"/>
+      <c r="R15" s="3" t="inlineStr">
+        <is>
+          <t>23 Sep 2026 01:51:51 PM</t>
+        </is>
+      </c>
+      <c r="S15" s="3" t="inlineStr"/>
+      <c r="T15" s="3" t="inlineStr"/>
+      <c r="U15" s="3" t="inlineStr">
+        <is>
+          <t>9866097024</t>
+        </is>
+      </c>
+      <c r="V15" s="3" t="inlineStr">
+        <is>
+          <t>22 Sep 2026 10:20:07 PM</t>
+        </is>
+      </c>
+      <c r="W15" s="3" t="inlineStr">
+        <is>
+          <t>23 Sep 2026 01:51:51 PM</t>
+        </is>
+      </c>
+      <c r="X15" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Y15" s="3" t="inlineStr">
+        <is>
+          <t>27.66151</t>
+        </is>
+      </c>
+      <c r="Z15" s="3" t="inlineStr">
+        <is>
+          <t>Hardware Damage / Malfunction</t>
+        </is>
+      </c>
+      <c r="AA15" s="3" t="inlineStr">
+        <is>
+          <t>Layer 1-User</t>
+        </is>
+      </c>
+      <c r="AB15" s="3" t="inlineStr">
+        <is>
+          <t>L1  Support</t>
+        </is>
+      </c>
+      <c r="AC15" s="3" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="AD15" s="3" t="inlineStr"/>
+      <c r="AE15" s="3" t="inlineStr">
+        <is>
+          <t>Near By Fresh Cup Bakery Damodar Marg, Lalitpur, Bagmati, Central, Nepal</t>
+        </is>
+      </c>
+      <c r="AF15" s="3" t="inlineStr">
+        <is>
+          <t>mnshsrrf@gmail.com</t>
+        </is>
+      </c>
+      <c r="AG15" s="3" t="inlineStr">
+        <is>
+          <t>Router Damage Issue</t>
+        </is>
+      </c>
+      <c r="AH15" s="3" t="inlineStr"/>
+      <c r="AI15" s="3" t="inlineStr">
+        <is>
+          <t>03:51 hour</t>
+        </is>
+      </c>
+      <c r="AJ15" s="3" t="inlineStr"/>
+      <c r="AK15" s="3" t="inlineStr"/>
+      <c r="AL15" s="3" t="inlineStr">
+        <is>
+          <t>Pratik Shrestha</t>
+        </is>
+      </c>
+      <c r="AM15" s="3" t="inlineStr">
+        <is>
+          <t>Rajesh Maharjan</t>
+        </is>
+      </c>
+      <c r="AN15" s="3" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AO15" s="3" t="inlineStr">
+        <is>
+          <t>1,1</t>
+        </is>
+      </c>
+      <c r="AP15" s="3" t="inlineStr">
+        <is>
+          <t>85.31385</t>
+        </is>
+      </c>
+      <c r="AQ15" s="3" t="inlineStr"/>
+      <c r="AR15" s="3" t="inlineStr">
+        <is>
+          <t>Case : 5g not working   has been updated by Rajesh Maharjan</t>
+        </is>
+      </c>
+      <c r="AS15" s="3" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="AT15" s="3" t="inlineStr">
+        <is>
+          <t>15h 31m</t>
+        </is>
+      </c>
+      <c r="AU15" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Completed)</t>
+        </is>
+      </c>
+      <c r="AV15" s="3" t="inlineStr">
+        <is>
+          <t>Case : 5g not working   has been updated by Rajesh Maharjan</t>
+        </is>
+      </c>
+      <c r="AW15" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="3" t="inlineStr">
+        <is>
+          <t>Ajit Shrestha</t>
+        </is>
+      </c>
+      <c r="B16" s="3" t="inlineStr">
+        <is>
+          <t>23 Sep 2026 1:57 PM</t>
+        </is>
+      </c>
+      <c r="C16" s="3" t="inlineStr">
+        <is>
+          <t>KK1e4rFHODw22QGqrKXwiw==</t>
+        </is>
+      </c>
+      <c r="D16" s="3" t="inlineStr">
+        <is>
+          <t>Ajit Shrestha</t>
+        </is>
+      </c>
+      <c r="E16" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F16" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G16" s="3" t="inlineStr"/>
+      <c r="H16" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi 6 upgrade  has been updated by Ajit Shrestha</t>
+        </is>
+      </c>
+      <c r="I16" s="3" t="inlineStr">
+        <is>
+          <t>wifi 6 upgrade</t>
+        </is>
+      </c>
+      <c r="J16" s="3" t="inlineStr">
+        <is>
+          <t>TKT1341465</t>
+        </is>
+      </c>
+      <c r="K16" s="3" t="inlineStr">
+        <is>
+          <t>samrat shrestha</t>
+        </is>
+      </c>
+      <c r="L16" s="3" t="inlineStr">
+        <is>
+          <t>On Hold</t>
+        </is>
+      </c>
+      <c r="M16" s="3" t="inlineStr">
+        <is>
+          <t>Self Care</t>
+        </is>
+      </c>
+      <c r="N16" s="3" t="inlineStr">
+        <is>
+          <t>samrat shrestha</t>
+        </is>
+      </c>
+      <c r="O16" s="3" t="inlineStr">
+        <is>
+          <t>9820084508</t>
+        </is>
+      </c>
+      <c r="P16" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="Q16" s="3" t="inlineStr"/>
+      <c r="R16" s="3" t="inlineStr">
+        <is>
+          <t>23 Sep 2026 10:23:23 AM</t>
+        </is>
+      </c>
+      <c r="S16" s="3" t="inlineStr"/>
+      <c r="T16" s="3" t="inlineStr"/>
+      <c r="U16" s="3" t="inlineStr">
+        <is>
+          <t>KLK9813561196</t>
+        </is>
+      </c>
+      <c r="V16" s="3" t="inlineStr">
+        <is>
+          <t>21 Sep 2026 03:17:02 PM</t>
+        </is>
+      </c>
+      <c r="W16" s="3" t="inlineStr">
+        <is>
+          <t>23 Sep 2026 01:57:44 PM</t>
+        </is>
+      </c>
+      <c r="X16" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Y16" s="3" t="inlineStr"/>
+      <c r="Z16" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="AA16" s="3" t="inlineStr">
+        <is>
+          <t>Layer 1-User</t>
+        </is>
+      </c>
+      <c r="AB16" s="3" t="inlineStr">
+        <is>
+          <t>Laxman Koirala</t>
+        </is>
+      </c>
+      <c r="AC16" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="AD16" s="3" t="inlineStr"/>
+      <c r="AE16" s="3" t="inlineStr">
+        <is>
+          <t>Dhumbakhel Youth Club - Youth club P852+7J3 ??????? ????? Kathmandu 44600, Bagmati, Nepal, Nepal</t>
+        </is>
+      </c>
+      <c r="AF16" s="3" t="inlineStr">
+        <is>
+          <t>samshrestha080@gmail.com</t>
+        </is>
+      </c>
+      <c r="AG16" s="3" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="AH16" s="3" t="inlineStr"/>
+      <c r="AI16" s="3" t="inlineStr"/>
+      <c r="AJ16" s="3" t="inlineStr"/>
+      <c r="AK16" s="3" t="inlineStr"/>
+      <c r="AL16" s="3" t="inlineStr">
+        <is>
+          <t>Sabina K.C</t>
+        </is>
+      </c>
+      <c r="AM16" s="3" t="inlineStr">
+        <is>
+          <t>Ajit Shrestha</t>
+        </is>
+      </c>
+      <c r="AN16" s="3" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AO16" s="3" t="inlineStr">
+        <is>
+          <t>CDB348</t>
+        </is>
+      </c>
+      <c r="AP16" s="3" t="inlineStr"/>
+      <c r="AQ16" s="3" t="inlineStr"/>
+      <c r="AR16" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi 6 upgrade  has been updated by Ajit Shrestha</t>
+        </is>
+      </c>
+      <c r="AS16" s="3" t="inlineStr">
+        <is>
+          <t>3h 34m</t>
+        </is>
+      </c>
+      <c r="AT16" s="3" t="inlineStr">
+        <is>
+          <t>1d 22h 40m</t>
+        </is>
+      </c>
+      <c r="AU16" s="3" t="inlineStr">
+        <is>
+          <t>Other / In Progress (On Hold)</t>
+        </is>
+      </c>
+      <c r="AV16" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi 6 upgrade  has been updated by Ajit Shrestha</t>
+        </is>
+      </c>
+      <c r="AW16" s="3" t="inlineStr">
         <is>
           <t>WiFi 6 Upgrade</t>
         </is>
@@ -3203,7 +3820,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M33"/>
+  <dimension ref="A1:M36"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="45" customWidth="1" min="1" max="1"/>
@@ -3212,7 +3829,7 @@
     <col width="29" customWidth="1" min="4" max="4"/>
     <col width="19" customWidth="1" min="5" max="5"/>
     <col width="25" customWidth="1" min="6" max="6"/>
-    <col width="35" customWidth="1" min="7" max="7"/>
+    <col width="45" customWidth="1" min="7" max="7"/>
     <col width="45" customWidth="1" min="8" max="8"/>
     <col width="27" customWidth="1" min="9" max="9"/>
     <col width="27" customWidth="1" min="10" max="10"/>
@@ -3240,7 +3857,7 @@
         </is>
       </c>
       <c r="B2" s="3" t="n">
-        <v>12</v>
+        <v>15</v>
       </c>
     </row>
     <row r="3">
@@ -3250,7 +3867,7 @@
         </is>
       </c>
       <c r="B3" s="5" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
     </row>
     <row r="4">
@@ -3261,7 +3878,7 @@
       </c>
       <c r="B4" s="3" t="inlineStr">
         <is>
-          <t>75.0%</t>
+          <t>73.3%</t>
         </is>
       </c>
     </row>
@@ -3273,7 +3890,7 @@
       </c>
       <c r="B5" s="5" t="inlineStr">
         <is>
-          <t>7h 45m</t>
+          <t>6h 21m</t>
         </is>
       </c>
     </row>
@@ -3285,7 +3902,7 @@
       </c>
       <c r="B6" s="3" t="inlineStr">
         <is>
-          <t>16h 13m</t>
+          <t>16h 29m</t>
         </is>
       </c>
     </row>
@@ -3326,14 +3943,14 @@
         </is>
       </c>
       <c r="B10" s="3" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="C10" s="3" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D10" s="3" t="inlineStr">
         <is>
-          <t>77.8%</t>
+          <t>72.7%</t>
         </is>
       </c>
     </row>
@@ -3344,10 +3961,10 @@
         </is>
       </c>
       <c r="B11" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C11" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D11" s="5" t="inlineStr">
         <is>
@@ -3438,14 +4055,14 @@
         </is>
       </c>
       <c r="C17" s="5" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="D17" s="5" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E17" s="5" t="inlineStr">
         <is>
-          <t>75.0%</t>
+          <t>70.0%</t>
         </is>
       </c>
     </row>
@@ -3498,12 +4115,12 @@
     <row r="20">
       <c r="A20" s="3" t="inlineStr">
         <is>
-          <t>No Internet Connection</t>
+          <t>Hardware Damage / Malfunction</t>
         </is>
       </c>
       <c r="B20" s="3" t="inlineStr">
         <is>
-          <t>Configuration Issue</t>
+          <t>Router Damage Issue</t>
         </is>
       </c>
       <c r="C20" s="3" t="n">
@@ -3521,177 +4138,133 @@
     <row r="21">
       <c r="A21" s="5" t="inlineStr">
         <is>
-          <t>Slow Internet Connection</t>
+          <t>No Internet Connection</t>
         </is>
       </c>
       <c r="B21" s="5" t="inlineStr">
         <is>
-          <t>Video content is Buffering</t>
+          <t>Configuration Issue</t>
         </is>
       </c>
       <c r="C21" s="5" t="n">
         <v>1</v>
       </c>
       <c r="D21" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="E21" s="5" t="inlineStr">
+        <is>
+          <t>100.0%</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="3" t="inlineStr">
+        <is>
+          <t>Slow Internet Connection</t>
+        </is>
+      </c>
+      <c r="B22" s="3" t="inlineStr">
+        <is>
+          <t>Video content is Buffering</t>
+        </is>
+      </c>
+      <c r="C22" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="D22" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="E21" s="5" t="inlineStr">
+      <c r="E22" s="3" t="inlineStr">
         <is>
           <t>0.0%</t>
         </is>
       </c>
     </row>
-    <row r="22"/>
-    <row r="23">
-      <c r="A23" s="6" t="inlineStr">
+    <row r="23"/>
+    <row r="24">
+      <c r="A24" s="6" t="inlineStr">
         <is>
           <t>Detailed Solved / Handled Tickets List</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" s="4" t="inlineStr">
-        <is>
-          <t>Ticket Number</t>
-        </is>
-      </c>
-      <c r="B24" s="4" t="inlineStr">
-        <is>
-          <t>Account Name</t>
-        </is>
-      </c>
-      <c r="C24" s="4" t="inlineStr">
-        <is>
-          <t>Category</t>
-        </is>
-      </c>
-      <c r="D24" s="4" t="inlineStr">
-        <is>
-          <t>Sub Category</t>
-        </is>
-      </c>
-      <c r="E24" s="4" t="inlineStr">
-        <is>
-          <t>Status</t>
-        </is>
-      </c>
-      <c r="F24" s="4" t="inlineStr">
-        <is>
-          <t>Resolution Type</t>
-        </is>
-      </c>
-      <c r="G24" s="4" t="inlineStr">
-        <is>
-          <t>Employee Remark / Solution Note</t>
-        </is>
-      </c>
-      <c r="H24" s="4" t="inlineStr">
-        <is>
-          <t>Action / Transfer Remark</t>
-        </is>
-      </c>
-      <c r="I24" s="4" t="inlineStr">
-        <is>
-          <t>Assigned Date</t>
-        </is>
-      </c>
-      <c r="J24" s="4" t="inlineStr">
-        <is>
-          <t>Created Date</t>
-        </is>
-      </c>
-      <c r="K24" s="4" t="inlineStr">
-        <is>
-          <t>Last Modified Date</t>
-        </is>
-      </c>
-      <c r="L24" s="4" t="inlineStr">
-        <is>
-          <t>Resolution Time (From Assigned)</t>
-        </is>
-      </c>
-      <c r="M24" s="4" t="inlineStr">
-        <is>
-          <t>Resolution Time (From Created)</t>
         </is>
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="5" t="inlineStr">
-        <is>
-          <t>TKT1342514</t>
-        </is>
-      </c>
-      <c r="B25" s="5" t="inlineStr">
-        <is>
-          <t>Bijay Carlos Rana</t>
-        </is>
-      </c>
-      <c r="C25" s="5" t="inlineStr">
-        <is>
-          <t>General / Other Issues</t>
-        </is>
-      </c>
-      <c r="D25" s="5" t="inlineStr">
-        <is>
-          <t>Router Upgrade  Wi-Fi 6</t>
-        </is>
-      </c>
-      <c r="E25" s="5" t="inlineStr">
-        <is>
-          <t>Completed</t>
-        </is>
-      </c>
-      <c r="F25" s="5" t="inlineStr">
-        <is>
-          <t>Completed (Completed)</t>
-        </is>
-      </c>
-      <c r="G25" s="5" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
-      <c r="H25" s="5" t="inlineStr">
-        <is>
-          <t>Case : WIFI 6  has been updated by Rajesh Maharjan</t>
-        </is>
-      </c>
-      <c r="I25" s="5" t="inlineStr">
-        <is>
-          <t>23 Sep 2026 11:16:05 AM</t>
-        </is>
-      </c>
-      <c r="J25" s="5" t="inlineStr">
-        <is>
-          <t>22 Sep 2026 02:29:16 PM</t>
-        </is>
-      </c>
-      <c r="K25" s="5" t="inlineStr">
-        <is>
-          <t>23 Sep 2026 11:16:05 AM</t>
-        </is>
-      </c>
-      <c r="L25" s="5" t="inlineStr">
-        <is>
-          <t>0m</t>
-        </is>
-      </c>
-      <c r="M25" s="5" t="inlineStr">
-        <is>
-          <t>20h 46m</t>
+      <c r="A25" s="4" t="inlineStr">
+        <is>
+          <t>Ticket Number</t>
+        </is>
+      </c>
+      <c r="B25" s="4" t="inlineStr">
+        <is>
+          <t>Account Name</t>
+        </is>
+      </c>
+      <c r="C25" s="4" t="inlineStr">
+        <is>
+          <t>Category</t>
+        </is>
+      </c>
+      <c r="D25" s="4" t="inlineStr">
+        <is>
+          <t>Sub Category</t>
+        </is>
+      </c>
+      <c r="E25" s="4" t="inlineStr">
+        <is>
+          <t>Status</t>
+        </is>
+      </c>
+      <c r="F25" s="4" t="inlineStr">
+        <is>
+          <t>Resolution Type</t>
+        </is>
+      </c>
+      <c r="G25" s="4" t="inlineStr">
+        <is>
+          <t>Employee Remark / Solution Note</t>
+        </is>
+      </c>
+      <c r="H25" s="4" t="inlineStr">
+        <is>
+          <t>Action / Transfer Remark</t>
+        </is>
+      </c>
+      <c r="I25" s="4" t="inlineStr">
+        <is>
+          <t>Assigned Date</t>
+        </is>
+      </c>
+      <c r="J25" s="4" t="inlineStr">
+        <is>
+          <t>Created Date</t>
+        </is>
+      </c>
+      <c r="K25" s="4" t="inlineStr">
+        <is>
+          <t>Last Modified Date</t>
+        </is>
+      </c>
+      <c r="L25" s="4" t="inlineStr">
+        <is>
+          <t>Resolution Time (From Assigned)</t>
+        </is>
+      </c>
+      <c r="M25" s="4" t="inlineStr">
+        <is>
+          <t>Resolution Time (From Created)</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="3" t="inlineStr">
         <is>
-          <t>TKT1343394</t>
+          <t>TKT1342514</t>
         </is>
       </c>
       <c r="B26" s="3" t="inlineStr">
         <is>
-          <t>Kaizen Business consultant</t>
+          <t>Bijay Carlos Rana</t>
         </is>
       </c>
       <c r="C26" s="3" t="inlineStr">
@@ -3721,22 +4294,22 @@
       </c>
       <c r="H26" s="3" t="inlineStr">
         <is>
-          <t>Case : wifi 6 router  has been updated by Sabin Giri</t>
+          <t>Case : WIFI 6  has been updated by Rajesh Maharjan</t>
         </is>
       </c>
       <c r="I26" s="3" t="inlineStr">
         <is>
-          <t>23 Sep 2026 12:31:18 PM</t>
+          <t>23 Sep 2026 11:16:05 AM</t>
         </is>
       </c>
       <c r="J26" s="3" t="inlineStr">
         <is>
-          <t>23 Sep 2026 09:53:33 AM</t>
+          <t>22 Sep 2026 02:29:16 PM</t>
         </is>
       </c>
       <c r="K26" s="3" t="inlineStr">
         <is>
-          <t>23 Sep 2026 12:31:18 PM</t>
+          <t>23 Sep 2026 11:16:05 AM</t>
         </is>
       </c>
       <c r="L26" s="3" t="inlineStr">
@@ -3746,19 +4319,19 @@
       </c>
       <c r="M26" s="3" t="inlineStr">
         <is>
-          <t>2h 37m</t>
+          <t>20h 46m</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="5" t="inlineStr">
         <is>
-          <t>TKT1343122</t>
+          <t>TKT1343394</t>
         </is>
       </c>
       <c r="B27" s="5" t="inlineStr">
         <is>
-          <t>Rajesh Shahi</t>
+          <t>Kaizen Business consultant</t>
         </is>
       </c>
       <c r="C27" s="5" t="inlineStr">
@@ -3788,22 +4361,22 @@
       </c>
       <c r="H27" s="5" t="inlineStr">
         <is>
-          <t>Case : wifi 6  has been updated by Shashikant Chaudhary</t>
+          <t>Case : wifi 6 router  has been updated by Sabin Giri</t>
         </is>
       </c>
       <c r="I27" s="5" t="inlineStr">
         <is>
-          <t>23 Sep 2026 12:37:13 PM</t>
+          <t>23 Sep 2026 12:31:18 PM</t>
         </is>
       </c>
       <c r="J27" s="5" t="inlineStr">
         <is>
-          <t>22 Sep 2026 09:56:18 PM</t>
+          <t>23 Sep 2026 09:53:33 AM</t>
         </is>
       </c>
       <c r="K27" s="5" t="inlineStr">
         <is>
-          <t>23 Sep 2026 12:37:13 PM</t>
+          <t>23 Sep 2026 12:31:18 PM</t>
         </is>
       </c>
       <c r="L27" s="5" t="inlineStr">
@@ -3813,19 +4386,19 @@
       </c>
       <c r="M27" s="5" t="inlineStr">
         <is>
-          <t>14h 40m</t>
+          <t>2h 37m</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="3" t="inlineStr">
         <is>
-          <t>TKT1343670</t>
+          <t>TKT1343122</t>
         </is>
       </c>
       <c r="B28" s="3" t="inlineStr">
         <is>
-          <t>Suman Shah</t>
+          <t>Rajesh Shahi</t>
         </is>
       </c>
       <c r="C28" s="3" t="inlineStr">
@@ -3835,7 +4408,7 @@
       </c>
       <c r="D28" s="3" t="inlineStr">
         <is>
-          <t>Router Upgrade Dual Band</t>
+          <t>Router Upgrade  Wi-Fi 6</t>
         </is>
       </c>
       <c r="E28" s="3" t="inlineStr">
@@ -3855,22 +4428,22 @@
       </c>
       <c r="H28" s="3" t="inlineStr">
         <is>
-          <t>Case : router change  has been updated by Shashikant Chaudhary</t>
+          <t>Case : wifi 6  has been updated by Shashikant Chaudhary</t>
         </is>
       </c>
       <c r="I28" s="3" t="inlineStr">
         <is>
-          <t>23 Sep 2026 12:59:40 PM</t>
+          <t>23 Sep 2026 12:37:13 PM</t>
         </is>
       </c>
       <c r="J28" s="3" t="inlineStr">
         <is>
-          <t>23 Sep 2026 12:23:42 PM</t>
+          <t>22 Sep 2026 09:56:18 PM</t>
         </is>
       </c>
       <c r="K28" s="3" t="inlineStr">
         <is>
-          <t>23 Sep 2026 12:59:40 PM</t>
+          <t>23 Sep 2026 12:37:13 PM</t>
         </is>
       </c>
       <c r="L28" s="3" t="inlineStr">
@@ -3880,39 +4453,39 @@
       </c>
       <c r="M28" s="3" t="inlineStr">
         <is>
-          <t>35m</t>
+          <t>14h 40m</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="5" t="inlineStr">
         <is>
-          <t>TKT1342524</t>
+          <t>TKT1343670</t>
         </is>
       </c>
       <c r="B29" s="5" t="inlineStr">
         <is>
-          <t>Nakul Bhandari</t>
+          <t>Suman Shah</t>
         </is>
       </c>
       <c r="C29" s="5" t="inlineStr">
         <is>
-          <t>No Internet Connection</t>
+          <t>General / Other Issues</t>
         </is>
       </c>
       <c r="D29" s="5" t="inlineStr">
         <is>
-          <t>Configuration Issue</t>
+          <t>Router Upgrade Dual Band</t>
         </is>
       </c>
       <c r="E29" s="5" t="inlineStr">
         <is>
-          <t>Closed</t>
+          <t>Completed</t>
         </is>
       </c>
       <c r="F29" s="5" t="inlineStr">
         <is>
-          <t>Completed (Closed)</t>
+          <t>Completed (Completed)</t>
         </is>
       </c>
       <c r="G29" s="5" t="inlineStr">
@@ -3922,64 +4495,64 @@
       </c>
       <c r="H29" s="5" t="inlineStr">
         <is>
-          <t>Case : CONFINGURE ISSUE  has been updated by Ajit Shrestha</t>
+          <t>Case : router change  has been updated by Shashikant Chaudhary</t>
         </is>
       </c>
       <c r="I29" s="5" t="inlineStr">
         <is>
-          <t>22 Sep 2026 02:52:24 PM</t>
+          <t>23 Sep 2026 12:59:40 PM</t>
         </is>
       </c>
       <c r="J29" s="5" t="inlineStr">
         <is>
-          <t>22 Sep 2026 02:35:30 PM</t>
+          <t>23 Sep 2026 12:23:42 PM</t>
         </is>
       </c>
       <c r="K29" s="5" t="inlineStr">
         <is>
-          <t>23 Sep 2026 12:57:31 PM</t>
+          <t>23 Sep 2026 12:59:40 PM</t>
         </is>
       </c>
       <c r="L29" s="5" t="inlineStr">
         <is>
-          <t>22h 5m</t>
+          <t>0m</t>
         </is>
       </c>
       <c r="M29" s="5" t="inlineStr">
         <is>
-          <t>22h 22m</t>
+          <t>35m</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="3" t="inlineStr">
         <is>
-          <t>TKT1342923</t>
+          <t>TKT1342524</t>
         </is>
       </c>
       <c r="B30" s="3" t="inlineStr">
         <is>
-          <t>Maan maya poon</t>
+          <t>Nakul Bhandari</t>
         </is>
       </c>
       <c r="C30" s="3" t="inlineStr">
         <is>
-          <t>General / Other Issues</t>
+          <t>No Internet Connection</t>
         </is>
       </c>
       <c r="D30" s="3" t="inlineStr">
         <is>
-          <t>Router Upgrade  Wi-Fi 6</t>
+          <t>Configuration Issue</t>
         </is>
       </c>
       <c r="E30" s="3" t="inlineStr">
         <is>
-          <t>Completed</t>
+          <t>Closed</t>
         </is>
       </c>
       <c r="F30" s="3" t="inlineStr">
         <is>
-          <t>Completed (Completed)</t>
+          <t>Completed (Closed)</t>
         </is>
       </c>
       <c r="G30" s="3" t="inlineStr">
@@ -3989,44 +4562,44 @@
       </c>
       <c r="H30" s="3" t="inlineStr">
         <is>
-          <t>Case : For upgradation to wifi6   has been updated by Sabin Giri</t>
+          <t>Case : CONFINGURE ISSUE  has been updated by Ajit Shrestha</t>
         </is>
       </c>
       <c r="I30" s="3" t="inlineStr">
         <is>
-          <t>23 Sep 2026 01:01:06 PM</t>
+          <t>22 Sep 2026 02:52:24 PM</t>
         </is>
       </c>
       <c r="J30" s="3" t="inlineStr">
         <is>
-          <t>22 Sep 2026 06:58:31 PM</t>
+          <t>22 Sep 2026 02:35:30 PM</t>
         </is>
       </c>
       <c r="K30" s="3" t="inlineStr">
         <is>
-          <t>23 Sep 2026 01:01:06 PM</t>
+          <t>23 Sep 2026 12:57:31 PM</t>
         </is>
       </c>
       <c r="L30" s="3" t="inlineStr">
         <is>
-          <t>0m</t>
+          <t>22h 5m</t>
         </is>
       </c>
       <c r="M30" s="3" t="inlineStr">
         <is>
-          <t>18h 2m</t>
+          <t>22h 22m</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="5" t="inlineStr">
         <is>
-          <t>TKT1343451</t>
+          <t>TKT1342923</t>
         </is>
       </c>
       <c r="B31" s="5" t="inlineStr">
         <is>
-          <t>Sabin Maharjan</t>
+          <t>Maan maya poon</t>
         </is>
       </c>
       <c r="C31" s="5" t="inlineStr">
@@ -4056,22 +4629,22 @@
       </c>
       <c r="H31" s="5" t="inlineStr">
         <is>
-          <t>Case : Wifi 6  has been updated by Sabin Giri</t>
+          <t>Case : For upgradation to wifi6   has been updated by Sabin Giri</t>
         </is>
       </c>
       <c r="I31" s="5" t="inlineStr">
         <is>
-          <t>23 Sep 2026 01:17:39 PM</t>
+          <t>23 Sep 2026 01:01:06 PM</t>
         </is>
       </c>
       <c r="J31" s="5" t="inlineStr">
         <is>
-          <t>23 Sep 2026 10:26:34 AM</t>
+          <t>22 Sep 2026 06:58:31 PM</t>
         </is>
       </c>
       <c r="K31" s="5" t="inlineStr">
         <is>
-          <t>23 Sep 2026 01:17:39 PM</t>
+          <t>23 Sep 2026 01:01:06 PM</t>
         </is>
       </c>
       <c r="L31" s="5" t="inlineStr">
@@ -4081,29 +4654,29 @@
       </c>
       <c r="M31" s="5" t="inlineStr">
         <is>
-          <t>2h 51m</t>
+          <t>18h 2m</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="3" t="inlineStr">
         <is>
-          <t>TKT1343062</t>
+          <t>TKT1343451</t>
         </is>
       </c>
       <c r="B32" s="3" t="inlineStr">
         <is>
-          <t>Sabin Magar</t>
+          <t>Sabin Maharjan</t>
         </is>
       </c>
       <c r="C32" s="3" t="inlineStr">
         <is>
-          <t>Hardware Damage / Malfunction</t>
+          <t>General / Other Issues</t>
         </is>
       </c>
       <c r="D32" s="3" t="inlineStr">
         <is>
-          <t>IPTV STB box Damage Issue</t>
+          <t>Router Upgrade  Wi-Fi 6</t>
         </is>
       </c>
       <c r="E32" s="3" t="inlineStr">
@@ -4123,22 +4696,22 @@
       </c>
       <c r="H32" s="3" t="inlineStr">
         <is>
-          <t>Case : IP TV not Working   has been updated by Ajit Shrestha</t>
+          <t>Case : Wifi 6  has been updated by Sabin Giri</t>
         </is>
       </c>
       <c r="I32" s="3" t="inlineStr">
         <is>
-          <t>23 Sep 2026 01:16:47 PM</t>
+          <t>23 Sep 2026 01:17:39 PM</t>
         </is>
       </c>
       <c r="J32" s="3" t="inlineStr">
         <is>
-          <t>22 Sep 2026 08:56:52 PM</t>
+          <t>23 Sep 2026 10:26:34 AM</t>
         </is>
       </c>
       <c r="K32" s="3" t="inlineStr">
         <is>
-          <t>23 Sep 2026 01:16:47 PM</t>
+          <t>23 Sep 2026 01:17:39 PM</t>
         </is>
       </c>
       <c r="L32" s="3" t="inlineStr">
@@ -4148,74 +4721,275 @@
       </c>
       <c r="M32" s="3" t="inlineStr">
         <is>
-          <t>16h 19m</t>
+          <t>2h 51m</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="5" t="inlineStr">
         <is>
+          <t>TKT1343062</t>
+        </is>
+      </c>
+      <c r="B33" s="5" t="inlineStr">
+        <is>
+          <t>Sabin Magar</t>
+        </is>
+      </c>
+      <c r="C33" s="5" t="inlineStr">
+        <is>
+          <t>Hardware Damage / Malfunction</t>
+        </is>
+      </c>
+      <c r="D33" s="5" t="inlineStr">
+        <is>
+          <t>IPTV STB box Damage Issue</t>
+        </is>
+      </c>
+      <c r="E33" s="5" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="F33" s="5" t="inlineStr">
+        <is>
+          <t>Completed (Completed)</t>
+        </is>
+      </c>
+      <c r="G33" s="5" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="H33" s="5" t="inlineStr">
+        <is>
+          <t>Case : IP TV not Working   has been updated by Ajit Shrestha</t>
+        </is>
+      </c>
+      <c r="I33" s="5" t="inlineStr">
+        <is>
+          <t>23 Sep 2026 01:16:47 PM</t>
+        </is>
+      </c>
+      <c r="J33" s="5" t="inlineStr">
+        <is>
+          <t>22 Sep 2026 08:56:52 PM</t>
+        </is>
+      </c>
+      <c r="K33" s="5" t="inlineStr">
+        <is>
+          <t>23 Sep 2026 01:16:47 PM</t>
+        </is>
+      </c>
+      <c r="L33" s="5" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="M33" s="5" t="inlineStr">
+        <is>
+          <t>16h 19m</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="3" t="inlineStr">
+        <is>
           <t>TKT1341347</t>
         </is>
       </c>
-      <c r="B33" s="5" t="inlineStr">
+      <c r="B34" s="3" t="inlineStr">
         <is>
           <t>Siddhartha Model School</t>
         </is>
       </c>
-      <c r="C33" s="5" t="inlineStr">
+      <c r="C34" s="3" t="inlineStr">
         <is>
           <t>General / Other Issues</t>
         </is>
       </c>
-      <c r="D33" s="5" t="inlineStr">
+      <c r="D34" s="3" t="inlineStr">
         <is>
           <t>Router Upgrade  Wi-Fi 6</t>
         </is>
       </c>
-      <c r="E33" s="5" t="inlineStr">
+      <c r="E34" s="3" t="inlineStr">
         <is>
           <t>Closed</t>
         </is>
       </c>
-      <c r="F33" s="5" t="inlineStr">
+      <c r="F34" s="3" t="inlineStr">
         <is>
           <t>Completed (Closed)</t>
         </is>
       </c>
-      <c r="G33" s="5" t="inlineStr">
+      <c r="G34" s="3" t="inlineStr">
         <is>
           <t>nan</t>
         </is>
       </c>
-      <c r="H33" s="5" t="inlineStr">
+      <c r="H34" s="3" t="inlineStr">
         <is>
           <t>Case : wifi 6  has been updated by Sunil Chaudhary</t>
         </is>
       </c>
-      <c r="I33" s="5" t="inlineStr">
+      <c r="I34" s="3" t="inlineStr">
         <is>
           <t>21 Sep 2026 01:35:47 PM</t>
         </is>
       </c>
-      <c r="J33" s="5" t="inlineStr">
+      <c r="J34" s="3" t="inlineStr">
         <is>
           <t>21 Sep 2026 01:35:47 PM</t>
         </is>
       </c>
-      <c r="K33" s="5" t="inlineStr">
+      <c r="K34" s="3" t="inlineStr">
         <is>
           <t>23 Sep 2026 01:22:44 PM</t>
         </is>
       </c>
-      <c r="L33" s="5" t="inlineStr">
+      <c r="L34" s="3" t="inlineStr">
         <is>
           <t>1d 23h 46m</t>
         </is>
       </c>
-      <c r="M33" s="5" t="inlineStr">
+      <c r="M34" s="3" t="inlineStr">
         <is>
           <t>1d 23h 46m</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="5" t="inlineStr">
+        <is>
+          <t>TKT1342867</t>
+        </is>
+      </c>
+      <c r="B35" s="5" t="inlineStr">
+        <is>
+          <t>Punit Kumar Barnawal</t>
+        </is>
+      </c>
+      <c r="C35" s="5" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="D35" s="5" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="E35" s="5" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="F35" s="5" t="inlineStr">
+        <is>
+          <t>Completed (Completed)</t>
+        </is>
+      </c>
+      <c r="G35" s="5" t="inlineStr">
+        <is>
+          <t>Case : Wifi 6  has been updated by Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="H35" s="5" t="inlineStr">
+        <is>
+          <t>Case : Wifi 6  has been updated by Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="I35" s="5" t="inlineStr">
+        <is>
+          <t>23 Sep 2026 01:48:42 PM</t>
+        </is>
+      </c>
+      <c r="J35" s="5" t="inlineStr">
+        <is>
+          <t>22 Sep 2026 06:02:29 PM</t>
+        </is>
+      </c>
+      <c r="K35" s="5" t="inlineStr">
+        <is>
+          <t>23 Sep 2026 01:48:42 PM</t>
+        </is>
+      </c>
+      <c r="L35" s="5" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="M35" s="5" t="inlineStr">
+        <is>
+          <t>19h 46m</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="3" t="inlineStr">
+        <is>
+          <t>TKT1343135</t>
+        </is>
+      </c>
+      <c r="B36" s="3" t="inlineStr">
+        <is>
+          <t>Ashish Shahbadi</t>
+        </is>
+      </c>
+      <c r="C36" s="3" t="inlineStr">
+        <is>
+          <t>Hardware Damage / Malfunction</t>
+        </is>
+      </c>
+      <c r="D36" s="3" t="inlineStr">
+        <is>
+          <t>Router Damage Issue</t>
+        </is>
+      </c>
+      <c r="E36" s="3" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="F36" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Completed)</t>
+        </is>
+      </c>
+      <c r="G36" s="3" t="inlineStr">
+        <is>
+          <t>Case : 5g not working   has been updated by Rajesh Maharjan</t>
+        </is>
+      </c>
+      <c r="H36" s="3" t="inlineStr">
+        <is>
+          <t>Case : 5g not working   has been updated by Rajesh Maharjan</t>
+        </is>
+      </c>
+      <c r="I36" s="3" t="inlineStr">
+        <is>
+          <t>23 Sep 2026 01:51:51 PM</t>
+        </is>
+      </c>
+      <c r="J36" s="3" t="inlineStr">
+        <is>
+          <t>22 Sep 2026 10:20:07 PM</t>
+        </is>
+      </c>
+      <c r="K36" s="3" t="inlineStr">
+        <is>
+          <t>23 Sep 2026 01:51:51 PM</t>
+        </is>
+      </c>
+      <c r="L36" s="3" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="M36" s="3" t="inlineStr">
+        <is>
+          <t>15h 31m</t>
         </is>
       </c>
     </row>

--- a/audit_report_ALL_TEAM_23_Sep_2026.xlsx
+++ b/audit_report_ALL_TEAM_23_Sep_2026.xlsx
@@ -483,7 +483,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AW16"/>
+  <dimension ref="A1:AW19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="23" customWidth="1" min="1" max="1"/>
@@ -3259,10 +3259,8 @@
           <t>Punit Kumar Barnawal</t>
         </is>
       </c>
-      <c r="O14" s="3" t="inlineStr">
-        <is>
-          <t>9845947695</t>
-        </is>
+      <c r="O14" s="3" t="n">
+        <v>9845947695</v>
       </c>
       <c r="P14" s="3" t="inlineStr">
         <is>
@@ -3297,10 +3295,8 @@
           <t>Active</t>
         </is>
       </c>
-      <c r="Y14" s="3" t="inlineStr">
-        <is>
-          <t>27.68099</t>
-        </is>
+      <c r="Y14" s="3" t="n">
+        <v>27.68099</v>
       </c>
       <c r="Z14" s="3" t="inlineStr">
         <is>
@@ -3352,25 +3348,21 @@
           <t>Shashikant Chaudhary</t>
         </is>
       </c>
-      <c r="AN14" s="3" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
+      <c r="AN14" s="3" t="n">
+        <v>4</v>
       </c>
       <c r="AO14" s="3" t="inlineStr">
         <is>
           <t>4,13</t>
         </is>
       </c>
-      <c r="AP14" s="3" t="inlineStr">
-        <is>
-          <t>85.3673</t>
-        </is>
+      <c r="AP14" s="3" t="n">
+        <v>85.3673</v>
       </c>
       <c r="AQ14" s="3" t="inlineStr"/>
       <c r="AR14" s="3" t="inlineStr">
         <is>
-          <t>Case : Wifi 6  has been updated by Shashikant Chaudhary</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="AS14" s="3" t="inlineStr">
@@ -3466,10 +3458,8 @@
           <t>Ashish Shahbadi</t>
         </is>
       </c>
-      <c r="O15" s="3" t="inlineStr">
-        <is>
-          <t>9845424784</t>
-        </is>
+      <c r="O15" s="3" t="n">
+        <v>9845424784</v>
       </c>
       <c r="P15" s="3" t="inlineStr">
         <is>
@@ -3504,10 +3494,8 @@
           <t>Active</t>
         </is>
       </c>
-      <c r="Y15" s="3" t="inlineStr">
-        <is>
-          <t>27.66151</t>
-        </is>
+      <c r="Y15" s="3" t="n">
+        <v>27.66151</v>
       </c>
       <c r="Z15" s="3" t="inlineStr">
         <is>
@@ -3563,25 +3551,21 @@
           <t>Rajesh Maharjan</t>
         </is>
       </c>
-      <c r="AN15" s="3" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
+      <c r="AN15" s="3" t="n">
+        <v>4</v>
       </c>
       <c r="AO15" s="3" t="inlineStr">
         <is>
           <t>1,1</t>
         </is>
       </c>
-      <c r="AP15" s="3" t="inlineStr">
-        <is>
-          <t>85.31385</t>
-        </is>
+      <c r="AP15" s="3" t="n">
+        <v>85.31385</v>
       </c>
       <c r="AQ15" s="3" t="inlineStr"/>
       <c r="AR15" s="3" t="inlineStr">
         <is>
-          <t>Case : 5g not working   has been updated by Rajesh Maharjan</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="AS15" s="3" t="inlineStr">
@@ -3677,10 +3661,8 @@
           <t>samrat shrestha</t>
         </is>
       </c>
-      <c r="O16" s="3" t="inlineStr">
-        <is>
-          <t>9820084508</t>
-        </is>
+      <c r="O16" s="3" t="n">
+        <v>9820084508</v>
       </c>
       <c r="P16" s="3" t="inlineStr">
         <is>
@@ -3766,10 +3748,8 @@
           <t>Ajit Shrestha</t>
         </is>
       </c>
-      <c r="AN16" s="3" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
+      <c r="AN16" s="3" t="n">
+        <v>6</v>
       </c>
       <c r="AO16" s="3" t="inlineStr">
         <is>
@@ -3780,32 +3760,665 @@
       <c r="AQ16" s="3" t="inlineStr"/>
       <c r="AR16" s="3" t="inlineStr">
         <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="AS16" s="3" t="inlineStr">
+        <is>
+          <t>3h 34m</t>
+        </is>
+      </c>
+      <c r="AT16" s="3" t="inlineStr">
+        <is>
+          <t>1d 22h 40m</t>
+        </is>
+      </c>
+      <c r="AU16" s="3" t="inlineStr">
+        <is>
+          <t>Other / In Progress (On Hold)</t>
+        </is>
+      </c>
+      <c r="AV16" s="3" t="inlineStr">
+        <is>
           <t>Case : wifi 6 upgrade  has been updated by Ajit Shrestha</t>
         </is>
       </c>
-      <c r="AS16" s="3" t="inlineStr">
-        <is>
-          <t>3h 34m</t>
-        </is>
-      </c>
-      <c r="AT16" s="3" t="inlineStr">
-        <is>
-          <t>1d 22h 40m</t>
-        </is>
-      </c>
-      <c r="AU16" s="3" t="inlineStr">
-        <is>
-          <t>Other / In Progress (On Hold)</t>
-        </is>
-      </c>
-      <c r="AV16" s="3" t="inlineStr">
-        <is>
-          <t>Case : wifi 6 upgrade  has been updated by Ajit Shrestha</t>
-        </is>
-      </c>
       <c r="AW16" s="3" t="inlineStr">
         <is>
           <t>WiFi 6 Upgrade</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="3" t="inlineStr">
+        <is>
+          <t>Sabin Giri</t>
+        </is>
+      </c>
+      <c r="B17" s="3" t="inlineStr">
+        <is>
+          <t>23 Sep 2026 2:03 PM</t>
+        </is>
+      </c>
+      <c r="C17" s="3" t="inlineStr">
+        <is>
+          <t>WGnmUJF06LTlUriJ5DeDBQ==</t>
+        </is>
+      </c>
+      <c r="D17" s="3" t="inlineStr">
+        <is>
+          <t>Sabin Giri</t>
+        </is>
+      </c>
+      <c r="E17" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F17" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G17" s="3" t="inlineStr"/>
+      <c r="H17" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi 6  has been updated by Sabin Giri</t>
+        </is>
+      </c>
+      <c r="I17" s="3" t="inlineStr">
+        <is>
+          <t>wifi 6</t>
+        </is>
+      </c>
+      <c r="J17" s="3" t="inlineStr">
+        <is>
+          <t>TKT1343287</t>
+        </is>
+      </c>
+      <c r="K17" s="3" t="inlineStr">
+        <is>
+          <t>Anup Chaudhary</t>
+        </is>
+      </c>
+      <c r="L17" s="3" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="M17" s="3" t="inlineStr">
+        <is>
+          <t>Phone</t>
+        </is>
+      </c>
+      <c r="N17" s="3" t="inlineStr">
+        <is>
+          <t>Anup Chaudhary</t>
+        </is>
+      </c>
+      <c r="O17" s="3" t="inlineStr">
+        <is>
+          <t>9818167512</t>
+        </is>
+      </c>
+      <c r="P17" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="Q17" s="3" t="inlineStr"/>
+      <c r="R17" s="3" t="inlineStr">
+        <is>
+          <t>23 Sep 2026 02:03:32 PM</t>
+        </is>
+      </c>
+      <c r="S17" s="3" t="inlineStr"/>
+      <c r="T17" s="3" t="inlineStr"/>
+      <c r="U17" s="3" t="inlineStr">
+        <is>
+          <t>9818167512</t>
+        </is>
+      </c>
+      <c r="V17" s="3" t="inlineStr">
+        <is>
+          <t>23 Sep 2026 08:37:17 AM</t>
+        </is>
+      </c>
+      <c r="W17" s="3" t="inlineStr">
+        <is>
+          <t>23 Sep 2026 02:03:32 PM</t>
+        </is>
+      </c>
+      <c r="X17" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Y17" s="3" t="inlineStr">
+        <is>
+          <t>27.74632</t>
+        </is>
+      </c>
+      <c r="Z17" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="AA17" s="3" t="inlineStr">
+        <is>
+          <t>Layer 1-User</t>
+        </is>
+      </c>
+      <c r="AB17" s="3" t="inlineStr">
+        <is>
+          <t>L1  Support</t>
+        </is>
+      </c>
+      <c r="AC17" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="AD17" s="3" t="inlineStr"/>
+      <c r="AE17" s="3" t="inlineStr">
+        <is>
+          <t>Near  Sumarga Hardware P8W7+8XH, Tarakeshwar 44610, Bagmati, Central, Nepal</t>
+        </is>
+      </c>
+      <c r="AF17" s="3" t="inlineStr">
+        <is>
+          <t>anupchaudhary009@gmail.com</t>
+        </is>
+      </c>
+      <c r="AG17" s="3" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="AH17" s="3" t="inlineStr"/>
+      <c r="AI17" s="3" t="inlineStr">
+        <is>
+          <t>04:03 hour</t>
+        </is>
+      </c>
+      <c r="AJ17" s="3" t="inlineStr"/>
+      <c r="AK17" s="3" t="inlineStr"/>
+      <c r="AL17" s="3" t="inlineStr">
+        <is>
+          <t>Monali Lohani</t>
+        </is>
+      </c>
+      <c r="AM17" s="3" t="inlineStr">
+        <is>
+          <t>Sabin Giri</t>
+        </is>
+      </c>
+      <c r="AN17" s="3" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AO17" s="3" t="inlineStr">
+        <is>
+          <t>3,11</t>
+        </is>
+      </c>
+      <c r="AP17" s="3" t="inlineStr">
+        <is>
+          <t>85.31467</t>
+        </is>
+      </c>
+      <c r="AQ17" s="3" t="inlineStr"/>
+      <c r="AR17" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi 6  has been updated by Sabin Giri</t>
+        </is>
+      </c>
+      <c r="AS17" s="3" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="AT17" s="3" t="inlineStr">
+        <is>
+          <t>5h 26m</t>
+        </is>
+      </c>
+      <c r="AU17" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Completed)</t>
+        </is>
+      </c>
+      <c r="AV17" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi 6  has been updated by Sabin Giri</t>
+        </is>
+      </c>
+      <c r="AW17" s="3" t="inlineStr">
+        <is>
+          <t>WiFi 6 Upgrade</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="3" t="inlineStr">
+        <is>
+          <t>Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="B18" s="3" t="inlineStr">
+        <is>
+          <t>23 Sep 2026 2:16 PM</t>
+        </is>
+      </c>
+      <c r="C18" s="3" t="inlineStr">
+        <is>
+          <t>Zg1bIUI+iSmQ1fi360NaxA==</t>
+        </is>
+      </c>
+      <c r="D18" s="3" t="inlineStr">
+        <is>
+          <t>Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="E18" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F18" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G18" s="3" t="inlineStr"/>
+      <c r="H18" s="3" t="inlineStr">
+        <is>
+          <t>Case : stb faulty  has been updated by Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="I18" s="3" t="inlineStr">
+        <is>
+          <t>stb faulty</t>
+        </is>
+      </c>
+      <c r="J18" s="3" t="inlineStr">
+        <is>
+          <t>TKT1342988</t>
+        </is>
+      </c>
+      <c r="K18" s="3" t="inlineStr">
+        <is>
+          <t>Kushal Neupane</t>
+        </is>
+      </c>
+      <c r="L18" s="3" t="inlineStr">
+        <is>
+          <t>Closed</t>
+        </is>
+      </c>
+      <c r="M18" s="3" t="inlineStr">
+        <is>
+          <t>Phone</t>
+        </is>
+      </c>
+      <c r="N18" s="3" t="inlineStr">
+        <is>
+          <t>Kushal Neupane</t>
+        </is>
+      </c>
+      <c r="O18" s="3" t="inlineStr">
+        <is>
+          <t>9860105575</t>
+        </is>
+      </c>
+      <c r="P18" s="3" t="inlineStr">
+        <is>
+          <t>Hardware Damage / Malfunction</t>
+        </is>
+      </c>
+      <c r="Q18" s="3" t="inlineStr"/>
+      <c r="R18" s="3" t="inlineStr">
+        <is>
+          <t>22 Sep 2026 08:27:54 PM</t>
+        </is>
+      </c>
+      <c r="S18" s="3" t="inlineStr"/>
+      <c r="T18" s="3" t="inlineStr"/>
+      <c r="U18" s="3" t="inlineStr">
+        <is>
+          <t>9860105575</t>
+        </is>
+      </c>
+      <c r="V18" s="3" t="inlineStr">
+        <is>
+          <t>22 Sep 2026 07:49:31 PM</t>
+        </is>
+      </c>
+      <c r="W18" s="3" t="inlineStr">
+        <is>
+          <t>23 Sep 2026 02:16:10 PM</t>
+        </is>
+      </c>
+      <c r="X18" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Y18" s="3" t="inlineStr">
+        <is>
+          <t>27.73739</t>
+        </is>
+      </c>
+      <c r="Z18" s="3" t="inlineStr">
+        <is>
+          <t>Hardware Damage / Malfunction</t>
+        </is>
+      </c>
+      <c r="AA18" s="3" t="inlineStr">
+        <is>
+          <t>Layer 1-</t>
+        </is>
+      </c>
+      <c r="AB18" s="3" t="inlineStr">
+        <is>
+          <t>Laxman Koirala</t>
+        </is>
+      </c>
+      <c r="AC18" s="3" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="AD18" s="3" t="inlineStr"/>
+      <c r="AE18" s="3" t="inlineStr">
+        <is>
+          <t>Near to A.B. Supply Store , Raniban , Kathmandu, Bagmati, Central, Nepal</t>
+        </is>
+      </c>
+      <c r="AF18" s="3" t="inlineStr">
+        <is>
+          <t>kushaln07@gmail.com</t>
+        </is>
+      </c>
+      <c r="AG18" s="3" t="inlineStr">
+        <is>
+          <t>IPTV STB box Damage Issue</t>
+        </is>
+      </c>
+      <c r="AH18" s="3" t="inlineStr"/>
+      <c r="AI18" s="3" t="inlineStr">
+        <is>
+          <t>04:26 hour</t>
+        </is>
+      </c>
+      <c r="AJ18" s="3" t="inlineStr"/>
+      <c r="AK18" s="3" t="inlineStr"/>
+      <c r="AL18" s="3" t="inlineStr">
+        <is>
+          <t>Bhumika Saud</t>
+        </is>
+      </c>
+      <c r="AM18" s="3" t="inlineStr">
+        <is>
+          <t>Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="AN18" s="3" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AO18" s="3" t="inlineStr">
+        <is>
+          <t>4,14</t>
+        </is>
+      </c>
+      <c r="AP18" s="3" t="inlineStr">
+        <is>
+          <t>85.28689</t>
+        </is>
+      </c>
+      <c r="AQ18" s="3" t="inlineStr"/>
+      <c r="AR18" s="3" t="inlineStr">
+        <is>
+          <t>Case : stb faulty  has been updated by Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="AS18" s="3" t="inlineStr">
+        <is>
+          <t>17h 48m</t>
+        </is>
+      </c>
+      <c r="AT18" s="3" t="inlineStr">
+        <is>
+          <t>18h 26m</t>
+        </is>
+      </c>
+      <c r="AU18" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Closed)</t>
+        </is>
+      </c>
+      <c r="AV18" s="3" t="inlineStr">
+        <is>
+          <t>Case : stb faulty  has been updated by Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="AW18" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="3" t="inlineStr">
+        <is>
+          <t>Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="B19" s="3" t="inlineStr">
+        <is>
+          <t>23 Sep 2026 2:15 PM</t>
+        </is>
+      </c>
+      <c r="C19" s="3" t="inlineStr">
+        <is>
+          <t>Zg1bIUI+iSmQ1fi360NaxA==</t>
+        </is>
+      </c>
+      <c r="D19" s="3" t="inlineStr">
+        <is>
+          <t>Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="E19" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F19" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G19" s="3" t="inlineStr"/>
+      <c r="H19" s="3" t="inlineStr">
+        <is>
+          <t>Case : stb faulty  has been updated by Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="I19" s="3" t="inlineStr">
+        <is>
+          <t>stb faulty</t>
+        </is>
+      </c>
+      <c r="J19" s="3" t="inlineStr">
+        <is>
+          <t>TKT1342988</t>
+        </is>
+      </c>
+      <c r="K19" s="3" t="inlineStr">
+        <is>
+          <t>Kushal Neupane</t>
+        </is>
+      </c>
+      <c r="L19" s="3" t="inlineStr">
+        <is>
+          <t>Closed</t>
+        </is>
+      </c>
+      <c r="M19" s="3" t="inlineStr">
+        <is>
+          <t>Phone</t>
+        </is>
+      </c>
+      <c r="N19" s="3" t="inlineStr">
+        <is>
+          <t>Kushal Neupane</t>
+        </is>
+      </c>
+      <c r="O19" s="3" t="inlineStr">
+        <is>
+          <t>9860105575</t>
+        </is>
+      </c>
+      <c r="P19" s="3" t="inlineStr">
+        <is>
+          <t>Hardware Damage / Malfunction</t>
+        </is>
+      </c>
+      <c r="Q19" s="3" t="inlineStr"/>
+      <c r="R19" s="3" t="inlineStr">
+        <is>
+          <t>22 Sep 2026 08:27:54 PM</t>
+        </is>
+      </c>
+      <c r="S19" s="3" t="inlineStr"/>
+      <c r="T19" s="3" t="inlineStr"/>
+      <c r="U19" s="3" t="inlineStr">
+        <is>
+          <t>9860105575</t>
+        </is>
+      </c>
+      <c r="V19" s="3" t="inlineStr">
+        <is>
+          <t>22 Sep 2026 07:49:31 PM</t>
+        </is>
+      </c>
+      <c r="W19" s="3" t="inlineStr">
+        <is>
+          <t>23 Sep 2026 02:16:10 PM</t>
+        </is>
+      </c>
+      <c r="X19" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Y19" s="3" t="inlineStr">
+        <is>
+          <t>27.73739</t>
+        </is>
+      </c>
+      <c r="Z19" s="3" t="inlineStr">
+        <is>
+          <t>Hardware Damage / Malfunction</t>
+        </is>
+      </c>
+      <c r="AA19" s="3" t="inlineStr">
+        <is>
+          <t>Layer 1-</t>
+        </is>
+      </c>
+      <c r="AB19" s="3" t="inlineStr">
+        <is>
+          <t>Laxman Koirala</t>
+        </is>
+      </c>
+      <c r="AC19" s="3" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="AD19" s="3" t="inlineStr"/>
+      <c r="AE19" s="3" t="inlineStr">
+        <is>
+          <t>Near to A.B. Supply Store , Raniban , Kathmandu, Bagmati, Central, Nepal</t>
+        </is>
+      </c>
+      <c r="AF19" s="3" t="inlineStr">
+        <is>
+          <t>kushaln07@gmail.com</t>
+        </is>
+      </c>
+      <c r="AG19" s="3" t="inlineStr">
+        <is>
+          <t>IPTV STB box Damage Issue</t>
+        </is>
+      </c>
+      <c r="AH19" s="3" t="inlineStr"/>
+      <c r="AI19" s="3" t="inlineStr">
+        <is>
+          <t>04:26 hour</t>
+        </is>
+      </c>
+      <c r="AJ19" s="3" t="inlineStr"/>
+      <c r="AK19" s="3" t="inlineStr"/>
+      <c r="AL19" s="3" t="inlineStr">
+        <is>
+          <t>Bhumika Saud</t>
+        </is>
+      </c>
+      <c r="AM19" s="3" t="inlineStr">
+        <is>
+          <t>Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="AN19" s="3" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AO19" s="3" t="inlineStr">
+        <is>
+          <t>4,14</t>
+        </is>
+      </c>
+      <c r="AP19" s="3" t="inlineStr">
+        <is>
+          <t>85.28689</t>
+        </is>
+      </c>
+      <c r="AQ19" s="3" t="inlineStr"/>
+      <c r="AR19" s="3" t="inlineStr">
+        <is>
+          <t>Case : stb faulty  has been updated by Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="AS19" s="3" t="inlineStr">
+        <is>
+          <t>17h 48m</t>
+        </is>
+      </c>
+      <c r="AT19" s="3" t="inlineStr">
+        <is>
+          <t>18h 26m</t>
+        </is>
+      </c>
+      <c r="AU19" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Closed)</t>
+        </is>
+      </c>
+      <c r="AV19" s="3" t="inlineStr">
+        <is>
+          <t>Case : stb faulty  has been updated by Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="AW19" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
         </is>
       </c>
     </row>
@@ -3820,7 +4433,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M36"/>
+  <dimension ref="A1:M39"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="45" customWidth="1" min="1" max="1"/>
@@ -3857,7 +4470,7 @@
         </is>
       </c>
       <c r="B2" s="3" t="n">
-        <v>15</v>
+        <v>18</v>
       </c>
     </row>
     <row r="3">
@@ -3867,7 +4480,7 @@
         </is>
       </c>
       <c r="B3" s="5" t="n">
-        <v>11</v>
+        <v>14</v>
       </c>
     </row>
     <row r="4">
@@ -3878,7 +4491,7 @@
       </c>
       <c r="B4" s="3" t="inlineStr">
         <is>
-          <t>73.3%</t>
+          <t>77.8%</t>
         </is>
       </c>
     </row>
@@ -3890,7 +4503,7 @@
       </c>
       <c r="B5" s="5" t="inlineStr">
         <is>
-          <t>6h 21m</t>
+          <t>7h 32m</t>
         </is>
       </c>
     </row>
@@ -3902,7 +4515,7 @@
       </c>
       <c r="B6" s="3" t="inlineStr">
         <is>
-          <t>16h 29m</t>
+          <t>15h 58m</t>
         </is>
       </c>
     </row>
@@ -3943,14 +4556,14 @@
         </is>
       </c>
       <c r="B10" s="3" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="C10" s="3" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D10" s="3" t="inlineStr">
         <is>
-          <t>72.7%</t>
+          <t>75.0%</t>
         </is>
       </c>
     </row>
@@ -3961,10 +4574,10 @@
         </is>
       </c>
       <c r="B11" s="5" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="C11" s="5" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="D11" s="5" t="inlineStr">
         <is>
@@ -4055,14 +4668,14 @@
         </is>
       </c>
       <c r="C17" s="5" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="D17" s="5" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="E17" s="5" t="inlineStr">
         <is>
-          <t>70.0%</t>
+          <t>72.7%</t>
         </is>
       </c>
     </row>
@@ -4101,10 +4714,10 @@
         </is>
       </c>
       <c r="C19" s="5" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D19" s="5" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E19" s="5" t="inlineStr">
         <is>
@@ -4892,7 +5505,7 @@
       </c>
       <c r="G35" s="5" t="inlineStr">
         <is>
-          <t>Case : Wifi 6  has been updated by Shashikant Chaudhary</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="H35" s="5" t="inlineStr">
@@ -4959,14 +5572,14 @@
       </c>
       <c r="G36" s="3" t="inlineStr">
         <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="H36" s="3" t="inlineStr">
+        <is>
           <t>Case : 5g not working   has been updated by Rajesh Maharjan</t>
         </is>
       </c>
-      <c r="H36" s="3" t="inlineStr">
-        <is>
-          <t>Case : 5g not working   has been updated by Rajesh Maharjan</t>
-        </is>
-      </c>
       <c r="I36" s="3" t="inlineStr">
         <is>
           <t>23 Sep 2026 01:51:51 PM</t>
@@ -4990,6 +5603,207 @@
       <c r="M36" s="3" t="inlineStr">
         <is>
           <t>15h 31m</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="5" t="inlineStr">
+        <is>
+          <t>TKT1343287</t>
+        </is>
+      </c>
+      <c r="B37" s="5" t="inlineStr">
+        <is>
+          <t>Anup Chaudhary</t>
+        </is>
+      </c>
+      <c r="C37" s="5" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="D37" s="5" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="E37" s="5" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="F37" s="5" t="inlineStr">
+        <is>
+          <t>Completed (Completed)</t>
+        </is>
+      </c>
+      <c r="G37" s="5" t="inlineStr">
+        <is>
+          <t>Case : wifi 6  has been updated by Sabin Giri</t>
+        </is>
+      </c>
+      <c r="H37" s="5" t="inlineStr">
+        <is>
+          <t>Case : wifi 6  has been updated by Sabin Giri</t>
+        </is>
+      </c>
+      <c r="I37" s="5" t="inlineStr">
+        <is>
+          <t>23 Sep 2026 02:03:32 PM</t>
+        </is>
+      </c>
+      <c r="J37" s="5" t="inlineStr">
+        <is>
+          <t>23 Sep 2026 08:37:17 AM</t>
+        </is>
+      </c>
+      <c r="K37" s="5" t="inlineStr">
+        <is>
+          <t>23 Sep 2026 02:03:32 PM</t>
+        </is>
+      </c>
+      <c r="L37" s="5" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="M37" s="5" t="inlineStr">
+        <is>
+          <t>5h 26m</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="3" t="inlineStr">
+        <is>
+          <t>TKT1342988</t>
+        </is>
+      </c>
+      <c r="B38" s="3" t="inlineStr">
+        <is>
+          <t>Kushal Neupane</t>
+        </is>
+      </c>
+      <c r="C38" s="3" t="inlineStr">
+        <is>
+          <t>Hardware Damage / Malfunction</t>
+        </is>
+      </c>
+      <c r="D38" s="3" t="inlineStr">
+        <is>
+          <t>IPTV STB box Damage Issue</t>
+        </is>
+      </c>
+      <c r="E38" s="3" t="inlineStr">
+        <is>
+          <t>Closed</t>
+        </is>
+      </c>
+      <c r="F38" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Closed)</t>
+        </is>
+      </c>
+      <c r="G38" s="3" t="inlineStr">
+        <is>
+          <t>Case : stb faulty  has been updated by Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="H38" s="3" t="inlineStr">
+        <is>
+          <t>Case : stb faulty  has been updated by Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="I38" s="3" t="inlineStr">
+        <is>
+          <t>22 Sep 2026 08:27:54 PM</t>
+        </is>
+      </c>
+      <c r="J38" s="3" t="inlineStr">
+        <is>
+          <t>22 Sep 2026 07:49:31 PM</t>
+        </is>
+      </c>
+      <c r="K38" s="3" t="inlineStr">
+        <is>
+          <t>23 Sep 2026 02:16:10 PM</t>
+        </is>
+      </c>
+      <c r="L38" s="3" t="inlineStr">
+        <is>
+          <t>17h 48m</t>
+        </is>
+      </c>
+      <c r="M38" s="3" t="inlineStr">
+        <is>
+          <t>18h 26m</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="5" t="inlineStr">
+        <is>
+          <t>TKT1342988</t>
+        </is>
+      </c>
+      <c r="B39" s="5" t="inlineStr">
+        <is>
+          <t>Kushal Neupane</t>
+        </is>
+      </c>
+      <c r="C39" s="5" t="inlineStr">
+        <is>
+          <t>Hardware Damage / Malfunction</t>
+        </is>
+      </c>
+      <c r="D39" s="5" t="inlineStr">
+        <is>
+          <t>IPTV STB box Damage Issue</t>
+        </is>
+      </c>
+      <c r="E39" s="5" t="inlineStr">
+        <is>
+          <t>Closed</t>
+        </is>
+      </c>
+      <c r="F39" s="5" t="inlineStr">
+        <is>
+          <t>Completed (Closed)</t>
+        </is>
+      </c>
+      <c r="G39" s="5" t="inlineStr">
+        <is>
+          <t>Case : stb faulty  has been updated by Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="H39" s="5" t="inlineStr">
+        <is>
+          <t>Case : stb faulty  has been updated by Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="I39" s="5" t="inlineStr">
+        <is>
+          <t>22 Sep 2026 08:27:54 PM</t>
+        </is>
+      </c>
+      <c r="J39" s="5" t="inlineStr">
+        <is>
+          <t>22 Sep 2026 07:49:31 PM</t>
+        </is>
+      </c>
+      <c r="K39" s="5" t="inlineStr">
+        <is>
+          <t>23 Sep 2026 02:16:10 PM</t>
+        </is>
+      </c>
+      <c r="L39" s="5" t="inlineStr">
+        <is>
+          <t>17h 48m</t>
+        </is>
+      </c>
+      <c r="M39" s="5" t="inlineStr">
+        <is>
+          <t>18h 26m</t>
         </is>
       </c>
     </row>

--- a/audit_report_ALL_TEAM_23_Sep_2026.xlsx
+++ b/audit_report_ALL_TEAM_23_Sep_2026.xlsx
@@ -483,7 +483,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AW19"/>
+  <dimension ref="A1:AW22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="23" customWidth="1" min="1" max="1"/>
@@ -494,19 +494,19 @@
     <col width="17" customWidth="1" min="6" max="6"/>
     <col width="18" customWidth="1" min="7" max="7"/>
     <col width="40" customWidth="1" min="8" max="8"/>
-    <col width="27" customWidth="1" min="9" max="9"/>
+    <col width="29" customWidth="1" min="9" max="9"/>
     <col width="16" customWidth="1" min="10" max="10"/>
-    <col width="29" customWidth="1" min="11" max="11"/>
+    <col width="31" customWidth="1" min="11" max="11"/>
     <col width="12" customWidth="1" min="12" max="12"/>
     <col width="14" customWidth="1" min="13" max="13"/>
-    <col width="29" customWidth="1" min="14" max="14"/>
+    <col width="31" customWidth="1" min="14" max="14"/>
     <col width="13" customWidth="1" min="15" max="15"/>
     <col width="32" customWidth="1" min="16" max="16"/>
     <col width="19" customWidth="1" min="17" max="17"/>
     <col width="26" customWidth="1" min="18" max="18"/>
     <col width="37" customWidth="1" min="19" max="19"/>
     <col width="37" customWidth="1" min="20" max="20"/>
-    <col width="16" customWidth="1" min="21" max="21"/>
+    <col width="19" customWidth="1" min="21" max="21"/>
     <col width="26" customWidth="1" min="22" max="22"/>
     <col width="26" customWidth="1" min="23" max="23"/>
     <col width="29" customWidth="1" min="24" max="24"/>
@@ -518,7 +518,7 @@
     <col width="10" customWidth="1" min="30" max="30"/>
     <col width="40" customWidth="1" min="31" max="31"/>
     <col width="34" customWidth="1" min="32" max="32"/>
-    <col width="29" customWidth="1" min="33" max="33"/>
+    <col width="39" customWidth="1" min="33" max="33"/>
     <col width="18" customWidth="1" min="34" max="34"/>
     <col width="13" customWidth="1" min="35" max="35"/>
     <col width="17" customWidth="1" min="36" max="36"/>
@@ -3856,10 +3856,8 @@
           <t>Anup Chaudhary</t>
         </is>
       </c>
-      <c r="O17" s="3" t="inlineStr">
-        <is>
-          <t>9818167512</t>
-        </is>
+      <c r="O17" s="3" t="n">
+        <v>9818167512</v>
       </c>
       <c r="P17" s="3" t="inlineStr">
         <is>
@@ -3894,10 +3892,8 @@
           <t>Active</t>
         </is>
       </c>
-      <c r="Y17" s="3" t="inlineStr">
-        <is>
-          <t>27.74632</t>
-        </is>
+      <c r="Y17" s="3" t="n">
+        <v>27.74632</v>
       </c>
       <c r="Z17" s="3" t="inlineStr">
         <is>
@@ -3953,25 +3949,21 @@
           <t>Sabin Giri</t>
         </is>
       </c>
-      <c r="AN17" s="3" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
+      <c r="AN17" s="3" t="n">
+        <v>4</v>
       </c>
       <c r="AO17" s="3" t="inlineStr">
         <is>
           <t>3,11</t>
         </is>
       </c>
-      <c r="AP17" s="3" t="inlineStr">
-        <is>
-          <t>85.31467</t>
-        </is>
+      <c r="AP17" s="3" t="n">
+        <v>85.31467000000001</v>
       </c>
       <c r="AQ17" s="3" t="inlineStr"/>
       <c r="AR17" s="3" t="inlineStr">
         <is>
-          <t>Case : wifi 6  has been updated by Sabin Giri</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="AS17" s="3" t="inlineStr">
@@ -4067,10 +4059,8 @@
           <t>Kushal Neupane</t>
         </is>
       </c>
-      <c r="O18" s="3" t="inlineStr">
-        <is>
-          <t>9860105575</t>
-        </is>
+      <c r="O18" s="3" t="n">
+        <v>9860105575</v>
       </c>
       <c r="P18" s="3" t="inlineStr">
         <is>
@@ -4105,10 +4095,8 @@
           <t>Active</t>
         </is>
       </c>
-      <c r="Y18" s="3" t="inlineStr">
-        <is>
-          <t>27.73739</t>
-        </is>
+      <c r="Y18" s="3" t="n">
+        <v>27.73739</v>
       </c>
       <c r="Z18" s="3" t="inlineStr">
         <is>
@@ -4164,25 +4152,21 @@
           <t>Sunil Chaudhary</t>
         </is>
       </c>
-      <c r="AN18" s="3" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
+      <c r="AN18" s="3" t="n">
+        <v>4</v>
       </c>
       <c r="AO18" s="3" t="inlineStr">
         <is>
           <t>4,14</t>
         </is>
       </c>
-      <c r="AP18" s="3" t="inlineStr">
-        <is>
-          <t>85.28689</t>
-        </is>
+      <c r="AP18" s="3" t="n">
+        <v>85.28689</v>
       </c>
       <c r="AQ18" s="3" t="inlineStr"/>
       <c r="AR18" s="3" t="inlineStr">
         <is>
-          <t>Case : stb faulty  has been updated by Sunil Chaudhary</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="AS18" s="3" t="inlineStr">
@@ -4278,10 +4262,8 @@
           <t>Kushal Neupane</t>
         </is>
       </c>
-      <c r="O19" s="3" t="inlineStr">
-        <is>
-          <t>9860105575</t>
-        </is>
+      <c r="O19" s="3" t="n">
+        <v>9860105575</v>
       </c>
       <c r="P19" s="3" t="inlineStr">
         <is>
@@ -4316,10 +4298,8 @@
           <t>Active</t>
         </is>
       </c>
-      <c r="Y19" s="3" t="inlineStr">
-        <is>
-          <t>27.73739</t>
-        </is>
+      <c r="Y19" s="3" t="n">
+        <v>27.73739</v>
       </c>
       <c r="Z19" s="3" t="inlineStr">
         <is>
@@ -4375,48 +4355,657 @@
           <t>Sunil Chaudhary</t>
         </is>
       </c>
-      <c r="AN19" s="3" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
+      <c r="AN19" s="3" t="n">
+        <v>4</v>
       </c>
       <c r="AO19" s="3" t="inlineStr">
         <is>
           <t>4,14</t>
         </is>
       </c>
-      <c r="AP19" s="3" t="inlineStr">
-        <is>
-          <t>85.28689</t>
-        </is>
+      <c r="AP19" s="3" t="n">
+        <v>85.28689</v>
       </c>
       <c r="AQ19" s="3" t="inlineStr"/>
       <c r="AR19" s="3" t="inlineStr">
         <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="AS19" s="3" t="inlineStr">
+        <is>
+          <t>17h 48m</t>
+        </is>
+      </c>
+      <c r="AT19" s="3" t="inlineStr">
+        <is>
+          <t>18h 26m</t>
+        </is>
+      </c>
+      <c r="AU19" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Closed)</t>
+        </is>
+      </c>
+      <c r="AV19" s="3" t="inlineStr">
+        <is>
           <t>Case : stb faulty  has been updated by Sunil Chaudhary</t>
         </is>
       </c>
-      <c r="AS19" s="3" t="inlineStr">
-        <is>
-          <t>17h 48m</t>
-        </is>
-      </c>
-      <c r="AT19" s="3" t="inlineStr">
-        <is>
-          <t>18h 26m</t>
-        </is>
-      </c>
-      <c r="AU19" s="3" t="inlineStr">
-        <is>
-          <t>Completed (Closed)</t>
-        </is>
-      </c>
-      <c r="AV19" s="3" t="inlineStr">
-        <is>
-          <t>Case : stb faulty  has been updated by Sunil Chaudhary</t>
-        </is>
-      </c>
       <c r="AW19" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="3" t="inlineStr">
+        <is>
+          <t>Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="B20" s="3" t="inlineStr">
+        <is>
+          <t>23 Sep 2026 2:18 PM</t>
+        </is>
+      </c>
+      <c r="C20" s="3" t="inlineStr">
+        <is>
+          <t>Zg1bIUI+iSmQ1fi360NaxA==</t>
+        </is>
+      </c>
+      <c r="D20" s="3" t="inlineStr">
+        <is>
+          <t>Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="E20" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F20" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G20" s="3" t="inlineStr"/>
+      <c r="H20" s="3" t="inlineStr">
+        <is>
+          <t>Case : Wifi 6  has been updated by Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="I20" s="3" t="inlineStr">
+        <is>
+          <t>Wifi 6</t>
+        </is>
+      </c>
+      <c r="J20" s="3" t="inlineStr">
+        <is>
+          <t>TKT1343621</t>
+        </is>
+      </c>
+      <c r="K20" s="3" t="inlineStr">
+        <is>
+          <t>Sabin Shrestha</t>
+        </is>
+      </c>
+      <c r="L20" s="3" t="inlineStr">
+        <is>
+          <t>On Hold</t>
+        </is>
+      </c>
+      <c r="M20" s="3" t="inlineStr">
+        <is>
+          <t>Phone</t>
+        </is>
+      </c>
+      <c r="N20" s="3" t="inlineStr">
+        <is>
+          <t>Sabin Shrestha</t>
+        </is>
+      </c>
+      <c r="O20" s="3" t="inlineStr">
+        <is>
+          <t>9818815777</t>
+        </is>
+      </c>
+      <c r="P20" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="Q20" s="3" t="inlineStr"/>
+      <c r="R20" s="3" t="inlineStr">
+        <is>
+          <t>23 Sep 2026 11:52:23 AM</t>
+        </is>
+      </c>
+      <c r="S20" s="3" t="inlineStr"/>
+      <c r="T20" s="3" t="inlineStr"/>
+      <c r="U20" s="3" t="inlineStr">
+        <is>
+          <t>9818815777</t>
+        </is>
+      </c>
+      <c r="V20" s="3" t="inlineStr">
+        <is>
+          <t>23 Sep 2026 11:52:23 AM</t>
+        </is>
+      </c>
+      <c r="W20" s="3" t="inlineStr">
+        <is>
+          <t>23 Sep 2026 02:18:50 PM</t>
+        </is>
+      </c>
+      <c r="X20" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Y20" s="3" t="inlineStr">
+        <is>
+          <t>27.72209</t>
+        </is>
+      </c>
+      <c r="Z20" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="AA20" s="3" t="inlineStr">
+        <is>
+          <t>Layer 1-User</t>
+        </is>
+      </c>
+      <c r="AB20" s="3" t="inlineStr">
+        <is>
+          <t>Laxman Koirala</t>
+        </is>
+      </c>
+      <c r="AC20" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="AD20" s="3" t="inlineStr"/>
+      <c r="AE20" s="3" t="inlineStr">
+        <is>
+          <t>Panchdhara Near Kamala beauty parlor , Bagmati, Central, Nepal</t>
+        </is>
+      </c>
+      <c r="AF20" s="3" t="inlineStr"/>
+      <c r="AG20" s="3" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="AH20" s="3" t="inlineStr"/>
+      <c r="AI20" s="3" t="inlineStr"/>
+      <c r="AJ20" s="3" t="inlineStr"/>
+      <c r="AK20" s="3" t="inlineStr"/>
+      <c r="AL20" s="3" t="inlineStr">
+        <is>
+          <t>Joshna Shrestha</t>
+        </is>
+      </c>
+      <c r="AM20" s="3" t="inlineStr">
+        <is>
+          <t>Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="AN20" s="3" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AO20" s="3" t="inlineStr">
+        <is>
+          <t>1,4</t>
+        </is>
+      </c>
+      <c r="AP20" s="3" t="inlineStr">
+        <is>
+          <t>85.27905</t>
+        </is>
+      </c>
+      <c r="AQ20" s="3" t="inlineStr"/>
+      <c r="AR20" s="3" t="inlineStr">
+        <is>
+          <t>Case : Wifi 6  has been updated by Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="AS20" s="3" t="inlineStr">
+        <is>
+          <t>2h 26m</t>
+        </is>
+      </c>
+      <c r="AT20" s="3" t="inlineStr">
+        <is>
+          <t>2h 26m</t>
+        </is>
+      </c>
+      <c r="AU20" s="3" t="inlineStr">
+        <is>
+          <t>Other / In Progress (On Hold)</t>
+        </is>
+      </c>
+      <c r="AV20" s="3" t="inlineStr">
+        <is>
+          <t>Case : Wifi 6  has been updated by Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="AW20" s="3" t="inlineStr">
+        <is>
+          <t>WiFi 6 Upgrade</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="3" t="inlineStr">
+        <is>
+          <t>Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="B21" s="3" t="inlineStr">
+        <is>
+          <t>23 Sep 2026 2:23 PM</t>
+        </is>
+      </c>
+      <c r="C21" s="3" t="inlineStr">
+        <is>
+          <t>atwz5SElGeKMz8qxsp3b6c34SBAfIMR+</t>
+        </is>
+      </c>
+      <c r="D21" s="3" t="inlineStr">
+        <is>
+          <t>Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="E21" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F21" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G21" s="3" t="inlineStr"/>
+      <c r="H21" s="3" t="inlineStr">
+        <is>
+          <t>Case : Secondary Router Connetion   has been updated by Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="I21" s="3" t="inlineStr">
+        <is>
+          <t>Secondary Router Connetion</t>
+        </is>
+      </c>
+      <c r="J21" s="3" t="inlineStr">
+        <is>
+          <t>TKT1340081</t>
+        </is>
+      </c>
+      <c r="K21" s="3" t="inlineStr">
+        <is>
+          <t>Anjan Khadka</t>
+        </is>
+      </c>
+      <c r="L21" s="3" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="M21" s="3" t="inlineStr">
+        <is>
+          <t>Phone</t>
+        </is>
+      </c>
+      <c r="N21" s="3" t="inlineStr">
+        <is>
+          <t>Anjan Khadka</t>
+        </is>
+      </c>
+      <c r="O21" s="3" t="inlineStr">
+        <is>
+          <t>9766884209</t>
+        </is>
+      </c>
+      <c r="P21" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="Q21" s="3" t="inlineStr"/>
+      <c r="R21" s="3" t="inlineStr">
+        <is>
+          <t>23 Sep 2026 02:23:04 PM</t>
+        </is>
+      </c>
+      <c r="S21" s="3" t="inlineStr"/>
+      <c r="T21" s="3" t="inlineStr"/>
+      <c r="U21" s="3" t="inlineStr">
+        <is>
+          <t>9864297931</t>
+        </is>
+      </c>
+      <c r="V21" s="3" t="inlineStr">
+        <is>
+          <t>20 Sep 2026 02:38:36 PM</t>
+        </is>
+      </c>
+      <c r="W21" s="3" t="inlineStr">
+        <is>
+          <t>23 Sep 2026 02:23:04 PM</t>
+        </is>
+      </c>
+      <c r="X21" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Y21" s="3" t="inlineStr">
+        <is>
+          <t>27.69419</t>
+        </is>
+      </c>
+      <c r="Z21" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="AA21" s="3" t="inlineStr">
+        <is>
+          <t>Layer 1-User</t>
+        </is>
+      </c>
+      <c r="AB21" s="3" t="inlineStr">
+        <is>
+          <t>L1  Support</t>
+        </is>
+      </c>
+      <c r="AC21" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="AD21" s="3" t="inlineStr"/>
+      <c r="AE21" s="3" t="inlineStr">
+        <is>
+          <t>Tripureshwor Near Kumari Devi Mandir, Bagmati, Central, Nepal</t>
+        </is>
+      </c>
+      <c r="AF21" s="3" t="inlineStr">
+        <is>
+          <t>work@cgnet.com.np</t>
+        </is>
+      </c>
+      <c r="AG21" s="3" t="inlineStr">
+        <is>
+          <t>Query For Secondary Router /Repeater</t>
+        </is>
+      </c>
+      <c r="AH21" s="3" t="inlineStr"/>
+      <c r="AI21" s="3" t="inlineStr">
+        <is>
+          <t>00:23 hour</t>
+        </is>
+      </c>
+      <c r="AJ21" s="3" t="inlineStr"/>
+      <c r="AK21" s="3" t="inlineStr"/>
+      <c r="AL21" s="3" t="inlineStr">
+        <is>
+          <t>Namrata Tamang</t>
+        </is>
+      </c>
+      <c r="AM21" s="3" t="inlineStr">
+        <is>
+          <t>Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="AN21" s="3" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AO21" s="3" t="inlineStr">
+        <is>
+          <t>1,7</t>
+        </is>
+      </c>
+      <c r="AP21" s="3" t="inlineStr">
+        <is>
+          <t>85.31665</t>
+        </is>
+      </c>
+      <c r="AQ21" s="3" t="inlineStr"/>
+      <c r="AR21" s="3" t="inlineStr">
+        <is>
+          <t>Case : Secondary Router Connetion   has been updated by Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="AS21" s="3" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="AT21" s="3" t="inlineStr">
+        <is>
+          <t>2d 23h 44m</t>
+        </is>
+      </c>
+      <c r="AU21" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Completed)</t>
+        </is>
+      </c>
+      <c r="AV21" s="3" t="inlineStr">
+        <is>
+          <t>Case : Secondary Router Connetion   has been updated by Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="AW21" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="3" t="inlineStr">
+        <is>
+          <t>Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="B22" s="3" t="inlineStr">
+        <is>
+          <t>23 Sep 2026 2:21 PM</t>
+        </is>
+      </c>
+      <c r="C22" s="3" t="inlineStr">
+        <is>
+          <t>atwz5SElGeKMz8qxsp3b6c34SBAfIMR+</t>
+        </is>
+      </c>
+      <c r="D22" s="3" t="inlineStr">
+        <is>
+          <t>Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="E22" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F22" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G22" s="3" t="inlineStr"/>
+      <c r="H22" s="3" t="inlineStr">
+        <is>
+          <t>Case : slow issue  has been updated by Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="I22" s="3" t="inlineStr">
+        <is>
+          <t>slow issue</t>
+        </is>
+      </c>
+      <c r="J22" s="3" t="inlineStr">
+        <is>
+          <t>TKT1339133</t>
+        </is>
+      </c>
+      <c r="K22" s="3" t="inlineStr">
+        <is>
+          <t>Chalachitra Chautari pvt.ltd</t>
+        </is>
+      </c>
+      <c r="L22" s="3" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="M22" s="3" t="inlineStr">
+        <is>
+          <t>Phone</t>
+        </is>
+      </c>
+      <c r="N22" s="3" t="inlineStr">
+        <is>
+          <t>Chalachitra Chautari pvt.ltd</t>
+        </is>
+      </c>
+      <c r="O22" s="3" t="inlineStr">
+        <is>
+          <t>9867020120</t>
+        </is>
+      </c>
+      <c r="P22" s="3" t="inlineStr">
+        <is>
+          <t>Slow Internet Connection</t>
+        </is>
+      </c>
+      <c r="Q22" s="3" t="inlineStr"/>
+      <c r="R22" s="3" t="inlineStr">
+        <is>
+          <t>23 Sep 2026 02:21:55 PM</t>
+        </is>
+      </c>
+      <c r="S22" s="3" t="inlineStr"/>
+      <c r="T22" s="3" t="inlineStr"/>
+      <c r="U22" s="3" t="inlineStr">
+        <is>
+          <t>chalachitra_fttx</t>
+        </is>
+      </c>
+      <c r="V22" s="3" t="inlineStr">
+        <is>
+          <t>19 Sep 2026 05:49:47 PM</t>
+        </is>
+      </c>
+      <c r="W22" s="3" t="inlineStr">
+        <is>
+          <t>23 Sep 2026 02:21:55 PM</t>
+        </is>
+      </c>
+      <c r="X22" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Y22" s="3" t="inlineStr"/>
+      <c r="Z22" s="3" t="inlineStr">
+        <is>
+          <t>Slow Internet Connection</t>
+        </is>
+      </c>
+      <c r="AA22" s="3" t="inlineStr">
+        <is>
+          <t>Layer 1-User</t>
+        </is>
+      </c>
+      <c r="AB22" s="3" t="inlineStr">
+        <is>
+          <t>L1  Support</t>
+        </is>
+      </c>
+      <c r="AC22" s="3" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="AD22" s="3" t="inlineStr"/>
+      <c r="AE22" s="3" t="inlineStr">
+        <is>
+          <t>kalikasthan dillibzar	, Bagmati, Central, Nepal</t>
+        </is>
+      </c>
+      <c r="AF22" s="3" t="inlineStr"/>
+      <c r="AG22" s="3" t="inlineStr">
+        <is>
+          <t>Video content is Buffering</t>
+        </is>
+      </c>
+      <c r="AH22" s="3" t="inlineStr"/>
+      <c r="AI22" s="3" t="inlineStr">
+        <is>
+          <t>02:32 hour</t>
+        </is>
+      </c>
+      <c r="AJ22" s="3" t="inlineStr"/>
+      <c r="AK22" s="3" t="inlineStr"/>
+      <c r="AL22" s="3" t="inlineStr">
+        <is>
+          <t>Bhumika Saud</t>
+        </is>
+      </c>
+      <c r="AM22" s="3" t="inlineStr">
+        <is>
+          <t>Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="AN22" s="3" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AO22" s="3" t="inlineStr">
+        <is>
+          <t>CDB258</t>
+        </is>
+      </c>
+      <c r="AP22" s="3" t="inlineStr"/>
+      <c r="AQ22" s="3" t="inlineStr"/>
+      <c r="AR22" s="3" t="inlineStr">
+        <is>
+          <t>Case : slow issue  has been updated by Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="AS22" s="3" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="AT22" s="3" t="inlineStr">
+        <is>
+          <t>3d 20h 32m</t>
+        </is>
+      </c>
+      <c r="AU22" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Completed)</t>
+        </is>
+      </c>
+      <c r="AV22" s="3" t="inlineStr">
+        <is>
+          <t>Case : slow issue  has been updated by Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="AW22" s="3" t="inlineStr">
         <is>
           <t>General / Other Issues</t>
         </is>
@@ -4433,13 +5022,13 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M39"/>
+  <dimension ref="A1:M42"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="45" customWidth="1" min="1" max="1"/>
-    <col width="30" customWidth="1" min="2" max="2"/>
+    <col width="40" customWidth="1" min="2" max="2"/>
     <col width="33" customWidth="1" min="3" max="3"/>
-    <col width="29" customWidth="1" min="4" max="4"/>
+    <col width="40" customWidth="1" min="4" max="4"/>
     <col width="19" customWidth="1" min="5" max="5"/>
     <col width="25" customWidth="1" min="6" max="6"/>
     <col width="45" customWidth="1" min="7" max="7"/>
@@ -4470,7 +5059,7 @@
         </is>
       </c>
       <c r="B2" s="3" t="n">
-        <v>18</v>
+        <v>21</v>
       </c>
     </row>
     <row r="3">
@@ -4480,7 +5069,7 @@
         </is>
       </c>
       <c r="B3" s="5" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
     </row>
     <row r="4">
@@ -4491,7 +5080,7 @@
       </c>
       <c r="B4" s="3" t="inlineStr">
         <is>
-          <t>77.8%</t>
+          <t>76.2%</t>
         </is>
       </c>
     </row>
@@ -4503,7 +5092,7 @@
       </c>
       <c r="B5" s="5" t="inlineStr">
         <is>
-          <t>7h 32m</t>
+          <t>6h 35m</t>
         </is>
       </c>
     </row>
@@ -4515,7 +5104,7 @@
       </c>
       <c r="B6" s="3" t="inlineStr">
         <is>
-          <t>15h 58m</t>
+          <t>1d 14m</t>
         </is>
       </c>
     </row>
@@ -4556,14 +5145,14 @@
         </is>
       </c>
       <c r="B10" s="3" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="C10" s="3" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D10" s="3" t="inlineStr">
         <is>
-          <t>75.0%</t>
+          <t>71.4%</t>
         </is>
       </c>
     </row>
@@ -4610,14 +5199,14 @@
         </is>
       </c>
       <c r="B13" s="5" t="n">
+        <v>2</v>
+      </c>
+      <c r="C13" s="5" t="n">
         <v>1</v>
       </c>
-      <c r="C13" s="5" t="n">
-        <v>0</v>
-      </c>
       <c r="D13" s="5" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>50.0%</t>
         </is>
       </c>
     </row>
@@ -4664,18 +5253,18 @@
       </c>
       <c r="B17" s="5" t="inlineStr">
         <is>
-          <t>Router Upgrade  Wi-Fi 6</t>
+          <t>Query For Secondary Router /Repeater</t>
         </is>
       </c>
       <c r="C17" s="5" t="n">
-        <v>11</v>
+        <v>1</v>
       </c>
       <c r="D17" s="5" t="n">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="E17" s="5" t="inlineStr">
         <is>
-          <t>72.7%</t>
+          <t>100.0%</t>
         </is>
       </c>
     </row>
@@ -4687,37 +5276,37 @@
       </c>
       <c r="B18" s="3" t="inlineStr">
         <is>
-          <t>Router Upgrade Dual Band</t>
+          <t>Router Upgrade  Wi-Fi 6</t>
         </is>
       </c>
       <c r="C18" s="3" t="n">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="D18" s="3" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="E18" s="3" t="inlineStr">
         <is>
-          <t>100.0%</t>
+          <t>66.7%</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="5" t="inlineStr">
         <is>
-          <t>Hardware Damage / Malfunction</t>
+          <t>General / Other Issues</t>
         </is>
       </c>
       <c r="B19" s="5" t="inlineStr">
         <is>
-          <t>IPTV STB box Damage Issue</t>
+          <t>Router Upgrade Dual Band</t>
         </is>
       </c>
       <c r="C19" s="5" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D19" s="5" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E19" s="5" t="inlineStr">
         <is>
@@ -4733,14 +5322,14 @@
       </c>
       <c r="B20" s="3" t="inlineStr">
         <is>
-          <t>Router Damage Issue</t>
+          <t>IPTV STB box Damage Issue</t>
         </is>
       </c>
       <c r="C20" s="3" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D20" s="3" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E20" s="3" t="inlineStr">
         <is>
@@ -4751,12 +5340,12 @@
     <row r="21">
       <c r="A21" s="5" t="inlineStr">
         <is>
-          <t>No Internet Connection</t>
+          <t>Hardware Damage / Malfunction</t>
         </is>
       </c>
       <c r="B21" s="5" t="inlineStr">
         <is>
-          <t>Configuration Issue</t>
+          <t>Router Damage Issue</t>
         </is>
       </c>
       <c r="C21" s="5" t="n">
@@ -4774,177 +5363,133 @@
     <row r="22">
       <c r="A22" s="3" t="inlineStr">
         <is>
-          <t>Slow Internet Connection</t>
+          <t>No Internet Connection</t>
         </is>
       </c>
       <c r="B22" s="3" t="inlineStr">
         <is>
-          <t>Video content is Buffering</t>
+          <t>Configuration Issue</t>
         </is>
       </c>
       <c r="C22" s="3" t="n">
         <v>1</v>
       </c>
       <c r="D22" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E22" s="3" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>100.0%</t>
         </is>
       </c>
     </row>
-    <row r="23"/>
-    <row r="24">
-      <c r="A24" s="6" t="inlineStr">
+    <row r="23">
+      <c r="A23" s="5" t="inlineStr">
+        <is>
+          <t>Slow Internet Connection</t>
+        </is>
+      </c>
+      <c r="B23" s="5" t="inlineStr">
+        <is>
+          <t>Video content is Buffering</t>
+        </is>
+      </c>
+      <c r="C23" s="5" t="n">
+        <v>2</v>
+      </c>
+      <c r="D23" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="E23" s="5" t="inlineStr">
+        <is>
+          <t>50.0%</t>
+        </is>
+      </c>
+    </row>
+    <row r="24"/>
+    <row r="25">
+      <c r="A25" s="6" t="inlineStr">
         <is>
           <t>Detailed Solved / Handled Tickets List</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" s="4" t="inlineStr">
-        <is>
-          <t>Ticket Number</t>
-        </is>
-      </c>
-      <c r="B25" s="4" t="inlineStr">
-        <is>
-          <t>Account Name</t>
-        </is>
-      </c>
-      <c r="C25" s="4" t="inlineStr">
-        <is>
-          <t>Category</t>
-        </is>
-      </c>
-      <c r="D25" s="4" t="inlineStr">
-        <is>
-          <t>Sub Category</t>
-        </is>
-      </c>
-      <c r="E25" s="4" t="inlineStr">
-        <is>
-          <t>Status</t>
-        </is>
-      </c>
-      <c r="F25" s="4" t="inlineStr">
-        <is>
-          <t>Resolution Type</t>
-        </is>
-      </c>
-      <c r="G25" s="4" t="inlineStr">
-        <is>
-          <t>Employee Remark / Solution Note</t>
-        </is>
-      </c>
-      <c r="H25" s="4" t="inlineStr">
-        <is>
-          <t>Action / Transfer Remark</t>
-        </is>
-      </c>
-      <c r="I25" s="4" t="inlineStr">
-        <is>
-          <t>Assigned Date</t>
-        </is>
-      </c>
-      <c r="J25" s="4" t="inlineStr">
-        <is>
-          <t>Created Date</t>
-        </is>
-      </c>
-      <c r="K25" s="4" t="inlineStr">
-        <is>
-          <t>Last Modified Date</t>
-        </is>
-      </c>
-      <c r="L25" s="4" t="inlineStr">
-        <is>
-          <t>Resolution Time (From Assigned)</t>
-        </is>
-      </c>
-      <c r="M25" s="4" t="inlineStr">
-        <is>
-          <t>Resolution Time (From Created)</t>
         </is>
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="3" t="inlineStr">
-        <is>
-          <t>TKT1342514</t>
-        </is>
-      </c>
-      <c r="B26" s="3" t="inlineStr">
-        <is>
-          <t>Bijay Carlos Rana</t>
-        </is>
-      </c>
-      <c r="C26" s="3" t="inlineStr">
-        <is>
-          <t>General / Other Issues</t>
-        </is>
-      </c>
-      <c r="D26" s="3" t="inlineStr">
-        <is>
-          <t>Router Upgrade  Wi-Fi 6</t>
-        </is>
-      </c>
-      <c r="E26" s="3" t="inlineStr">
-        <is>
-          <t>Completed</t>
-        </is>
-      </c>
-      <c r="F26" s="3" t="inlineStr">
-        <is>
-          <t>Completed (Completed)</t>
-        </is>
-      </c>
-      <c r="G26" s="3" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
-      <c r="H26" s="3" t="inlineStr">
-        <is>
-          <t>Case : WIFI 6  has been updated by Rajesh Maharjan</t>
-        </is>
-      </c>
-      <c r="I26" s="3" t="inlineStr">
-        <is>
-          <t>23 Sep 2026 11:16:05 AM</t>
-        </is>
-      </c>
-      <c r="J26" s="3" t="inlineStr">
-        <is>
-          <t>22 Sep 2026 02:29:16 PM</t>
-        </is>
-      </c>
-      <c r="K26" s="3" t="inlineStr">
-        <is>
-          <t>23 Sep 2026 11:16:05 AM</t>
-        </is>
-      </c>
-      <c r="L26" s="3" t="inlineStr">
-        <is>
-          <t>0m</t>
-        </is>
-      </c>
-      <c r="M26" s="3" t="inlineStr">
-        <is>
-          <t>20h 46m</t>
+      <c r="A26" s="4" t="inlineStr">
+        <is>
+          <t>Ticket Number</t>
+        </is>
+      </c>
+      <c r="B26" s="4" t="inlineStr">
+        <is>
+          <t>Account Name</t>
+        </is>
+      </c>
+      <c r="C26" s="4" t="inlineStr">
+        <is>
+          <t>Category</t>
+        </is>
+      </c>
+      <c r="D26" s="4" t="inlineStr">
+        <is>
+          <t>Sub Category</t>
+        </is>
+      </c>
+      <c r="E26" s="4" t="inlineStr">
+        <is>
+          <t>Status</t>
+        </is>
+      </c>
+      <c r="F26" s="4" t="inlineStr">
+        <is>
+          <t>Resolution Type</t>
+        </is>
+      </c>
+      <c r="G26" s="4" t="inlineStr">
+        <is>
+          <t>Employee Remark / Solution Note</t>
+        </is>
+      </c>
+      <c r="H26" s="4" t="inlineStr">
+        <is>
+          <t>Action / Transfer Remark</t>
+        </is>
+      </c>
+      <c r="I26" s="4" t="inlineStr">
+        <is>
+          <t>Assigned Date</t>
+        </is>
+      </c>
+      <c r="J26" s="4" t="inlineStr">
+        <is>
+          <t>Created Date</t>
+        </is>
+      </c>
+      <c r="K26" s="4" t="inlineStr">
+        <is>
+          <t>Last Modified Date</t>
+        </is>
+      </c>
+      <c r="L26" s="4" t="inlineStr">
+        <is>
+          <t>Resolution Time (From Assigned)</t>
+        </is>
+      </c>
+      <c r="M26" s="4" t="inlineStr">
+        <is>
+          <t>Resolution Time (From Created)</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="5" t="inlineStr">
         <is>
-          <t>TKT1343394</t>
+          <t>TKT1342514</t>
         </is>
       </c>
       <c r="B27" s="5" t="inlineStr">
         <is>
-          <t>Kaizen Business consultant</t>
+          <t>Bijay Carlos Rana</t>
         </is>
       </c>
       <c r="C27" s="5" t="inlineStr">
@@ -4974,22 +5519,22 @@
       </c>
       <c r="H27" s="5" t="inlineStr">
         <is>
-          <t>Case : wifi 6 router  has been updated by Sabin Giri</t>
+          <t>Case : WIFI 6  has been updated by Rajesh Maharjan</t>
         </is>
       </c>
       <c r="I27" s="5" t="inlineStr">
         <is>
-          <t>23 Sep 2026 12:31:18 PM</t>
+          <t>23 Sep 2026 11:16:05 AM</t>
         </is>
       </c>
       <c r="J27" s="5" t="inlineStr">
         <is>
-          <t>23 Sep 2026 09:53:33 AM</t>
+          <t>22 Sep 2026 02:29:16 PM</t>
         </is>
       </c>
       <c r="K27" s="5" t="inlineStr">
         <is>
-          <t>23 Sep 2026 12:31:18 PM</t>
+          <t>23 Sep 2026 11:16:05 AM</t>
         </is>
       </c>
       <c r="L27" s="5" t="inlineStr">
@@ -4999,19 +5544,19 @@
       </c>
       <c r="M27" s="5" t="inlineStr">
         <is>
-          <t>2h 37m</t>
+          <t>20h 46m</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="3" t="inlineStr">
         <is>
-          <t>TKT1343122</t>
+          <t>TKT1343394</t>
         </is>
       </c>
       <c r="B28" s="3" t="inlineStr">
         <is>
-          <t>Rajesh Shahi</t>
+          <t>Kaizen Business consultant</t>
         </is>
       </c>
       <c r="C28" s="3" t="inlineStr">
@@ -5041,22 +5586,22 @@
       </c>
       <c r="H28" s="3" t="inlineStr">
         <is>
-          <t>Case : wifi 6  has been updated by Shashikant Chaudhary</t>
+          <t>Case : wifi 6 router  has been updated by Sabin Giri</t>
         </is>
       </c>
       <c r="I28" s="3" t="inlineStr">
         <is>
-          <t>23 Sep 2026 12:37:13 PM</t>
+          <t>23 Sep 2026 12:31:18 PM</t>
         </is>
       </c>
       <c r="J28" s="3" t="inlineStr">
         <is>
-          <t>22 Sep 2026 09:56:18 PM</t>
+          <t>23 Sep 2026 09:53:33 AM</t>
         </is>
       </c>
       <c r="K28" s="3" t="inlineStr">
         <is>
-          <t>23 Sep 2026 12:37:13 PM</t>
+          <t>23 Sep 2026 12:31:18 PM</t>
         </is>
       </c>
       <c r="L28" s="3" t="inlineStr">
@@ -5066,19 +5611,19 @@
       </c>
       <c r="M28" s="3" t="inlineStr">
         <is>
-          <t>14h 40m</t>
+          <t>2h 37m</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="5" t="inlineStr">
         <is>
-          <t>TKT1343670</t>
+          <t>TKT1343122</t>
         </is>
       </c>
       <c r="B29" s="5" t="inlineStr">
         <is>
-          <t>Suman Shah</t>
+          <t>Rajesh Shahi</t>
         </is>
       </c>
       <c r="C29" s="5" t="inlineStr">
@@ -5088,7 +5633,7 @@
       </c>
       <c r="D29" s="5" t="inlineStr">
         <is>
-          <t>Router Upgrade Dual Band</t>
+          <t>Router Upgrade  Wi-Fi 6</t>
         </is>
       </c>
       <c r="E29" s="5" t="inlineStr">
@@ -5108,22 +5653,22 @@
       </c>
       <c r="H29" s="5" t="inlineStr">
         <is>
-          <t>Case : router change  has been updated by Shashikant Chaudhary</t>
+          <t>Case : wifi 6  has been updated by Shashikant Chaudhary</t>
         </is>
       </c>
       <c r="I29" s="5" t="inlineStr">
         <is>
-          <t>23 Sep 2026 12:59:40 PM</t>
+          <t>23 Sep 2026 12:37:13 PM</t>
         </is>
       </c>
       <c r="J29" s="5" t="inlineStr">
         <is>
-          <t>23 Sep 2026 12:23:42 PM</t>
+          <t>22 Sep 2026 09:56:18 PM</t>
         </is>
       </c>
       <c r="K29" s="5" t="inlineStr">
         <is>
-          <t>23 Sep 2026 12:59:40 PM</t>
+          <t>23 Sep 2026 12:37:13 PM</t>
         </is>
       </c>
       <c r="L29" s="5" t="inlineStr">
@@ -5133,39 +5678,39 @@
       </c>
       <c r="M29" s="5" t="inlineStr">
         <is>
-          <t>35m</t>
+          <t>14h 40m</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="3" t="inlineStr">
         <is>
-          <t>TKT1342524</t>
+          <t>TKT1343670</t>
         </is>
       </c>
       <c r="B30" s="3" t="inlineStr">
         <is>
-          <t>Nakul Bhandari</t>
+          <t>Suman Shah</t>
         </is>
       </c>
       <c r="C30" s="3" t="inlineStr">
         <is>
-          <t>No Internet Connection</t>
+          <t>General / Other Issues</t>
         </is>
       </c>
       <c r="D30" s="3" t="inlineStr">
         <is>
-          <t>Configuration Issue</t>
+          <t>Router Upgrade Dual Band</t>
         </is>
       </c>
       <c r="E30" s="3" t="inlineStr">
         <is>
-          <t>Closed</t>
+          <t>Completed</t>
         </is>
       </c>
       <c r="F30" s="3" t="inlineStr">
         <is>
-          <t>Completed (Closed)</t>
+          <t>Completed (Completed)</t>
         </is>
       </c>
       <c r="G30" s="3" t="inlineStr">
@@ -5175,64 +5720,64 @@
       </c>
       <c r="H30" s="3" t="inlineStr">
         <is>
-          <t>Case : CONFINGURE ISSUE  has been updated by Ajit Shrestha</t>
+          <t>Case : router change  has been updated by Shashikant Chaudhary</t>
         </is>
       </c>
       <c r="I30" s="3" t="inlineStr">
         <is>
-          <t>22 Sep 2026 02:52:24 PM</t>
+          <t>23 Sep 2026 12:59:40 PM</t>
         </is>
       </c>
       <c r="J30" s="3" t="inlineStr">
         <is>
-          <t>22 Sep 2026 02:35:30 PM</t>
+          <t>23 Sep 2026 12:23:42 PM</t>
         </is>
       </c>
       <c r="K30" s="3" t="inlineStr">
         <is>
-          <t>23 Sep 2026 12:57:31 PM</t>
+          <t>23 Sep 2026 12:59:40 PM</t>
         </is>
       </c>
       <c r="L30" s="3" t="inlineStr">
         <is>
-          <t>22h 5m</t>
+          <t>0m</t>
         </is>
       </c>
       <c r="M30" s="3" t="inlineStr">
         <is>
-          <t>22h 22m</t>
+          <t>35m</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="5" t="inlineStr">
         <is>
-          <t>TKT1342923</t>
+          <t>TKT1342524</t>
         </is>
       </c>
       <c r="B31" s="5" t="inlineStr">
         <is>
-          <t>Maan maya poon</t>
+          <t>Nakul Bhandari</t>
         </is>
       </c>
       <c r="C31" s="5" t="inlineStr">
         <is>
-          <t>General / Other Issues</t>
+          <t>No Internet Connection</t>
         </is>
       </c>
       <c r="D31" s="5" t="inlineStr">
         <is>
-          <t>Router Upgrade  Wi-Fi 6</t>
+          <t>Configuration Issue</t>
         </is>
       </c>
       <c r="E31" s="5" t="inlineStr">
         <is>
-          <t>Completed</t>
+          <t>Closed</t>
         </is>
       </c>
       <c r="F31" s="5" t="inlineStr">
         <is>
-          <t>Completed (Completed)</t>
+          <t>Completed (Closed)</t>
         </is>
       </c>
       <c r="G31" s="5" t="inlineStr">
@@ -5242,44 +5787,44 @@
       </c>
       <c r="H31" s="5" t="inlineStr">
         <is>
-          <t>Case : For upgradation to wifi6   has been updated by Sabin Giri</t>
+          <t>Case : CONFINGURE ISSUE  has been updated by Ajit Shrestha</t>
         </is>
       </c>
       <c r="I31" s="5" t="inlineStr">
         <is>
-          <t>23 Sep 2026 01:01:06 PM</t>
+          <t>22 Sep 2026 02:52:24 PM</t>
         </is>
       </c>
       <c r="J31" s="5" t="inlineStr">
         <is>
-          <t>22 Sep 2026 06:58:31 PM</t>
+          <t>22 Sep 2026 02:35:30 PM</t>
         </is>
       </c>
       <c r="K31" s="5" t="inlineStr">
         <is>
-          <t>23 Sep 2026 01:01:06 PM</t>
+          <t>23 Sep 2026 12:57:31 PM</t>
         </is>
       </c>
       <c r="L31" s="5" t="inlineStr">
         <is>
-          <t>0m</t>
+          <t>22h 5m</t>
         </is>
       </c>
       <c r="M31" s="5" t="inlineStr">
         <is>
-          <t>18h 2m</t>
+          <t>22h 22m</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="3" t="inlineStr">
         <is>
-          <t>TKT1343451</t>
+          <t>TKT1342923</t>
         </is>
       </c>
       <c r="B32" s="3" t="inlineStr">
         <is>
-          <t>Sabin Maharjan</t>
+          <t>Maan maya poon</t>
         </is>
       </c>
       <c r="C32" s="3" t="inlineStr">
@@ -5309,22 +5854,22 @@
       </c>
       <c r="H32" s="3" t="inlineStr">
         <is>
-          <t>Case : Wifi 6  has been updated by Sabin Giri</t>
+          <t>Case : For upgradation to wifi6   has been updated by Sabin Giri</t>
         </is>
       </c>
       <c r="I32" s="3" t="inlineStr">
         <is>
-          <t>23 Sep 2026 01:17:39 PM</t>
+          <t>23 Sep 2026 01:01:06 PM</t>
         </is>
       </c>
       <c r="J32" s="3" t="inlineStr">
         <is>
-          <t>23 Sep 2026 10:26:34 AM</t>
+          <t>22 Sep 2026 06:58:31 PM</t>
         </is>
       </c>
       <c r="K32" s="3" t="inlineStr">
         <is>
-          <t>23 Sep 2026 01:17:39 PM</t>
+          <t>23 Sep 2026 01:01:06 PM</t>
         </is>
       </c>
       <c r="L32" s="3" t="inlineStr">
@@ -5334,29 +5879,29 @@
       </c>
       <c r="M32" s="3" t="inlineStr">
         <is>
-          <t>2h 51m</t>
+          <t>18h 2m</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="5" t="inlineStr">
         <is>
-          <t>TKT1343062</t>
+          <t>TKT1343451</t>
         </is>
       </c>
       <c r="B33" s="5" t="inlineStr">
         <is>
-          <t>Sabin Magar</t>
+          <t>Sabin Maharjan</t>
         </is>
       </c>
       <c r="C33" s="5" t="inlineStr">
         <is>
-          <t>Hardware Damage / Malfunction</t>
+          <t>General / Other Issues</t>
         </is>
       </c>
       <c r="D33" s="5" t="inlineStr">
         <is>
-          <t>IPTV STB box Damage Issue</t>
+          <t>Router Upgrade  Wi-Fi 6</t>
         </is>
       </c>
       <c r="E33" s="5" t="inlineStr">
@@ -5376,22 +5921,22 @@
       </c>
       <c r="H33" s="5" t="inlineStr">
         <is>
-          <t>Case : IP TV not Working   has been updated by Ajit Shrestha</t>
+          <t>Case : Wifi 6  has been updated by Sabin Giri</t>
         </is>
       </c>
       <c r="I33" s="5" t="inlineStr">
         <is>
-          <t>23 Sep 2026 01:16:47 PM</t>
+          <t>23 Sep 2026 01:17:39 PM</t>
         </is>
       </c>
       <c r="J33" s="5" t="inlineStr">
         <is>
-          <t>22 Sep 2026 08:56:52 PM</t>
+          <t>23 Sep 2026 10:26:34 AM</t>
         </is>
       </c>
       <c r="K33" s="5" t="inlineStr">
         <is>
-          <t>23 Sep 2026 01:16:47 PM</t>
+          <t>23 Sep 2026 01:17:39 PM</t>
         </is>
       </c>
       <c r="L33" s="5" t="inlineStr">
@@ -5401,39 +5946,39 @@
       </c>
       <c r="M33" s="5" t="inlineStr">
         <is>
-          <t>16h 19m</t>
+          <t>2h 51m</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="3" t="inlineStr">
         <is>
-          <t>TKT1341347</t>
+          <t>TKT1343062</t>
         </is>
       </c>
       <c r="B34" s="3" t="inlineStr">
         <is>
-          <t>Siddhartha Model School</t>
+          <t>Sabin Magar</t>
         </is>
       </c>
       <c r="C34" s="3" t="inlineStr">
         <is>
-          <t>General / Other Issues</t>
+          <t>Hardware Damage / Malfunction</t>
         </is>
       </c>
       <c r="D34" s="3" t="inlineStr">
         <is>
-          <t>Router Upgrade  Wi-Fi 6</t>
+          <t>IPTV STB box Damage Issue</t>
         </is>
       </c>
       <c r="E34" s="3" t="inlineStr">
         <is>
-          <t>Closed</t>
+          <t>Completed</t>
         </is>
       </c>
       <c r="F34" s="3" t="inlineStr">
         <is>
-          <t>Completed (Closed)</t>
+          <t>Completed (Completed)</t>
         </is>
       </c>
       <c r="G34" s="3" t="inlineStr">
@@ -5443,44 +5988,44 @@
       </c>
       <c r="H34" s="3" t="inlineStr">
         <is>
-          <t>Case : wifi 6  has been updated by Sunil Chaudhary</t>
+          <t>Case : IP TV not Working   has been updated by Ajit Shrestha</t>
         </is>
       </c>
       <c r="I34" s="3" t="inlineStr">
         <is>
-          <t>21 Sep 2026 01:35:47 PM</t>
+          <t>23 Sep 2026 01:16:47 PM</t>
         </is>
       </c>
       <c r="J34" s="3" t="inlineStr">
         <is>
-          <t>21 Sep 2026 01:35:47 PM</t>
+          <t>22 Sep 2026 08:56:52 PM</t>
         </is>
       </c>
       <c r="K34" s="3" t="inlineStr">
         <is>
-          <t>23 Sep 2026 01:22:44 PM</t>
+          <t>23 Sep 2026 01:16:47 PM</t>
         </is>
       </c>
       <c r="L34" s="3" t="inlineStr">
         <is>
-          <t>1d 23h 46m</t>
+          <t>0m</t>
         </is>
       </c>
       <c r="M34" s="3" t="inlineStr">
         <is>
-          <t>1d 23h 46m</t>
+          <t>16h 19m</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="5" t="inlineStr">
         <is>
-          <t>TKT1342867</t>
+          <t>TKT1341347</t>
         </is>
       </c>
       <c r="B35" s="5" t="inlineStr">
         <is>
-          <t>Punit Kumar Barnawal</t>
+          <t>Siddhartha Model School</t>
         </is>
       </c>
       <c r="C35" s="5" t="inlineStr">
@@ -5495,12 +6040,12 @@
       </c>
       <c r="E35" s="5" t="inlineStr">
         <is>
-          <t>Completed</t>
+          <t>Closed</t>
         </is>
       </c>
       <c r="F35" s="5" t="inlineStr">
         <is>
-          <t>Completed (Completed)</t>
+          <t>Completed (Closed)</t>
         </is>
       </c>
       <c r="G35" s="5" t="inlineStr">
@@ -5510,54 +6055,54 @@
       </c>
       <c r="H35" s="5" t="inlineStr">
         <is>
-          <t>Case : Wifi 6  has been updated by Shashikant Chaudhary</t>
+          <t>Case : wifi 6  has been updated by Sunil Chaudhary</t>
         </is>
       </c>
       <c r="I35" s="5" t="inlineStr">
         <is>
-          <t>23 Sep 2026 01:48:42 PM</t>
+          <t>21 Sep 2026 01:35:47 PM</t>
         </is>
       </c>
       <c r="J35" s="5" t="inlineStr">
         <is>
-          <t>22 Sep 2026 06:02:29 PM</t>
+          <t>21 Sep 2026 01:35:47 PM</t>
         </is>
       </c>
       <c r="K35" s="5" t="inlineStr">
         <is>
-          <t>23 Sep 2026 01:48:42 PM</t>
+          <t>23 Sep 2026 01:22:44 PM</t>
         </is>
       </c>
       <c r="L35" s="5" t="inlineStr">
         <is>
-          <t>0m</t>
+          <t>1d 23h 46m</t>
         </is>
       </c>
       <c r="M35" s="5" t="inlineStr">
         <is>
-          <t>19h 46m</t>
+          <t>1d 23h 46m</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="3" t="inlineStr">
         <is>
-          <t>TKT1343135</t>
+          <t>TKT1342867</t>
         </is>
       </c>
       <c r="B36" s="3" t="inlineStr">
         <is>
-          <t>Ashish Shahbadi</t>
+          <t>Punit Kumar Barnawal</t>
         </is>
       </c>
       <c r="C36" s="3" t="inlineStr">
         <is>
-          <t>Hardware Damage / Malfunction</t>
+          <t>General / Other Issues</t>
         </is>
       </c>
       <c r="D36" s="3" t="inlineStr">
         <is>
-          <t>Router Damage Issue</t>
+          <t>Router Upgrade  Wi-Fi 6</t>
         </is>
       </c>
       <c r="E36" s="3" t="inlineStr">
@@ -5577,22 +6122,22 @@
       </c>
       <c r="H36" s="3" t="inlineStr">
         <is>
-          <t>Case : 5g not working   has been updated by Rajesh Maharjan</t>
+          <t>Case : Wifi 6  has been updated by Shashikant Chaudhary</t>
         </is>
       </c>
       <c r="I36" s="3" t="inlineStr">
         <is>
-          <t>23 Sep 2026 01:51:51 PM</t>
+          <t>23 Sep 2026 01:48:42 PM</t>
         </is>
       </c>
       <c r="J36" s="3" t="inlineStr">
         <is>
-          <t>22 Sep 2026 10:20:07 PM</t>
+          <t>22 Sep 2026 06:02:29 PM</t>
         </is>
       </c>
       <c r="K36" s="3" t="inlineStr">
         <is>
-          <t>23 Sep 2026 01:51:51 PM</t>
+          <t>23 Sep 2026 01:48:42 PM</t>
         </is>
       </c>
       <c r="L36" s="3" t="inlineStr">
@@ -5602,29 +6147,29 @@
       </c>
       <c r="M36" s="3" t="inlineStr">
         <is>
-          <t>15h 31m</t>
+          <t>19h 46m</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="5" t="inlineStr">
         <is>
-          <t>TKT1343287</t>
+          <t>TKT1343135</t>
         </is>
       </c>
       <c r="B37" s="5" t="inlineStr">
         <is>
-          <t>Anup Chaudhary</t>
+          <t>Ashish Shahbadi</t>
         </is>
       </c>
       <c r="C37" s="5" t="inlineStr">
         <is>
-          <t>General / Other Issues</t>
+          <t>Hardware Damage / Malfunction</t>
         </is>
       </c>
       <c r="D37" s="5" t="inlineStr">
         <is>
-          <t>Router Upgrade  Wi-Fi 6</t>
+          <t>Router Damage Issue</t>
         </is>
       </c>
       <c r="E37" s="5" t="inlineStr">
@@ -5639,27 +6184,27 @@
       </c>
       <c r="G37" s="5" t="inlineStr">
         <is>
-          <t>Case : wifi 6  has been updated by Sabin Giri</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="H37" s="5" t="inlineStr">
         <is>
-          <t>Case : wifi 6  has been updated by Sabin Giri</t>
+          <t>Case : 5g not working   has been updated by Rajesh Maharjan</t>
         </is>
       </c>
       <c r="I37" s="5" t="inlineStr">
         <is>
-          <t>23 Sep 2026 02:03:32 PM</t>
+          <t>23 Sep 2026 01:51:51 PM</t>
         </is>
       </c>
       <c r="J37" s="5" t="inlineStr">
         <is>
-          <t>23 Sep 2026 08:37:17 AM</t>
+          <t>22 Sep 2026 10:20:07 PM</t>
         </is>
       </c>
       <c r="K37" s="5" t="inlineStr">
         <is>
-          <t>23 Sep 2026 02:03:32 PM</t>
+          <t>23 Sep 2026 01:51:51 PM</t>
         </is>
       </c>
       <c r="L37" s="5" t="inlineStr">
@@ -5669,74 +6214,74 @@
       </c>
       <c r="M37" s="5" t="inlineStr">
         <is>
-          <t>5h 26m</t>
+          <t>15h 31m</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="3" t="inlineStr">
         <is>
-          <t>TKT1342988</t>
+          <t>TKT1343287</t>
         </is>
       </c>
       <c r="B38" s="3" t="inlineStr">
         <is>
-          <t>Kushal Neupane</t>
+          <t>Anup Chaudhary</t>
         </is>
       </c>
       <c r="C38" s="3" t="inlineStr">
         <is>
-          <t>Hardware Damage / Malfunction</t>
+          <t>General / Other Issues</t>
         </is>
       </c>
       <c r="D38" s="3" t="inlineStr">
         <is>
-          <t>IPTV STB box Damage Issue</t>
+          <t>Router Upgrade  Wi-Fi 6</t>
         </is>
       </c>
       <c r="E38" s="3" t="inlineStr">
         <is>
-          <t>Closed</t>
+          <t>Completed</t>
         </is>
       </c>
       <c r="F38" s="3" t="inlineStr">
         <is>
-          <t>Completed (Closed)</t>
+          <t>Completed (Completed)</t>
         </is>
       </c>
       <c r="G38" s="3" t="inlineStr">
         <is>
-          <t>Case : stb faulty  has been updated by Sunil Chaudhary</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="H38" s="3" t="inlineStr">
         <is>
-          <t>Case : stb faulty  has been updated by Sunil Chaudhary</t>
+          <t>Case : wifi 6  has been updated by Sabin Giri</t>
         </is>
       </c>
       <c r="I38" s="3" t="inlineStr">
         <is>
-          <t>22 Sep 2026 08:27:54 PM</t>
+          <t>23 Sep 2026 02:03:32 PM</t>
         </is>
       </c>
       <c r="J38" s="3" t="inlineStr">
         <is>
-          <t>22 Sep 2026 07:49:31 PM</t>
+          <t>23 Sep 2026 08:37:17 AM</t>
         </is>
       </c>
       <c r="K38" s="3" t="inlineStr">
         <is>
-          <t>23 Sep 2026 02:16:10 PM</t>
+          <t>23 Sep 2026 02:03:32 PM</t>
         </is>
       </c>
       <c r="L38" s="3" t="inlineStr">
         <is>
-          <t>17h 48m</t>
+          <t>0m</t>
         </is>
       </c>
       <c r="M38" s="3" t="inlineStr">
         <is>
-          <t>18h 26m</t>
+          <t>5h 26m</t>
         </is>
       </c>
     </row>
@@ -5773,37 +6318,238 @@
       </c>
       <c r="G39" s="5" t="inlineStr">
         <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="H39" s="5" t="inlineStr">
+        <is>
           <t>Case : stb faulty  has been updated by Sunil Chaudhary</t>
         </is>
       </c>
-      <c r="H39" s="5" t="inlineStr">
+      <c r="I39" s="5" t="inlineStr">
+        <is>
+          <t>22 Sep 2026 08:27:54 PM</t>
+        </is>
+      </c>
+      <c r="J39" s="5" t="inlineStr">
+        <is>
+          <t>22 Sep 2026 07:49:31 PM</t>
+        </is>
+      </c>
+      <c r="K39" s="5" t="inlineStr">
+        <is>
+          <t>23 Sep 2026 02:16:10 PM</t>
+        </is>
+      </c>
+      <c r="L39" s="5" t="inlineStr">
+        <is>
+          <t>17h 48m</t>
+        </is>
+      </c>
+      <c r="M39" s="5" t="inlineStr">
+        <is>
+          <t>18h 26m</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="3" t="inlineStr">
+        <is>
+          <t>TKT1342988</t>
+        </is>
+      </c>
+      <c r="B40" s="3" t="inlineStr">
+        <is>
+          <t>Kushal Neupane</t>
+        </is>
+      </c>
+      <c r="C40" s="3" t="inlineStr">
+        <is>
+          <t>Hardware Damage / Malfunction</t>
+        </is>
+      </c>
+      <c r="D40" s="3" t="inlineStr">
+        <is>
+          <t>IPTV STB box Damage Issue</t>
+        </is>
+      </c>
+      <c r="E40" s="3" t="inlineStr">
+        <is>
+          <t>Closed</t>
+        </is>
+      </c>
+      <c r="F40" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Closed)</t>
+        </is>
+      </c>
+      <c r="G40" s="3" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="H40" s="3" t="inlineStr">
         <is>
           <t>Case : stb faulty  has been updated by Sunil Chaudhary</t>
         </is>
       </c>
-      <c r="I39" s="5" t="inlineStr">
+      <c r="I40" s="3" t="inlineStr">
         <is>
           <t>22 Sep 2026 08:27:54 PM</t>
         </is>
       </c>
-      <c r="J39" s="5" t="inlineStr">
+      <c r="J40" s="3" t="inlineStr">
         <is>
           <t>22 Sep 2026 07:49:31 PM</t>
         </is>
       </c>
-      <c r="K39" s="5" t="inlineStr">
+      <c r="K40" s="3" t="inlineStr">
         <is>
           <t>23 Sep 2026 02:16:10 PM</t>
         </is>
       </c>
-      <c r="L39" s="5" t="inlineStr">
+      <c r="L40" s="3" t="inlineStr">
         <is>
           <t>17h 48m</t>
         </is>
       </c>
-      <c r="M39" s="5" t="inlineStr">
+      <c r="M40" s="3" t="inlineStr">
         <is>
           <t>18h 26m</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="5" t="inlineStr">
+        <is>
+          <t>TKT1340081</t>
+        </is>
+      </c>
+      <c r="B41" s="5" t="inlineStr">
+        <is>
+          <t>Anjan Khadka</t>
+        </is>
+      </c>
+      <c r="C41" s="5" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="D41" s="5" t="inlineStr">
+        <is>
+          <t>Query For Secondary Router /Repeater</t>
+        </is>
+      </c>
+      <c r="E41" s="5" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="F41" s="5" t="inlineStr">
+        <is>
+          <t>Completed (Completed)</t>
+        </is>
+      </c>
+      <c r="G41" s="5" t="inlineStr">
+        <is>
+          <t>Case : Secondary Router Connetion   has been updated by Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="H41" s="5" t="inlineStr">
+        <is>
+          <t>Case : Secondary Router Connetion   has been updated by Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="I41" s="5" t="inlineStr">
+        <is>
+          <t>23 Sep 2026 02:23:04 PM</t>
+        </is>
+      </c>
+      <c r="J41" s="5" t="inlineStr">
+        <is>
+          <t>20 Sep 2026 02:38:36 PM</t>
+        </is>
+      </c>
+      <c r="K41" s="5" t="inlineStr">
+        <is>
+          <t>23 Sep 2026 02:23:04 PM</t>
+        </is>
+      </c>
+      <c r="L41" s="5" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="M41" s="5" t="inlineStr">
+        <is>
+          <t>2d 23h 44m</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="3" t="inlineStr">
+        <is>
+          <t>TKT1339133</t>
+        </is>
+      </c>
+      <c r="B42" s="3" t="inlineStr">
+        <is>
+          <t>Chalachitra Chautari pvt.ltd</t>
+        </is>
+      </c>
+      <c r="C42" s="3" t="inlineStr">
+        <is>
+          <t>Slow Internet Connection</t>
+        </is>
+      </c>
+      <c r="D42" s="3" t="inlineStr">
+        <is>
+          <t>Video content is Buffering</t>
+        </is>
+      </c>
+      <c r="E42" s="3" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="F42" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Completed)</t>
+        </is>
+      </c>
+      <c r="G42" s="3" t="inlineStr">
+        <is>
+          <t>Case : slow issue  has been updated by Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="H42" s="3" t="inlineStr">
+        <is>
+          <t>Case : slow issue  has been updated by Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="I42" s="3" t="inlineStr">
+        <is>
+          <t>23 Sep 2026 02:21:55 PM</t>
+        </is>
+      </c>
+      <c r="J42" s="3" t="inlineStr">
+        <is>
+          <t>19 Sep 2026 05:49:47 PM</t>
+        </is>
+      </c>
+      <c r="K42" s="3" t="inlineStr">
+        <is>
+          <t>23 Sep 2026 02:21:55 PM</t>
+        </is>
+      </c>
+      <c r="L42" s="3" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="M42" s="3" t="inlineStr">
+        <is>
+          <t>3d 20h 32m</t>
         </is>
       </c>
     </row>

--- a/audit_report_ALL_TEAM_23_Sep_2026.xlsx
+++ b/audit_report_ALL_TEAM_23_Sep_2026.xlsx
@@ -483,7 +483,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AW22"/>
+  <dimension ref="A1:AW23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="23" customWidth="1" min="1" max="1"/>
@@ -4465,10 +4465,8 @@
           <t>Sabin Shrestha</t>
         </is>
       </c>
-      <c r="O20" s="3" t="inlineStr">
-        <is>
-          <t>9818815777</t>
-        </is>
+      <c r="O20" s="3" t="n">
+        <v>9818815777</v>
       </c>
       <c r="P20" s="3" t="inlineStr">
         <is>
@@ -4503,10 +4501,8 @@
           <t>Active</t>
         </is>
       </c>
-      <c r="Y20" s="3" t="inlineStr">
-        <is>
-          <t>27.72209</t>
-        </is>
+      <c r="Y20" s="3" t="n">
+        <v>27.72209</v>
       </c>
       <c r="Z20" s="3" t="inlineStr">
         <is>
@@ -4554,25 +4550,21 @@
           <t>Sunil Chaudhary</t>
         </is>
       </c>
-      <c r="AN20" s="3" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
+      <c r="AN20" s="3" t="n">
+        <v>4</v>
       </c>
       <c r="AO20" s="3" t="inlineStr">
         <is>
           <t>1,4</t>
         </is>
       </c>
-      <c r="AP20" s="3" t="inlineStr">
-        <is>
-          <t>85.27905</t>
-        </is>
+      <c r="AP20" s="3" t="n">
+        <v>85.27905</v>
       </c>
       <c r="AQ20" s="3" t="inlineStr"/>
       <c r="AR20" s="3" t="inlineStr">
         <is>
-          <t>Case : Wifi 6  has been updated by Sunil Chaudhary</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="AS20" s="3" t="inlineStr">
@@ -4668,10 +4660,8 @@
           <t>Anjan Khadka</t>
         </is>
       </c>
-      <c r="O21" s="3" t="inlineStr">
-        <is>
-          <t>9766884209</t>
-        </is>
+      <c r="O21" s="3" t="n">
+        <v>9766884209</v>
       </c>
       <c r="P21" s="3" t="inlineStr">
         <is>
@@ -4706,10 +4696,8 @@
           <t>Active</t>
         </is>
       </c>
-      <c r="Y21" s="3" t="inlineStr">
-        <is>
-          <t>27.69419</t>
-        </is>
+      <c r="Y21" s="3" t="n">
+        <v>27.69419</v>
       </c>
       <c r="Z21" s="3" t="inlineStr">
         <is>
@@ -4765,25 +4753,21 @@
           <t>Chandramani Tharu</t>
         </is>
       </c>
-      <c r="AN21" s="3" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
+      <c r="AN21" s="3" t="n">
+        <v>4</v>
       </c>
       <c r="AO21" s="3" t="inlineStr">
         <is>
           <t>1,7</t>
         </is>
       </c>
-      <c r="AP21" s="3" t="inlineStr">
-        <is>
-          <t>85.31665</t>
-        </is>
+      <c r="AP21" s="3" t="n">
+        <v>85.31665</v>
       </c>
       <c r="AQ21" s="3" t="inlineStr"/>
       <c r="AR21" s="3" t="inlineStr">
         <is>
-          <t>Case : Secondary Router Connetion   has been updated by Chandramani Tharu</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="AS21" s="3" t="inlineStr">
@@ -4879,10 +4863,8 @@
           <t>Chalachitra Chautari pvt.ltd</t>
         </is>
       </c>
-      <c r="O22" s="3" t="inlineStr">
-        <is>
-          <t>9867020120</t>
-        </is>
+      <c r="O22" s="3" t="n">
+        <v>9867020120</v>
       </c>
       <c r="P22" s="3" t="inlineStr">
         <is>
@@ -4968,10 +4950,8 @@
           <t>Chandramani Tharu</t>
         </is>
       </c>
-      <c r="AN22" s="3" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
+      <c r="AN22" s="3" t="n">
+        <v>6</v>
       </c>
       <c r="AO22" s="3" t="inlineStr">
         <is>
@@ -4982,32 +4962,243 @@
       <c r="AQ22" s="3" t="inlineStr"/>
       <c r="AR22" s="3" t="inlineStr">
         <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="AS22" s="3" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="AT22" s="3" t="inlineStr">
+        <is>
+          <t>3d 20h 32m</t>
+        </is>
+      </c>
+      <c r="AU22" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Completed)</t>
+        </is>
+      </c>
+      <c r="AV22" s="3" t="inlineStr">
+        <is>
           <t>Case : slow issue  has been updated by Chandramani Tharu</t>
         </is>
       </c>
-      <c r="AS22" s="3" t="inlineStr">
+      <c r="AW22" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="3" t="inlineStr">
+        <is>
+          <t>Sabin Giri</t>
+        </is>
+      </c>
+      <c r="B23" s="3" t="inlineStr">
+        <is>
+          <t>23 Sep 2026 2:41 PM</t>
+        </is>
+      </c>
+      <c r="C23" s="3" t="inlineStr">
+        <is>
+          <t>WGnmUJF06LTlUriJ5DeDBQ==</t>
+        </is>
+      </c>
+      <c r="D23" s="3" t="inlineStr">
+        <is>
+          <t>Sabin Giri</t>
+        </is>
+      </c>
+      <c r="E23" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F23" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G23" s="3" t="inlineStr"/>
+      <c r="H23" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi 6  has been updated by Sabin Giri</t>
+        </is>
+      </c>
+      <c r="I23" s="3" t="inlineStr">
+        <is>
+          <t>wifi 6</t>
+        </is>
+      </c>
+      <c r="J23" s="3" t="inlineStr">
+        <is>
+          <t>TKT1343230</t>
+        </is>
+      </c>
+      <c r="K23" s="3" t="inlineStr">
+        <is>
+          <t>Bikesh Shrestha</t>
+        </is>
+      </c>
+      <c r="L23" s="3" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="M23" s="3" t="inlineStr">
+        <is>
+          <t>Phone</t>
+        </is>
+      </c>
+      <c r="N23" s="3" t="inlineStr">
+        <is>
+          <t>Bikesh Shrestha</t>
+        </is>
+      </c>
+      <c r="O23" s="3" t="inlineStr">
+        <is>
+          <t>9843828157</t>
+        </is>
+      </c>
+      <c r="P23" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="Q23" s="3" t="inlineStr"/>
+      <c r="R23" s="3" t="inlineStr">
+        <is>
+          <t>23 Sep 2026 02:41:26 PM</t>
+        </is>
+      </c>
+      <c r="S23" s="3" t="inlineStr"/>
+      <c r="T23" s="3" t="inlineStr"/>
+      <c r="U23" s="3" t="inlineStr">
+        <is>
+          <t>9843828157</t>
+        </is>
+      </c>
+      <c r="V23" s="3" t="inlineStr">
+        <is>
+          <t>23 Sep 2026 07:43:57 AM</t>
+        </is>
+      </c>
+      <c r="W23" s="3" t="inlineStr">
+        <is>
+          <t>23 Sep 2026 02:41:26 PM</t>
+        </is>
+      </c>
+      <c r="X23" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Y23" s="3" t="inlineStr">
+        <is>
+          <t>27.774</t>
+        </is>
+      </c>
+      <c r="Z23" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="AA23" s="3" t="inlineStr">
+        <is>
+          <t>Layer 1-User</t>
+        </is>
+      </c>
+      <c r="AB23" s="3" t="inlineStr">
+        <is>
+          <t>L1  Support</t>
+        </is>
+      </c>
+      <c r="AC23" s="3" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="AD23" s="3" t="inlineStr"/>
+      <c r="AE23" s="3" t="inlineStr">
+        <is>
+          <t>Budhanilkantha Near By Park Village Resort,03, Bagmati, Central, Nepal</t>
+        </is>
+      </c>
+      <c r="AF23" s="3" t="inlineStr">
+        <is>
+          <t>shresthabikesh824@gmail.com</t>
+        </is>
+      </c>
+      <c r="AG23" s="3" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="AH23" s="3" t="inlineStr"/>
+      <c r="AI23" s="3" t="inlineStr">
+        <is>
+          <t>04:41 hour</t>
+        </is>
+      </c>
+      <c r="AJ23" s="3" t="inlineStr"/>
+      <c r="AK23" s="3" t="inlineStr"/>
+      <c r="AL23" s="3" t="inlineStr">
+        <is>
+          <t>Sandesh Ghale</t>
+        </is>
+      </c>
+      <c r="AM23" s="3" t="inlineStr">
+        <is>
+          <t>Sabin Giri</t>
+        </is>
+      </c>
+      <c r="AN23" s="3" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AO23" s="3" t="inlineStr">
+        <is>
+          <t>L54-2</t>
+        </is>
+      </c>
+      <c r="AP23" s="3" t="inlineStr">
+        <is>
+          <t>85.36046</t>
+        </is>
+      </c>
+      <c r="AQ23" s="3" t="inlineStr"/>
+      <c r="AR23" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi 6  has been updated by Sabin Giri</t>
+        </is>
+      </c>
+      <c r="AS23" s="3" t="inlineStr">
         <is>
           <t>0m</t>
         </is>
       </c>
-      <c r="AT22" s="3" t="inlineStr">
-        <is>
-          <t>3d 20h 32m</t>
-        </is>
-      </c>
-      <c r="AU22" s="3" t="inlineStr">
+      <c r="AT23" s="3" t="inlineStr">
+        <is>
+          <t>6h 57m</t>
+        </is>
+      </c>
+      <c r="AU23" s="3" t="inlineStr">
         <is>
           <t>Completed (Completed)</t>
         </is>
       </c>
-      <c r="AV22" s="3" t="inlineStr">
-        <is>
-          <t>Case : slow issue  has been updated by Chandramani Tharu</t>
-        </is>
-      </c>
-      <c r="AW22" s="3" t="inlineStr">
-        <is>
-          <t>General / Other Issues</t>
+      <c r="AV23" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi 6  has been updated by Sabin Giri</t>
+        </is>
+      </c>
+      <c r="AW23" s="3" t="inlineStr">
+        <is>
+          <t>WiFi 6 Upgrade</t>
         </is>
       </c>
     </row>
@@ -5022,7 +5213,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M42"/>
+  <dimension ref="A1:M43"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="45" customWidth="1" min="1" max="1"/>
@@ -5059,7 +5250,7 @@
         </is>
       </c>
       <c r="B2" s="3" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="3">
@@ -5069,7 +5260,7 @@
         </is>
       </c>
       <c r="B3" s="5" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
     </row>
     <row r="4">
@@ -5080,7 +5271,7 @@
       </c>
       <c r="B4" s="3" t="inlineStr">
         <is>
-          <t>76.2%</t>
+          <t>77.3%</t>
         </is>
       </c>
     </row>
@@ -5092,7 +5283,7 @@
       </c>
       <c r="B5" s="5" t="inlineStr">
         <is>
-          <t>6h 35m</t>
+          <t>6h 12m</t>
         </is>
       </c>
     </row>
@@ -5104,7 +5295,7 @@
       </c>
       <c r="B6" s="3" t="inlineStr">
         <is>
-          <t>1d 14m</t>
+          <t>23h 13m</t>
         </is>
       </c>
     </row>
@@ -5145,14 +5336,14 @@
         </is>
       </c>
       <c r="B10" s="3" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C10" s="3" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="D10" s="3" t="inlineStr">
         <is>
-          <t>71.4%</t>
+          <t>73.3%</t>
         </is>
       </c>
     </row>
@@ -5280,14 +5471,14 @@
         </is>
       </c>
       <c r="C18" s="3" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="D18" s="3" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E18" s="3" t="inlineStr">
         <is>
-          <t>66.7%</t>
+          <t>69.2%</t>
         </is>
       </c>
     </row>
@@ -6452,7 +6643,7 @@
       </c>
       <c r="G41" s="5" t="inlineStr">
         <is>
-          <t>Case : Secondary Router Connetion   has been updated by Chandramani Tharu</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="H41" s="5" t="inlineStr">
@@ -6519,14 +6710,14 @@
       </c>
       <c r="G42" s="3" t="inlineStr">
         <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="H42" s="3" t="inlineStr">
+        <is>
           <t>Case : slow issue  has been updated by Chandramani Tharu</t>
         </is>
       </c>
-      <c r="H42" s="3" t="inlineStr">
-        <is>
-          <t>Case : slow issue  has been updated by Chandramani Tharu</t>
-        </is>
-      </c>
       <c r="I42" s="3" t="inlineStr">
         <is>
           <t>23 Sep 2026 02:21:55 PM</t>
@@ -6550,6 +6741,73 @@
       <c r="M42" s="3" t="inlineStr">
         <is>
           <t>3d 20h 32m</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="5" t="inlineStr">
+        <is>
+          <t>TKT1343230</t>
+        </is>
+      </c>
+      <c r="B43" s="5" t="inlineStr">
+        <is>
+          <t>Bikesh Shrestha</t>
+        </is>
+      </c>
+      <c r="C43" s="5" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="D43" s="5" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="E43" s="5" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="F43" s="5" t="inlineStr">
+        <is>
+          <t>Completed (Completed)</t>
+        </is>
+      </c>
+      <c r="G43" s="5" t="inlineStr">
+        <is>
+          <t>Case : wifi 6  has been updated by Sabin Giri</t>
+        </is>
+      </c>
+      <c r="H43" s="5" t="inlineStr">
+        <is>
+          <t>Case : wifi 6  has been updated by Sabin Giri</t>
+        </is>
+      </c>
+      <c r="I43" s="5" t="inlineStr">
+        <is>
+          <t>23 Sep 2026 02:41:26 PM</t>
+        </is>
+      </c>
+      <c r="J43" s="5" t="inlineStr">
+        <is>
+          <t>23 Sep 2026 07:43:57 AM</t>
+        </is>
+      </c>
+      <c r="K43" s="5" t="inlineStr">
+        <is>
+          <t>23 Sep 2026 02:41:26 PM</t>
+        </is>
+      </c>
+      <c r="L43" s="5" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="M43" s="5" t="inlineStr">
+        <is>
+          <t>6h 57m</t>
         </is>
       </c>
     </row>

--- a/audit_report_ALL_TEAM_23_Sep_2026.xlsx
+++ b/audit_report_ALL_TEAM_23_Sep_2026.xlsx
@@ -483,7 +483,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AW23"/>
+  <dimension ref="A1:AW25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="23" customWidth="1" min="1" max="1"/>
@@ -5058,10 +5058,8 @@
           <t>Bikesh Shrestha</t>
         </is>
       </c>
-      <c r="O23" s="3" t="inlineStr">
-        <is>
-          <t>9843828157</t>
-        </is>
+      <c r="O23" s="3" t="n">
+        <v>9843828157</v>
       </c>
       <c r="P23" s="3" t="inlineStr">
         <is>
@@ -5096,10 +5094,8 @@
           <t>Active</t>
         </is>
       </c>
-      <c r="Y23" s="3" t="inlineStr">
-        <is>
-          <t>27.774</t>
-        </is>
+      <c r="Y23" s="3" t="n">
+        <v>27.774</v>
       </c>
       <c r="Z23" s="3" t="inlineStr">
         <is>
@@ -5155,48 +5151,358 @@
           <t>Sabin Giri</t>
         </is>
       </c>
-      <c r="AN23" s="3" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
+      <c r="AN23" s="3" t="n">
+        <v>6</v>
       </c>
       <c r="AO23" s="3" t="inlineStr">
         <is>
           <t>L54-2</t>
         </is>
       </c>
-      <c r="AP23" s="3" t="inlineStr">
-        <is>
-          <t>85.36046</t>
-        </is>
+      <c r="AP23" s="3" t="n">
+        <v>85.36046</v>
       </c>
       <c r="AQ23" s="3" t="inlineStr"/>
       <c r="AR23" s="3" t="inlineStr">
         <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="AS23" s="3" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="AT23" s="3" t="inlineStr">
+        <is>
+          <t>6h 57m</t>
+        </is>
+      </c>
+      <c r="AU23" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Completed)</t>
+        </is>
+      </c>
+      <c r="AV23" s="3" t="inlineStr">
+        <is>
           <t>Case : wifi 6  has been updated by Sabin Giri</t>
         </is>
       </c>
-      <c r="AS23" s="3" t="inlineStr">
+      <c r="AW23" s="3" t="inlineStr">
+        <is>
+          <t>WiFi 6 Upgrade</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="3" t="inlineStr">
+        <is>
+          <t>Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="B24" s="3" t="inlineStr">
+        <is>
+          <t>23 Sep 2026 2:53 PM</t>
+        </is>
+      </c>
+      <c r="C24" s="3" t="inlineStr">
+        <is>
+          <t>atwz5SElGeKMz8qxsp3b6c34SBAfIMR+</t>
+        </is>
+      </c>
+      <c r="D24" s="3" t="inlineStr">
+        <is>
+          <t>Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="E24" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F24" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G24" s="3" t="inlineStr"/>
+      <c r="H24" s="3" t="inlineStr">
+        <is>
+          <t>Case : Wi-Fi 6  has been updated by Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="I24" s="3" t="inlineStr">
+        <is>
+          <t>Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="J24" s="3" t="inlineStr">
+        <is>
+          <t>TKT1342466</t>
+        </is>
+      </c>
+      <c r="K24" s="3" t="inlineStr">
+        <is>
+          <t>Dharmesh Maharjan</t>
+        </is>
+      </c>
+      <c r="L24" s="3" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="M24" s="3" t="inlineStr">
+        <is>
+          <t>Email</t>
+        </is>
+      </c>
+      <c r="N24" s="3" t="inlineStr">
+        <is>
+          <t>Dharmesh Maharjan</t>
+        </is>
+      </c>
+      <c r="O24" s="3" t="inlineStr">
+        <is>
+          <t>9869862918</t>
+        </is>
+      </c>
+      <c r="P24" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="Q24" s="3" t="inlineStr"/>
+      <c r="R24" s="3" t="inlineStr">
+        <is>
+          <t>23 Sep 2026 02:53:32 PM</t>
+        </is>
+      </c>
+      <c r="S24" s="3" t="inlineStr"/>
+      <c r="T24" s="3" t="inlineStr"/>
+      <c r="U24" s="3" t="inlineStr">
+        <is>
+          <t>9880539300</t>
+        </is>
+      </c>
+      <c r="V24" s="3" t="inlineStr">
+        <is>
+          <t>22 Sep 2026 01:51:09 PM</t>
+        </is>
+      </c>
+      <c r="W24" s="3" t="inlineStr">
+        <is>
+          <t>23 Sep 2026 02:53:32 PM</t>
+        </is>
+      </c>
+      <c r="X24" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Y24" s="3" t="inlineStr">
+        <is>
+          <t>27.69889</t>
+        </is>
+      </c>
+      <c r="Z24" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="AA24" s="3" t="inlineStr">
+        <is>
+          <t>Layer 1-User</t>
+        </is>
+      </c>
+      <c r="AB24" s="3" t="inlineStr">
+        <is>
+          <t>L1  Support</t>
+        </is>
+      </c>
+      <c r="AC24" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="AD24" s="3" t="inlineStr"/>
+      <c r="AE24" s="3" t="inlineStr">
+        <is>
+          <t>Near Jubilant College, Kalimati, Tankeshwar Marg, Bagmati, Central, Nepal</t>
+        </is>
+      </c>
+      <c r="AF24" s="3" t="inlineStr">
+        <is>
+          <t>Type</t>
+        </is>
+      </c>
+      <c r="AG24" s="3" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="AH24" s="3" t="inlineStr"/>
+      <c r="AI24" s="3" t="inlineStr">
+        <is>
+          <t>11:02 hour</t>
+        </is>
+      </c>
+      <c r="AJ24" s="3" t="inlineStr"/>
+      <c r="AK24" s="3" t="inlineStr"/>
+      <c r="AL24" s="3" t="inlineStr">
+        <is>
+          <t>Susmita Thapa</t>
+        </is>
+      </c>
+      <c r="AM24" s="3" t="inlineStr">
+        <is>
+          <t>Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="AN24" s="3" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AO24" s="3" t="inlineStr">
+        <is>
+          <t>CDB266</t>
+        </is>
+      </c>
+      <c r="AP24" s="3" t="inlineStr">
+        <is>
+          <t>85.30064</t>
+        </is>
+      </c>
+      <c r="AQ24" s="3" t="inlineStr"/>
+      <c r="AR24" s="3" t="inlineStr">
+        <is>
+          <t>Case : Wi-Fi 6  has been updated by Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="AS24" s="3" t="inlineStr">
         <is>
           <t>0m</t>
         </is>
       </c>
-      <c r="AT23" s="3" t="inlineStr">
-        <is>
-          <t>6h 57m</t>
-        </is>
-      </c>
-      <c r="AU23" s="3" t="inlineStr">
+      <c r="AT24" s="3" t="inlineStr">
+        <is>
+          <t>1d 1h 2m</t>
+        </is>
+      </c>
+      <c r="AU24" s="3" t="inlineStr">
         <is>
           <t>Completed (Completed)</t>
         </is>
       </c>
-      <c r="AV23" s="3" t="inlineStr">
-        <is>
-          <t>Case : wifi 6  has been updated by Sabin Giri</t>
-        </is>
-      </c>
-      <c r="AW23" s="3" t="inlineStr">
+      <c r="AV24" s="3" t="inlineStr">
+        <is>
+          <t>Case : Wi-Fi 6  has been updated by Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="AW24" s="3" t="inlineStr">
+        <is>
+          <t>WiFi 6 Upgrade</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="3" t="inlineStr">
+        <is>
+          <t>Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="B25" s="3" t="inlineStr">
+        <is>
+          <t>23 Sep 2026 2:50 PM</t>
+        </is>
+      </c>
+      <c r="C25" s="3" t="inlineStr">
+        <is>
+          <t>w7A8I7MXNVw6IhJoudC/TknnOVKMobUO</t>
+        </is>
+      </c>
+      <c r="D25" s="3" t="inlineStr">
+        <is>
+          <t>Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="E25" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F25" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G25" s="3" t="inlineStr"/>
+      <c r="H25" s="3" t="inlineStr">
+        <is>
+          <t>Case : For upgradation to wifi6   has been updated by Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="I25" s="3" t="inlineStr"/>
+      <c r="J25" s="3" t="inlineStr"/>
+      <c r="K25" s="3" t="inlineStr"/>
+      <c r="L25" s="3" t="inlineStr"/>
+      <c r="M25" s="3" t="inlineStr"/>
+      <c r="N25" s="3" t="inlineStr"/>
+      <c r="O25" s="3" t="inlineStr"/>
+      <c r="P25" s="3" t="inlineStr"/>
+      <c r="Q25" s="3" t="inlineStr"/>
+      <c r="R25" s="3" t="inlineStr"/>
+      <c r="S25" s="3" t="inlineStr"/>
+      <c r="T25" s="3" t="inlineStr"/>
+      <c r="U25" s="3" t="inlineStr"/>
+      <c r="V25" s="3" t="inlineStr"/>
+      <c r="W25" s="3" t="inlineStr"/>
+      <c r="X25" s="3" t="inlineStr"/>
+      <c r="Y25" s="3" t="inlineStr"/>
+      <c r="Z25" s="3" t="inlineStr"/>
+      <c r="AA25" s="3" t="inlineStr"/>
+      <c r="AB25" s="3" t="inlineStr"/>
+      <c r="AC25" s="3" t="inlineStr"/>
+      <c r="AD25" s="3" t="inlineStr"/>
+      <c r="AE25" s="3" t="inlineStr"/>
+      <c r="AF25" s="3" t="inlineStr"/>
+      <c r="AG25" s="3" t="inlineStr"/>
+      <c r="AH25" s="3" t="inlineStr"/>
+      <c r="AI25" s="3" t="inlineStr"/>
+      <c r="AJ25" s="3" t="inlineStr"/>
+      <c r="AK25" s="3" t="inlineStr"/>
+      <c r="AL25" s="3" t="inlineStr"/>
+      <c r="AM25" s="3" t="inlineStr"/>
+      <c r="AN25" s="3" t="inlineStr"/>
+      <c r="AO25" s="3" t="inlineStr"/>
+      <c r="AP25" s="3" t="inlineStr"/>
+      <c r="AQ25" s="3" t="inlineStr"/>
+      <c r="AR25" s="3" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="AS25" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="AT25" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="AU25" s="3" t="inlineStr">
+        <is>
+          <t>Other / In Progress (nan)</t>
+        </is>
+      </c>
+      <c r="AV25" s="3" t="inlineStr">
+        <is>
+          <t>Case : For upgradation to wifi6   has been updated by Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="AW25" s="3" t="inlineStr">
         <is>
           <t>WiFi 6 Upgrade</t>
         </is>
@@ -5213,7 +5519,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M43"/>
+  <dimension ref="A1:M46"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="45" customWidth="1" min="1" max="1"/>
@@ -5250,7 +5556,7 @@
         </is>
       </c>
       <c r="B2" s="3" t="n">
-        <v>22</v>
+        <v>24</v>
       </c>
     </row>
     <row r="3">
@@ -5260,7 +5566,7 @@
         </is>
       </c>
       <c r="B3" s="5" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
     </row>
     <row r="4">
@@ -5271,7 +5577,7 @@
       </c>
       <c r="B4" s="3" t="inlineStr">
         <is>
-          <t>77.3%</t>
+          <t>75.0%</t>
         </is>
       </c>
     </row>
@@ -5283,7 +5589,7 @@
       </c>
       <c r="B5" s="5" t="inlineStr">
         <is>
-          <t>6h 12m</t>
+          <t>5h 51m</t>
         </is>
       </c>
     </row>
@@ -5295,7 +5601,7 @@
       </c>
       <c r="B6" s="3" t="inlineStr">
         <is>
-          <t>23h 13m</t>
+          <t>23h 19m</t>
         </is>
       </c>
     </row>
@@ -5336,14 +5642,14 @@
         </is>
       </c>
       <c r="B10" s="3" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C10" s="3" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="D10" s="3" t="inlineStr">
         <is>
-          <t>73.3%</t>
+          <t>75.0%</t>
         </is>
       </c>
     </row>
@@ -5401,61 +5707,52 @@
         </is>
       </c>
     </row>
-    <row r="14"/>
-    <row r="15">
-      <c r="A15" s="6" t="inlineStr">
+    <row r="14">
+      <c r="A14" s="3" t="inlineStr"/>
+      <c r="B14" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C14" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D14" s="3" t="inlineStr">
+        <is>
+          <t>nan%</t>
+        </is>
+      </c>
+    </row>
+    <row r="15"/>
+    <row r="16">
+      <c r="A16" s="6" t="inlineStr">
         <is>
           <t>Total Tickets Breakdown by Category &amp; Sub Category</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" s="4" t="inlineStr">
-        <is>
-          <t>Category</t>
-        </is>
-      </c>
-      <c r="B16" s="4" t="inlineStr">
-        <is>
-          <t>Sub Category</t>
-        </is>
-      </c>
-      <c r="C16" s="4" t="inlineStr">
-        <is>
-          <t>Total Scraped Tickets</t>
-        </is>
-      </c>
-      <c r="D16" s="4" t="inlineStr">
-        <is>
-          <t>Solved / Handled Count</t>
-        </is>
-      </c>
-      <c r="E16" s="4" t="inlineStr">
-        <is>
-          <t>Solution Rate %</t>
         </is>
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="5" t="inlineStr">
-        <is>
-          <t>General / Other Issues</t>
-        </is>
-      </c>
-      <c r="B17" s="5" t="inlineStr">
-        <is>
-          <t>Query For Secondary Router /Repeater</t>
-        </is>
-      </c>
-      <c r="C17" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="D17" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="E17" s="5" t="inlineStr">
-        <is>
-          <t>100.0%</t>
+      <c r="A17" s="4" t="inlineStr">
+        <is>
+          <t>Category</t>
+        </is>
+      </c>
+      <c r="B17" s="4" t="inlineStr">
+        <is>
+          <t>Sub Category</t>
+        </is>
+      </c>
+      <c r="C17" s="4" t="inlineStr">
+        <is>
+          <t>Total Scraped Tickets</t>
+        </is>
+      </c>
+      <c r="D17" s="4" t="inlineStr">
+        <is>
+          <t>Solved / Handled Count</t>
+        </is>
+      </c>
+      <c r="E17" s="4" t="inlineStr">
+        <is>
+          <t>Solution Rate %</t>
         </is>
       </c>
     </row>
@@ -5467,18 +5764,18 @@
       </c>
       <c r="B18" s="3" t="inlineStr">
         <is>
-          <t>Router Upgrade  Wi-Fi 6</t>
+          <t>Query For Secondary Router /Repeater</t>
         </is>
       </c>
       <c r="C18" s="3" t="n">
-        <v>13</v>
+        <v>1</v>
       </c>
       <c r="D18" s="3" t="n">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="E18" s="3" t="inlineStr">
         <is>
-          <t>69.2%</t>
+          <t>100.0%</t>
         </is>
       </c>
     </row>
@@ -5490,37 +5787,37 @@
       </c>
       <c r="B19" s="5" t="inlineStr">
         <is>
-          <t>Router Upgrade Dual Band</t>
+          <t>Router Upgrade  Wi-Fi 6</t>
         </is>
       </c>
       <c r="C19" s="5" t="n">
-        <v>1</v>
+        <v>14</v>
       </c>
       <c r="D19" s="5" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="E19" s="5" t="inlineStr">
         <is>
-          <t>100.0%</t>
+          <t>71.4%</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="3" t="inlineStr">
         <is>
-          <t>Hardware Damage / Malfunction</t>
+          <t>General / Other Issues</t>
         </is>
       </c>
       <c r="B20" s="3" t="inlineStr">
         <is>
-          <t>IPTV STB box Damage Issue</t>
+          <t>Router Upgrade Dual Band</t>
         </is>
       </c>
       <c r="C20" s="3" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D20" s="3" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E20" s="3" t="inlineStr">
         <is>
@@ -5536,14 +5833,14 @@
       </c>
       <c r="B21" s="5" t="inlineStr">
         <is>
-          <t>Router Damage Issue</t>
+          <t>IPTV STB box Damage Issue</t>
         </is>
       </c>
       <c r="C21" s="5" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D21" s="5" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E21" s="5" t="inlineStr">
         <is>
@@ -5554,12 +5851,12 @@
     <row r="22">
       <c r="A22" s="3" t="inlineStr">
         <is>
-          <t>No Internet Connection</t>
+          <t>Hardware Damage / Malfunction</t>
         </is>
       </c>
       <c r="B22" s="3" t="inlineStr">
         <is>
-          <t>Configuration Issue</t>
+          <t>Router Damage Issue</t>
         </is>
       </c>
       <c r="C22" s="3" t="n">
@@ -5577,244 +5874,148 @@
     <row r="23">
       <c r="A23" s="5" t="inlineStr">
         <is>
-          <t>Slow Internet Connection</t>
+          <t>No Internet Connection</t>
         </is>
       </c>
       <c r="B23" s="5" t="inlineStr">
         <is>
-          <t>Video content is Buffering</t>
+          <t>Configuration Issue</t>
         </is>
       </c>
       <c r="C23" s="5" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D23" s="5" t="n">
         <v>1</v>
       </c>
       <c r="E23" s="5" t="inlineStr">
         <is>
+          <t>100.0%</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="3" t="inlineStr">
+        <is>
+          <t>Slow Internet Connection</t>
+        </is>
+      </c>
+      <c r="B24" s="3" t="inlineStr">
+        <is>
+          <t>Video content is Buffering</t>
+        </is>
+      </c>
+      <c r="C24" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="D24" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="E24" s="3" t="inlineStr">
+        <is>
           <t>50.0%</t>
         </is>
       </c>
     </row>
-    <row r="24"/>
     <row r="25">
-      <c r="A25" s="6" t="inlineStr">
+      <c r="A25" s="5" t="inlineStr"/>
+      <c r="B25" s="5" t="inlineStr"/>
+      <c r="C25" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="D25" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="E25" s="5" t="inlineStr">
+        <is>
+          <t>nan%</t>
+        </is>
+      </c>
+    </row>
+    <row r="26"/>
+    <row r="27">
+      <c r="A27" s="6" t="inlineStr">
         <is>
           <t>Detailed Solved / Handled Tickets List</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" s="4" t="inlineStr">
-        <is>
-          <t>Ticket Number</t>
-        </is>
-      </c>
-      <c r="B26" s="4" t="inlineStr">
-        <is>
-          <t>Account Name</t>
-        </is>
-      </c>
-      <c r="C26" s="4" t="inlineStr">
-        <is>
-          <t>Category</t>
-        </is>
-      </c>
-      <c r="D26" s="4" t="inlineStr">
-        <is>
-          <t>Sub Category</t>
-        </is>
-      </c>
-      <c r="E26" s="4" t="inlineStr">
-        <is>
-          <t>Status</t>
-        </is>
-      </c>
-      <c r="F26" s="4" t="inlineStr">
-        <is>
-          <t>Resolution Type</t>
-        </is>
-      </c>
-      <c r="G26" s="4" t="inlineStr">
-        <is>
-          <t>Employee Remark / Solution Note</t>
-        </is>
-      </c>
-      <c r="H26" s="4" t="inlineStr">
-        <is>
-          <t>Action / Transfer Remark</t>
-        </is>
-      </c>
-      <c r="I26" s="4" t="inlineStr">
-        <is>
-          <t>Assigned Date</t>
-        </is>
-      </c>
-      <c r="J26" s="4" t="inlineStr">
-        <is>
-          <t>Created Date</t>
-        </is>
-      </c>
-      <c r="K26" s="4" t="inlineStr">
-        <is>
-          <t>Last Modified Date</t>
-        </is>
-      </c>
-      <c r="L26" s="4" t="inlineStr">
-        <is>
-          <t>Resolution Time (From Assigned)</t>
-        </is>
-      </c>
-      <c r="M26" s="4" t="inlineStr">
-        <is>
-          <t>Resolution Time (From Created)</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" s="5" t="inlineStr">
-        <is>
-          <t>TKT1342514</t>
-        </is>
-      </c>
-      <c r="B27" s="5" t="inlineStr">
-        <is>
-          <t>Bijay Carlos Rana</t>
-        </is>
-      </c>
-      <c r="C27" s="5" t="inlineStr">
-        <is>
-          <t>General / Other Issues</t>
-        </is>
-      </c>
-      <c r="D27" s="5" t="inlineStr">
-        <is>
-          <t>Router Upgrade  Wi-Fi 6</t>
-        </is>
-      </c>
-      <c r="E27" s="5" t="inlineStr">
-        <is>
-          <t>Completed</t>
-        </is>
-      </c>
-      <c r="F27" s="5" t="inlineStr">
-        <is>
-          <t>Completed (Completed)</t>
-        </is>
-      </c>
-      <c r="G27" s="5" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
-      <c r="H27" s="5" t="inlineStr">
-        <is>
-          <t>Case : WIFI 6  has been updated by Rajesh Maharjan</t>
-        </is>
-      </c>
-      <c r="I27" s="5" t="inlineStr">
-        <is>
-          <t>23 Sep 2026 11:16:05 AM</t>
-        </is>
-      </c>
-      <c r="J27" s="5" t="inlineStr">
-        <is>
-          <t>22 Sep 2026 02:29:16 PM</t>
-        </is>
-      </c>
-      <c r="K27" s="5" t="inlineStr">
-        <is>
-          <t>23 Sep 2026 11:16:05 AM</t>
-        </is>
-      </c>
-      <c r="L27" s="5" t="inlineStr">
-        <is>
-          <t>0m</t>
-        </is>
-      </c>
-      <c r="M27" s="5" t="inlineStr">
-        <is>
-          <t>20h 46m</t>
         </is>
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="3" t="inlineStr">
-        <is>
-          <t>TKT1343394</t>
-        </is>
-      </c>
-      <c r="B28" s="3" t="inlineStr">
-        <is>
-          <t>Kaizen Business consultant</t>
-        </is>
-      </c>
-      <c r="C28" s="3" t="inlineStr">
-        <is>
-          <t>General / Other Issues</t>
-        </is>
-      </c>
-      <c r="D28" s="3" t="inlineStr">
-        <is>
-          <t>Router Upgrade  Wi-Fi 6</t>
-        </is>
-      </c>
-      <c r="E28" s="3" t="inlineStr">
-        <is>
-          <t>Completed</t>
-        </is>
-      </c>
-      <c r="F28" s="3" t="inlineStr">
-        <is>
-          <t>Completed (Completed)</t>
-        </is>
-      </c>
-      <c r="G28" s="3" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
-      <c r="H28" s="3" t="inlineStr">
-        <is>
-          <t>Case : wifi 6 router  has been updated by Sabin Giri</t>
-        </is>
-      </c>
-      <c r="I28" s="3" t="inlineStr">
-        <is>
-          <t>23 Sep 2026 12:31:18 PM</t>
-        </is>
-      </c>
-      <c r="J28" s="3" t="inlineStr">
-        <is>
-          <t>23 Sep 2026 09:53:33 AM</t>
-        </is>
-      </c>
-      <c r="K28" s="3" t="inlineStr">
-        <is>
-          <t>23 Sep 2026 12:31:18 PM</t>
-        </is>
-      </c>
-      <c r="L28" s="3" t="inlineStr">
-        <is>
-          <t>0m</t>
-        </is>
-      </c>
-      <c r="M28" s="3" t="inlineStr">
-        <is>
-          <t>2h 37m</t>
+      <c r="A28" s="4" t="inlineStr">
+        <is>
+          <t>Ticket Number</t>
+        </is>
+      </c>
+      <c r="B28" s="4" t="inlineStr">
+        <is>
+          <t>Account Name</t>
+        </is>
+      </c>
+      <c r="C28" s="4" t="inlineStr">
+        <is>
+          <t>Category</t>
+        </is>
+      </c>
+      <c r="D28" s="4" t="inlineStr">
+        <is>
+          <t>Sub Category</t>
+        </is>
+      </c>
+      <c r="E28" s="4" t="inlineStr">
+        <is>
+          <t>Status</t>
+        </is>
+      </c>
+      <c r="F28" s="4" t="inlineStr">
+        <is>
+          <t>Resolution Type</t>
+        </is>
+      </c>
+      <c r="G28" s="4" t="inlineStr">
+        <is>
+          <t>Employee Remark / Solution Note</t>
+        </is>
+      </c>
+      <c r="H28" s="4" t="inlineStr">
+        <is>
+          <t>Action / Transfer Remark</t>
+        </is>
+      </c>
+      <c r="I28" s="4" t="inlineStr">
+        <is>
+          <t>Assigned Date</t>
+        </is>
+      </c>
+      <c r="J28" s="4" t="inlineStr">
+        <is>
+          <t>Created Date</t>
+        </is>
+      </c>
+      <c r="K28" s="4" t="inlineStr">
+        <is>
+          <t>Last Modified Date</t>
+        </is>
+      </c>
+      <c r="L28" s="4" t="inlineStr">
+        <is>
+          <t>Resolution Time (From Assigned)</t>
+        </is>
+      </c>
+      <c r="M28" s="4" t="inlineStr">
+        <is>
+          <t>Resolution Time (From Created)</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="5" t="inlineStr">
         <is>
-          <t>TKT1343122</t>
+          <t>TKT1342514</t>
         </is>
       </c>
       <c r="B29" s="5" t="inlineStr">
         <is>
-          <t>Rajesh Shahi</t>
+          <t>Bijay Carlos Rana</t>
         </is>
       </c>
       <c r="C29" s="5" t="inlineStr">
@@ -5844,22 +6045,22 @@
       </c>
       <c r="H29" s="5" t="inlineStr">
         <is>
-          <t>Case : wifi 6  has been updated by Shashikant Chaudhary</t>
+          <t>Case : WIFI 6  has been updated by Rajesh Maharjan</t>
         </is>
       </c>
       <c r="I29" s="5" t="inlineStr">
         <is>
-          <t>23 Sep 2026 12:37:13 PM</t>
+          <t>23 Sep 2026 11:16:05 AM</t>
         </is>
       </c>
       <c r="J29" s="5" t="inlineStr">
         <is>
-          <t>22 Sep 2026 09:56:18 PM</t>
+          <t>22 Sep 2026 02:29:16 PM</t>
         </is>
       </c>
       <c r="K29" s="5" t="inlineStr">
         <is>
-          <t>23 Sep 2026 12:37:13 PM</t>
+          <t>23 Sep 2026 11:16:05 AM</t>
         </is>
       </c>
       <c r="L29" s="5" t="inlineStr">
@@ -5869,19 +6070,19 @@
       </c>
       <c r="M29" s="5" t="inlineStr">
         <is>
-          <t>14h 40m</t>
+          <t>20h 46m</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="3" t="inlineStr">
         <is>
-          <t>TKT1343670</t>
+          <t>TKT1343394</t>
         </is>
       </c>
       <c r="B30" s="3" t="inlineStr">
         <is>
-          <t>Suman Shah</t>
+          <t>Kaizen Business consultant</t>
         </is>
       </c>
       <c r="C30" s="3" t="inlineStr">
@@ -5891,7 +6092,7 @@
       </c>
       <c r="D30" s="3" t="inlineStr">
         <is>
-          <t>Router Upgrade Dual Band</t>
+          <t>Router Upgrade  Wi-Fi 6</t>
         </is>
       </c>
       <c r="E30" s="3" t="inlineStr">
@@ -5911,22 +6112,22 @@
       </c>
       <c r="H30" s="3" t="inlineStr">
         <is>
-          <t>Case : router change  has been updated by Shashikant Chaudhary</t>
+          <t>Case : wifi 6 router  has been updated by Sabin Giri</t>
         </is>
       </c>
       <c r="I30" s="3" t="inlineStr">
         <is>
-          <t>23 Sep 2026 12:59:40 PM</t>
+          <t>23 Sep 2026 12:31:18 PM</t>
         </is>
       </c>
       <c r="J30" s="3" t="inlineStr">
         <is>
-          <t>23 Sep 2026 12:23:42 PM</t>
+          <t>23 Sep 2026 09:53:33 AM</t>
         </is>
       </c>
       <c r="K30" s="3" t="inlineStr">
         <is>
-          <t>23 Sep 2026 12:59:40 PM</t>
+          <t>23 Sep 2026 12:31:18 PM</t>
         </is>
       </c>
       <c r="L30" s="3" t="inlineStr">
@@ -5936,39 +6137,39 @@
       </c>
       <c r="M30" s="3" t="inlineStr">
         <is>
-          <t>35m</t>
+          <t>2h 37m</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="5" t="inlineStr">
         <is>
-          <t>TKT1342524</t>
+          <t>TKT1343122</t>
         </is>
       </c>
       <c r="B31" s="5" t="inlineStr">
         <is>
-          <t>Nakul Bhandari</t>
+          <t>Rajesh Shahi</t>
         </is>
       </c>
       <c r="C31" s="5" t="inlineStr">
         <is>
-          <t>No Internet Connection</t>
+          <t>General / Other Issues</t>
         </is>
       </c>
       <c r="D31" s="5" t="inlineStr">
         <is>
-          <t>Configuration Issue</t>
+          <t>Router Upgrade  Wi-Fi 6</t>
         </is>
       </c>
       <c r="E31" s="5" t="inlineStr">
         <is>
-          <t>Closed</t>
+          <t>Completed</t>
         </is>
       </c>
       <c r="F31" s="5" t="inlineStr">
         <is>
-          <t>Completed (Closed)</t>
+          <t>Completed (Completed)</t>
         </is>
       </c>
       <c r="G31" s="5" t="inlineStr">
@@ -5978,44 +6179,44 @@
       </c>
       <c r="H31" s="5" t="inlineStr">
         <is>
-          <t>Case : CONFINGURE ISSUE  has been updated by Ajit Shrestha</t>
+          <t>Case : wifi 6  has been updated by Shashikant Chaudhary</t>
         </is>
       </c>
       <c r="I31" s="5" t="inlineStr">
         <is>
-          <t>22 Sep 2026 02:52:24 PM</t>
+          <t>23 Sep 2026 12:37:13 PM</t>
         </is>
       </c>
       <c r="J31" s="5" t="inlineStr">
         <is>
-          <t>22 Sep 2026 02:35:30 PM</t>
+          <t>22 Sep 2026 09:56:18 PM</t>
         </is>
       </c>
       <c r="K31" s="5" t="inlineStr">
         <is>
-          <t>23 Sep 2026 12:57:31 PM</t>
+          <t>23 Sep 2026 12:37:13 PM</t>
         </is>
       </c>
       <c r="L31" s="5" t="inlineStr">
         <is>
-          <t>22h 5m</t>
+          <t>0m</t>
         </is>
       </c>
       <c r="M31" s="5" t="inlineStr">
         <is>
-          <t>22h 22m</t>
+          <t>14h 40m</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="3" t="inlineStr">
         <is>
-          <t>TKT1342923</t>
+          <t>TKT1343670</t>
         </is>
       </c>
       <c r="B32" s="3" t="inlineStr">
         <is>
-          <t>Maan maya poon</t>
+          <t>Suman Shah</t>
         </is>
       </c>
       <c r="C32" s="3" t="inlineStr">
@@ -6025,7 +6226,7 @@
       </c>
       <c r="D32" s="3" t="inlineStr">
         <is>
-          <t>Router Upgrade  Wi-Fi 6</t>
+          <t>Router Upgrade Dual Band</t>
         </is>
       </c>
       <c r="E32" s="3" t="inlineStr">
@@ -6045,22 +6246,22 @@
       </c>
       <c r="H32" s="3" t="inlineStr">
         <is>
-          <t>Case : For upgradation to wifi6   has been updated by Sabin Giri</t>
+          <t>Case : router change  has been updated by Shashikant Chaudhary</t>
         </is>
       </c>
       <c r="I32" s="3" t="inlineStr">
         <is>
-          <t>23 Sep 2026 01:01:06 PM</t>
+          <t>23 Sep 2026 12:59:40 PM</t>
         </is>
       </c>
       <c r="J32" s="3" t="inlineStr">
         <is>
-          <t>22 Sep 2026 06:58:31 PM</t>
+          <t>23 Sep 2026 12:23:42 PM</t>
         </is>
       </c>
       <c r="K32" s="3" t="inlineStr">
         <is>
-          <t>23 Sep 2026 01:01:06 PM</t>
+          <t>23 Sep 2026 12:59:40 PM</t>
         </is>
       </c>
       <c r="L32" s="3" t="inlineStr">
@@ -6070,39 +6271,39 @@
       </c>
       <c r="M32" s="3" t="inlineStr">
         <is>
-          <t>18h 2m</t>
+          <t>35m</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="5" t="inlineStr">
         <is>
-          <t>TKT1343451</t>
+          <t>TKT1342524</t>
         </is>
       </c>
       <c r="B33" s="5" t="inlineStr">
         <is>
-          <t>Sabin Maharjan</t>
+          <t>Nakul Bhandari</t>
         </is>
       </c>
       <c r="C33" s="5" t="inlineStr">
         <is>
-          <t>General / Other Issues</t>
+          <t>No Internet Connection</t>
         </is>
       </c>
       <c r="D33" s="5" t="inlineStr">
         <is>
-          <t>Router Upgrade  Wi-Fi 6</t>
+          <t>Configuration Issue</t>
         </is>
       </c>
       <c r="E33" s="5" t="inlineStr">
         <is>
-          <t>Completed</t>
+          <t>Closed</t>
         </is>
       </c>
       <c r="F33" s="5" t="inlineStr">
         <is>
-          <t>Completed (Completed)</t>
+          <t>Completed (Closed)</t>
         </is>
       </c>
       <c r="G33" s="5" t="inlineStr">
@@ -6112,54 +6313,54 @@
       </c>
       <c r="H33" s="5" t="inlineStr">
         <is>
-          <t>Case : Wifi 6  has been updated by Sabin Giri</t>
+          <t>Case : CONFINGURE ISSUE  has been updated by Ajit Shrestha</t>
         </is>
       </c>
       <c r="I33" s="5" t="inlineStr">
         <is>
-          <t>23 Sep 2026 01:17:39 PM</t>
+          <t>22 Sep 2026 02:52:24 PM</t>
         </is>
       </c>
       <c r="J33" s="5" t="inlineStr">
         <is>
-          <t>23 Sep 2026 10:26:34 AM</t>
+          <t>22 Sep 2026 02:35:30 PM</t>
         </is>
       </c>
       <c r="K33" s="5" t="inlineStr">
         <is>
-          <t>23 Sep 2026 01:17:39 PM</t>
+          <t>23 Sep 2026 12:57:31 PM</t>
         </is>
       </c>
       <c r="L33" s="5" t="inlineStr">
         <is>
-          <t>0m</t>
+          <t>22h 5m</t>
         </is>
       </c>
       <c r="M33" s="5" t="inlineStr">
         <is>
-          <t>2h 51m</t>
+          <t>22h 22m</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="3" t="inlineStr">
         <is>
-          <t>TKT1343062</t>
+          <t>TKT1342923</t>
         </is>
       </c>
       <c r="B34" s="3" t="inlineStr">
         <is>
-          <t>Sabin Magar</t>
+          <t>Maan maya poon</t>
         </is>
       </c>
       <c r="C34" s="3" t="inlineStr">
         <is>
-          <t>Hardware Damage / Malfunction</t>
+          <t>General / Other Issues</t>
         </is>
       </c>
       <c r="D34" s="3" t="inlineStr">
         <is>
-          <t>IPTV STB box Damage Issue</t>
+          <t>Router Upgrade  Wi-Fi 6</t>
         </is>
       </c>
       <c r="E34" s="3" t="inlineStr">
@@ -6179,22 +6380,22 @@
       </c>
       <c r="H34" s="3" t="inlineStr">
         <is>
-          <t>Case : IP TV not Working   has been updated by Ajit Shrestha</t>
+          <t>Case : For upgradation to wifi6   has been updated by Sabin Giri</t>
         </is>
       </c>
       <c r="I34" s="3" t="inlineStr">
         <is>
-          <t>23 Sep 2026 01:16:47 PM</t>
+          <t>23 Sep 2026 01:01:06 PM</t>
         </is>
       </c>
       <c r="J34" s="3" t="inlineStr">
         <is>
-          <t>22 Sep 2026 08:56:52 PM</t>
+          <t>22 Sep 2026 06:58:31 PM</t>
         </is>
       </c>
       <c r="K34" s="3" t="inlineStr">
         <is>
-          <t>23 Sep 2026 01:16:47 PM</t>
+          <t>23 Sep 2026 01:01:06 PM</t>
         </is>
       </c>
       <c r="L34" s="3" t="inlineStr">
@@ -6204,19 +6405,19 @@
       </c>
       <c r="M34" s="3" t="inlineStr">
         <is>
-          <t>16h 19m</t>
+          <t>18h 2m</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="5" t="inlineStr">
         <is>
-          <t>TKT1341347</t>
+          <t>TKT1343451</t>
         </is>
       </c>
       <c r="B35" s="5" t="inlineStr">
         <is>
-          <t>Siddhartha Model School</t>
+          <t>Sabin Maharjan</t>
         </is>
       </c>
       <c r="C35" s="5" t="inlineStr">
@@ -6231,12 +6432,12 @@
       </c>
       <c r="E35" s="5" t="inlineStr">
         <is>
-          <t>Closed</t>
+          <t>Completed</t>
         </is>
       </c>
       <c r="F35" s="5" t="inlineStr">
         <is>
-          <t>Completed (Closed)</t>
+          <t>Completed (Completed)</t>
         </is>
       </c>
       <c r="G35" s="5" t="inlineStr">
@@ -6246,54 +6447,54 @@
       </c>
       <c r="H35" s="5" t="inlineStr">
         <is>
-          <t>Case : wifi 6  has been updated by Sunil Chaudhary</t>
+          <t>Case : Wifi 6  has been updated by Sabin Giri</t>
         </is>
       </c>
       <c r="I35" s="5" t="inlineStr">
         <is>
-          <t>21 Sep 2026 01:35:47 PM</t>
+          <t>23 Sep 2026 01:17:39 PM</t>
         </is>
       </c>
       <c r="J35" s="5" t="inlineStr">
         <is>
-          <t>21 Sep 2026 01:35:47 PM</t>
+          <t>23 Sep 2026 10:26:34 AM</t>
         </is>
       </c>
       <c r="K35" s="5" t="inlineStr">
         <is>
-          <t>23 Sep 2026 01:22:44 PM</t>
+          <t>23 Sep 2026 01:17:39 PM</t>
         </is>
       </c>
       <c r="L35" s="5" t="inlineStr">
         <is>
-          <t>1d 23h 46m</t>
+          <t>0m</t>
         </is>
       </c>
       <c r="M35" s="5" t="inlineStr">
         <is>
-          <t>1d 23h 46m</t>
+          <t>2h 51m</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="3" t="inlineStr">
         <is>
-          <t>TKT1342867</t>
+          <t>TKT1343062</t>
         </is>
       </c>
       <c r="B36" s="3" t="inlineStr">
         <is>
-          <t>Punit Kumar Barnawal</t>
+          <t>Sabin Magar</t>
         </is>
       </c>
       <c r="C36" s="3" t="inlineStr">
         <is>
-          <t>General / Other Issues</t>
+          <t>Hardware Damage / Malfunction</t>
         </is>
       </c>
       <c r="D36" s="3" t="inlineStr">
         <is>
-          <t>Router Upgrade  Wi-Fi 6</t>
+          <t>IPTV STB box Damage Issue</t>
         </is>
       </c>
       <c r="E36" s="3" t="inlineStr">
@@ -6313,22 +6514,22 @@
       </c>
       <c r="H36" s="3" t="inlineStr">
         <is>
-          <t>Case : Wifi 6  has been updated by Shashikant Chaudhary</t>
+          <t>Case : IP TV not Working   has been updated by Ajit Shrestha</t>
         </is>
       </c>
       <c r="I36" s="3" t="inlineStr">
         <is>
-          <t>23 Sep 2026 01:48:42 PM</t>
+          <t>23 Sep 2026 01:16:47 PM</t>
         </is>
       </c>
       <c r="J36" s="3" t="inlineStr">
         <is>
-          <t>22 Sep 2026 06:02:29 PM</t>
+          <t>22 Sep 2026 08:56:52 PM</t>
         </is>
       </c>
       <c r="K36" s="3" t="inlineStr">
         <is>
-          <t>23 Sep 2026 01:48:42 PM</t>
+          <t>23 Sep 2026 01:16:47 PM</t>
         </is>
       </c>
       <c r="L36" s="3" t="inlineStr">
@@ -6338,39 +6539,39 @@
       </c>
       <c r="M36" s="3" t="inlineStr">
         <is>
-          <t>19h 46m</t>
+          <t>16h 19m</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="5" t="inlineStr">
         <is>
-          <t>TKT1343135</t>
+          <t>TKT1341347</t>
         </is>
       </c>
       <c r="B37" s="5" t="inlineStr">
         <is>
-          <t>Ashish Shahbadi</t>
+          <t>Siddhartha Model School</t>
         </is>
       </c>
       <c r="C37" s="5" t="inlineStr">
         <is>
-          <t>Hardware Damage / Malfunction</t>
+          <t>General / Other Issues</t>
         </is>
       </c>
       <c r="D37" s="5" t="inlineStr">
         <is>
-          <t>Router Damage Issue</t>
+          <t>Router Upgrade  Wi-Fi 6</t>
         </is>
       </c>
       <c r="E37" s="5" t="inlineStr">
         <is>
-          <t>Completed</t>
+          <t>Closed</t>
         </is>
       </c>
       <c r="F37" s="5" t="inlineStr">
         <is>
-          <t>Completed (Completed)</t>
+          <t>Completed (Closed)</t>
         </is>
       </c>
       <c r="G37" s="5" t="inlineStr">
@@ -6380,44 +6581,44 @@
       </c>
       <c r="H37" s="5" t="inlineStr">
         <is>
-          <t>Case : 5g not working   has been updated by Rajesh Maharjan</t>
+          <t>Case : wifi 6  has been updated by Sunil Chaudhary</t>
         </is>
       </c>
       <c r="I37" s="5" t="inlineStr">
         <is>
-          <t>23 Sep 2026 01:51:51 PM</t>
+          <t>21 Sep 2026 01:35:47 PM</t>
         </is>
       </c>
       <c r="J37" s="5" t="inlineStr">
         <is>
-          <t>22 Sep 2026 10:20:07 PM</t>
+          <t>21 Sep 2026 01:35:47 PM</t>
         </is>
       </c>
       <c r="K37" s="5" t="inlineStr">
         <is>
-          <t>23 Sep 2026 01:51:51 PM</t>
+          <t>23 Sep 2026 01:22:44 PM</t>
         </is>
       </c>
       <c r="L37" s="5" t="inlineStr">
         <is>
-          <t>0m</t>
+          <t>1d 23h 46m</t>
         </is>
       </c>
       <c r="M37" s="5" t="inlineStr">
         <is>
-          <t>15h 31m</t>
+          <t>1d 23h 46m</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="3" t="inlineStr">
         <is>
-          <t>TKT1343287</t>
+          <t>TKT1342867</t>
         </is>
       </c>
       <c r="B38" s="3" t="inlineStr">
         <is>
-          <t>Anup Chaudhary</t>
+          <t>Punit Kumar Barnawal</t>
         </is>
       </c>
       <c r="C38" s="3" t="inlineStr">
@@ -6447,22 +6648,22 @@
       </c>
       <c r="H38" s="3" t="inlineStr">
         <is>
-          <t>Case : wifi 6  has been updated by Sabin Giri</t>
+          <t>Case : Wifi 6  has been updated by Shashikant Chaudhary</t>
         </is>
       </c>
       <c r="I38" s="3" t="inlineStr">
         <is>
-          <t>23 Sep 2026 02:03:32 PM</t>
+          <t>23 Sep 2026 01:48:42 PM</t>
         </is>
       </c>
       <c r="J38" s="3" t="inlineStr">
         <is>
-          <t>23 Sep 2026 08:37:17 AM</t>
+          <t>22 Sep 2026 06:02:29 PM</t>
         </is>
       </c>
       <c r="K38" s="3" t="inlineStr">
         <is>
-          <t>23 Sep 2026 02:03:32 PM</t>
+          <t>23 Sep 2026 01:48:42 PM</t>
         </is>
       </c>
       <c r="L38" s="3" t="inlineStr">
@@ -6472,19 +6673,19 @@
       </c>
       <c r="M38" s="3" t="inlineStr">
         <is>
-          <t>5h 26m</t>
+          <t>19h 46m</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="5" t="inlineStr">
         <is>
-          <t>TKT1342988</t>
+          <t>TKT1343135</t>
         </is>
       </c>
       <c r="B39" s="5" t="inlineStr">
         <is>
-          <t>Kushal Neupane</t>
+          <t>Ashish Shahbadi</t>
         </is>
       </c>
       <c r="C39" s="5" t="inlineStr">
@@ -6494,17 +6695,17 @@
       </c>
       <c r="D39" s="5" t="inlineStr">
         <is>
-          <t>IPTV STB box Damage Issue</t>
+          <t>Router Damage Issue</t>
         </is>
       </c>
       <c r="E39" s="5" t="inlineStr">
         <is>
-          <t>Closed</t>
+          <t>Completed</t>
         </is>
       </c>
       <c r="F39" s="5" t="inlineStr">
         <is>
-          <t>Completed (Closed)</t>
+          <t>Completed (Completed)</t>
         </is>
       </c>
       <c r="G39" s="5" t="inlineStr">
@@ -6514,64 +6715,64 @@
       </c>
       <c r="H39" s="5" t="inlineStr">
         <is>
-          <t>Case : stb faulty  has been updated by Sunil Chaudhary</t>
+          <t>Case : 5g not working   has been updated by Rajesh Maharjan</t>
         </is>
       </c>
       <c r="I39" s="5" t="inlineStr">
         <is>
-          <t>22 Sep 2026 08:27:54 PM</t>
+          <t>23 Sep 2026 01:51:51 PM</t>
         </is>
       </c>
       <c r="J39" s="5" t="inlineStr">
         <is>
-          <t>22 Sep 2026 07:49:31 PM</t>
+          <t>22 Sep 2026 10:20:07 PM</t>
         </is>
       </c>
       <c r="K39" s="5" t="inlineStr">
         <is>
-          <t>23 Sep 2026 02:16:10 PM</t>
+          <t>23 Sep 2026 01:51:51 PM</t>
         </is>
       </c>
       <c r="L39" s="5" t="inlineStr">
         <is>
-          <t>17h 48m</t>
+          <t>0m</t>
         </is>
       </c>
       <c r="M39" s="5" t="inlineStr">
         <is>
-          <t>18h 26m</t>
+          <t>15h 31m</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="3" t="inlineStr">
         <is>
-          <t>TKT1342988</t>
+          <t>TKT1343287</t>
         </is>
       </c>
       <c r="B40" s="3" t="inlineStr">
         <is>
-          <t>Kushal Neupane</t>
+          <t>Anup Chaudhary</t>
         </is>
       </c>
       <c r="C40" s="3" t="inlineStr">
         <is>
-          <t>Hardware Damage / Malfunction</t>
+          <t>General / Other Issues</t>
         </is>
       </c>
       <c r="D40" s="3" t="inlineStr">
         <is>
-          <t>IPTV STB box Damage Issue</t>
+          <t>Router Upgrade  Wi-Fi 6</t>
         </is>
       </c>
       <c r="E40" s="3" t="inlineStr">
         <is>
-          <t>Closed</t>
+          <t>Completed</t>
         </is>
       </c>
       <c r="F40" s="3" t="inlineStr">
         <is>
-          <t>Completed (Closed)</t>
+          <t>Completed (Completed)</t>
         </is>
       </c>
       <c r="G40" s="3" t="inlineStr">
@@ -6581,64 +6782,64 @@
       </c>
       <c r="H40" s="3" t="inlineStr">
         <is>
-          <t>Case : stb faulty  has been updated by Sunil Chaudhary</t>
+          <t>Case : wifi 6  has been updated by Sabin Giri</t>
         </is>
       </c>
       <c r="I40" s="3" t="inlineStr">
         <is>
-          <t>22 Sep 2026 08:27:54 PM</t>
+          <t>23 Sep 2026 02:03:32 PM</t>
         </is>
       </c>
       <c r="J40" s="3" t="inlineStr">
         <is>
-          <t>22 Sep 2026 07:49:31 PM</t>
+          <t>23 Sep 2026 08:37:17 AM</t>
         </is>
       </c>
       <c r="K40" s="3" t="inlineStr">
         <is>
-          <t>23 Sep 2026 02:16:10 PM</t>
+          <t>23 Sep 2026 02:03:32 PM</t>
         </is>
       </c>
       <c r="L40" s="3" t="inlineStr">
         <is>
-          <t>17h 48m</t>
+          <t>0m</t>
         </is>
       </c>
       <c r="M40" s="3" t="inlineStr">
         <is>
-          <t>18h 26m</t>
+          <t>5h 26m</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="5" t="inlineStr">
         <is>
-          <t>TKT1340081</t>
+          <t>TKT1342988</t>
         </is>
       </c>
       <c r="B41" s="5" t="inlineStr">
         <is>
-          <t>Anjan Khadka</t>
+          <t>Kushal Neupane</t>
         </is>
       </c>
       <c r="C41" s="5" t="inlineStr">
         <is>
-          <t>General / Other Issues</t>
+          <t>Hardware Damage / Malfunction</t>
         </is>
       </c>
       <c r="D41" s="5" t="inlineStr">
         <is>
-          <t>Query For Secondary Router /Repeater</t>
+          <t>IPTV STB box Damage Issue</t>
         </is>
       </c>
       <c r="E41" s="5" t="inlineStr">
         <is>
-          <t>Completed</t>
+          <t>Closed</t>
         </is>
       </c>
       <c r="F41" s="5" t="inlineStr">
         <is>
-          <t>Completed (Completed)</t>
+          <t>Completed (Closed)</t>
         </is>
       </c>
       <c r="G41" s="5" t="inlineStr">
@@ -6648,64 +6849,64 @@
       </c>
       <c r="H41" s="5" t="inlineStr">
         <is>
-          <t>Case : Secondary Router Connetion   has been updated by Chandramani Tharu</t>
+          <t>Case : stb faulty  has been updated by Sunil Chaudhary</t>
         </is>
       </c>
       <c r="I41" s="5" t="inlineStr">
         <is>
-          <t>23 Sep 2026 02:23:04 PM</t>
+          <t>22 Sep 2026 08:27:54 PM</t>
         </is>
       </c>
       <c r="J41" s="5" t="inlineStr">
         <is>
-          <t>20 Sep 2026 02:38:36 PM</t>
+          <t>22 Sep 2026 07:49:31 PM</t>
         </is>
       </c>
       <c r="K41" s="5" t="inlineStr">
         <is>
-          <t>23 Sep 2026 02:23:04 PM</t>
+          <t>23 Sep 2026 02:16:10 PM</t>
         </is>
       </c>
       <c r="L41" s="5" t="inlineStr">
         <is>
-          <t>0m</t>
+          <t>17h 48m</t>
         </is>
       </c>
       <c r="M41" s="5" t="inlineStr">
         <is>
-          <t>2d 23h 44m</t>
+          <t>18h 26m</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="3" t="inlineStr">
         <is>
-          <t>TKT1339133</t>
+          <t>TKT1342988</t>
         </is>
       </c>
       <c r="B42" s="3" t="inlineStr">
         <is>
-          <t>Chalachitra Chautari pvt.ltd</t>
+          <t>Kushal Neupane</t>
         </is>
       </c>
       <c r="C42" s="3" t="inlineStr">
         <is>
-          <t>Slow Internet Connection</t>
+          <t>Hardware Damage / Malfunction</t>
         </is>
       </c>
       <c r="D42" s="3" t="inlineStr">
         <is>
-          <t>Video content is Buffering</t>
+          <t>IPTV STB box Damage Issue</t>
         </is>
       </c>
       <c r="E42" s="3" t="inlineStr">
         <is>
-          <t>Completed</t>
+          <t>Closed</t>
         </is>
       </c>
       <c r="F42" s="3" t="inlineStr">
         <is>
-          <t>Completed (Completed)</t>
+          <t>Completed (Closed)</t>
         </is>
       </c>
       <c r="G42" s="3" t="inlineStr">
@@ -6715,99 +6916,300 @@
       </c>
       <c r="H42" s="3" t="inlineStr">
         <is>
-          <t>Case : slow issue  has been updated by Chandramani Tharu</t>
+          <t>Case : stb faulty  has been updated by Sunil Chaudhary</t>
         </is>
       </c>
       <c r="I42" s="3" t="inlineStr">
         <is>
-          <t>23 Sep 2026 02:21:55 PM</t>
+          <t>22 Sep 2026 08:27:54 PM</t>
         </is>
       </c>
       <c r="J42" s="3" t="inlineStr">
         <is>
-          <t>19 Sep 2026 05:49:47 PM</t>
+          <t>22 Sep 2026 07:49:31 PM</t>
         </is>
       </c>
       <c r="K42" s="3" t="inlineStr">
         <is>
-          <t>23 Sep 2026 02:21:55 PM</t>
+          <t>23 Sep 2026 02:16:10 PM</t>
         </is>
       </c>
       <c r="L42" s="3" t="inlineStr">
         <is>
-          <t>0m</t>
+          <t>17h 48m</t>
         </is>
       </c>
       <c r="M42" s="3" t="inlineStr">
         <is>
-          <t>3d 20h 32m</t>
+          <t>18h 26m</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="5" t="inlineStr">
         <is>
+          <t>TKT1340081</t>
+        </is>
+      </c>
+      <c r="B43" s="5" t="inlineStr">
+        <is>
+          <t>Anjan Khadka</t>
+        </is>
+      </c>
+      <c r="C43" s="5" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="D43" s="5" t="inlineStr">
+        <is>
+          <t>Query For Secondary Router /Repeater</t>
+        </is>
+      </c>
+      <c r="E43" s="5" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="F43" s="5" t="inlineStr">
+        <is>
+          <t>Completed (Completed)</t>
+        </is>
+      </c>
+      <c r="G43" s="5" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="H43" s="5" t="inlineStr">
+        <is>
+          <t>Case : Secondary Router Connetion   has been updated by Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="I43" s="5" t="inlineStr">
+        <is>
+          <t>23 Sep 2026 02:23:04 PM</t>
+        </is>
+      </c>
+      <c r="J43" s="5" t="inlineStr">
+        <is>
+          <t>20 Sep 2026 02:38:36 PM</t>
+        </is>
+      </c>
+      <c r="K43" s="5" t="inlineStr">
+        <is>
+          <t>23 Sep 2026 02:23:04 PM</t>
+        </is>
+      </c>
+      <c r="L43" s="5" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="M43" s="5" t="inlineStr">
+        <is>
+          <t>2d 23h 44m</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="3" t="inlineStr">
+        <is>
+          <t>TKT1339133</t>
+        </is>
+      </c>
+      <c r="B44" s="3" t="inlineStr">
+        <is>
+          <t>Chalachitra Chautari pvt.ltd</t>
+        </is>
+      </c>
+      <c r="C44" s="3" t="inlineStr">
+        <is>
+          <t>Slow Internet Connection</t>
+        </is>
+      </c>
+      <c r="D44" s="3" t="inlineStr">
+        <is>
+          <t>Video content is Buffering</t>
+        </is>
+      </c>
+      <c r="E44" s="3" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="F44" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Completed)</t>
+        </is>
+      </c>
+      <c r="G44" s="3" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="H44" s="3" t="inlineStr">
+        <is>
+          <t>Case : slow issue  has been updated by Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="I44" s="3" t="inlineStr">
+        <is>
+          <t>23 Sep 2026 02:21:55 PM</t>
+        </is>
+      </c>
+      <c r="J44" s="3" t="inlineStr">
+        <is>
+          <t>19 Sep 2026 05:49:47 PM</t>
+        </is>
+      </c>
+      <c r="K44" s="3" t="inlineStr">
+        <is>
+          <t>23 Sep 2026 02:21:55 PM</t>
+        </is>
+      </c>
+      <c r="L44" s="3" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="M44" s="3" t="inlineStr">
+        <is>
+          <t>3d 20h 32m</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="5" t="inlineStr">
+        <is>
           <t>TKT1343230</t>
         </is>
       </c>
-      <c r="B43" s="5" t="inlineStr">
+      <c r="B45" s="5" t="inlineStr">
         <is>
           <t>Bikesh Shrestha</t>
         </is>
       </c>
-      <c r="C43" s="5" t="inlineStr">
+      <c r="C45" s="5" t="inlineStr">
         <is>
           <t>General / Other Issues</t>
         </is>
       </c>
-      <c r="D43" s="5" t="inlineStr">
+      <c r="D45" s="5" t="inlineStr">
         <is>
           <t>Router Upgrade  Wi-Fi 6</t>
         </is>
       </c>
-      <c r="E43" s="5" t="inlineStr">
+      <c r="E45" s="5" t="inlineStr">
         <is>
           <t>Completed</t>
         </is>
       </c>
-      <c r="F43" s="5" t="inlineStr">
+      <c r="F45" s="5" t="inlineStr">
         <is>
           <t>Completed (Completed)</t>
         </is>
       </c>
-      <c r="G43" s="5" t="inlineStr">
+      <c r="G45" s="5" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="H45" s="5" t="inlineStr">
         <is>
           <t>Case : wifi 6  has been updated by Sabin Giri</t>
         </is>
       </c>
-      <c r="H43" s="5" t="inlineStr">
-        <is>
-          <t>Case : wifi 6  has been updated by Sabin Giri</t>
-        </is>
-      </c>
-      <c r="I43" s="5" t="inlineStr">
+      <c r="I45" s="5" t="inlineStr">
         <is>
           <t>23 Sep 2026 02:41:26 PM</t>
         </is>
       </c>
-      <c r="J43" s="5" t="inlineStr">
+      <c r="J45" s="5" t="inlineStr">
         <is>
           <t>23 Sep 2026 07:43:57 AM</t>
         </is>
       </c>
-      <c r="K43" s="5" t="inlineStr">
+      <c r="K45" s="5" t="inlineStr">
         <is>
           <t>23 Sep 2026 02:41:26 PM</t>
         </is>
       </c>
-      <c r="L43" s="5" t="inlineStr">
+      <c r="L45" s="5" t="inlineStr">
         <is>
           <t>0m</t>
         </is>
       </c>
-      <c r="M43" s="5" t="inlineStr">
+      <c r="M45" s="5" t="inlineStr">
         <is>
           <t>6h 57m</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="3" t="inlineStr">
+        <is>
+          <t>TKT1342466</t>
+        </is>
+      </c>
+      <c r="B46" s="3" t="inlineStr">
+        <is>
+          <t>Dharmesh Maharjan</t>
+        </is>
+      </c>
+      <c r="C46" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="D46" s="3" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="E46" s="3" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="F46" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Completed)</t>
+        </is>
+      </c>
+      <c r="G46" s="3" t="inlineStr">
+        <is>
+          <t>Case : Wi-Fi 6  has been updated by Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="H46" s="3" t="inlineStr">
+        <is>
+          <t>Case : Wi-Fi 6  has been updated by Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="I46" s="3" t="inlineStr">
+        <is>
+          <t>23 Sep 2026 02:53:32 PM</t>
+        </is>
+      </c>
+      <c r="J46" s="3" t="inlineStr">
+        <is>
+          <t>22 Sep 2026 01:51:09 PM</t>
+        </is>
+      </c>
+      <c r="K46" s="3" t="inlineStr">
+        <is>
+          <t>23 Sep 2026 02:53:32 PM</t>
+        </is>
+      </c>
+      <c r="L46" s="3" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="M46" s="3" t="inlineStr">
+        <is>
+          <t>1d 1h 2m</t>
         </is>
       </c>
     </row>

--- a/audit_report_ALL_TEAM_23_Sep_2026.xlsx
+++ b/audit_report_ALL_TEAM_23_Sep_2026.xlsx
@@ -529,7 +529,7 @@
     <col width="27" customWidth="1" min="41" max="41"/>
     <col width="12" customWidth="1" min="42" max="42"/>
     <col width="17" customWidth="1" min="43" max="43"/>
-    <col width="40" customWidth="1" min="44" max="44"/>
+    <col width="34" customWidth="1" min="44" max="44"/>
     <col width="34" customWidth="1" min="45" max="45"/>
     <col width="33" customWidth="1" min="46" max="46"/>
     <col width="32" customWidth="1" min="47" max="47"/>
@@ -5261,10 +5261,8 @@
           <t>Dharmesh Maharjan</t>
         </is>
       </c>
-      <c r="O24" s="3" t="inlineStr">
-        <is>
-          <t>9869862918</t>
-        </is>
+      <c r="O24" s="3" t="n">
+        <v>9869862918</v>
       </c>
       <c r="P24" s="3" t="inlineStr">
         <is>
@@ -5299,10 +5297,8 @@
           <t>Active</t>
         </is>
       </c>
-      <c r="Y24" s="3" t="inlineStr">
-        <is>
-          <t>27.69889</t>
-        </is>
+      <c r="Y24" s="3" t="n">
+        <v>27.69889</v>
       </c>
       <c r="Z24" s="3" t="inlineStr">
         <is>
@@ -5358,25 +5354,21 @@
           <t>Chandramani Tharu</t>
         </is>
       </c>
-      <c r="AN24" s="3" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
+      <c r="AN24" s="3" t="n">
+        <v>6</v>
       </c>
       <c r="AO24" s="3" t="inlineStr">
         <is>
           <t>CDB266</t>
         </is>
       </c>
-      <c r="AP24" s="3" t="inlineStr">
-        <is>
-          <t>85.30064</t>
-        </is>
+      <c r="AP24" s="3" t="n">
+        <v>85.30064</v>
       </c>
       <c r="AQ24" s="3" t="inlineStr"/>
       <c r="AR24" s="3" t="inlineStr">
         <is>
-          <t>Case : Wi-Fi 6  has been updated by Chandramani Tharu</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="AS24" s="3" t="inlineStr">
@@ -5528,7 +5520,7 @@
     <col width="40" customWidth="1" min="4" max="4"/>
     <col width="19" customWidth="1" min="5" max="5"/>
     <col width="25" customWidth="1" min="6" max="6"/>
-    <col width="45" customWidth="1" min="7" max="7"/>
+    <col width="35" customWidth="1" min="7" max="7"/>
     <col width="45" customWidth="1" min="8" max="8"/>
     <col width="27" customWidth="1" min="9" max="9"/>
     <col width="27" customWidth="1" min="10" max="10"/>
@@ -7179,7 +7171,7 @@
       </c>
       <c r="G46" s="3" t="inlineStr">
         <is>
-          <t>Case : Wi-Fi 6  has been updated by Chandramani Tharu</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="H46" s="3" t="inlineStr">

--- a/audit_report_ALL_TEAM_23_Sep_2026.xlsx
+++ b/audit_report_ALL_TEAM_23_Sep_2026.xlsx
@@ -483,7 +483,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AW25"/>
+  <dimension ref="A1:AW30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="23" customWidth="1" min="1" max="1"/>
@@ -5500,6 +5500,521 @@
         </is>
       </c>
     </row>
+    <row r="26">
+      <c r="A26" s="3" t="inlineStr">
+        <is>
+          <t>Rajesh Maharjan</t>
+        </is>
+      </c>
+      <c r="B26" s="3" t="inlineStr">
+        <is>
+          <t>23 Sep 2026 3:10 PM</t>
+        </is>
+      </c>
+      <c r="C26" s="3" t="inlineStr">
+        <is>
+          <t>/Oi+2zlne73U37ZA62PktA==</t>
+        </is>
+      </c>
+      <c r="D26" s="3" t="inlineStr">
+        <is>
+          <t>Rajesh Maharjan</t>
+        </is>
+      </c>
+      <c r="E26" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F26" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G26" s="3" t="inlineStr"/>
+      <c r="H26" s="3" t="inlineStr">
+        <is>
+          <t>Case : WIFi 6  has been updated by Rajesh Maharjan</t>
+        </is>
+      </c>
+      <c r="I26" s="3" t="inlineStr"/>
+      <c r="J26" s="3" t="inlineStr"/>
+      <c r="K26" s="3" t="inlineStr"/>
+      <c r="L26" s="3" t="inlineStr"/>
+      <c r="M26" s="3" t="inlineStr"/>
+      <c r="N26" s="3" t="inlineStr"/>
+      <c r="O26" s="3" t="inlineStr"/>
+      <c r="P26" s="3" t="inlineStr"/>
+      <c r="Q26" s="3" t="inlineStr"/>
+      <c r="R26" s="3" t="inlineStr"/>
+      <c r="S26" s="3" t="inlineStr"/>
+      <c r="T26" s="3" t="inlineStr"/>
+      <c r="U26" s="3" t="inlineStr"/>
+      <c r="V26" s="3" t="inlineStr"/>
+      <c r="W26" s="3" t="inlineStr"/>
+      <c r="X26" s="3" t="inlineStr"/>
+      <c r="Y26" s="3" t="inlineStr"/>
+      <c r="Z26" s="3" t="inlineStr"/>
+      <c r="AA26" s="3" t="inlineStr"/>
+      <c r="AB26" s="3" t="inlineStr"/>
+      <c r="AC26" s="3" t="inlineStr"/>
+      <c r="AD26" s="3" t="inlineStr"/>
+      <c r="AE26" s="3" t="inlineStr"/>
+      <c r="AF26" s="3" t="inlineStr"/>
+      <c r="AG26" s="3" t="inlineStr"/>
+      <c r="AH26" s="3" t="inlineStr"/>
+      <c r="AI26" s="3" t="inlineStr"/>
+      <c r="AJ26" s="3" t="inlineStr"/>
+      <c r="AK26" s="3" t="inlineStr"/>
+      <c r="AL26" s="3" t="inlineStr"/>
+      <c r="AM26" s="3" t="inlineStr"/>
+      <c r="AN26" s="3" t="inlineStr"/>
+      <c r="AO26" s="3" t="inlineStr"/>
+      <c r="AP26" s="3" t="inlineStr"/>
+      <c r="AQ26" s="3" t="inlineStr"/>
+      <c r="AR26" s="3" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="AS26" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="AT26" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="AU26" s="3" t="inlineStr">
+        <is>
+          <t>Other / In Progress (nan)</t>
+        </is>
+      </c>
+      <c r="AV26" s="3" t="inlineStr">
+        <is>
+          <t>Case : WIFi 6  has been updated by Rajesh Maharjan</t>
+        </is>
+      </c>
+      <c r="AW26" s="3" t="inlineStr">
+        <is>
+          <t>WiFi 6 Upgrade</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="3" t="inlineStr">
+        <is>
+          <t>Sabin Giri</t>
+        </is>
+      </c>
+      <c r="B27" s="3" t="inlineStr">
+        <is>
+          <t>23 Sep 2026 3:23 PM</t>
+        </is>
+      </c>
+      <c r="C27" s="3" t="inlineStr">
+        <is>
+          <t>WGnmUJF06LTlUriJ5DeDBQ==</t>
+        </is>
+      </c>
+      <c r="D27" s="3" t="inlineStr">
+        <is>
+          <t>Sabin Giri</t>
+        </is>
+      </c>
+      <c r="E27" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F27" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G27" s="3" t="inlineStr"/>
+      <c r="H27" s="3" t="inlineStr">
+        <is>
+          <t>Case : no light blinking  has been updated by Sabin Giri</t>
+        </is>
+      </c>
+      <c r="I27" s="3" t="inlineStr"/>
+      <c r="J27" s="3" t="inlineStr"/>
+      <c r="K27" s="3" t="inlineStr"/>
+      <c r="L27" s="3" t="inlineStr"/>
+      <c r="M27" s="3" t="inlineStr"/>
+      <c r="N27" s="3" t="inlineStr"/>
+      <c r="O27" s="3" t="inlineStr"/>
+      <c r="P27" s="3" t="inlineStr"/>
+      <c r="Q27" s="3" t="inlineStr"/>
+      <c r="R27" s="3" t="inlineStr"/>
+      <c r="S27" s="3" t="inlineStr"/>
+      <c r="T27" s="3" t="inlineStr"/>
+      <c r="U27" s="3" t="inlineStr"/>
+      <c r="V27" s="3" t="inlineStr"/>
+      <c r="W27" s="3" t="inlineStr"/>
+      <c r="X27" s="3" t="inlineStr"/>
+      <c r="Y27" s="3" t="inlineStr"/>
+      <c r="Z27" s="3" t="inlineStr"/>
+      <c r="AA27" s="3" t="inlineStr"/>
+      <c r="AB27" s="3" t="inlineStr"/>
+      <c r="AC27" s="3" t="inlineStr"/>
+      <c r="AD27" s="3" t="inlineStr"/>
+      <c r="AE27" s="3" t="inlineStr"/>
+      <c r="AF27" s="3" t="inlineStr"/>
+      <c r="AG27" s="3" t="inlineStr"/>
+      <c r="AH27" s="3" t="inlineStr"/>
+      <c r="AI27" s="3" t="inlineStr"/>
+      <c r="AJ27" s="3" t="inlineStr"/>
+      <c r="AK27" s="3" t="inlineStr"/>
+      <c r="AL27" s="3" t="inlineStr"/>
+      <c r="AM27" s="3" t="inlineStr"/>
+      <c r="AN27" s="3" t="inlineStr"/>
+      <c r="AO27" s="3" t="inlineStr"/>
+      <c r="AP27" s="3" t="inlineStr"/>
+      <c r="AQ27" s="3" t="inlineStr"/>
+      <c r="AR27" s="3" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="AS27" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="AT27" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="AU27" s="3" t="inlineStr">
+        <is>
+          <t>Other / In Progress (nan)</t>
+        </is>
+      </c>
+      <c r="AV27" s="3" t="inlineStr">
+        <is>
+          <t>Case : no light blinking  has been updated by Sabin Giri</t>
+        </is>
+      </c>
+      <c r="AW27" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="3" t="inlineStr">
+        <is>
+          <t>Sabin Giri</t>
+        </is>
+      </c>
+      <c r="B28" s="3" t="inlineStr">
+        <is>
+          <t>23 Sep 2026 3:09 PM</t>
+        </is>
+      </c>
+      <c r="C28" s="3" t="inlineStr">
+        <is>
+          <t>WGnmUJF06LTlUriJ5DeDBQ==</t>
+        </is>
+      </c>
+      <c r="D28" s="3" t="inlineStr">
+        <is>
+          <t>Sabin Giri</t>
+        </is>
+      </c>
+      <c r="E28" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F28" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G28" s="3" t="inlineStr"/>
+      <c r="H28" s="3" t="inlineStr">
+        <is>
+          <t>Case : For upgradation to wifi6   has been updated by Sabin Giri</t>
+        </is>
+      </c>
+      <c r="I28" s="3" t="inlineStr"/>
+      <c r="J28" s="3" t="inlineStr"/>
+      <c r="K28" s="3" t="inlineStr"/>
+      <c r="L28" s="3" t="inlineStr"/>
+      <c r="M28" s="3" t="inlineStr"/>
+      <c r="N28" s="3" t="inlineStr"/>
+      <c r="O28" s="3" t="inlineStr"/>
+      <c r="P28" s="3" t="inlineStr"/>
+      <c r="Q28" s="3" t="inlineStr"/>
+      <c r="R28" s="3" t="inlineStr"/>
+      <c r="S28" s="3" t="inlineStr"/>
+      <c r="T28" s="3" t="inlineStr"/>
+      <c r="U28" s="3" t="inlineStr"/>
+      <c r="V28" s="3" t="inlineStr"/>
+      <c r="W28" s="3" t="inlineStr"/>
+      <c r="X28" s="3" t="inlineStr"/>
+      <c r="Y28" s="3" t="inlineStr"/>
+      <c r="Z28" s="3" t="inlineStr"/>
+      <c r="AA28" s="3" t="inlineStr"/>
+      <c r="AB28" s="3" t="inlineStr"/>
+      <c r="AC28" s="3" t="inlineStr"/>
+      <c r="AD28" s="3" t="inlineStr"/>
+      <c r="AE28" s="3" t="inlineStr"/>
+      <c r="AF28" s="3" t="inlineStr"/>
+      <c r="AG28" s="3" t="inlineStr"/>
+      <c r="AH28" s="3" t="inlineStr"/>
+      <c r="AI28" s="3" t="inlineStr"/>
+      <c r="AJ28" s="3" t="inlineStr"/>
+      <c r="AK28" s="3" t="inlineStr"/>
+      <c r="AL28" s="3" t="inlineStr"/>
+      <c r="AM28" s="3" t="inlineStr"/>
+      <c r="AN28" s="3" t="inlineStr"/>
+      <c r="AO28" s="3" t="inlineStr"/>
+      <c r="AP28" s="3" t="inlineStr"/>
+      <c r="AQ28" s="3" t="inlineStr"/>
+      <c r="AR28" s="3" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="AS28" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="AT28" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="AU28" s="3" t="inlineStr">
+        <is>
+          <t>Other / In Progress (nan)</t>
+        </is>
+      </c>
+      <c r="AV28" s="3" t="inlineStr">
+        <is>
+          <t>Case : For upgradation to wifi6   has been updated by Sabin Giri</t>
+        </is>
+      </c>
+      <c r="AW28" s="3" t="inlineStr">
+        <is>
+          <t>WiFi 6 Upgrade</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="3" t="inlineStr">
+        <is>
+          <t>Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="B29" s="3" t="inlineStr">
+        <is>
+          <t>23 Sep 2026 3:09 PM</t>
+        </is>
+      </c>
+      <c r="C29" s="3" t="inlineStr">
+        <is>
+          <t>Zg1bIUI+iSmQ1fi360NaxA==</t>
+        </is>
+      </c>
+      <c r="D29" s="3" t="inlineStr">
+        <is>
+          <t>Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="E29" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F29" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G29" s="3" t="inlineStr"/>
+      <c r="H29" s="3" t="inlineStr">
+        <is>
+          <t>Case : no internet  has been updated by Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="I29" s="3" t="inlineStr"/>
+      <c r="J29" s="3" t="inlineStr"/>
+      <c r="K29" s="3" t="inlineStr"/>
+      <c r="L29" s="3" t="inlineStr"/>
+      <c r="M29" s="3" t="inlineStr"/>
+      <c r="N29" s="3" t="inlineStr"/>
+      <c r="O29" s="3" t="inlineStr"/>
+      <c r="P29" s="3" t="inlineStr"/>
+      <c r="Q29" s="3" t="inlineStr"/>
+      <c r="R29" s="3" t="inlineStr"/>
+      <c r="S29" s="3" t="inlineStr"/>
+      <c r="T29" s="3" t="inlineStr"/>
+      <c r="U29" s="3" t="inlineStr"/>
+      <c r="V29" s="3" t="inlineStr"/>
+      <c r="W29" s="3" t="inlineStr"/>
+      <c r="X29" s="3" t="inlineStr"/>
+      <c r="Y29" s="3" t="inlineStr"/>
+      <c r="Z29" s="3" t="inlineStr"/>
+      <c r="AA29" s="3" t="inlineStr"/>
+      <c r="AB29" s="3" t="inlineStr"/>
+      <c r="AC29" s="3" t="inlineStr"/>
+      <c r="AD29" s="3" t="inlineStr"/>
+      <c r="AE29" s="3" t="inlineStr"/>
+      <c r="AF29" s="3" t="inlineStr"/>
+      <c r="AG29" s="3" t="inlineStr"/>
+      <c r="AH29" s="3" t="inlineStr"/>
+      <c r="AI29" s="3" t="inlineStr"/>
+      <c r="AJ29" s="3" t="inlineStr"/>
+      <c r="AK29" s="3" t="inlineStr"/>
+      <c r="AL29" s="3" t="inlineStr"/>
+      <c r="AM29" s="3" t="inlineStr"/>
+      <c r="AN29" s="3" t="inlineStr"/>
+      <c r="AO29" s="3" t="inlineStr"/>
+      <c r="AP29" s="3" t="inlineStr"/>
+      <c r="AQ29" s="3" t="inlineStr"/>
+      <c r="AR29" s="3" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="AS29" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="AT29" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="AU29" s="3" t="inlineStr">
+        <is>
+          <t>Other / In Progress (nan)</t>
+        </is>
+      </c>
+      <c r="AV29" s="3" t="inlineStr">
+        <is>
+          <t>Case : no internet  has been updated by Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="AW29" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="3" t="inlineStr">
+        <is>
+          <t>Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="B30" s="3" t="inlineStr">
+        <is>
+          <t>23 Sep 2026 3:08 PM</t>
+        </is>
+      </c>
+      <c r="C30" s="3" t="inlineStr">
+        <is>
+          <t>Zg1bIUI+iSmQ1fi360NaxA==</t>
+        </is>
+      </c>
+      <c r="D30" s="3" t="inlineStr">
+        <is>
+          <t>Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="E30" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F30" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G30" s="3" t="inlineStr"/>
+      <c r="H30" s="3" t="inlineStr">
+        <is>
+          <t>Case : no internet  has been updated by Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="I30" s="3" t="inlineStr"/>
+      <c r="J30" s="3" t="inlineStr"/>
+      <c r="K30" s="3" t="inlineStr"/>
+      <c r="L30" s="3" t="inlineStr"/>
+      <c r="M30" s="3" t="inlineStr"/>
+      <c r="N30" s="3" t="inlineStr"/>
+      <c r="O30" s="3" t="inlineStr"/>
+      <c r="P30" s="3" t="inlineStr"/>
+      <c r="Q30" s="3" t="inlineStr"/>
+      <c r="R30" s="3" t="inlineStr"/>
+      <c r="S30" s="3" t="inlineStr"/>
+      <c r="T30" s="3" t="inlineStr"/>
+      <c r="U30" s="3" t="inlineStr"/>
+      <c r="V30" s="3" t="inlineStr"/>
+      <c r="W30" s="3" t="inlineStr"/>
+      <c r="X30" s="3" t="inlineStr"/>
+      <c r="Y30" s="3" t="inlineStr"/>
+      <c r="Z30" s="3" t="inlineStr"/>
+      <c r="AA30" s="3" t="inlineStr"/>
+      <c r="AB30" s="3" t="inlineStr"/>
+      <c r="AC30" s="3" t="inlineStr"/>
+      <c r="AD30" s="3" t="inlineStr"/>
+      <c r="AE30" s="3" t="inlineStr"/>
+      <c r="AF30" s="3" t="inlineStr"/>
+      <c r="AG30" s="3" t="inlineStr"/>
+      <c r="AH30" s="3" t="inlineStr"/>
+      <c r="AI30" s="3" t="inlineStr"/>
+      <c r="AJ30" s="3" t="inlineStr"/>
+      <c r="AK30" s="3" t="inlineStr"/>
+      <c r="AL30" s="3" t="inlineStr"/>
+      <c r="AM30" s="3" t="inlineStr"/>
+      <c r="AN30" s="3" t="inlineStr"/>
+      <c r="AO30" s="3" t="inlineStr"/>
+      <c r="AP30" s="3" t="inlineStr"/>
+      <c r="AQ30" s="3" t="inlineStr"/>
+      <c r="AR30" s="3" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="AS30" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="AT30" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="AU30" s="3" t="inlineStr">
+        <is>
+          <t>Other / In Progress (nan)</t>
+        </is>
+      </c>
+      <c r="AV30" s="3" t="inlineStr">
+        <is>
+          <t>Case : no internet  has been updated by Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="AW30" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -5548,7 +6063,7 @@
         </is>
       </c>
       <c r="B2" s="3" t="n">
-        <v>24</v>
+        <v>29</v>
       </c>
     </row>
     <row r="3">
@@ -5569,7 +6084,7 @@
       </c>
       <c r="B4" s="3" t="inlineStr">
         <is>
-          <t>75.0%</t>
+          <t>62.1%</t>
         </is>
       </c>
     </row>

--- a/audit_report_ALL_TEAM_23_Sep_2026.xlsx
+++ b/audit_report_ALL_TEAM_23_Sep_2026.xlsx
@@ -483,7 +483,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AW30"/>
+  <dimension ref="A1:AW33"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="23" customWidth="1" min="1" max="1"/>
@@ -529,7 +529,7 @@
     <col width="27" customWidth="1" min="41" max="41"/>
     <col width="12" customWidth="1" min="42" max="42"/>
     <col width="17" customWidth="1" min="43" max="43"/>
-    <col width="34" customWidth="1" min="44" max="44"/>
+    <col width="40" customWidth="1" min="44" max="44"/>
     <col width="34" customWidth="1" min="45" max="45"/>
     <col width="33" customWidth="1" min="46" max="46"/>
     <col width="32" customWidth="1" min="47" max="47"/>
@@ -6015,6 +6015,615 @@
         </is>
       </c>
     </row>
+    <row r="31">
+      <c r="A31" s="3" t="inlineStr">
+        <is>
+          <t>Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="B31" s="3" t="inlineStr">
+        <is>
+          <t>23 Sep 2026 3:46 PM</t>
+        </is>
+      </c>
+      <c r="C31" s="3" t="inlineStr">
+        <is>
+          <t>Zg1bIUI+iSmQ1fi360NaxA==</t>
+        </is>
+      </c>
+      <c r="D31" s="3" t="inlineStr">
+        <is>
+          <t>Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="E31" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F31" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G31" s="3" t="inlineStr"/>
+      <c r="H31" s="3" t="inlineStr">
+        <is>
+          <t>Case : IPTV  Isssue  has been updated by Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="I31" s="3" t="inlineStr">
+        <is>
+          <t>IPTV  Isssue</t>
+        </is>
+      </c>
+      <c r="J31" s="3" t="inlineStr">
+        <is>
+          <t>TKT1342232</t>
+        </is>
+      </c>
+      <c r="K31" s="3" t="inlineStr">
+        <is>
+          <t>Dipendra khanal</t>
+        </is>
+      </c>
+      <c r="L31" s="3" t="inlineStr">
+        <is>
+          <t>Closed</t>
+        </is>
+      </c>
+      <c r="M31" s="3" t="inlineStr">
+        <is>
+          <t>Phone</t>
+        </is>
+      </c>
+      <c r="N31" s="3" t="inlineStr">
+        <is>
+          <t>Dipendra khanal</t>
+        </is>
+      </c>
+      <c r="O31" s="3" t="inlineStr">
+        <is>
+          <t>9841410905</t>
+        </is>
+      </c>
+      <c r="P31" s="3" t="inlineStr">
+        <is>
+          <t>IPTV Related Issues</t>
+        </is>
+      </c>
+      <c r="Q31" s="3" t="inlineStr"/>
+      <c r="R31" s="3" t="inlineStr">
+        <is>
+          <t>22 Sep 2026 08:25:10 PM</t>
+        </is>
+      </c>
+      <c r="S31" s="3" t="inlineStr"/>
+      <c r="T31" s="3" t="inlineStr"/>
+      <c r="U31" s="3" t="inlineStr">
+        <is>
+          <t>9841410905</t>
+        </is>
+      </c>
+      <c r="V31" s="3" t="inlineStr">
+        <is>
+          <t>22 Sep 2026 11:24:09 AM</t>
+        </is>
+      </c>
+      <c r="W31" s="3" t="inlineStr">
+        <is>
+          <t>23 Sep 2026 03:46:01 PM</t>
+        </is>
+      </c>
+      <c r="X31" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Y31" s="3" t="inlineStr"/>
+      <c r="Z31" s="3" t="inlineStr">
+        <is>
+          <t>IPTV Related Issues</t>
+        </is>
+      </c>
+      <c r="AA31" s="3" t="inlineStr">
+        <is>
+          <t>Layer 1-</t>
+        </is>
+      </c>
+      <c r="AB31" s="3" t="inlineStr">
+        <is>
+          <t>Laxman Koirala</t>
+        </is>
+      </c>
+      <c r="AC31" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="AD31" s="3" t="inlineStr"/>
+      <c r="AE31" s="3" t="inlineStr">
+        <is>
+          <t>Kalanki, Bagmati, Central, Nepal</t>
+        </is>
+      </c>
+      <c r="AF31" s="3" t="inlineStr"/>
+      <c r="AG31" s="3" t="inlineStr">
+        <is>
+          <t>SKYCOM-Audio &amp; Video Syn Issue</t>
+        </is>
+      </c>
+      <c r="AH31" s="3" t="inlineStr"/>
+      <c r="AI31" s="3" t="inlineStr">
+        <is>
+          <t>14:21 hour</t>
+        </is>
+      </c>
+      <c r="AJ31" s="3" t="inlineStr"/>
+      <c r="AK31" s="3" t="inlineStr"/>
+      <c r="AL31" s="3" t="inlineStr">
+        <is>
+          <t>Joshna Shrestha</t>
+        </is>
+      </c>
+      <c r="AM31" s="3" t="inlineStr">
+        <is>
+          <t>Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="AN31" s="3" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AO31" s="3" t="inlineStr">
+        <is>
+          <t>3,5</t>
+        </is>
+      </c>
+      <c r="AP31" s="3" t="inlineStr"/>
+      <c r="AQ31" s="3" t="inlineStr"/>
+      <c r="AR31" s="3" t="inlineStr">
+        <is>
+          <t>Case : IPTV  Isssue  has been updated by Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="AS31" s="3" t="inlineStr">
+        <is>
+          <t>19h 20m</t>
+        </is>
+      </c>
+      <c r="AT31" s="3" t="inlineStr">
+        <is>
+          <t>1d 4h 21m</t>
+        </is>
+      </c>
+      <c r="AU31" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Closed)</t>
+        </is>
+      </c>
+      <c r="AV31" s="3" t="inlineStr">
+        <is>
+          <t>Case : IPTV  Isssue  has been updated by Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="AW31" s="3" t="inlineStr">
+        <is>
+          <t>IPTV Issue</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="3" t="inlineStr">
+        <is>
+          <t>Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="B32" s="3" t="inlineStr">
+        <is>
+          <t>23 Sep 2026 3:45 PM</t>
+        </is>
+      </c>
+      <c r="C32" s="3" t="inlineStr">
+        <is>
+          <t>Zg1bIUI+iSmQ1fi360NaxA==</t>
+        </is>
+      </c>
+      <c r="D32" s="3" t="inlineStr">
+        <is>
+          <t>Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="E32" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F32" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G32" s="3" t="inlineStr"/>
+      <c r="H32" s="3" t="inlineStr">
+        <is>
+          <t>Case : IPTV  Isssue  has been updated by Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="I32" s="3" t="inlineStr">
+        <is>
+          <t>IPTV  Isssue</t>
+        </is>
+      </c>
+      <c r="J32" s="3" t="inlineStr">
+        <is>
+          <t>TKT1342232</t>
+        </is>
+      </c>
+      <c r="K32" s="3" t="inlineStr">
+        <is>
+          <t>Dipendra khanal</t>
+        </is>
+      </c>
+      <c r="L32" s="3" t="inlineStr">
+        <is>
+          <t>Closed</t>
+        </is>
+      </c>
+      <c r="M32" s="3" t="inlineStr">
+        <is>
+          <t>Phone</t>
+        </is>
+      </c>
+      <c r="N32" s="3" t="inlineStr">
+        <is>
+          <t>Dipendra khanal</t>
+        </is>
+      </c>
+      <c r="O32" s="3" t="inlineStr">
+        <is>
+          <t>9841410905</t>
+        </is>
+      </c>
+      <c r="P32" s="3" t="inlineStr">
+        <is>
+          <t>IPTV Related Issues</t>
+        </is>
+      </c>
+      <c r="Q32" s="3" t="inlineStr"/>
+      <c r="R32" s="3" t="inlineStr">
+        <is>
+          <t>22 Sep 2026 08:25:10 PM</t>
+        </is>
+      </c>
+      <c r="S32" s="3" t="inlineStr"/>
+      <c r="T32" s="3" t="inlineStr"/>
+      <c r="U32" s="3" t="inlineStr">
+        <is>
+          <t>9841410905</t>
+        </is>
+      </c>
+      <c r="V32" s="3" t="inlineStr">
+        <is>
+          <t>22 Sep 2026 11:24:09 AM</t>
+        </is>
+      </c>
+      <c r="W32" s="3" t="inlineStr">
+        <is>
+          <t>23 Sep 2026 03:46:01 PM</t>
+        </is>
+      </c>
+      <c r="X32" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Y32" s="3" t="inlineStr"/>
+      <c r="Z32" s="3" t="inlineStr">
+        <is>
+          <t>IPTV Related Issues</t>
+        </is>
+      </c>
+      <c r="AA32" s="3" t="inlineStr">
+        <is>
+          <t>Layer 1-</t>
+        </is>
+      </c>
+      <c r="AB32" s="3" t="inlineStr">
+        <is>
+          <t>Laxman Koirala</t>
+        </is>
+      </c>
+      <c r="AC32" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="AD32" s="3" t="inlineStr"/>
+      <c r="AE32" s="3" t="inlineStr">
+        <is>
+          <t>Kalanki, Bagmati, Central, Nepal</t>
+        </is>
+      </c>
+      <c r="AF32" s="3" t="inlineStr"/>
+      <c r="AG32" s="3" t="inlineStr">
+        <is>
+          <t>SKYCOM-Audio &amp; Video Syn Issue</t>
+        </is>
+      </c>
+      <c r="AH32" s="3" t="inlineStr"/>
+      <c r="AI32" s="3" t="inlineStr">
+        <is>
+          <t>14:21 hour</t>
+        </is>
+      </c>
+      <c r="AJ32" s="3" t="inlineStr"/>
+      <c r="AK32" s="3" t="inlineStr"/>
+      <c r="AL32" s="3" t="inlineStr">
+        <is>
+          <t>Joshna Shrestha</t>
+        </is>
+      </c>
+      <c r="AM32" s="3" t="inlineStr">
+        <is>
+          <t>Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="AN32" s="3" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AO32" s="3" t="inlineStr">
+        <is>
+          <t>3,5</t>
+        </is>
+      </c>
+      <c r="AP32" s="3" t="inlineStr"/>
+      <c r="AQ32" s="3" t="inlineStr"/>
+      <c r="AR32" s="3" t="inlineStr">
+        <is>
+          <t>Case : IPTV  Isssue  has been updated by Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="AS32" s="3" t="inlineStr">
+        <is>
+          <t>19h 20m</t>
+        </is>
+      </c>
+      <c r="AT32" s="3" t="inlineStr">
+        <is>
+          <t>1d 4h 21m</t>
+        </is>
+      </c>
+      <c r="AU32" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Closed)</t>
+        </is>
+      </c>
+      <c r="AV32" s="3" t="inlineStr">
+        <is>
+          <t>Case : IPTV  Isssue  has been updated by Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="AW32" s="3" t="inlineStr">
+        <is>
+          <t>IPTV Issue</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="3" t="inlineStr">
+        <is>
+          <t>Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="B33" s="3" t="inlineStr">
+        <is>
+          <t>23 Sep 2026 3:21 PM</t>
+        </is>
+      </c>
+      <c r="C33" s="3" t="inlineStr">
+        <is>
+          <t>atwz5SElGeKMz8qxsp3b6c34SBAfIMR+</t>
+        </is>
+      </c>
+      <c r="D33" s="3" t="inlineStr">
+        <is>
+          <t>Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="E33" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F33" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G33" s="3" t="inlineStr"/>
+      <c r="H33" s="3" t="inlineStr">
+        <is>
+          <t>Case : For upgradation to wifi6   has been updated by Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="I33" s="3" t="inlineStr">
+        <is>
+          <t>For upgradation to wifi6</t>
+        </is>
+      </c>
+      <c r="J33" s="3" t="inlineStr">
+        <is>
+          <t>TKT1343067</t>
+        </is>
+      </c>
+      <c r="K33" s="3" t="inlineStr">
+        <is>
+          <t>Aaryan Kumar Jha</t>
+        </is>
+      </c>
+      <c r="L33" s="3" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="M33" s="3" t="inlineStr">
+        <is>
+          <t>Phone</t>
+        </is>
+      </c>
+      <c r="N33" s="3" t="inlineStr">
+        <is>
+          <t>Aaryan Kumar Jha</t>
+        </is>
+      </c>
+      <c r="O33" s="3" t="inlineStr">
+        <is>
+          <t>9841597524</t>
+        </is>
+      </c>
+      <c r="P33" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="Q33" s="3" t="inlineStr"/>
+      <c r="R33" s="3" t="inlineStr">
+        <is>
+          <t>23 Sep 2026 03:21:49 PM</t>
+        </is>
+      </c>
+      <c r="S33" s="3" t="inlineStr"/>
+      <c r="T33" s="3" t="inlineStr"/>
+      <c r="U33" s="3" t="inlineStr">
+        <is>
+          <t>9801123058</t>
+        </is>
+      </c>
+      <c r="V33" s="3" t="inlineStr">
+        <is>
+          <t>22 Sep 2026 08:58:59 PM</t>
+        </is>
+      </c>
+      <c r="W33" s="3" t="inlineStr">
+        <is>
+          <t>23 Sep 2026 03:21:49 PM</t>
+        </is>
+      </c>
+      <c r="X33" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Y33" s="3" t="inlineStr">
+        <is>
+          <t>27.69001</t>
+        </is>
+      </c>
+      <c r="Z33" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="AA33" s="3" t="inlineStr">
+        <is>
+          <t>Layer 1-User</t>
+        </is>
+      </c>
+      <c r="AB33" s="3" t="inlineStr">
+        <is>
+          <t>L1  Support</t>
+        </is>
+      </c>
+      <c r="AC33" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="AD33" s="3" t="inlineStr"/>
+      <c r="AE33" s="3" t="inlineStr">
+        <is>
+          <t>Radiant Readers' Acadmey,M8Q4+V44, Lalitpur Lalitpur Municipality Lalitpur, Lalitpur, Nepal, Nepal</t>
+        </is>
+      </c>
+      <c r="AF33" s="3" t="inlineStr">
+        <is>
+          <t>gha652589@gmail.com</t>
+        </is>
+      </c>
+      <c r="AG33" s="3" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="AH33" s="3" t="inlineStr"/>
+      <c r="AI33" s="3" t="inlineStr">
+        <is>
+          <t>05:21 hour</t>
+        </is>
+      </c>
+      <c r="AJ33" s="3" t="inlineStr"/>
+      <c r="AK33" s="3" t="inlineStr"/>
+      <c r="AL33" s="3" t="inlineStr">
+        <is>
+          <t>Pradeep Yadav</t>
+        </is>
+      </c>
+      <c r="AM33" s="3" t="inlineStr">
+        <is>
+          <t>Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="AN33" s="3" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AO33" s="3" t="inlineStr">
+        <is>
+          <t>1,9</t>
+        </is>
+      </c>
+      <c r="AP33" s="3" t="inlineStr">
+        <is>
+          <t>85.30437</t>
+        </is>
+      </c>
+      <c r="AQ33" s="3" t="inlineStr"/>
+      <c r="AR33" s="3" t="inlineStr">
+        <is>
+          <t>Case : For upgradation to wifi6   has been updated by Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="AS33" s="3" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="AT33" s="3" t="inlineStr">
+        <is>
+          <t>18h 22m</t>
+        </is>
+      </c>
+      <c r="AU33" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Completed)</t>
+        </is>
+      </c>
+      <c r="AV33" s="3" t="inlineStr">
+        <is>
+          <t>Case : For upgradation to wifi6   has been updated by Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="AW33" s="3" t="inlineStr">
+        <is>
+          <t>WiFi 6 Upgrade</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -6026,7 +6635,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M46"/>
+  <dimension ref="A1:M51"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="45" customWidth="1" min="1" max="1"/>
@@ -6035,7 +6644,7 @@
     <col width="40" customWidth="1" min="4" max="4"/>
     <col width="19" customWidth="1" min="5" max="5"/>
     <col width="25" customWidth="1" min="6" max="6"/>
-    <col width="35" customWidth="1" min="7" max="7"/>
+    <col width="45" customWidth="1" min="7" max="7"/>
     <col width="45" customWidth="1" min="8" max="8"/>
     <col width="27" customWidth="1" min="9" max="9"/>
     <col width="27" customWidth="1" min="10" max="10"/>
@@ -6063,7 +6672,7 @@
         </is>
       </c>
       <c r="B2" s="3" t="n">
-        <v>29</v>
+        <v>32</v>
       </c>
     </row>
     <row r="3">
@@ -6073,7 +6682,7 @@
         </is>
       </c>
       <c r="B3" s="5" t="n">
-        <v>18</v>
+        <v>21</v>
       </c>
     </row>
     <row r="4">
@@ -6084,7 +6693,7 @@
       </c>
       <c r="B4" s="3" t="inlineStr">
         <is>
-          <t>62.1%</t>
+          <t>65.6%</t>
         </is>
       </c>
     </row>
@@ -6096,7 +6705,7 @@
       </c>
       <c r="B5" s="5" t="inlineStr">
         <is>
-          <t>5h 51m</t>
+          <t>6h 51m</t>
         </is>
       </c>
     </row>
@@ -6108,7 +6717,7 @@
       </c>
       <c r="B6" s="3" t="inlineStr">
         <is>
-          <t>23h 19m</t>
+          <t>23h 34m</t>
         </is>
       </c>
     </row>
@@ -6149,14 +6758,14 @@
         </is>
       </c>
       <c r="B10" s="3" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C10" s="3" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="D10" s="3" t="inlineStr">
         <is>
-          <t>75.0%</t>
+          <t>76.5%</t>
         </is>
       </c>
     </row>
@@ -6181,14 +6790,14 @@
     <row r="12">
       <c r="A12" s="3" t="inlineStr">
         <is>
-          <t>No Internet Connection</t>
+          <t>IPTV Related Issues</t>
         </is>
       </c>
       <c r="B12" s="3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C12" s="3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D12" s="3" t="inlineStr">
         <is>
@@ -6199,90 +6808,85 @@
     <row r="13">
       <c r="A13" s="5" t="inlineStr">
         <is>
-          <t>Slow Internet Connection</t>
+          <t>No Internet Connection</t>
         </is>
       </c>
       <c r="B13" s="5" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C13" s="5" t="n">
         <v>1</v>
       </c>
       <c r="D13" s="5" t="inlineStr">
         <is>
-          <t>50.0%</t>
+          <t>100.0%</t>
         </is>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="3" t="inlineStr"/>
+      <c r="A14" s="3" t="inlineStr">
+        <is>
+          <t>Slow Internet Connection</t>
+        </is>
+      </c>
       <c r="B14" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="C14" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="D14" s="3" t="inlineStr">
+        <is>
+          <t>50.0%</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="5" t="inlineStr"/>
+      <c r="B15" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="C14" s="3" t="n">
+      <c r="C15" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="D14" s="3" t="inlineStr">
+      <c r="D15" s="5" t="inlineStr">
         <is>
           <t>nan%</t>
         </is>
       </c>
     </row>
-    <row r="15"/>
-    <row r="16">
-      <c r="A16" s="6" t="inlineStr">
+    <row r="16"/>
+    <row r="17">
+      <c r="A17" s="6" t="inlineStr">
         <is>
           <t>Total Tickets Breakdown by Category &amp; Sub Category</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="4" t="inlineStr">
-        <is>
-          <t>Category</t>
-        </is>
-      </c>
-      <c r="B17" s="4" t="inlineStr">
-        <is>
-          <t>Sub Category</t>
-        </is>
-      </c>
-      <c r="C17" s="4" t="inlineStr">
-        <is>
-          <t>Total Scraped Tickets</t>
-        </is>
-      </c>
-      <c r="D17" s="4" t="inlineStr">
-        <is>
-          <t>Solved / Handled Count</t>
-        </is>
-      </c>
-      <c r="E17" s="4" t="inlineStr">
-        <is>
-          <t>Solution Rate %</t>
         </is>
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="3" t="inlineStr">
-        <is>
-          <t>General / Other Issues</t>
-        </is>
-      </c>
-      <c r="B18" s="3" t="inlineStr">
-        <is>
-          <t>Query For Secondary Router /Repeater</t>
-        </is>
-      </c>
-      <c r="C18" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="D18" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="E18" s="3" t="inlineStr">
-        <is>
-          <t>100.0%</t>
+      <c r="A18" s="4" t="inlineStr">
+        <is>
+          <t>Category</t>
+        </is>
+      </c>
+      <c r="B18" s="4" t="inlineStr">
+        <is>
+          <t>Sub Category</t>
+        </is>
+      </c>
+      <c r="C18" s="4" t="inlineStr">
+        <is>
+          <t>Total Scraped Tickets</t>
+        </is>
+      </c>
+      <c r="D18" s="4" t="inlineStr">
+        <is>
+          <t>Solved / Handled Count</t>
+        </is>
+      </c>
+      <c r="E18" s="4" t="inlineStr">
+        <is>
+          <t>Solution Rate %</t>
         </is>
       </c>
     </row>
@@ -6294,18 +6898,18 @@
       </c>
       <c r="B19" s="5" t="inlineStr">
         <is>
-          <t>Router Upgrade  Wi-Fi 6</t>
+          <t>Query For Secondary Router /Repeater</t>
         </is>
       </c>
       <c r="C19" s="5" t="n">
-        <v>14</v>
+        <v>1</v>
       </c>
       <c r="D19" s="5" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="E19" s="5" t="inlineStr">
         <is>
-          <t>71.4%</t>
+          <t>100.0%</t>
         </is>
       </c>
     </row>
@@ -6317,37 +6921,37 @@
       </c>
       <c r="B20" s="3" t="inlineStr">
         <is>
-          <t>Router Upgrade Dual Band</t>
+          <t>Router Upgrade  Wi-Fi 6</t>
         </is>
       </c>
       <c r="C20" s="3" t="n">
-        <v>1</v>
+        <v>15</v>
       </c>
       <c r="D20" s="3" t="n">
-        <v>1</v>
+        <v>11</v>
       </c>
       <c r="E20" s="3" t="inlineStr">
         <is>
-          <t>100.0%</t>
+          <t>73.3%</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="5" t="inlineStr">
         <is>
-          <t>Hardware Damage / Malfunction</t>
+          <t>General / Other Issues</t>
         </is>
       </c>
       <c r="B21" s="5" t="inlineStr">
         <is>
-          <t>IPTV STB box Damage Issue</t>
+          <t>Router Upgrade Dual Band</t>
         </is>
       </c>
       <c r="C21" s="5" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D21" s="5" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E21" s="5" t="inlineStr">
         <is>
@@ -6363,14 +6967,14 @@
       </c>
       <c r="B22" s="3" t="inlineStr">
         <is>
-          <t>Router Damage Issue</t>
+          <t>IPTV STB box Damage Issue</t>
         </is>
       </c>
       <c r="C22" s="3" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D22" s="3" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E22" s="3" t="inlineStr">
         <is>
@@ -6381,12 +6985,12 @@
     <row r="23">
       <c r="A23" s="5" t="inlineStr">
         <is>
-          <t>No Internet Connection</t>
+          <t>Hardware Damage / Malfunction</t>
         </is>
       </c>
       <c r="B23" s="5" t="inlineStr">
         <is>
-          <t>Configuration Issue</t>
+          <t>Router Damage Issue</t>
         </is>
       </c>
       <c r="C23" s="5" t="n">
@@ -6404,259 +7008,171 @@
     <row r="24">
       <c r="A24" s="3" t="inlineStr">
         <is>
-          <t>Slow Internet Connection</t>
+          <t>IPTV Related Issues</t>
         </is>
       </c>
       <c r="B24" s="3" t="inlineStr">
         <is>
-          <t>Video content is Buffering</t>
+          <t>SKYCOM-Audio &amp; Video Syn Issue</t>
         </is>
       </c>
       <c r="C24" s="3" t="n">
         <v>2</v>
       </c>
       <c r="D24" s="3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E24" s="3" t="inlineStr">
         <is>
-          <t>50.0%</t>
+          <t>100.0%</t>
         </is>
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="5" t="inlineStr"/>
-      <c r="B25" s="5" t="inlineStr"/>
+      <c r="A25" s="5" t="inlineStr">
+        <is>
+          <t>No Internet Connection</t>
+        </is>
+      </c>
+      <c r="B25" s="5" t="inlineStr">
+        <is>
+          <t>Configuration Issue</t>
+        </is>
+      </c>
       <c r="C25" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="D25" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="E25" s="5" t="inlineStr">
+        <is>
+          <t>100.0%</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="3" t="inlineStr">
+        <is>
+          <t>Slow Internet Connection</t>
+        </is>
+      </c>
+      <c r="B26" s="3" t="inlineStr">
+        <is>
+          <t>Video content is Buffering</t>
+        </is>
+      </c>
+      <c r="C26" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="D26" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="E26" s="3" t="inlineStr">
+        <is>
+          <t>50.0%</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="5" t="inlineStr"/>
+      <c r="B27" s="5" t="inlineStr"/>
+      <c r="C27" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="D25" s="5" t="n">
+      <c r="D27" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="E25" s="5" t="inlineStr">
+      <c r="E27" s="5" t="inlineStr">
         <is>
           <t>nan%</t>
         </is>
       </c>
     </row>
-    <row r="26"/>
-    <row r="27">
-      <c r="A27" s="6" t="inlineStr">
+    <row r="28"/>
+    <row r="29">
+      <c r="A29" s="6" t="inlineStr">
         <is>
           <t>Detailed Solved / Handled Tickets List</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" s="4" t="inlineStr">
-        <is>
-          <t>Ticket Number</t>
-        </is>
-      </c>
-      <c r="B28" s="4" t="inlineStr">
-        <is>
-          <t>Account Name</t>
-        </is>
-      </c>
-      <c r="C28" s="4" t="inlineStr">
-        <is>
-          <t>Category</t>
-        </is>
-      </c>
-      <c r="D28" s="4" t="inlineStr">
-        <is>
-          <t>Sub Category</t>
-        </is>
-      </c>
-      <c r="E28" s="4" t="inlineStr">
-        <is>
-          <t>Status</t>
-        </is>
-      </c>
-      <c r="F28" s="4" t="inlineStr">
-        <is>
-          <t>Resolution Type</t>
-        </is>
-      </c>
-      <c r="G28" s="4" t="inlineStr">
-        <is>
-          <t>Employee Remark / Solution Note</t>
-        </is>
-      </c>
-      <c r="H28" s="4" t="inlineStr">
-        <is>
-          <t>Action / Transfer Remark</t>
-        </is>
-      </c>
-      <c r="I28" s="4" t="inlineStr">
-        <is>
-          <t>Assigned Date</t>
-        </is>
-      </c>
-      <c r="J28" s="4" t="inlineStr">
-        <is>
-          <t>Created Date</t>
-        </is>
-      </c>
-      <c r="K28" s="4" t="inlineStr">
-        <is>
-          <t>Last Modified Date</t>
-        </is>
-      </c>
-      <c r="L28" s="4" t="inlineStr">
-        <is>
-          <t>Resolution Time (From Assigned)</t>
-        </is>
-      </c>
-      <c r="M28" s="4" t="inlineStr">
-        <is>
-          <t>Resolution Time (From Created)</t>
-        </is>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" s="5" t="inlineStr">
-        <is>
-          <t>TKT1342514</t>
-        </is>
-      </c>
-      <c r="B29" s="5" t="inlineStr">
-        <is>
-          <t>Bijay Carlos Rana</t>
-        </is>
-      </c>
-      <c r="C29" s="5" t="inlineStr">
-        <is>
-          <t>General / Other Issues</t>
-        </is>
-      </c>
-      <c r="D29" s="5" t="inlineStr">
-        <is>
-          <t>Router Upgrade  Wi-Fi 6</t>
-        </is>
-      </c>
-      <c r="E29" s="5" t="inlineStr">
-        <is>
-          <t>Completed</t>
-        </is>
-      </c>
-      <c r="F29" s="5" t="inlineStr">
-        <is>
-          <t>Completed (Completed)</t>
-        </is>
-      </c>
-      <c r="G29" s="5" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
-      <c r="H29" s="5" t="inlineStr">
-        <is>
-          <t>Case : WIFI 6  has been updated by Rajesh Maharjan</t>
-        </is>
-      </c>
-      <c r="I29" s="5" t="inlineStr">
-        <is>
-          <t>23 Sep 2026 11:16:05 AM</t>
-        </is>
-      </c>
-      <c r="J29" s="5" t="inlineStr">
-        <is>
-          <t>22 Sep 2026 02:29:16 PM</t>
-        </is>
-      </c>
-      <c r="K29" s="5" t="inlineStr">
-        <is>
-          <t>23 Sep 2026 11:16:05 AM</t>
-        </is>
-      </c>
-      <c r="L29" s="5" t="inlineStr">
-        <is>
-          <t>0m</t>
-        </is>
-      </c>
-      <c r="M29" s="5" t="inlineStr">
-        <is>
-          <t>20h 46m</t>
         </is>
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="3" t="inlineStr">
-        <is>
-          <t>TKT1343394</t>
-        </is>
-      </c>
-      <c r="B30" s="3" t="inlineStr">
-        <is>
-          <t>Kaizen Business consultant</t>
-        </is>
-      </c>
-      <c r="C30" s="3" t="inlineStr">
-        <is>
-          <t>General / Other Issues</t>
-        </is>
-      </c>
-      <c r="D30" s="3" t="inlineStr">
-        <is>
-          <t>Router Upgrade  Wi-Fi 6</t>
-        </is>
-      </c>
-      <c r="E30" s="3" t="inlineStr">
-        <is>
-          <t>Completed</t>
-        </is>
-      </c>
-      <c r="F30" s="3" t="inlineStr">
-        <is>
-          <t>Completed (Completed)</t>
-        </is>
-      </c>
-      <c r="G30" s="3" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
-      <c r="H30" s="3" t="inlineStr">
-        <is>
-          <t>Case : wifi 6 router  has been updated by Sabin Giri</t>
-        </is>
-      </c>
-      <c r="I30" s="3" t="inlineStr">
-        <is>
-          <t>23 Sep 2026 12:31:18 PM</t>
-        </is>
-      </c>
-      <c r="J30" s="3" t="inlineStr">
-        <is>
-          <t>23 Sep 2026 09:53:33 AM</t>
-        </is>
-      </c>
-      <c r="K30" s="3" t="inlineStr">
-        <is>
-          <t>23 Sep 2026 12:31:18 PM</t>
-        </is>
-      </c>
-      <c r="L30" s="3" t="inlineStr">
-        <is>
-          <t>0m</t>
-        </is>
-      </c>
-      <c r="M30" s="3" t="inlineStr">
-        <is>
-          <t>2h 37m</t>
+      <c r="A30" s="4" t="inlineStr">
+        <is>
+          <t>Ticket Number</t>
+        </is>
+      </c>
+      <c r="B30" s="4" t="inlineStr">
+        <is>
+          <t>Account Name</t>
+        </is>
+      </c>
+      <c r="C30" s="4" t="inlineStr">
+        <is>
+          <t>Category</t>
+        </is>
+      </c>
+      <c r="D30" s="4" t="inlineStr">
+        <is>
+          <t>Sub Category</t>
+        </is>
+      </c>
+      <c r="E30" s="4" t="inlineStr">
+        <is>
+          <t>Status</t>
+        </is>
+      </c>
+      <c r="F30" s="4" t="inlineStr">
+        <is>
+          <t>Resolution Type</t>
+        </is>
+      </c>
+      <c r="G30" s="4" t="inlineStr">
+        <is>
+          <t>Employee Remark / Solution Note</t>
+        </is>
+      </c>
+      <c r="H30" s="4" t="inlineStr">
+        <is>
+          <t>Action / Transfer Remark</t>
+        </is>
+      </c>
+      <c r="I30" s="4" t="inlineStr">
+        <is>
+          <t>Assigned Date</t>
+        </is>
+      </c>
+      <c r="J30" s="4" t="inlineStr">
+        <is>
+          <t>Created Date</t>
+        </is>
+      </c>
+      <c r="K30" s="4" t="inlineStr">
+        <is>
+          <t>Last Modified Date</t>
+        </is>
+      </c>
+      <c r="L30" s="4" t="inlineStr">
+        <is>
+          <t>Resolution Time (From Assigned)</t>
+        </is>
+      </c>
+      <c r="M30" s="4" t="inlineStr">
+        <is>
+          <t>Resolution Time (From Created)</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="5" t="inlineStr">
         <is>
-          <t>TKT1343122</t>
+          <t>TKT1342514</t>
         </is>
       </c>
       <c r="B31" s="5" t="inlineStr">
         <is>
-          <t>Rajesh Shahi</t>
+          <t>Bijay Carlos Rana</t>
         </is>
       </c>
       <c r="C31" s="5" t="inlineStr">
@@ -6686,22 +7202,22 @@
       </c>
       <c r="H31" s="5" t="inlineStr">
         <is>
-          <t>Case : wifi 6  has been updated by Shashikant Chaudhary</t>
+          <t>Case : WIFI 6  has been updated by Rajesh Maharjan</t>
         </is>
       </c>
       <c r="I31" s="5" t="inlineStr">
         <is>
-          <t>23 Sep 2026 12:37:13 PM</t>
+          <t>23 Sep 2026 11:16:05 AM</t>
         </is>
       </c>
       <c r="J31" s="5" t="inlineStr">
         <is>
-          <t>22 Sep 2026 09:56:18 PM</t>
+          <t>22 Sep 2026 02:29:16 PM</t>
         </is>
       </c>
       <c r="K31" s="5" t="inlineStr">
         <is>
-          <t>23 Sep 2026 12:37:13 PM</t>
+          <t>23 Sep 2026 11:16:05 AM</t>
         </is>
       </c>
       <c r="L31" s="5" t="inlineStr">
@@ -6711,19 +7227,19 @@
       </c>
       <c r="M31" s="5" t="inlineStr">
         <is>
-          <t>14h 40m</t>
+          <t>20h 46m</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="3" t="inlineStr">
         <is>
-          <t>TKT1343670</t>
+          <t>TKT1343394</t>
         </is>
       </c>
       <c r="B32" s="3" t="inlineStr">
         <is>
-          <t>Suman Shah</t>
+          <t>Kaizen Business consultant</t>
         </is>
       </c>
       <c r="C32" s="3" t="inlineStr">
@@ -6733,7 +7249,7 @@
       </c>
       <c r="D32" s="3" t="inlineStr">
         <is>
-          <t>Router Upgrade Dual Band</t>
+          <t>Router Upgrade  Wi-Fi 6</t>
         </is>
       </c>
       <c r="E32" s="3" t="inlineStr">
@@ -6753,22 +7269,22 @@
       </c>
       <c r="H32" s="3" t="inlineStr">
         <is>
-          <t>Case : router change  has been updated by Shashikant Chaudhary</t>
+          <t>Case : wifi 6 router  has been updated by Sabin Giri</t>
         </is>
       </c>
       <c r="I32" s="3" t="inlineStr">
         <is>
-          <t>23 Sep 2026 12:59:40 PM</t>
+          <t>23 Sep 2026 12:31:18 PM</t>
         </is>
       </c>
       <c r="J32" s="3" t="inlineStr">
         <is>
-          <t>23 Sep 2026 12:23:42 PM</t>
+          <t>23 Sep 2026 09:53:33 AM</t>
         </is>
       </c>
       <c r="K32" s="3" t="inlineStr">
         <is>
-          <t>23 Sep 2026 12:59:40 PM</t>
+          <t>23 Sep 2026 12:31:18 PM</t>
         </is>
       </c>
       <c r="L32" s="3" t="inlineStr">
@@ -6778,39 +7294,39 @@
       </c>
       <c r="M32" s="3" t="inlineStr">
         <is>
-          <t>35m</t>
+          <t>2h 37m</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="5" t="inlineStr">
         <is>
-          <t>TKT1342524</t>
+          <t>TKT1343122</t>
         </is>
       </c>
       <c r="B33" s="5" t="inlineStr">
         <is>
-          <t>Nakul Bhandari</t>
+          <t>Rajesh Shahi</t>
         </is>
       </c>
       <c r="C33" s="5" t="inlineStr">
         <is>
-          <t>No Internet Connection</t>
+          <t>General / Other Issues</t>
         </is>
       </c>
       <c r="D33" s="5" t="inlineStr">
         <is>
-          <t>Configuration Issue</t>
+          <t>Router Upgrade  Wi-Fi 6</t>
         </is>
       </c>
       <c r="E33" s="5" t="inlineStr">
         <is>
-          <t>Closed</t>
+          <t>Completed</t>
         </is>
       </c>
       <c r="F33" s="5" t="inlineStr">
         <is>
-          <t>Completed (Closed)</t>
+          <t>Completed (Completed)</t>
         </is>
       </c>
       <c r="G33" s="5" t="inlineStr">
@@ -6820,44 +7336,44 @@
       </c>
       <c r="H33" s="5" t="inlineStr">
         <is>
-          <t>Case : CONFINGURE ISSUE  has been updated by Ajit Shrestha</t>
+          <t>Case : wifi 6  has been updated by Shashikant Chaudhary</t>
         </is>
       </c>
       <c r="I33" s="5" t="inlineStr">
         <is>
-          <t>22 Sep 2026 02:52:24 PM</t>
+          <t>23 Sep 2026 12:37:13 PM</t>
         </is>
       </c>
       <c r="J33" s="5" t="inlineStr">
         <is>
-          <t>22 Sep 2026 02:35:30 PM</t>
+          <t>22 Sep 2026 09:56:18 PM</t>
         </is>
       </c>
       <c r="K33" s="5" t="inlineStr">
         <is>
-          <t>23 Sep 2026 12:57:31 PM</t>
+          <t>23 Sep 2026 12:37:13 PM</t>
         </is>
       </c>
       <c r="L33" s="5" t="inlineStr">
         <is>
-          <t>22h 5m</t>
+          <t>0m</t>
         </is>
       </c>
       <c r="M33" s="5" t="inlineStr">
         <is>
-          <t>22h 22m</t>
+          <t>14h 40m</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="3" t="inlineStr">
         <is>
-          <t>TKT1342923</t>
+          <t>TKT1343670</t>
         </is>
       </c>
       <c r="B34" s="3" t="inlineStr">
         <is>
-          <t>Maan maya poon</t>
+          <t>Suman Shah</t>
         </is>
       </c>
       <c r="C34" s="3" t="inlineStr">
@@ -6867,7 +7383,7 @@
       </c>
       <c r="D34" s="3" t="inlineStr">
         <is>
-          <t>Router Upgrade  Wi-Fi 6</t>
+          <t>Router Upgrade Dual Band</t>
         </is>
       </c>
       <c r="E34" s="3" t="inlineStr">
@@ -6887,22 +7403,22 @@
       </c>
       <c r="H34" s="3" t="inlineStr">
         <is>
-          <t>Case : For upgradation to wifi6   has been updated by Sabin Giri</t>
+          <t>Case : router change  has been updated by Shashikant Chaudhary</t>
         </is>
       </c>
       <c r="I34" s="3" t="inlineStr">
         <is>
-          <t>23 Sep 2026 01:01:06 PM</t>
+          <t>23 Sep 2026 12:59:40 PM</t>
         </is>
       </c>
       <c r="J34" s="3" t="inlineStr">
         <is>
-          <t>22 Sep 2026 06:58:31 PM</t>
+          <t>23 Sep 2026 12:23:42 PM</t>
         </is>
       </c>
       <c r="K34" s="3" t="inlineStr">
         <is>
-          <t>23 Sep 2026 01:01:06 PM</t>
+          <t>23 Sep 2026 12:59:40 PM</t>
         </is>
       </c>
       <c r="L34" s="3" t="inlineStr">
@@ -6912,39 +7428,39 @@
       </c>
       <c r="M34" s="3" t="inlineStr">
         <is>
-          <t>18h 2m</t>
+          <t>35m</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="5" t="inlineStr">
         <is>
-          <t>TKT1343451</t>
+          <t>TKT1342524</t>
         </is>
       </c>
       <c r="B35" s="5" t="inlineStr">
         <is>
-          <t>Sabin Maharjan</t>
+          <t>Nakul Bhandari</t>
         </is>
       </c>
       <c r="C35" s="5" t="inlineStr">
         <is>
-          <t>General / Other Issues</t>
+          <t>No Internet Connection</t>
         </is>
       </c>
       <c r="D35" s="5" t="inlineStr">
         <is>
-          <t>Router Upgrade  Wi-Fi 6</t>
+          <t>Configuration Issue</t>
         </is>
       </c>
       <c r="E35" s="5" t="inlineStr">
         <is>
-          <t>Completed</t>
+          <t>Closed</t>
         </is>
       </c>
       <c r="F35" s="5" t="inlineStr">
         <is>
-          <t>Completed (Completed)</t>
+          <t>Completed (Closed)</t>
         </is>
       </c>
       <c r="G35" s="5" t="inlineStr">
@@ -6954,54 +7470,54 @@
       </c>
       <c r="H35" s="5" t="inlineStr">
         <is>
-          <t>Case : Wifi 6  has been updated by Sabin Giri</t>
+          <t>Case : CONFINGURE ISSUE  has been updated by Ajit Shrestha</t>
         </is>
       </c>
       <c r="I35" s="5" t="inlineStr">
         <is>
-          <t>23 Sep 2026 01:17:39 PM</t>
+          <t>22 Sep 2026 02:52:24 PM</t>
         </is>
       </c>
       <c r="J35" s="5" t="inlineStr">
         <is>
-          <t>23 Sep 2026 10:26:34 AM</t>
+          <t>22 Sep 2026 02:35:30 PM</t>
         </is>
       </c>
       <c r="K35" s="5" t="inlineStr">
         <is>
-          <t>23 Sep 2026 01:17:39 PM</t>
+          <t>23 Sep 2026 12:57:31 PM</t>
         </is>
       </c>
       <c r="L35" s="5" t="inlineStr">
         <is>
-          <t>0m</t>
+          <t>22h 5m</t>
         </is>
       </c>
       <c r="M35" s="5" t="inlineStr">
         <is>
-          <t>2h 51m</t>
+          <t>22h 22m</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="3" t="inlineStr">
         <is>
-          <t>TKT1343062</t>
+          <t>TKT1342923</t>
         </is>
       </c>
       <c r="B36" s="3" t="inlineStr">
         <is>
-          <t>Sabin Magar</t>
+          <t>Maan maya poon</t>
         </is>
       </c>
       <c r="C36" s="3" t="inlineStr">
         <is>
-          <t>Hardware Damage / Malfunction</t>
+          <t>General / Other Issues</t>
         </is>
       </c>
       <c r="D36" s="3" t="inlineStr">
         <is>
-          <t>IPTV STB box Damage Issue</t>
+          <t>Router Upgrade  Wi-Fi 6</t>
         </is>
       </c>
       <c r="E36" s="3" t="inlineStr">
@@ -7021,22 +7537,22 @@
       </c>
       <c r="H36" s="3" t="inlineStr">
         <is>
-          <t>Case : IP TV not Working   has been updated by Ajit Shrestha</t>
+          <t>Case : For upgradation to wifi6   has been updated by Sabin Giri</t>
         </is>
       </c>
       <c r="I36" s="3" t="inlineStr">
         <is>
-          <t>23 Sep 2026 01:16:47 PM</t>
+          <t>23 Sep 2026 01:01:06 PM</t>
         </is>
       </c>
       <c r="J36" s="3" t="inlineStr">
         <is>
-          <t>22 Sep 2026 08:56:52 PM</t>
+          <t>22 Sep 2026 06:58:31 PM</t>
         </is>
       </c>
       <c r="K36" s="3" t="inlineStr">
         <is>
-          <t>23 Sep 2026 01:16:47 PM</t>
+          <t>23 Sep 2026 01:01:06 PM</t>
         </is>
       </c>
       <c r="L36" s="3" t="inlineStr">
@@ -7046,19 +7562,19 @@
       </c>
       <c r="M36" s="3" t="inlineStr">
         <is>
-          <t>16h 19m</t>
+          <t>18h 2m</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="5" t="inlineStr">
         <is>
-          <t>TKT1341347</t>
+          <t>TKT1343451</t>
         </is>
       </c>
       <c r="B37" s="5" t="inlineStr">
         <is>
-          <t>Siddhartha Model School</t>
+          <t>Sabin Maharjan</t>
         </is>
       </c>
       <c r="C37" s="5" t="inlineStr">
@@ -7073,12 +7589,12 @@
       </c>
       <c r="E37" s="5" t="inlineStr">
         <is>
-          <t>Closed</t>
+          <t>Completed</t>
         </is>
       </c>
       <c r="F37" s="5" t="inlineStr">
         <is>
-          <t>Completed (Closed)</t>
+          <t>Completed (Completed)</t>
         </is>
       </c>
       <c r="G37" s="5" t="inlineStr">
@@ -7088,54 +7604,54 @@
       </c>
       <c r="H37" s="5" t="inlineStr">
         <is>
-          <t>Case : wifi 6  has been updated by Sunil Chaudhary</t>
+          <t>Case : Wifi 6  has been updated by Sabin Giri</t>
         </is>
       </c>
       <c r="I37" s="5" t="inlineStr">
         <is>
-          <t>21 Sep 2026 01:35:47 PM</t>
+          <t>23 Sep 2026 01:17:39 PM</t>
         </is>
       </c>
       <c r="J37" s="5" t="inlineStr">
         <is>
-          <t>21 Sep 2026 01:35:47 PM</t>
+          <t>23 Sep 2026 10:26:34 AM</t>
         </is>
       </c>
       <c r="K37" s="5" t="inlineStr">
         <is>
-          <t>23 Sep 2026 01:22:44 PM</t>
+          <t>23 Sep 2026 01:17:39 PM</t>
         </is>
       </c>
       <c r="L37" s="5" t="inlineStr">
         <is>
-          <t>1d 23h 46m</t>
+          <t>0m</t>
         </is>
       </c>
       <c r="M37" s="5" t="inlineStr">
         <is>
-          <t>1d 23h 46m</t>
+          <t>2h 51m</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="3" t="inlineStr">
         <is>
-          <t>TKT1342867</t>
+          <t>TKT1343062</t>
         </is>
       </c>
       <c r="B38" s="3" t="inlineStr">
         <is>
-          <t>Punit Kumar Barnawal</t>
+          <t>Sabin Magar</t>
         </is>
       </c>
       <c r="C38" s="3" t="inlineStr">
         <is>
-          <t>General / Other Issues</t>
+          <t>Hardware Damage / Malfunction</t>
         </is>
       </c>
       <c r="D38" s="3" t="inlineStr">
         <is>
-          <t>Router Upgrade  Wi-Fi 6</t>
+          <t>IPTV STB box Damage Issue</t>
         </is>
       </c>
       <c r="E38" s="3" t="inlineStr">
@@ -7155,22 +7671,22 @@
       </c>
       <c r="H38" s="3" t="inlineStr">
         <is>
-          <t>Case : Wifi 6  has been updated by Shashikant Chaudhary</t>
+          <t>Case : IP TV not Working   has been updated by Ajit Shrestha</t>
         </is>
       </c>
       <c r="I38" s="3" t="inlineStr">
         <is>
-          <t>23 Sep 2026 01:48:42 PM</t>
+          <t>23 Sep 2026 01:16:47 PM</t>
         </is>
       </c>
       <c r="J38" s="3" t="inlineStr">
         <is>
-          <t>22 Sep 2026 06:02:29 PM</t>
+          <t>22 Sep 2026 08:56:52 PM</t>
         </is>
       </c>
       <c r="K38" s="3" t="inlineStr">
         <is>
-          <t>23 Sep 2026 01:48:42 PM</t>
+          <t>23 Sep 2026 01:16:47 PM</t>
         </is>
       </c>
       <c r="L38" s="3" t="inlineStr">
@@ -7180,39 +7696,39 @@
       </c>
       <c r="M38" s="3" t="inlineStr">
         <is>
-          <t>19h 46m</t>
+          <t>16h 19m</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="5" t="inlineStr">
         <is>
-          <t>TKT1343135</t>
+          <t>TKT1341347</t>
         </is>
       </c>
       <c r="B39" s="5" t="inlineStr">
         <is>
-          <t>Ashish Shahbadi</t>
+          <t>Siddhartha Model School</t>
         </is>
       </c>
       <c r="C39" s="5" t="inlineStr">
         <is>
-          <t>Hardware Damage / Malfunction</t>
+          <t>General / Other Issues</t>
         </is>
       </c>
       <c r="D39" s="5" t="inlineStr">
         <is>
-          <t>Router Damage Issue</t>
+          <t>Router Upgrade  Wi-Fi 6</t>
         </is>
       </c>
       <c r="E39" s="5" t="inlineStr">
         <is>
-          <t>Completed</t>
+          <t>Closed</t>
         </is>
       </c>
       <c r="F39" s="5" t="inlineStr">
         <is>
-          <t>Completed (Completed)</t>
+          <t>Completed (Closed)</t>
         </is>
       </c>
       <c r="G39" s="5" t="inlineStr">
@@ -7222,44 +7738,44 @@
       </c>
       <c r="H39" s="5" t="inlineStr">
         <is>
-          <t>Case : 5g not working   has been updated by Rajesh Maharjan</t>
+          <t>Case : wifi 6  has been updated by Sunil Chaudhary</t>
         </is>
       </c>
       <c r="I39" s="5" t="inlineStr">
         <is>
-          <t>23 Sep 2026 01:51:51 PM</t>
+          <t>21 Sep 2026 01:35:47 PM</t>
         </is>
       </c>
       <c r="J39" s="5" t="inlineStr">
         <is>
-          <t>22 Sep 2026 10:20:07 PM</t>
+          <t>21 Sep 2026 01:35:47 PM</t>
         </is>
       </c>
       <c r="K39" s="5" t="inlineStr">
         <is>
-          <t>23 Sep 2026 01:51:51 PM</t>
+          <t>23 Sep 2026 01:22:44 PM</t>
         </is>
       </c>
       <c r="L39" s="5" t="inlineStr">
         <is>
-          <t>0m</t>
+          <t>1d 23h 46m</t>
         </is>
       </c>
       <c r="M39" s="5" t="inlineStr">
         <is>
-          <t>15h 31m</t>
+          <t>1d 23h 46m</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="3" t="inlineStr">
         <is>
-          <t>TKT1343287</t>
+          <t>TKT1342867</t>
         </is>
       </c>
       <c r="B40" s="3" t="inlineStr">
         <is>
-          <t>Anup Chaudhary</t>
+          <t>Punit Kumar Barnawal</t>
         </is>
       </c>
       <c r="C40" s="3" t="inlineStr">
@@ -7289,22 +7805,22 @@
       </c>
       <c r="H40" s="3" t="inlineStr">
         <is>
-          <t>Case : wifi 6  has been updated by Sabin Giri</t>
+          <t>Case : Wifi 6  has been updated by Shashikant Chaudhary</t>
         </is>
       </c>
       <c r="I40" s="3" t="inlineStr">
         <is>
-          <t>23 Sep 2026 02:03:32 PM</t>
+          <t>23 Sep 2026 01:48:42 PM</t>
         </is>
       </c>
       <c r="J40" s="3" t="inlineStr">
         <is>
-          <t>23 Sep 2026 08:37:17 AM</t>
+          <t>22 Sep 2026 06:02:29 PM</t>
         </is>
       </c>
       <c r="K40" s="3" t="inlineStr">
         <is>
-          <t>23 Sep 2026 02:03:32 PM</t>
+          <t>23 Sep 2026 01:48:42 PM</t>
         </is>
       </c>
       <c r="L40" s="3" t="inlineStr">
@@ -7314,19 +7830,19 @@
       </c>
       <c r="M40" s="3" t="inlineStr">
         <is>
-          <t>5h 26m</t>
+          <t>19h 46m</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="5" t="inlineStr">
         <is>
-          <t>TKT1342988</t>
+          <t>TKT1343135</t>
         </is>
       </c>
       <c r="B41" s="5" t="inlineStr">
         <is>
-          <t>Kushal Neupane</t>
+          <t>Ashish Shahbadi</t>
         </is>
       </c>
       <c r="C41" s="5" t="inlineStr">
@@ -7336,17 +7852,17 @@
       </c>
       <c r="D41" s="5" t="inlineStr">
         <is>
-          <t>IPTV STB box Damage Issue</t>
+          <t>Router Damage Issue</t>
         </is>
       </c>
       <c r="E41" s="5" t="inlineStr">
         <is>
-          <t>Closed</t>
+          <t>Completed</t>
         </is>
       </c>
       <c r="F41" s="5" t="inlineStr">
         <is>
-          <t>Completed (Closed)</t>
+          <t>Completed (Completed)</t>
         </is>
       </c>
       <c r="G41" s="5" t="inlineStr">
@@ -7356,64 +7872,64 @@
       </c>
       <c r="H41" s="5" t="inlineStr">
         <is>
-          <t>Case : stb faulty  has been updated by Sunil Chaudhary</t>
+          <t>Case : 5g not working   has been updated by Rajesh Maharjan</t>
         </is>
       </c>
       <c r="I41" s="5" t="inlineStr">
         <is>
-          <t>22 Sep 2026 08:27:54 PM</t>
+          <t>23 Sep 2026 01:51:51 PM</t>
         </is>
       </c>
       <c r="J41" s="5" t="inlineStr">
         <is>
-          <t>22 Sep 2026 07:49:31 PM</t>
+          <t>22 Sep 2026 10:20:07 PM</t>
         </is>
       </c>
       <c r="K41" s="5" t="inlineStr">
         <is>
-          <t>23 Sep 2026 02:16:10 PM</t>
+          <t>23 Sep 2026 01:51:51 PM</t>
         </is>
       </c>
       <c r="L41" s="5" t="inlineStr">
         <is>
-          <t>17h 48m</t>
+          <t>0m</t>
         </is>
       </c>
       <c r="M41" s="5" t="inlineStr">
         <is>
-          <t>18h 26m</t>
+          <t>15h 31m</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="3" t="inlineStr">
         <is>
-          <t>TKT1342988</t>
+          <t>TKT1343287</t>
         </is>
       </c>
       <c r="B42" s="3" t="inlineStr">
         <is>
-          <t>Kushal Neupane</t>
+          <t>Anup Chaudhary</t>
         </is>
       </c>
       <c r="C42" s="3" t="inlineStr">
         <is>
-          <t>Hardware Damage / Malfunction</t>
+          <t>General / Other Issues</t>
         </is>
       </c>
       <c r="D42" s="3" t="inlineStr">
         <is>
-          <t>IPTV STB box Damage Issue</t>
+          <t>Router Upgrade  Wi-Fi 6</t>
         </is>
       </c>
       <c r="E42" s="3" t="inlineStr">
         <is>
-          <t>Closed</t>
+          <t>Completed</t>
         </is>
       </c>
       <c r="F42" s="3" t="inlineStr">
         <is>
-          <t>Completed (Closed)</t>
+          <t>Completed (Completed)</t>
         </is>
       </c>
       <c r="G42" s="3" t="inlineStr">
@@ -7423,64 +7939,64 @@
       </c>
       <c r="H42" s="3" t="inlineStr">
         <is>
-          <t>Case : stb faulty  has been updated by Sunil Chaudhary</t>
+          <t>Case : wifi 6  has been updated by Sabin Giri</t>
         </is>
       </c>
       <c r="I42" s="3" t="inlineStr">
         <is>
-          <t>22 Sep 2026 08:27:54 PM</t>
+          <t>23 Sep 2026 02:03:32 PM</t>
         </is>
       </c>
       <c r="J42" s="3" t="inlineStr">
         <is>
-          <t>22 Sep 2026 07:49:31 PM</t>
+          <t>23 Sep 2026 08:37:17 AM</t>
         </is>
       </c>
       <c r="K42" s="3" t="inlineStr">
         <is>
-          <t>23 Sep 2026 02:16:10 PM</t>
+          <t>23 Sep 2026 02:03:32 PM</t>
         </is>
       </c>
       <c r="L42" s="3" t="inlineStr">
         <is>
-          <t>17h 48m</t>
+          <t>0m</t>
         </is>
       </c>
       <c r="M42" s="3" t="inlineStr">
         <is>
-          <t>18h 26m</t>
+          <t>5h 26m</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="5" t="inlineStr">
         <is>
-          <t>TKT1340081</t>
+          <t>TKT1342988</t>
         </is>
       </c>
       <c r="B43" s="5" t="inlineStr">
         <is>
-          <t>Anjan Khadka</t>
+          <t>Kushal Neupane</t>
         </is>
       </c>
       <c r="C43" s="5" t="inlineStr">
         <is>
-          <t>General / Other Issues</t>
+          <t>Hardware Damage / Malfunction</t>
         </is>
       </c>
       <c r="D43" s="5" t="inlineStr">
         <is>
-          <t>Query For Secondary Router /Repeater</t>
+          <t>IPTV STB box Damage Issue</t>
         </is>
       </c>
       <c r="E43" s="5" t="inlineStr">
         <is>
-          <t>Completed</t>
+          <t>Closed</t>
         </is>
       </c>
       <c r="F43" s="5" t="inlineStr">
         <is>
-          <t>Completed (Completed)</t>
+          <t>Completed (Closed)</t>
         </is>
       </c>
       <c r="G43" s="5" t="inlineStr">
@@ -7490,64 +8006,64 @@
       </c>
       <c r="H43" s="5" t="inlineStr">
         <is>
-          <t>Case : Secondary Router Connetion   has been updated by Chandramani Tharu</t>
+          <t>Case : stb faulty  has been updated by Sunil Chaudhary</t>
         </is>
       </c>
       <c r="I43" s="5" t="inlineStr">
         <is>
-          <t>23 Sep 2026 02:23:04 PM</t>
+          <t>22 Sep 2026 08:27:54 PM</t>
         </is>
       </c>
       <c r="J43" s="5" t="inlineStr">
         <is>
-          <t>20 Sep 2026 02:38:36 PM</t>
+          <t>22 Sep 2026 07:49:31 PM</t>
         </is>
       </c>
       <c r="K43" s="5" t="inlineStr">
         <is>
-          <t>23 Sep 2026 02:23:04 PM</t>
+          <t>23 Sep 2026 02:16:10 PM</t>
         </is>
       </c>
       <c r="L43" s="5" t="inlineStr">
         <is>
-          <t>0m</t>
+          <t>17h 48m</t>
         </is>
       </c>
       <c r="M43" s="5" t="inlineStr">
         <is>
-          <t>2d 23h 44m</t>
+          <t>18h 26m</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="3" t="inlineStr">
         <is>
-          <t>TKT1339133</t>
+          <t>TKT1342988</t>
         </is>
       </c>
       <c r="B44" s="3" t="inlineStr">
         <is>
-          <t>Chalachitra Chautari pvt.ltd</t>
+          <t>Kushal Neupane</t>
         </is>
       </c>
       <c r="C44" s="3" t="inlineStr">
         <is>
-          <t>Slow Internet Connection</t>
+          <t>Hardware Damage / Malfunction</t>
         </is>
       </c>
       <c r="D44" s="3" t="inlineStr">
         <is>
-          <t>Video content is Buffering</t>
+          <t>IPTV STB box Damage Issue</t>
         </is>
       </c>
       <c r="E44" s="3" t="inlineStr">
         <is>
-          <t>Completed</t>
+          <t>Closed</t>
         </is>
       </c>
       <c r="F44" s="3" t="inlineStr">
         <is>
-          <t>Completed (Completed)</t>
+          <t>Completed (Closed)</t>
         </is>
       </c>
       <c r="G44" s="3" t="inlineStr">
@@ -7557,44 +8073,44 @@
       </c>
       <c r="H44" s="3" t="inlineStr">
         <is>
-          <t>Case : slow issue  has been updated by Chandramani Tharu</t>
+          <t>Case : stb faulty  has been updated by Sunil Chaudhary</t>
         </is>
       </c>
       <c r="I44" s="3" t="inlineStr">
         <is>
-          <t>23 Sep 2026 02:21:55 PM</t>
+          <t>22 Sep 2026 08:27:54 PM</t>
         </is>
       </c>
       <c r="J44" s="3" t="inlineStr">
         <is>
-          <t>19 Sep 2026 05:49:47 PM</t>
+          <t>22 Sep 2026 07:49:31 PM</t>
         </is>
       </c>
       <c r="K44" s="3" t="inlineStr">
         <is>
-          <t>23 Sep 2026 02:21:55 PM</t>
+          <t>23 Sep 2026 02:16:10 PM</t>
         </is>
       </c>
       <c r="L44" s="3" t="inlineStr">
         <is>
-          <t>0m</t>
+          <t>17h 48m</t>
         </is>
       </c>
       <c r="M44" s="3" t="inlineStr">
         <is>
-          <t>3d 20h 32m</t>
+          <t>18h 26m</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="5" t="inlineStr">
         <is>
-          <t>TKT1343230</t>
+          <t>TKT1340081</t>
         </is>
       </c>
       <c r="B45" s="5" t="inlineStr">
         <is>
-          <t>Bikesh Shrestha</t>
+          <t>Anjan Khadka</t>
         </is>
       </c>
       <c r="C45" s="5" t="inlineStr">
@@ -7604,7 +8120,7 @@
       </c>
       <c r="D45" s="5" t="inlineStr">
         <is>
-          <t>Router Upgrade  Wi-Fi 6</t>
+          <t>Query For Secondary Router /Repeater</t>
         </is>
       </c>
       <c r="E45" s="5" t="inlineStr">
@@ -7624,22 +8140,22 @@
       </c>
       <c r="H45" s="5" t="inlineStr">
         <is>
-          <t>Case : wifi 6  has been updated by Sabin Giri</t>
+          <t>Case : Secondary Router Connetion   has been updated by Chandramani Tharu</t>
         </is>
       </c>
       <c r="I45" s="5" t="inlineStr">
         <is>
-          <t>23 Sep 2026 02:41:26 PM</t>
+          <t>23 Sep 2026 02:23:04 PM</t>
         </is>
       </c>
       <c r="J45" s="5" t="inlineStr">
         <is>
-          <t>23 Sep 2026 07:43:57 AM</t>
+          <t>20 Sep 2026 02:38:36 PM</t>
         </is>
       </c>
       <c r="K45" s="5" t="inlineStr">
         <is>
-          <t>23 Sep 2026 02:41:26 PM</t>
+          <t>23 Sep 2026 02:23:04 PM</t>
         </is>
       </c>
       <c r="L45" s="5" t="inlineStr">
@@ -7649,74 +8165,409 @@
       </c>
       <c r="M45" s="5" t="inlineStr">
         <is>
-          <t>6h 57m</t>
+          <t>2d 23h 44m</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="3" t="inlineStr">
         <is>
+          <t>TKT1339133</t>
+        </is>
+      </c>
+      <c r="B46" s="3" t="inlineStr">
+        <is>
+          <t>Chalachitra Chautari pvt.ltd</t>
+        </is>
+      </c>
+      <c r="C46" s="3" t="inlineStr">
+        <is>
+          <t>Slow Internet Connection</t>
+        </is>
+      </c>
+      <c r="D46" s="3" t="inlineStr">
+        <is>
+          <t>Video content is Buffering</t>
+        </is>
+      </c>
+      <c r="E46" s="3" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="F46" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Completed)</t>
+        </is>
+      </c>
+      <c r="G46" s="3" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="H46" s="3" t="inlineStr">
+        <is>
+          <t>Case : slow issue  has been updated by Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="I46" s="3" t="inlineStr">
+        <is>
+          <t>23 Sep 2026 02:21:55 PM</t>
+        </is>
+      </c>
+      <c r="J46" s="3" t="inlineStr">
+        <is>
+          <t>19 Sep 2026 05:49:47 PM</t>
+        </is>
+      </c>
+      <c r="K46" s="3" t="inlineStr">
+        <is>
+          <t>23 Sep 2026 02:21:55 PM</t>
+        </is>
+      </c>
+      <c r="L46" s="3" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="M46" s="3" t="inlineStr">
+        <is>
+          <t>3d 20h 32m</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="5" t="inlineStr">
+        <is>
+          <t>TKT1343230</t>
+        </is>
+      </c>
+      <c r="B47" s="5" t="inlineStr">
+        <is>
+          <t>Bikesh Shrestha</t>
+        </is>
+      </c>
+      <c r="C47" s="5" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="D47" s="5" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="E47" s="5" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="F47" s="5" t="inlineStr">
+        <is>
+          <t>Completed (Completed)</t>
+        </is>
+      </c>
+      <c r="G47" s="5" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="H47" s="5" t="inlineStr">
+        <is>
+          <t>Case : wifi 6  has been updated by Sabin Giri</t>
+        </is>
+      </c>
+      <c r="I47" s="5" t="inlineStr">
+        <is>
+          <t>23 Sep 2026 02:41:26 PM</t>
+        </is>
+      </c>
+      <c r="J47" s="5" t="inlineStr">
+        <is>
+          <t>23 Sep 2026 07:43:57 AM</t>
+        </is>
+      </c>
+      <c r="K47" s="5" t="inlineStr">
+        <is>
+          <t>23 Sep 2026 02:41:26 PM</t>
+        </is>
+      </c>
+      <c r="L47" s="5" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="M47" s="5" t="inlineStr">
+        <is>
+          <t>6h 57m</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="3" t="inlineStr">
+        <is>
           <t>TKT1342466</t>
         </is>
       </c>
-      <c r="B46" s="3" t="inlineStr">
+      <c r="B48" s="3" t="inlineStr">
         <is>
           <t>Dharmesh Maharjan</t>
         </is>
       </c>
-      <c r="C46" s="3" t="inlineStr">
+      <c r="C48" s="3" t="inlineStr">
         <is>
           <t>General / Other Issues</t>
         </is>
       </c>
-      <c r="D46" s="3" t="inlineStr">
+      <c r="D48" s="3" t="inlineStr">
         <is>
           <t>Router Upgrade  Wi-Fi 6</t>
         </is>
       </c>
-      <c r="E46" s="3" t="inlineStr">
+      <c r="E48" s="3" t="inlineStr">
         <is>
           <t>Completed</t>
         </is>
       </c>
-      <c r="F46" s="3" t="inlineStr">
+      <c r="F48" s="3" t="inlineStr">
         <is>
           <t>Completed (Completed)</t>
         </is>
       </c>
-      <c r="G46" s="3" t="inlineStr">
+      <c r="G48" s="3" t="inlineStr">
         <is>
           <t>nan</t>
         </is>
       </c>
-      <c r="H46" s="3" t="inlineStr">
+      <c r="H48" s="3" t="inlineStr">
         <is>
           <t>Case : Wi-Fi 6  has been updated by Chandramani Tharu</t>
         </is>
       </c>
-      <c r="I46" s="3" t="inlineStr">
+      <c r="I48" s="3" t="inlineStr">
         <is>
           <t>23 Sep 2026 02:53:32 PM</t>
         </is>
       </c>
-      <c r="J46" s="3" t="inlineStr">
+      <c r="J48" s="3" t="inlineStr">
         <is>
           <t>22 Sep 2026 01:51:09 PM</t>
         </is>
       </c>
-      <c r="K46" s="3" t="inlineStr">
+      <c r="K48" s="3" t="inlineStr">
         <is>
           <t>23 Sep 2026 02:53:32 PM</t>
         </is>
       </c>
-      <c r="L46" s="3" t="inlineStr">
+      <c r="L48" s="3" t="inlineStr">
         <is>
           <t>0m</t>
         </is>
       </c>
-      <c r="M46" s="3" t="inlineStr">
+      <c r="M48" s="3" t="inlineStr">
         <is>
           <t>1d 1h 2m</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="5" t="inlineStr">
+        <is>
+          <t>TKT1342232</t>
+        </is>
+      </c>
+      <c r="B49" s="5" t="inlineStr">
+        <is>
+          <t>Dipendra khanal</t>
+        </is>
+      </c>
+      <c r="C49" s="5" t="inlineStr">
+        <is>
+          <t>IPTV Related Issues</t>
+        </is>
+      </c>
+      <c r="D49" s="5" t="inlineStr">
+        <is>
+          <t>SKYCOM-Audio &amp; Video Syn Issue</t>
+        </is>
+      </c>
+      <c r="E49" s="5" t="inlineStr">
+        <is>
+          <t>Closed</t>
+        </is>
+      </c>
+      <c r="F49" s="5" t="inlineStr">
+        <is>
+          <t>Completed (Closed)</t>
+        </is>
+      </c>
+      <c r="G49" s="5" t="inlineStr">
+        <is>
+          <t>Case : IPTV  Isssue  has been updated by Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="H49" s="5" t="inlineStr">
+        <is>
+          <t>Case : IPTV  Isssue  has been updated by Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="I49" s="5" t="inlineStr">
+        <is>
+          <t>22 Sep 2026 08:25:10 PM</t>
+        </is>
+      </c>
+      <c r="J49" s="5" t="inlineStr">
+        <is>
+          <t>22 Sep 2026 11:24:09 AM</t>
+        </is>
+      </c>
+      <c r="K49" s="5" t="inlineStr">
+        <is>
+          <t>23 Sep 2026 03:46:01 PM</t>
+        </is>
+      </c>
+      <c r="L49" s="5" t="inlineStr">
+        <is>
+          <t>19h 20m</t>
+        </is>
+      </c>
+      <c r="M49" s="5" t="inlineStr">
+        <is>
+          <t>1d 4h 21m</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="3" t="inlineStr">
+        <is>
+          <t>TKT1342232</t>
+        </is>
+      </c>
+      <c r="B50" s="3" t="inlineStr">
+        <is>
+          <t>Dipendra khanal</t>
+        </is>
+      </c>
+      <c r="C50" s="3" t="inlineStr">
+        <is>
+          <t>IPTV Related Issues</t>
+        </is>
+      </c>
+      <c r="D50" s="3" t="inlineStr">
+        <is>
+          <t>SKYCOM-Audio &amp; Video Syn Issue</t>
+        </is>
+      </c>
+      <c r="E50" s="3" t="inlineStr">
+        <is>
+          <t>Closed</t>
+        </is>
+      </c>
+      <c r="F50" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Closed)</t>
+        </is>
+      </c>
+      <c r="G50" s="3" t="inlineStr">
+        <is>
+          <t>Case : IPTV  Isssue  has been updated by Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="H50" s="3" t="inlineStr">
+        <is>
+          <t>Case : IPTV  Isssue  has been updated by Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="I50" s="3" t="inlineStr">
+        <is>
+          <t>22 Sep 2026 08:25:10 PM</t>
+        </is>
+      </c>
+      <c r="J50" s="3" t="inlineStr">
+        <is>
+          <t>22 Sep 2026 11:24:09 AM</t>
+        </is>
+      </c>
+      <c r="K50" s="3" t="inlineStr">
+        <is>
+          <t>23 Sep 2026 03:46:01 PM</t>
+        </is>
+      </c>
+      <c r="L50" s="3" t="inlineStr">
+        <is>
+          <t>19h 20m</t>
+        </is>
+      </c>
+      <c r="M50" s="3" t="inlineStr">
+        <is>
+          <t>1d 4h 21m</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="5" t="inlineStr">
+        <is>
+          <t>TKT1343067</t>
+        </is>
+      </c>
+      <c r="B51" s="5" t="inlineStr">
+        <is>
+          <t>Aaryan Kumar Jha</t>
+        </is>
+      </c>
+      <c r="C51" s="5" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="D51" s="5" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="E51" s="5" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="F51" s="5" t="inlineStr">
+        <is>
+          <t>Completed (Completed)</t>
+        </is>
+      </c>
+      <c r="G51" s="5" t="inlineStr">
+        <is>
+          <t>Case : For upgradation to wifi6   has been updated by Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="H51" s="5" t="inlineStr">
+        <is>
+          <t>Case : For upgradation to wifi6   has been updated by Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="I51" s="5" t="inlineStr">
+        <is>
+          <t>23 Sep 2026 03:21:49 PM</t>
+        </is>
+      </c>
+      <c r="J51" s="5" t="inlineStr">
+        <is>
+          <t>22 Sep 2026 08:58:59 PM</t>
+        </is>
+      </c>
+      <c r="K51" s="5" t="inlineStr">
+        <is>
+          <t>23 Sep 2026 03:21:49 PM</t>
+        </is>
+      </c>
+      <c r="L51" s="5" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="M51" s="5" t="inlineStr">
+        <is>
+          <t>18h 22m</t>
         </is>
       </c>
     </row>

--- a/audit_report_ALL_TEAM_23_Sep_2026.xlsx
+++ b/audit_report_ALL_TEAM_23_Sep_2026.xlsx
@@ -483,7 +483,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AW33"/>
+  <dimension ref="A1:AW36"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="23" customWidth="1" min="1" max="1"/>
@@ -6082,10 +6082,8 @@
           <t>Dipendra khanal</t>
         </is>
       </c>
-      <c r="O31" s="3" t="inlineStr">
-        <is>
-          <t>9841410905</t>
-        </is>
+      <c r="O31" s="3" t="n">
+        <v>9841410905</v>
       </c>
       <c r="P31" s="3" t="inlineStr">
         <is>
@@ -6171,10 +6169,8 @@
           <t>Sunil Chaudhary</t>
         </is>
       </c>
-      <c r="AN31" s="3" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
+      <c r="AN31" s="3" t="n">
+        <v>4</v>
       </c>
       <c r="AO31" s="3" t="inlineStr">
         <is>
@@ -6185,7 +6181,7 @@
       <c r="AQ31" s="3" t="inlineStr"/>
       <c r="AR31" s="3" t="inlineStr">
         <is>
-          <t>Case : IPTV  Isssue  has been updated by Sunil Chaudhary</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="AS31" s="3" t="inlineStr">
@@ -6281,10 +6277,8 @@
           <t>Dipendra khanal</t>
         </is>
       </c>
-      <c r="O32" s="3" t="inlineStr">
-        <is>
-          <t>9841410905</t>
-        </is>
+      <c r="O32" s="3" t="n">
+        <v>9841410905</v>
       </c>
       <c r="P32" s="3" t="inlineStr">
         <is>
@@ -6370,10 +6364,8 @@
           <t>Sunil Chaudhary</t>
         </is>
       </c>
-      <c r="AN32" s="3" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
+      <c r="AN32" s="3" t="n">
+        <v>4</v>
       </c>
       <c r="AO32" s="3" t="inlineStr">
         <is>
@@ -6384,7 +6376,7 @@
       <c r="AQ32" s="3" t="inlineStr"/>
       <c r="AR32" s="3" t="inlineStr">
         <is>
-          <t>Case : IPTV  Isssue  has been updated by Sunil Chaudhary</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="AS32" s="3" t="inlineStr">
@@ -6480,10 +6472,8 @@
           <t>Aaryan Kumar Jha</t>
         </is>
       </c>
-      <c r="O33" s="3" t="inlineStr">
-        <is>
-          <t>9841597524</t>
-        </is>
+      <c r="O33" s="3" t="n">
+        <v>9841597524</v>
       </c>
       <c r="P33" s="3" t="inlineStr">
         <is>
@@ -6518,10 +6508,8 @@
           <t>Active</t>
         </is>
       </c>
-      <c r="Y33" s="3" t="inlineStr">
-        <is>
-          <t>27.69001</t>
-        </is>
+      <c r="Y33" s="3" t="n">
+        <v>27.69001</v>
       </c>
       <c r="Z33" s="3" t="inlineStr">
         <is>
@@ -6577,48 +6565,677 @@
           <t>Chandramani Tharu</t>
         </is>
       </c>
-      <c r="AN33" s="3" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
+      <c r="AN33" s="3" t="n">
+        <v>4</v>
       </c>
       <c r="AO33" s="3" t="inlineStr">
         <is>
           <t>1,9</t>
         </is>
       </c>
-      <c r="AP33" s="3" t="inlineStr">
-        <is>
-          <t>85.30437</t>
-        </is>
+      <c r="AP33" s="3" t="n">
+        <v>85.30437000000001</v>
       </c>
       <c r="AQ33" s="3" t="inlineStr"/>
       <c r="AR33" s="3" t="inlineStr">
         <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="AS33" s="3" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="AT33" s="3" t="inlineStr">
+        <is>
+          <t>18h 22m</t>
+        </is>
+      </c>
+      <c r="AU33" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Completed)</t>
+        </is>
+      </c>
+      <c r="AV33" s="3" t="inlineStr">
+        <is>
           <t>Case : For upgradation to wifi6   has been updated by Chandramani Tharu</t>
         </is>
       </c>
-      <c r="AS33" s="3" t="inlineStr">
+      <c r="AW33" s="3" t="inlineStr">
+        <is>
+          <t>WiFi 6 Upgrade</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="3" t="inlineStr">
+        <is>
+          <t>Rajesh Maharjan</t>
+        </is>
+      </c>
+      <c r="B34" s="3" t="inlineStr">
+        <is>
+          <t>23 Sep 2026 3:58 PM</t>
+        </is>
+      </c>
+      <c r="C34" s="3" t="inlineStr">
+        <is>
+          <t>/Oi+2zlne73U37ZA62PktA==</t>
+        </is>
+      </c>
+      <c r="D34" s="3" t="inlineStr">
+        <is>
+          <t>Rajesh Maharjan</t>
+        </is>
+      </c>
+      <c r="E34" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F34" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G34" s="3" t="inlineStr"/>
+      <c r="H34" s="3" t="inlineStr">
+        <is>
+          <t>Case : WIFI 6  has been updated by Rajesh Maharjan</t>
+        </is>
+      </c>
+      <c r="I34" s="3" t="inlineStr">
+        <is>
+          <t>WIFI 6</t>
+        </is>
+      </c>
+      <c r="J34" s="3" t="inlineStr">
+        <is>
+          <t>TKT1343673</t>
+        </is>
+      </c>
+      <c r="K34" s="3" t="inlineStr">
+        <is>
+          <t>Bello World Pvt.Ltd</t>
+        </is>
+      </c>
+      <c r="L34" s="3" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="M34" s="3" t="inlineStr">
+        <is>
+          <t>Phone</t>
+        </is>
+      </c>
+      <c r="N34" s="3" t="inlineStr">
+        <is>
+          <t>Bello World Pvt.Ltd</t>
+        </is>
+      </c>
+      <c r="O34" s="3" t="inlineStr">
+        <is>
+          <t>9702651054</t>
+        </is>
+      </c>
+      <c r="P34" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="Q34" s="3" t="inlineStr"/>
+      <c r="R34" s="3" t="inlineStr">
+        <is>
+          <t>23 Sep 2026 03:58:20 PM</t>
+        </is>
+      </c>
+      <c r="S34" s="3" t="inlineStr"/>
+      <c r="T34" s="3" t="inlineStr"/>
+      <c r="U34" s="3" t="inlineStr">
+        <is>
+          <t>9702651074</t>
+        </is>
+      </c>
+      <c r="V34" s="3" t="inlineStr">
+        <is>
+          <t>23 Sep 2026 12:25:04 PM</t>
+        </is>
+      </c>
+      <c r="W34" s="3" t="inlineStr">
+        <is>
+          <t>23 Sep 2026 03:58:20 PM</t>
+        </is>
+      </c>
+      <c r="X34" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Y34" s="3" t="inlineStr">
+        <is>
+          <t>27.6721</t>
+        </is>
+      </c>
+      <c r="Z34" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="AA34" s="3" t="inlineStr">
+        <is>
+          <t>Layer 1-User</t>
+        </is>
+      </c>
+      <c r="AB34" s="3" t="inlineStr">
+        <is>
+          <t>L1  Support</t>
+        </is>
+      </c>
+      <c r="AC34" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="AD34" s="3" t="inlineStr"/>
+      <c r="AE34" s="3" t="inlineStr">
+        <is>
+          <t>Basemark, Jawalakhel 1st Floor, ??????? 44600, Bagmati, Central, Nepal</t>
+        </is>
+      </c>
+      <c r="AF34" s="3" t="inlineStr">
+        <is>
+          <t>bellofornepal@gmail.com</t>
+        </is>
+      </c>
+      <c r="AG34" s="3" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="AH34" s="3" t="inlineStr"/>
+      <c r="AI34" s="3" t="inlineStr">
+        <is>
+          <t>03:33 hour</t>
+        </is>
+      </c>
+      <c r="AJ34" s="3" t="inlineStr"/>
+      <c r="AK34" s="3" t="inlineStr"/>
+      <c r="AL34" s="3" t="inlineStr">
+        <is>
+          <t>Puja Khadka</t>
+        </is>
+      </c>
+      <c r="AM34" s="3" t="inlineStr">
+        <is>
+          <t>Rajesh Maharjan</t>
+        </is>
+      </c>
+      <c r="AN34" s="3" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AO34" s="3" t="inlineStr">
+        <is>
+          <t>1,7</t>
+        </is>
+      </c>
+      <c r="AP34" s="3" t="inlineStr">
+        <is>
+          <t>85.31601</t>
+        </is>
+      </c>
+      <c r="AQ34" s="3" t="inlineStr"/>
+      <c r="AR34" s="3" t="inlineStr">
+        <is>
+          <t>Case : WIFI 6  has been updated by Rajesh Maharjan</t>
+        </is>
+      </c>
+      <c r="AS34" s="3" t="inlineStr">
         <is>
           <t>0m</t>
         </is>
       </c>
-      <c r="AT33" s="3" t="inlineStr">
-        <is>
-          <t>18h 22m</t>
-        </is>
-      </c>
-      <c r="AU33" s="3" t="inlineStr">
+      <c r="AT34" s="3" t="inlineStr">
+        <is>
+          <t>3h 33m</t>
+        </is>
+      </c>
+      <c r="AU34" s="3" t="inlineStr">
         <is>
           <t>Completed (Completed)</t>
         </is>
       </c>
-      <c r="AV33" s="3" t="inlineStr">
-        <is>
-          <t>Case : For upgradation to wifi6   has been updated by Chandramani Tharu</t>
-        </is>
-      </c>
-      <c r="AW33" s="3" t="inlineStr">
+      <c r="AV34" s="3" t="inlineStr">
+        <is>
+          <t>Case : WIFI 6  has been updated by Rajesh Maharjan</t>
+        </is>
+      </c>
+      <c r="AW34" s="3" t="inlineStr">
+        <is>
+          <t>WiFi 6 Upgrade</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="3" t="inlineStr">
+        <is>
+          <t>Ajit Shrestha</t>
+        </is>
+      </c>
+      <c r="B35" s="3" t="inlineStr">
+        <is>
+          <t>23 Sep 2026 3:48 PM</t>
+        </is>
+      </c>
+      <c r="C35" s="3" t="inlineStr">
+        <is>
+          <t>KK1e4rFHODw22QGqrKXwiw==</t>
+        </is>
+      </c>
+      <c r="D35" s="3" t="inlineStr">
+        <is>
+          <t>Ajit Shrestha</t>
+        </is>
+      </c>
+      <c r="E35" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F35" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G35" s="3" t="inlineStr"/>
+      <c r="H35" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi 6  has been updated by Ajit Shrestha</t>
+        </is>
+      </c>
+      <c r="I35" s="3" t="inlineStr">
+        <is>
+          <t>wifi 6</t>
+        </is>
+      </c>
+      <c r="J35" s="3" t="inlineStr">
+        <is>
+          <t>TKT1343460</t>
+        </is>
+      </c>
+      <c r="K35" s="3" t="inlineStr">
+        <is>
+          <t>GPRS Mobile</t>
+        </is>
+      </c>
+      <c r="L35" s="3" t="inlineStr">
+        <is>
+          <t>Closed</t>
+        </is>
+      </c>
+      <c r="M35" s="3" t="inlineStr">
+        <is>
+          <t>Phone</t>
+        </is>
+      </c>
+      <c r="N35" s="3" t="inlineStr">
+        <is>
+          <t>GPRS Mobile</t>
+        </is>
+      </c>
+      <c r="O35" s="3" t="inlineStr">
+        <is>
+          <t>9851325203</t>
+        </is>
+      </c>
+      <c r="P35" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="Q35" s="3" t="inlineStr"/>
+      <c r="R35" s="3" t="inlineStr">
+        <is>
+          <t>23 Sep 2026 10:29:49 AM</t>
+        </is>
+      </c>
+      <c r="S35" s="3" t="inlineStr"/>
+      <c r="T35" s="3" t="inlineStr"/>
+      <c r="U35" s="3" t="inlineStr">
+        <is>
+          <t>9801134229g</t>
+        </is>
+      </c>
+      <c r="V35" s="3" t="inlineStr">
+        <is>
+          <t>23 Sep 2026 10:29:49 AM</t>
+        </is>
+      </c>
+      <c r="W35" s="3" t="inlineStr">
+        <is>
+          <t>23 Sep 2026 03:48:08 PM</t>
+        </is>
+      </c>
+      <c r="X35" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Y35" s="3" t="inlineStr">
+        <is>
+          <t>27.69255</t>
+        </is>
+      </c>
+      <c r="Z35" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="AA35" s="3" t="inlineStr">
+        <is>
+          <t>Layer 1-</t>
+        </is>
+      </c>
+      <c r="AB35" s="3" t="inlineStr">
+        <is>
+          <t>Laxman Koirala</t>
+        </is>
+      </c>
+      <c r="AC35" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="AD35" s="3" t="inlineStr"/>
+      <c r="AE35" s="3" t="inlineStr">
+        <is>
+          <t>Sanrachana Gall Near Astanga Ayurveda Hospital And Research Center,Kathmandu, Bagmati, Central, Nepa</t>
+        </is>
+      </c>
+      <c r="AF35" s="3" t="inlineStr">
+        <is>
+          <t>rinashrestha443@gmail.com</t>
+        </is>
+      </c>
+      <c r="AG35" s="3" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="AH35" s="3" t="inlineStr"/>
+      <c r="AI35" s="3" t="inlineStr">
+        <is>
+          <t>05:18 hour</t>
+        </is>
+      </c>
+      <c r="AJ35" s="3" t="inlineStr"/>
+      <c r="AK35" s="3" t="inlineStr"/>
+      <c r="AL35" s="3" t="inlineStr">
+        <is>
+          <t>Bipana Neupane</t>
+        </is>
+      </c>
+      <c r="AM35" s="3" t="inlineStr">
+        <is>
+          <t>Ajit Shrestha</t>
+        </is>
+      </c>
+      <c r="AN35" s="3" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AO35" s="3" t="inlineStr">
+        <is>
+          <t>2,6</t>
+        </is>
+      </c>
+      <c r="AP35" s="3" t="inlineStr">
+        <is>
+          <t>85.28275</t>
+        </is>
+      </c>
+      <c r="AQ35" s="3" t="inlineStr"/>
+      <c r="AR35" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi 6  has been updated by Ajit Shrestha</t>
+        </is>
+      </c>
+      <c r="AS35" s="3" t="inlineStr">
+        <is>
+          <t>5h 18m</t>
+        </is>
+      </c>
+      <c r="AT35" s="3" t="inlineStr">
+        <is>
+          <t>5h 18m</t>
+        </is>
+      </c>
+      <c r="AU35" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Closed)</t>
+        </is>
+      </c>
+      <c r="AV35" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi 6  has been updated by Ajit Shrestha</t>
+        </is>
+      </c>
+      <c r="AW35" s="3" t="inlineStr">
+        <is>
+          <t>WiFi 6 Upgrade</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="3" t="inlineStr">
+        <is>
+          <t>Ajit Shrestha</t>
+        </is>
+      </c>
+      <c r="B36" s="3" t="inlineStr">
+        <is>
+          <t>23 Sep 2026 3:47 PM</t>
+        </is>
+      </c>
+      <c r="C36" s="3" t="inlineStr">
+        <is>
+          <t>KK1e4rFHODw22QGqrKXwiw==</t>
+        </is>
+      </c>
+      <c r="D36" s="3" t="inlineStr">
+        <is>
+          <t>Ajit Shrestha</t>
+        </is>
+      </c>
+      <c r="E36" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F36" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G36" s="3" t="inlineStr"/>
+      <c r="H36" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi 6  has been updated by Ajit Shrestha</t>
+        </is>
+      </c>
+      <c r="I36" s="3" t="inlineStr">
+        <is>
+          <t>wifi 6</t>
+        </is>
+      </c>
+      <c r="J36" s="3" t="inlineStr">
+        <is>
+          <t>TKT1343460</t>
+        </is>
+      </c>
+      <c r="K36" s="3" t="inlineStr">
+        <is>
+          <t>GPRS Mobile</t>
+        </is>
+      </c>
+      <c r="L36" s="3" t="inlineStr">
+        <is>
+          <t>Closed</t>
+        </is>
+      </c>
+      <c r="M36" s="3" t="inlineStr">
+        <is>
+          <t>Phone</t>
+        </is>
+      </c>
+      <c r="N36" s="3" t="inlineStr">
+        <is>
+          <t>GPRS Mobile</t>
+        </is>
+      </c>
+      <c r="O36" s="3" t="inlineStr">
+        <is>
+          <t>9851325203</t>
+        </is>
+      </c>
+      <c r="P36" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="Q36" s="3" t="inlineStr"/>
+      <c r="R36" s="3" t="inlineStr">
+        <is>
+          <t>23 Sep 2026 10:29:49 AM</t>
+        </is>
+      </c>
+      <c r="S36" s="3" t="inlineStr"/>
+      <c r="T36" s="3" t="inlineStr"/>
+      <c r="U36" s="3" t="inlineStr">
+        <is>
+          <t>9801134229g</t>
+        </is>
+      </c>
+      <c r="V36" s="3" t="inlineStr">
+        <is>
+          <t>23 Sep 2026 10:29:49 AM</t>
+        </is>
+      </c>
+      <c r="W36" s="3" t="inlineStr">
+        <is>
+          <t>23 Sep 2026 03:48:08 PM</t>
+        </is>
+      </c>
+      <c r="X36" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Y36" s="3" t="inlineStr">
+        <is>
+          <t>27.69255</t>
+        </is>
+      </c>
+      <c r="Z36" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="AA36" s="3" t="inlineStr">
+        <is>
+          <t>Layer 1-</t>
+        </is>
+      </c>
+      <c r="AB36" s="3" t="inlineStr">
+        <is>
+          <t>Laxman Koirala</t>
+        </is>
+      </c>
+      <c r="AC36" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="AD36" s="3" t="inlineStr"/>
+      <c r="AE36" s="3" t="inlineStr">
+        <is>
+          <t>Sanrachana Gall Near Astanga Ayurveda Hospital And Research Center,Kathmandu, Bagmati, Central, Nepa</t>
+        </is>
+      </c>
+      <c r="AF36" s="3" t="inlineStr">
+        <is>
+          <t>rinashrestha443@gmail.com</t>
+        </is>
+      </c>
+      <c r="AG36" s="3" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="AH36" s="3" t="inlineStr"/>
+      <c r="AI36" s="3" t="inlineStr">
+        <is>
+          <t>05:18 hour</t>
+        </is>
+      </c>
+      <c r="AJ36" s="3" t="inlineStr"/>
+      <c r="AK36" s="3" t="inlineStr"/>
+      <c r="AL36" s="3" t="inlineStr">
+        <is>
+          <t>Bipana Neupane</t>
+        </is>
+      </c>
+      <c r="AM36" s="3" t="inlineStr">
+        <is>
+          <t>Ajit Shrestha</t>
+        </is>
+      </c>
+      <c r="AN36" s="3" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AO36" s="3" t="inlineStr">
+        <is>
+          <t>2,6</t>
+        </is>
+      </c>
+      <c r="AP36" s="3" t="inlineStr">
+        <is>
+          <t>85.28275</t>
+        </is>
+      </c>
+      <c r="AQ36" s="3" t="inlineStr"/>
+      <c r="AR36" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi 6  has been updated by Ajit Shrestha</t>
+        </is>
+      </c>
+      <c r="AS36" s="3" t="inlineStr">
+        <is>
+          <t>5h 18m</t>
+        </is>
+      </c>
+      <c r="AT36" s="3" t="inlineStr">
+        <is>
+          <t>5h 18m</t>
+        </is>
+      </c>
+      <c r="AU36" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Closed)</t>
+        </is>
+      </c>
+      <c r="AV36" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi 6  has been updated by Ajit Shrestha</t>
+        </is>
+      </c>
+      <c r="AW36" s="3" t="inlineStr">
         <is>
           <t>WiFi 6 Upgrade</t>
         </is>
@@ -6635,7 +7252,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M51"/>
+  <dimension ref="A1:M54"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="45" customWidth="1" min="1" max="1"/>
@@ -6672,7 +7289,7 @@
         </is>
       </c>
       <c r="B2" s="3" t="n">
-        <v>32</v>
+        <v>35</v>
       </c>
     </row>
     <row r="3">
@@ -6682,7 +7299,7 @@
         </is>
       </c>
       <c r="B3" s="5" t="n">
-        <v>21</v>
+        <v>24</v>
       </c>
     </row>
     <row r="4">
@@ -6693,7 +7310,7 @@
       </c>
       <c r="B4" s="3" t="inlineStr">
         <is>
-          <t>65.6%</t>
+          <t>68.6%</t>
         </is>
       </c>
     </row>
@@ -6705,7 +7322,7 @@
       </c>
       <c r="B5" s="5" t="inlineStr">
         <is>
-          <t>6h 51m</t>
+          <t>6h 26m</t>
         </is>
       </c>
     </row>
@@ -6717,7 +7334,7 @@
       </c>
       <c r="B6" s="3" t="inlineStr">
         <is>
-          <t>23h 34m</t>
+          <t>21h 13m</t>
         </is>
       </c>
     </row>
@@ -6758,14 +7375,14 @@
         </is>
       </c>
       <c r="B10" s="3" t="n">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="C10" s="3" t="n">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="D10" s="3" t="inlineStr">
         <is>
-          <t>76.5%</t>
+          <t>80.0%</t>
         </is>
       </c>
     </row>
@@ -6925,14 +7542,14 @@
         </is>
       </c>
       <c r="C20" s="3" t="n">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="D20" s="3" t="n">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="E20" s="3" t="inlineStr">
         <is>
-          <t>73.3%</t>
+          <t>77.8%</t>
         </is>
       </c>
     </row>
@@ -8403,7 +9020,7 @@
       </c>
       <c r="G49" s="5" t="inlineStr">
         <is>
-          <t>Case : IPTV  Isssue  has been updated by Sunil Chaudhary</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="H49" s="5" t="inlineStr">
@@ -8470,7 +9087,7 @@
       </c>
       <c r="G50" s="3" t="inlineStr">
         <is>
-          <t>Case : IPTV  Isssue  has been updated by Sunil Chaudhary</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="H50" s="3" t="inlineStr">
@@ -8537,14 +9154,14 @@
       </c>
       <c r="G51" s="5" t="inlineStr">
         <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="H51" s="5" t="inlineStr">
+        <is>
           <t>Case : For upgradation to wifi6   has been updated by Chandramani Tharu</t>
         </is>
       </c>
-      <c r="H51" s="5" t="inlineStr">
-        <is>
-          <t>Case : For upgradation to wifi6   has been updated by Chandramani Tharu</t>
-        </is>
-      </c>
       <c r="I51" s="5" t="inlineStr">
         <is>
           <t>23 Sep 2026 03:21:49 PM</t>
@@ -8568,6 +9185,207 @@
       <c r="M51" s="5" t="inlineStr">
         <is>
           <t>18h 22m</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="3" t="inlineStr">
+        <is>
+          <t>TKT1343673</t>
+        </is>
+      </c>
+      <c r="B52" s="3" t="inlineStr">
+        <is>
+          <t>Bello World Pvt.Ltd</t>
+        </is>
+      </c>
+      <c r="C52" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="D52" s="3" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="E52" s="3" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="F52" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Completed)</t>
+        </is>
+      </c>
+      <c r="G52" s="3" t="inlineStr">
+        <is>
+          <t>Case : WIFI 6  has been updated by Rajesh Maharjan</t>
+        </is>
+      </c>
+      <c r="H52" s="3" t="inlineStr">
+        <is>
+          <t>Case : WIFI 6  has been updated by Rajesh Maharjan</t>
+        </is>
+      </c>
+      <c r="I52" s="3" t="inlineStr">
+        <is>
+          <t>23 Sep 2026 03:58:20 PM</t>
+        </is>
+      </c>
+      <c r="J52" s="3" t="inlineStr">
+        <is>
+          <t>23 Sep 2026 12:25:04 PM</t>
+        </is>
+      </c>
+      <c r="K52" s="3" t="inlineStr">
+        <is>
+          <t>23 Sep 2026 03:58:20 PM</t>
+        </is>
+      </c>
+      <c r="L52" s="3" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="M52" s="3" t="inlineStr">
+        <is>
+          <t>3h 33m</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="5" t="inlineStr">
+        <is>
+          <t>TKT1343460</t>
+        </is>
+      </c>
+      <c r="B53" s="5" t="inlineStr">
+        <is>
+          <t>GPRS Mobile</t>
+        </is>
+      </c>
+      <c r="C53" s="5" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="D53" s="5" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="E53" s="5" t="inlineStr">
+        <is>
+          <t>Closed</t>
+        </is>
+      </c>
+      <c r="F53" s="5" t="inlineStr">
+        <is>
+          <t>Completed (Closed)</t>
+        </is>
+      </c>
+      <c r="G53" s="5" t="inlineStr">
+        <is>
+          <t>Case : wifi 6  has been updated by Ajit Shrestha</t>
+        </is>
+      </c>
+      <c r="H53" s="5" t="inlineStr">
+        <is>
+          <t>Case : wifi 6  has been updated by Ajit Shrestha</t>
+        </is>
+      </c>
+      <c r="I53" s="5" t="inlineStr">
+        <is>
+          <t>23 Sep 2026 10:29:49 AM</t>
+        </is>
+      </c>
+      <c r="J53" s="5" t="inlineStr">
+        <is>
+          <t>23 Sep 2026 10:29:49 AM</t>
+        </is>
+      </c>
+      <c r="K53" s="5" t="inlineStr">
+        <is>
+          <t>23 Sep 2026 03:48:08 PM</t>
+        </is>
+      </c>
+      <c r="L53" s="5" t="inlineStr">
+        <is>
+          <t>5h 18m</t>
+        </is>
+      </c>
+      <c r="M53" s="5" t="inlineStr">
+        <is>
+          <t>5h 18m</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="3" t="inlineStr">
+        <is>
+          <t>TKT1343460</t>
+        </is>
+      </c>
+      <c r="B54" s="3" t="inlineStr">
+        <is>
+          <t>GPRS Mobile</t>
+        </is>
+      </c>
+      <c r="C54" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="D54" s="3" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="E54" s="3" t="inlineStr">
+        <is>
+          <t>Closed</t>
+        </is>
+      </c>
+      <c r="F54" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Closed)</t>
+        </is>
+      </c>
+      <c r="G54" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi 6  has been updated by Ajit Shrestha</t>
+        </is>
+      </c>
+      <c r="H54" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi 6  has been updated by Ajit Shrestha</t>
+        </is>
+      </c>
+      <c r="I54" s="3" t="inlineStr">
+        <is>
+          <t>23 Sep 2026 10:29:49 AM</t>
+        </is>
+      </c>
+      <c r="J54" s="3" t="inlineStr">
+        <is>
+          <t>23 Sep 2026 10:29:49 AM</t>
+        </is>
+      </c>
+      <c r="K54" s="3" t="inlineStr">
+        <is>
+          <t>23 Sep 2026 03:48:08 PM</t>
+        </is>
+      </c>
+      <c r="L54" s="3" t="inlineStr">
+        <is>
+          <t>5h 18m</t>
+        </is>
+      </c>
+      <c r="M54" s="3" t="inlineStr">
+        <is>
+          <t>5h 18m</t>
         </is>
       </c>
     </row>

--- a/audit_report_ALL_TEAM_23_Sep_2026.xlsx
+++ b/audit_report_ALL_TEAM_23_Sep_2026.xlsx
@@ -483,7 +483,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AW36"/>
+  <dimension ref="A1:AW39"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="23" customWidth="1" min="1" max="1"/>
@@ -6675,10 +6675,8 @@
           <t>Bello World Pvt.Ltd</t>
         </is>
       </c>
-      <c r="O34" s="3" t="inlineStr">
-        <is>
-          <t>9702651054</t>
-        </is>
+      <c r="O34" s="3" t="n">
+        <v>9702651054</v>
       </c>
       <c r="P34" s="3" t="inlineStr">
         <is>
@@ -6713,10 +6711,8 @@
           <t>Active</t>
         </is>
       </c>
-      <c r="Y34" s="3" t="inlineStr">
-        <is>
-          <t>27.6721</t>
-        </is>
+      <c r="Y34" s="3" t="n">
+        <v>27.6721</v>
       </c>
       <c r="Z34" s="3" t="inlineStr">
         <is>
@@ -6772,25 +6768,21 @@
           <t>Rajesh Maharjan</t>
         </is>
       </c>
-      <c r="AN34" s="3" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
+      <c r="AN34" s="3" t="n">
+        <v>4</v>
       </c>
       <c r="AO34" s="3" t="inlineStr">
         <is>
           <t>1,7</t>
         </is>
       </c>
-      <c r="AP34" s="3" t="inlineStr">
-        <is>
-          <t>85.31601</t>
-        </is>
+      <c r="AP34" s="3" t="n">
+        <v>85.31601000000001</v>
       </c>
       <c r="AQ34" s="3" t="inlineStr"/>
       <c r="AR34" s="3" t="inlineStr">
         <is>
-          <t>Case : WIFI 6  has been updated by Rajesh Maharjan</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="AS34" s="3" t="inlineStr">
@@ -6886,10 +6878,8 @@
           <t>GPRS Mobile</t>
         </is>
       </c>
-      <c r="O35" s="3" t="inlineStr">
-        <is>
-          <t>9851325203</t>
-        </is>
+      <c r="O35" s="3" t="n">
+        <v>9851325203</v>
       </c>
       <c r="P35" s="3" t="inlineStr">
         <is>
@@ -6924,10 +6914,8 @@
           <t>Active</t>
         </is>
       </c>
-      <c r="Y35" s="3" t="inlineStr">
-        <is>
-          <t>27.69255</t>
-        </is>
+      <c r="Y35" s="3" t="n">
+        <v>27.69255</v>
       </c>
       <c r="Z35" s="3" t="inlineStr">
         <is>
@@ -6983,25 +6971,21 @@
           <t>Ajit Shrestha</t>
         </is>
       </c>
-      <c r="AN35" s="3" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
+      <c r="AN35" s="3" t="n">
+        <v>4</v>
       </c>
       <c r="AO35" s="3" t="inlineStr">
         <is>
           <t>2,6</t>
         </is>
       </c>
-      <c r="AP35" s="3" t="inlineStr">
-        <is>
-          <t>85.28275</t>
-        </is>
+      <c r="AP35" s="3" t="n">
+        <v>85.28274999999999</v>
       </c>
       <c r="AQ35" s="3" t="inlineStr"/>
       <c r="AR35" s="3" t="inlineStr">
         <is>
-          <t>Case : wifi 6  has been updated by Ajit Shrestha</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="AS35" s="3" t="inlineStr">
@@ -7097,10 +7081,8 @@
           <t>GPRS Mobile</t>
         </is>
       </c>
-      <c r="O36" s="3" t="inlineStr">
-        <is>
-          <t>9851325203</t>
-        </is>
+      <c r="O36" s="3" t="n">
+        <v>9851325203</v>
       </c>
       <c r="P36" s="3" t="inlineStr">
         <is>
@@ -7135,10 +7117,8 @@
           <t>Active</t>
         </is>
       </c>
-      <c r="Y36" s="3" t="inlineStr">
-        <is>
-          <t>27.69255</t>
-        </is>
+      <c r="Y36" s="3" t="n">
+        <v>27.69255</v>
       </c>
       <c r="Z36" s="3" t="inlineStr">
         <is>
@@ -7194,50 +7174,663 @@
           <t>Ajit Shrestha</t>
         </is>
       </c>
-      <c r="AN36" s="3" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
+      <c r="AN36" s="3" t="n">
+        <v>4</v>
       </c>
       <c r="AO36" s="3" t="inlineStr">
         <is>
           <t>2,6</t>
         </is>
       </c>
-      <c r="AP36" s="3" t="inlineStr">
-        <is>
-          <t>85.28275</t>
-        </is>
+      <c r="AP36" s="3" t="n">
+        <v>85.28274999999999</v>
       </c>
       <c r="AQ36" s="3" t="inlineStr"/>
       <c r="AR36" s="3" t="inlineStr">
         <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="AS36" s="3" t="inlineStr">
+        <is>
+          <t>5h 18m</t>
+        </is>
+      </c>
+      <c r="AT36" s="3" t="inlineStr">
+        <is>
+          <t>5h 18m</t>
+        </is>
+      </c>
+      <c r="AU36" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Closed)</t>
+        </is>
+      </c>
+      <c r="AV36" s="3" t="inlineStr">
+        <is>
           <t>Case : wifi 6  has been updated by Ajit Shrestha</t>
         </is>
       </c>
-      <c r="AS36" s="3" t="inlineStr">
-        <is>
-          <t>5h 18m</t>
-        </is>
-      </c>
-      <c r="AT36" s="3" t="inlineStr">
-        <is>
-          <t>5h 18m</t>
-        </is>
-      </c>
-      <c r="AU36" s="3" t="inlineStr">
+      <c r="AW36" s="3" t="inlineStr">
+        <is>
+          <t>WiFi 6 Upgrade</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="3" t="inlineStr">
+        <is>
+          <t>Sabin Giri</t>
+        </is>
+      </c>
+      <c r="B37" s="3" t="inlineStr">
+        <is>
+          <t>23 Sep 2026 4:03 PM</t>
+        </is>
+      </c>
+      <c r="C37" s="3" t="inlineStr">
+        <is>
+          <t>WGnmUJF06LTlUriJ5DeDBQ==</t>
+        </is>
+      </c>
+      <c r="D37" s="3" t="inlineStr">
+        <is>
+          <t>Sabin Giri</t>
+        </is>
+      </c>
+      <c r="E37" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F37" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G37" s="3" t="inlineStr"/>
+      <c r="H37" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi6  has been updated by Sabin Giri</t>
+        </is>
+      </c>
+      <c r="I37" s="3" t="inlineStr">
+        <is>
+          <t>wifi6</t>
+        </is>
+      </c>
+      <c r="J37" s="3" t="inlineStr">
+        <is>
+          <t>TKT1343757</t>
+        </is>
+      </c>
+      <c r="K37" s="3" t="inlineStr">
+        <is>
+          <t>Manish Poudel</t>
+        </is>
+      </c>
+      <c r="L37" s="3" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="M37" s="3" t="inlineStr">
+        <is>
+          <t>Phone</t>
+        </is>
+      </c>
+      <c r="N37" s="3" t="inlineStr">
+        <is>
+          <t>Manish Poudel</t>
+        </is>
+      </c>
+      <c r="O37" s="3" t="inlineStr">
+        <is>
+          <t>9849603523</t>
+        </is>
+      </c>
+      <c r="P37" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="Q37" s="3" t="inlineStr"/>
+      <c r="R37" s="3" t="inlineStr">
+        <is>
+          <t>23 Sep 2026 04:03:26 PM</t>
+        </is>
+      </c>
+      <c r="S37" s="3" t="inlineStr"/>
+      <c r="T37" s="3" t="inlineStr"/>
+      <c r="U37" s="3" t="inlineStr">
+        <is>
+          <t>9849603523</t>
+        </is>
+      </c>
+      <c r="V37" s="3" t="inlineStr">
+        <is>
+          <t>23 Sep 2026 01:35:27 PM</t>
+        </is>
+      </c>
+      <c r="W37" s="3" t="inlineStr">
+        <is>
+          <t>23 Sep 2026 04:03:26 PM</t>
+        </is>
+      </c>
+      <c r="X37" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Y37" s="3" t="inlineStr">
+        <is>
+          <t>27.69003</t>
+        </is>
+      </c>
+      <c r="Z37" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="AA37" s="3" t="inlineStr">
+        <is>
+          <t>Layer 1-User</t>
+        </is>
+      </c>
+      <c r="AB37" s="3" t="inlineStr">
+        <is>
+          <t>L1  Support</t>
+        </is>
+      </c>
+      <c r="AC37" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="AD37" s="3" t="inlineStr"/>
+      <c r="AE37" s="3" t="inlineStr">
+        <is>
+          <t>pepsicola ward no 32 near GetUp Men's Wear, kathmandu, Bagmati, Central, Nepal</t>
+        </is>
+      </c>
+      <c r="AF37" s="3" t="inlineStr">
+        <is>
+          <t>poudelmanissh@gmail.com</t>
+        </is>
+      </c>
+      <c r="AG37" s="3" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="AH37" s="3" t="inlineStr"/>
+      <c r="AI37" s="3" t="inlineStr">
+        <is>
+          <t>02:28 hour</t>
+        </is>
+      </c>
+      <c r="AJ37" s="3" t="inlineStr"/>
+      <c r="AK37" s="3" t="inlineStr"/>
+      <c r="AL37" s="3" t="inlineStr">
+        <is>
+          <t>Swastima Silwal</t>
+        </is>
+      </c>
+      <c r="AM37" s="3" t="inlineStr">
+        <is>
+          <t>Sabin Giri</t>
+        </is>
+      </c>
+      <c r="AN37" s="3" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AO37" s="3" t="inlineStr">
+        <is>
+          <t>L11-5</t>
+        </is>
+      </c>
+      <c r="AP37" s="3" t="inlineStr">
+        <is>
+          <t>85.36531</t>
+        </is>
+      </c>
+      <c r="AQ37" s="3" t="inlineStr"/>
+      <c r="AR37" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi6  has been updated by Sabin Giri</t>
+        </is>
+      </c>
+      <c r="AS37" s="3" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="AT37" s="3" t="inlineStr">
+        <is>
+          <t>2h 27m</t>
+        </is>
+      </c>
+      <c r="AU37" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Completed)</t>
+        </is>
+      </c>
+      <c r="AV37" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi6  has been updated by Sabin Giri</t>
+        </is>
+      </c>
+      <c r="AW37" s="3" t="inlineStr">
+        <is>
+          <t>WiFi 6 Upgrade</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="3" t="inlineStr">
+        <is>
+          <t>Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="B38" s="3" t="inlineStr">
+        <is>
+          <t>23 Sep 2026 4:15 PM</t>
+        </is>
+      </c>
+      <c r="C38" s="3" t="inlineStr">
+        <is>
+          <t>Zg1bIUI+iSmQ1fi360NaxA==</t>
+        </is>
+      </c>
+      <c r="D38" s="3" t="inlineStr">
+        <is>
+          <t>Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="E38" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F38" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G38" s="3" t="inlineStr"/>
+      <c r="H38" s="3" t="inlineStr">
+        <is>
+          <t>Case : Wifi 6  has been updated by Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="I38" s="3" t="inlineStr">
+        <is>
+          <t>Wifi 6</t>
+        </is>
+      </c>
+      <c r="J38" s="3" t="inlineStr">
+        <is>
+          <t>TKT1343695</t>
+        </is>
+      </c>
+      <c r="K38" s="3" t="inlineStr">
+        <is>
+          <t>Kabiraj Maharjan</t>
+        </is>
+      </c>
+      <c r="L38" s="3" t="inlineStr">
+        <is>
+          <t>Closed</t>
+        </is>
+      </c>
+      <c r="M38" s="3" t="inlineStr">
+        <is>
+          <t>Phone</t>
+        </is>
+      </c>
+      <c r="N38" s="3" t="inlineStr">
+        <is>
+          <t>Kabiraj Maharjan</t>
+        </is>
+      </c>
+      <c r="O38" s="3" t="inlineStr">
+        <is>
+          <t>9841731762</t>
+        </is>
+      </c>
+      <c r="P38" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="Q38" s="3" t="inlineStr"/>
+      <c r="R38" s="3" t="inlineStr">
+        <is>
+          <t>23 Sep 2026 12:45:30 PM</t>
+        </is>
+      </c>
+      <c r="S38" s="3" t="inlineStr"/>
+      <c r="T38" s="3" t="inlineStr"/>
+      <c r="U38" s="3" t="inlineStr">
+        <is>
+          <t>9841559266</t>
+        </is>
+      </c>
+      <c r="V38" s="3" t="inlineStr">
+        <is>
+          <t>23 Sep 2026 12:45:30 PM</t>
+        </is>
+      </c>
+      <c r="W38" s="3" t="inlineStr">
+        <is>
+          <t>23 Sep 2026 04:15:46 PM</t>
+        </is>
+      </c>
+      <c r="X38" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Y38" s="3" t="inlineStr">
+        <is>
+          <t>27.68864</t>
+        </is>
+      </c>
+      <c r="Z38" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="AA38" s="3" t="inlineStr">
+        <is>
+          <t>Layer 1-</t>
+        </is>
+      </c>
+      <c r="AB38" s="3" t="inlineStr">
+        <is>
+          <t>Laxman Koirala</t>
+        </is>
+      </c>
+      <c r="AC38" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="AD38" s="3" t="inlineStr"/>
+      <c r="AE38" s="3" t="inlineStr">
+        <is>
+          <t>M7QC+C7R, Prithvi Hwy, Chandragiri ,Near by Tasty MoMo , Bagmati, Central, Nepal</t>
+        </is>
+      </c>
+      <c r="AF38" s="3" t="inlineStr"/>
+      <c r="AG38" s="3" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="AH38" s="3" t="inlineStr"/>
+      <c r="AI38" s="3" t="inlineStr">
+        <is>
+          <t>03:30 hour</t>
+        </is>
+      </c>
+      <c r="AJ38" s="3" t="inlineStr"/>
+      <c r="AK38" s="3" t="inlineStr"/>
+      <c r="AL38" s="3" t="inlineStr">
+        <is>
+          <t>Joshna Shrestha</t>
+        </is>
+      </c>
+      <c r="AM38" s="3" t="inlineStr">
+        <is>
+          <t>Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="AN38" s="3" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AO38" s="3" t="inlineStr">
+        <is>
+          <t>4,7</t>
+        </is>
+      </c>
+      <c r="AP38" s="3" t="inlineStr">
+        <is>
+          <t>85.27068</t>
+        </is>
+      </c>
+      <c r="AQ38" s="3" t="inlineStr"/>
+      <c r="AR38" s="3" t="inlineStr">
+        <is>
+          <t>Case : Wifi 6  has been updated by Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="AS38" s="3" t="inlineStr">
+        <is>
+          <t>3h 30m</t>
+        </is>
+      </c>
+      <c r="AT38" s="3" t="inlineStr">
+        <is>
+          <t>3h 30m</t>
+        </is>
+      </c>
+      <c r="AU38" s="3" t="inlineStr">
         <is>
           <t>Completed (Closed)</t>
         </is>
       </c>
-      <c r="AV36" s="3" t="inlineStr">
-        <is>
-          <t>Case : wifi 6  has been updated by Ajit Shrestha</t>
-        </is>
-      </c>
-      <c r="AW36" s="3" t="inlineStr">
+      <c r="AV38" s="3" t="inlineStr">
+        <is>
+          <t>Case : Wifi 6  has been updated by Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="AW38" s="3" t="inlineStr">
         <is>
           <t>WiFi 6 Upgrade</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="3" t="inlineStr">
+        <is>
+          <t>Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="B39" s="3" t="inlineStr">
+        <is>
+          <t>23 Sep 2026 4:06 PM</t>
+        </is>
+      </c>
+      <c r="C39" s="3" t="inlineStr">
+        <is>
+          <t>atwz5SElGeKMz8qxsp3b6c34SBAfIMR+</t>
+        </is>
+      </c>
+      <c r="D39" s="3" t="inlineStr">
+        <is>
+          <t>Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="E39" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F39" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G39" s="3" t="inlineStr"/>
+      <c r="H39" s="3" t="inlineStr">
+        <is>
+          <t>Case : slow issue field visit  has been updated by Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="I39" s="3" t="inlineStr">
+        <is>
+          <t>slow issue field visit</t>
+        </is>
+      </c>
+      <c r="J39" s="3" t="inlineStr">
+        <is>
+          <t>TKT1342535</t>
+        </is>
+      </c>
+      <c r="K39" s="3" t="inlineStr">
+        <is>
+          <t>madan shahi</t>
+        </is>
+      </c>
+      <c r="L39" s="3" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="M39" s="3" t="inlineStr">
+        <is>
+          <t>Phone</t>
+        </is>
+      </c>
+      <c r="N39" s="3" t="inlineStr">
+        <is>
+          <t>madan shahi</t>
+        </is>
+      </c>
+      <c r="O39" s="3" t="inlineStr">
+        <is>
+          <t>9851079058</t>
+        </is>
+      </c>
+      <c r="P39" s="3" t="inlineStr">
+        <is>
+          <t>Slow Internet Connection</t>
+        </is>
+      </c>
+      <c r="Q39" s="3" t="inlineStr"/>
+      <c r="R39" s="3" t="inlineStr">
+        <is>
+          <t>23 Sep 2026 04:06:38 PM</t>
+        </is>
+      </c>
+      <c r="S39" s="3" t="inlineStr"/>
+      <c r="T39" s="3" t="inlineStr"/>
+      <c r="U39" s="3" t="inlineStr">
+        <is>
+          <t>9851079058M</t>
+        </is>
+      </c>
+      <c r="V39" s="3" t="inlineStr">
+        <is>
+          <t>22 Sep 2026 02:45:24 PM</t>
+        </is>
+      </c>
+      <c r="W39" s="3" t="inlineStr">
+        <is>
+          <t>23 Sep 2026 04:06:38 PM</t>
+        </is>
+      </c>
+      <c r="X39" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Y39" s="3" t="inlineStr"/>
+      <c r="Z39" s="3" t="inlineStr">
+        <is>
+          <t>Slow Internet Connection</t>
+        </is>
+      </c>
+      <c r="AA39" s="3" t="inlineStr">
+        <is>
+          <t>Layer 1-User</t>
+        </is>
+      </c>
+      <c r="AB39" s="3" t="inlineStr">
+        <is>
+          <t>L1  Support</t>
+        </is>
+      </c>
+      <c r="AC39" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="AD39" s="3" t="inlineStr"/>
+      <c r="AE39" s="3" t="inlineStr">
+        <is>
+          <t>27.686027,85.332714, Bagmati, Nepal, Nepal</t>
+        </is>
+      </c>
+      <c r="AF39" s="3" t="inlineStr"/>
+      <c r="AG39" s="3" t="inlineStr">
+        <is>
+          <t>Video content is Buffering</t>
+        </is>
+      </c>
+      <c r="AH39" s="3" t="inlineStr"/>
+      <c r="AI39" s="3" t="inlineStr">
+        <is>
+          <t>11:21 hour</t>
+        </is>
+      </c>
+      <c r="AJ39" s="3" t="inlineStr"/>
+      <c r="AK39" s="3" t="inlineStr"/>
+      <c r="AL39" s="3" t="inlineStr">
+        <is>
+          <t>Aashna Pulami</t>
+        </is>
+      </c>
+      <c r="AM39" s="3" t="inlineStr">
+        <is>
+          <t>Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="AN39" s="3" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AO39" s="3" t="inlineStr">
+        <is>
+          <t>1,3</t>
+        </is>
+      </c>
+      <c r="AP39" s="3" t="inlineStr"/>
+      <c r="AQ39" s="3" t="inlineStr"/>
+      <c r="AR39" s="3" t="inlineStr">
+        <is>
+          <t>Case : slow issue field visit  has been updated by Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="AS39" s="3" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="AT39" s="3" t="inlineStr">
+        <is>
+          <t>1d 1h 21m</t>
+        </is>
+      </c>
+      <c r="AU39" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Completed)</t>
+        </is>
+      </c>
+      <c r="AV39" s="3" t="inlineStr">
+        <is>
+          <t>Case : slow issue field visit  has been updated by Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="AW39" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
         </is>
       </c>
     </row>
@@ -7252,7 +7845,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M54"/>
+  <dimension ref="A1:M57"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="45" customWidth="1" min="1" max="1"/>
@@ -7289,7 +7882,7 @@
         </is>
       </c>
       <c r="B2" s="3" t="n">
-        <v>35</v>
+        <v>38</v>
       </c>
     </row>
     <row r="3">
@@ -7299,7 +7892,7 @@
         </is>
       </c>
       <c r="B3" s="5" t="n">
-        <v>24</v>
+        <v>27</v>
       </c>
     </row>
     <row r="4">
@@ -7310,7 +7903,7 @@
       </c>
       <c r="B4" s="3" t="inlineStr">
         <is>
-          <t>68.6%</t>
+          <t>71.1%</t>
         </is>
       </c>
     </row>
@@ -7322,7 +7915,7 @@
       </c>
       <c r="B5" s="5" t="inlineStr">
         <is>
-          <t>6h 26m</t>
+          <t>5h 51m</t>
         </is>
       </c>
     </row>
@@ -7334,7 +7927,7 @@
       </c>
       <c r="B6" s="3" t="inlineStr">
         <is>
-          <t>21h 13m</t>
+          <t>20h 1m</t>
         </is>
       </c>
     </row>
@@ -7375,14 +7968,14 @@
         </is>
       </c>
       <c r="B10" s="3" t="n">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="C10" s="3" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="D10" s="3" t="inlineStr">
         <is>
-          <t>80.0%</t>
+          <t>81.8%</t>
         </is>
       </c>
     </row>
@@ -7447,14 +8040,14 @@
         </is>
       </c>
       <c r="B14" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="C14" s="3" t="n">
         <v>2</v>
       </c>
-      <c r="C14" s="3" t="n">
-        <v>1</v>
-      </c>
       <c r="D14" s="3" t="inlineStr">
         <is>
-          <t>50.0%</t>
+          <t>66.7%</t>
         </is>
       </c>
     </row>
@@ -7542,14 +8135,14 @@
         </is>
       </c>
       <c r="C20" s="3" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="D20" s="3" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="E20" s="3" t="inlineStr">
         <is>
-          <t>77.8%</t>
+          <t>80.0%</t>
         </is>
       </c>
     </row>
@@ -7680,14 +8273,14 @@
         </is>
       </c>
       <c r="C26" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="D26" s="3" t="n">
         <v>2</v>
       </c>
-      <c r="D26" s="3" t="n">
-        <v>1</v>
-      </c>
       <c r="E26" s="3" t="inlineStr">
         <is>
-          <t>50.0%</t>
+          <t>66.7%</t>
         </is>
       </c>
     </row>
@@ -9221,7 +9814,7 @@
       </c>
       <c r="G52" s="3" t="inlineStr">
         <is>
-          <t>Case : WIFI 6  has been updated by Rajesh Maharjan</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="H52" s="3" t="inlineStr">
@@ -9288,7 +9881,7 @@
       </c>
       <c r="G53" s="5" t="inlineStr">
         <is>
-          <t>Case : wifi 6  has been updated by Ajit Shrestha</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="H53" s="5" t="inlineStr">
@@ -9355,14 +9948,14 @@
       </c>
       <c r="G54" s="3" t="inlineStr">
         <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="H54" s="3" t="inlineStr">
+        <is>
           <t>Case : wifi 6  has been updated by Ajit Shrestha</t>
         </is>
       </c>
-      <c r="H54" s="3" t="inlineStr">
-        <is>
-          <t>Case : wifi 6  has been updated by Ajit Shrestha</t>
-        </is>
-      </c>
       <c r="I54" s="3" t="inlineStr">
         <is>
           <t>23 Sep 2026 10:29:49 AM</t>
@@ -9386,6 +9979,207 @@
       <c r="M54" s="3" t="inlineStr">
         <is>
           <t>5h 18m</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="5" t="inlineStr">
+        <is>
+          <t>TKT1343757</t>
+        </is>
+      </c>
+      <c r="B55" s="5" t="inlineStr">
+        <is>
+          <t>Manish Poudel</t>
+        </is>
+      </c>
+      <c r="C55" s="5" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="D55" s="5" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="E55" s="5" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="F55" s="5" t="inlineStr">
+        <is>
+          <t>Completed (Completed)</t>
+        </is>
+      </c>
+      <c r="G55" s="5" t="inlineStr">
+        <is>
+          <t>Case : wifi6  has been updated by Sabin Giri</t>
+        </is>
+      </c>
+      <c r="H55" s="5" t="inlineStr">
+        <is>
+          <t>Case : wifi6  has been updated by Sabin Giri</t>
+        </is>
+      </c>
+      <c r="I55" s="5" t="inlineStr">
+        <is>
+          <t>23 Sep 2026 04:03:26 PM</t>
+        </is>
+      </c>
+      <c r="J55" s="5" t="inlineStr">
+        <is>
+          <t>23 Sep 2026 01:35:27 PM</t>
+        </is>
+      </c>
+      <c r="K55" s="5" t="inlineStr">
+        <is>
+          <t>23 Sep 2026 04:03:26 PM</t>
+        </is>
+      </c>
+      <c r="L55" s="5" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="M55" s="5" t="inlineStr">
+        <is>
+          <t>2h 27m</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="3" t="inlineStr">
+        <is>
+          <t>TKT1343695</t>
+        </is>
+      </c>
+      <c r="B56" s="3" t="inlineStr">
+        <is>
+          <t>Kabiraj Maharjan</t>
+        </is>
+      </c>
+      <c r="C56" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="D56" s="3" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="E56" s="3" t="inlineStr">
+        <is>
+          <t>Closed</t>
+        </is>
+      </c>
+      <c r="F56" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Closed)</t>
+        </is>
+      </c>
+      <c r="G56" s="3" t="inlineStr">
+        <is>
+          <t>Case : Wifi 6  has been updated by Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="H56" s="3" t="inlineStr">
+        <is>
+          <t>Case : Wifi 6  has been updated by Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="I56" s="3" t="inlineStr">
+        <is>
+          <t>23 Sep 2026 12:45:30 PM</t>
+        </is>
+      </c>
+      <c r="J56" s="3" t="inlineStr">
+        <is>
+          <t>23 Sep 2026 12:45:30 PM</t>
+        </is>
+      </c>
+      <c r="K56" s="3" t="inlineStr">
+        <is>
+          <t>23 Sep 2026 04:15:46 PM</t>
+        </is>
+      </c>
+      <c r="L56" s="3" t="inlineStr">
+        <is>
+          <t>3h 30m</t>
+        </is>
+      </c>
+      <c r="M56" s="3" t="inlineStr">
+        <is>
+          <t>3h 30m</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" s="5" t="inlineStr">
+        <is>
+          <t>TKT1342535</t>
+        </is>
+      </c>
+      <c r="B57" s="5" t="inlineStr">
+        <is>
+          <t>madan shahi</t>
+        </is>
+      </c>
+      <c r="C57" s="5" t="inlineStr">
+        <is>
+          <t>Slow Internet Connection</t>
+        </is>
+      </c>
+      <c r="D57" s="5" t="inlineStr">
+        <is>
+          <t>Video content is Buffering</t>
+        </is>
+      </c>
+      <c r="E57" s="5" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="F57" s="5" t="inlineStr">
+        <is>
+          <t>Completed (Completed)</t>
+        </is>
+      </c>
+      <c r="G57" s="5" t="inlineStr">
+        <is>
+          <t>Case : slow issue field visit  has been updated by Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="H57" s="5" t="inlineStr">
+        <is>
+          <t>Case : slow issue field visit  has been updated by Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="I57" s="5" t="inlineStr">
+        <is>
+          <t>23 Sep 2026 04:06:38 PM</t>
+        </is>
+      </c>
+      <c r="J57" s="5" t="inlineStr">
+        <is>
+          <t>22 Sep 2026 02:45:24 PM</t>
+        </is>
+      </c>
+      <c r="K57" s="5" t="inlineStr">
+        <is>
+          <t>23 Sep 2026 04:06:38 PM</t>
+        </is>
+      </c>
+      <c r="L57" s="5" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="M57" s="5" t="inlineStr">
+        <is>
+          <t>1d 1h 21m</t>
         </is>
       </c>
     </row>

--- a/audit_report_ALL_TEAM_23_Sep_2026.xlsx
+++ b/audit_report_ALL_TEAM_23_Sep_2026.xlsx
@@ -529,7 +529,7 @@
     <col width="27" customWidth="1" min="41" max="41"/>
     <col width="12" customWidth="1" min="42" max="42"/>
     <col width="17" customWidth="1" min="43" max="43"/>
-    <col width="40" customWidth="1" min="44" max="44"/>
+    <col width="34" customWidth="1" min="44" max="44"/>
     <col width="34" customWidth="1" min="45" max="45"/>
     <col width="33" customWidth="1" min="46" max="46"/>
     <col width="32" customWidth="1" min="47" max="47"/>
@@ -7284,10 +7284,8 @@
           <t>Manish Poudel</t>
         </is>
       </c>
-      <c r="O37" s="3" t="inlineStr">
-        <is>
-          <t>9849603523</t>
-        </is>
+      <c r="O37" s="3" t="n">
+        <v>9849603523</v>
       </c>
       <c r="P37" s="3" t="inlineStr">
         <is>
@@ -7322,10 +7320,8 @@
           <t>Active</t>
         </is>
       </c>
-      <c r="Y37" s="3" t="inlineStr">
-        <is>
-          <t>27.69003</t>
-        </is>
+      <c r="Y37" s="3" t="n">
+        <v>27.69003</v>
       </c>
       <c r="Z37" s="3" t="inlineStr">
         <is>
@@ -7381,25 +7377,21 @@
           <t>Sabin Giri</t>
         </is>
       </c>
-      <c r="AN37" s="3" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
+      <c r="AN37" s="3" t="n">
+        <v>6</v>
       </c>
       <c r="AO37" s="3" t="inlineStr">
         <is>
           <t>L11-5</t>
         </is>
       </c>
-      <c r="AP37" s="3" t="inlineStr">
-        <is>
-          <t>85.36531</t>
-        </is>
+      <c r="AP37" s="3" t="n">
+        <v>85.36530999999999</v>
       </c>
       <c r="AQ37" s="3" t="inlineStr"/>
       <c r="AR37" s="3" t="inlineStr">
         <is>
-          <t>Case : wifi6  has been updated by Sabin Giri</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="AS37" s="3" t="inlineStr">
@@ -7495,10 +7487,8 @@
           <t>Kabiraj Maharjan</t>
         </is>
       </c>
-      <c r="O38" s="3" t="inlineStr">
-        <is>
-          <t>9841731762</t>
-        </is>
+      <c r="O38" s="3" t="n">
+        <v>9841731762</v>
       </c>
       <c r="P38" s="3" t="inlineStr">
         <is>
@@ -7533,10 +7523,8 @@
           <t>Active</t>
         </is>
       </c>
-      <c r="Y38" s="3" t="inlineStr">
-        <is>
-          <t>27.68864</t>
-        </is>
+      <c r="Y38" s="3" t="n">
+        <v>27.68864</v>
       </c>
       <c r="Z38" s="3" t="inlineStr">
         <is>
@@ -7588,25 +7576,21 @@
           <t>Sunil Chaudhary</t>
         </is>
       </c>
-      <c r="AN38" s="3" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
+      <c r="AN38" s="3" t="n">
+        <v>4</v>
       </c>
       <c r="AO38" s="3" t="inlineStr">
         <is>
           <t>4,7</t>
         </is>
       </c>
-      <c r="AP38" s="3" t="inlineStr">
-        <is>
-          <t>85.27068</t>
-        </is>
+      <c r="AP38" s="3" t="n">
+        <v>85.27068</v>
       </c>
       <c r="AQ38" s="3" t="inlineStr"/>
       <c r="AR38" s="3" t="inlineStr">
         <is>
-          <t>Case : Wifi 6  has been updated by Sunil Chaudhary</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="AS38" s="3" t="inlineStr">
@@ -7702,10 +7686,8 @@
           <t>madan shahi</t>
         </is>
       </c>
-      <c r="O39" s="3" t="inlineStr">
-        <is>
-          <t>9851079058</t>
-        </is>
+      <c r="O39" s="3" t="n">
+        <v>9851079058</v>
       </c>
       <c r="P39" s="3" t="inlineStr">
         <is>
@@ -7791,10 +7773,8 @@
           <t>Chandramani Tharu</t>
         </is>
       </c>
-      <c r="AN39" s="3" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
+      <c r="AN39" s="3" t="n">
+        <v>4</v>
       </c>
       <c r="AO39" s="3" t="inlineStr">
         <is>
@@ -7805,7 +7785,7 @@
       <c r="AQ39" s="3" t="inlineStr"/>
       <c r="AR39" s="3" t="inlineStr">
         <is>
-          <t>Case : slow issue field visit  has been updated by Chandramani Tharu</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="AS39" s="3" t="inlineStr">
@@ -7854,7 +7834,7 @@
     <col width="40" customWidth="1" min="4" max="4"/>
     <col width="19" customWidth="1" min="5" max="5"/>
     <col width="25" customWidth="1" min="6" max="6"/>
-    <col width="45" customWidth="1" min="7" max="7"/>
+    <col width="35" customWidth="1" min="7" max="7"/>
     <col width="45" customWidth="1" min="8" max="8"/>
     <col width="27" customWidth="1" min="9" max="9"/>
     <col width="27" customWidth="1" min="10" max="10"/>
@@ -10015,7 +9995,7 @@
       </c>
       <c r="G55" s="5" t="inlineStr">
         <is>
-          <t>Case : wifi6  has been updated by Sabin Giri</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="H55" s="5" t="inlineStr">
@@ -10082,7 +10062,7 @@
       </c>
       <c r="G56" s="3" t="inlineStr">
         <is>
-          <t>Case : Wifi 6  has been updated by Sunil Chaudhary</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="H56" s="3" t="inlineStr">
@@ -10149,7 +10129,7 @@
       </c>
       <c r="G57" s="5" t="inlineStr">
         <is>
-          <t>Case : slow issue field visit  has been updated by Chandramani Tharu</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="H57" s="5" t="inlineStr">

--- a/audit_report_ALL_TEAM_23_Sep_2026.xlsx
+++ b/audit_report_ALL_TEAM_23_Sep_2026.xlsx
@@ -483,7 +483,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AW39"/>
+  <dimension ref="A1:AW45"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="23" customWidth="1" min="1" max="1"/>
@@ -506,11 +506,11 @@
     <col width="26" customWidth="1" min="18" max="18"/>
     <col width="37" customWidth="1" min="19" max="19"/>
     <col width="37" customWidth="1" min="20" max="20"/>
-    <col width="19" customWidth="1" min="21" max="21"/>
+    <col width="20" customWidth="1" min="21" max="21"/>
     <col width="26" customWidth="1" min="22" max="22"/>
     <col width="26" customWidth="1" min="23" max="23"/>
     <col width="29" customWidth="1" min="24" max="24"/>
-    <col width="11" customWidth="1" min="25" max="25"/>
+    <col width="12" customWidth="1" min="25" max="25"/>
     <col width="32" customWidth="1" min="26" max="26"/>
     <col width="19" customWidth="1" min="27" max="27"/>
     <col width="17" customWidth="1" min="28" max="28"/>
@@ -529,7 +529,7 @@
     <col width="27" customWidth="1" min="41" max="41"/>
     <col width="12" customWidth="1" min="42" max="42"/>
     <col width="17" customWidth="1" min="43" max="43"/>
-    <col width="34" customWidth="1" min="44" max="44"/>
+    <col width="40" customWidth="1" min="44" max="44"/>
     <col width="34" customWidth="1" min="45" max="45"/>
     <col width="33" customWidth="1" min="46" max="46"/>
     <col width="32" customWidth="1" min="47" max="47"/>
@@ -7814,6 +7814,1268 @@
         </is>
       </c>
     </row>
+    <row r="40">
+      <c r="A40" s="3" t="inlineStr">
+        <is>
+          <t>Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="B40" s="3" t="inlineStr">
+        <is>
+          <t>23 Sep 2026 4:42 PM</t>
+        </is>
+      </c>
+      <c r="C40" s="3" t="inlineStr">
+        <is>
+          <t>atwz5SElGeKMz8qxsp3b6c34SBAfIMR+</t>
+        </is>
+      </c>
+      <c r="D40" s="3" t="inlineStr">
+        <is>
+          <t>Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="E40" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F40" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G40" s="3" t="inlineStr"/>
+      <c r="H40" s="3" t="inlineStr">
+        <is>
+          <t>Case : WIFI6 Router Upgrade   has been updated by Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="I40" s="3" t="inlineStr">
+        <is>
+          <t>WIFI6 Router Upgrade</t>
+        </is>
+      </c>
+      <c r="J40" s="3" t="inlineStr">
+        <is>
+          <t>TKT1343717</t>
+        </is>
+      </c>
+      <c r="K40" s="3" t="inlineStr">
+        <is>
+          <t>Jagaran Media Center</t>
+        </is>
+      </c>
+      <c r="L40" s="3" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="M40" s="3" t="inlineStr">
+        <is>
+          <t>Phone</t>
+        </is>
+      </c>
+      <c r="N40" s="3" t="inlineStr">
+        <is>
+          <t>Jagaran Media Center</t>
+        </is>
+      </c>
+      <c r="O40" s="3" t="inlineStr">
+        <is>
+          <t>9841022343</t>
+        </is>
+      </c>
+      <c r="P40" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="Q40" s="3" t="inlineStr"/>
+      <c r="R40" s="3" t="inlineStr">
+        <is>
+          <t>23 Sep 2026 04:42:34 PM</t>
+        </is>
+      </c>
+      <c r="S40" s="3" t="inlineStr"/>
+      <c r="T40" s="3" t="inlineStr"/>
+      <c r="U40" s="3" t="inlineStr">
+        <is>
+          <t>jagaranmedia_fttx</t>
+        </is>
+      </c>
+      <c r="V40" s="3" t="inlineStr">
+        <is>
+          <t>23 Sep 2026 12:59:27 PM</t>
+        </is>
+      </c>
+      <c r="W40" s="3" t="inlineStr">
+        <is>
+          <t>23 Sep 2026 04:42:34 PM</t>
+        </is>
+      </c>
+      <c r="X40" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Y40" s="3" t="inlineStr">
+        <is>
+          <t>27.694641</t>
+        </is>
+      </c>
+      <c r="Z40" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="AA40" s="3" t="inlineStr">
+        <is>
+          <t>Layer 1-User</t>
+        </is>
+      </c>
+      <c r="AB40" s="3" t="inlineStr">
+        <is>
+          <t>L1  Support</t>
+        </is>
+      </c>
+      <c r="AC40" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="AD40" s="3" t="inlineStr"/>
+      <c r="AE40" s="3" t="inlineStr">
+        <is>
+          <t>Jagaran Media Center, M8VH+WRG, Gautam Buddha Marg, Kathmandu 44600, Bagmati, Nepal, Nepal</t>
+        </is>
+      </c>
+      <c r="AF40" s="3" t="inlineStr">
+        <is>
+          <t>info@jagaranmedia.org.np</t>
+        </is>
+      </c>
+      <c r="AG40" s="3" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="AH40" s="3" t="inlineStr"/>
+      <c r="AI40" s="3" t="inlineStr">
+        <is>
+          <t>03:43 hour</t>
+        </is>
+      </c>
+      <c r="AJ40" s="3" t="inlineStr"/>
+      <c r="AK40" s="3" t="inlineStr"/>
+      <c r="AL40" s="3" t="inlineStr">
+        <is>
+          <t>Aashna Pulami</t>
+        </is>
+      </c>
+      <c r="AM40" s="3" t="inlineStr">
+        <is>
+          <t>Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="AN40" s="3" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AO40" s="3" t="inlineStr">
+        <is>
+          <t>L56-3</t>
+        </is>
+      </c>
+      <c r="AP40" s="3" t="inlineStr">
+        <is>
+          <t>85.330157</t>
+        </is>
+      </c>
+      <c r="AQ40" s="3" t="inlineStr"/>
+      <c r="AR40" s="3" t="inlineStr">
+        <is>
+          <t>Case : WIFI6 Router Upgrade   has been updated by Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="AS40" s="3" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="AT40" s="3" t="inlineStr">
+        <is>
+          <t>3h 43m</t>
+        </is>
+      </c>
+      <c r="AU40" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Completed)</t>
+        </is>
+      </c>
+      <c r="AV40" s="3" t="inlineStr">
+        <is>
+          <t>Case : WIFI6 Router Upgrade   has been updated by Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="AW40" s="3" t="inlineStr">
+        <is>
+          <t>WiFi 6 Upgrade</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="3" t="inlineStr">
+        <is>
+          <t>Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="B41" s="3" t="inlineStr">
+        <is>
+          <t>23 Sep 2026 4:36 PM</t>
+        </is>
+      </c>
+      <c r="C41" s="3" t="inlineStr">
+        <is>
+          <t>w7A8I7MXNVw6IhJoudC/TknnOVKMobUO</t>
+        </is>
+      </c>
+      <c r="D41" s="3" t="inlineStr">
+        <is>
+          <t>Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="E41" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F41" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G41" s="3" t="inlineStr"/>
+      <c r="H41" s="3" t="inlineStr">
+        <is>
+          <t>Case : SLOW ISSUE   has been updated by Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="I41" s="3" t="inlineStr">
+        <is>
+          <t>SLOW ISSUE</t>
+        </is>
+      </c>
+      <c r="J41" s="3" t="inlineStr">
+        <is>
+          <t>TKT1342843</t>
+        </is>
+      </c>
+      <c r="K41" s="3" t="inlineStr">
+        <is>
+          <t>Krishna Prasad Paudel</t>
+        </is>
+      </c>
+      <c r="L41" s="3" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="M41" s="3" t="inlineStr">
+        <is>
+          <t>Phone</t>
+        </is>
+      </c>
+      <c r="N41" s="3" t="inlineStr">
+        <is>
+          <t>Krishna Prasad Paudel</t>
+        </is>
+      </c>
+      <c r="O41" s="3" t="inlineStr">
+        <is>
+          <t>9849481434</t>
+        </is>
+      </c>
+      <c r="P41" s="3" t="inlineStr">
+        <is>
+          <t>Slow Internet Connection</t>
+        </is>
+      </c>
+      <c r="Q41" s="3" t="inlineStr"/>
+      <c r="R41" s="3" t="inlineStr">
+        <is>
+          <t>23 Sep 2026 04:36:44 PM</t>
+        </is>
+      </c>
+      <c r="S41" s="3" t="inlineStr"/>
+      <c r="T41" s="3" t="inlineStr"/>
+      <c r="U41" s="3" t="inlineStr">
+        <is>
+          <t>9849481434</t>
+        </is>
+      </c>
+      <c r="V41" s="3" t="inlineStr">
+        <is>
+          <t>22 Sep 2026 05:38:25 PM</t>
+        </is>
+      </c>
+      <c r="W41" s="3" t="inlineStr">
+        <is>
+          <t>23 Sep 2026 04:36:44 PM</t>
+        </is>
+      </c>
+      <c r="X41" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Y41" s="3" t="inlineStr">
+        <is>
+          <t>27.67106</t>
+        </is>
+      </c>
+      <c r="Z41" s="3" t="inlineStr">
+        <is>
+          <t>Slow Internet Connection</t>
+        </is>
+      </c>
+      <c r="AA41" s="3" t="inlineStr">
+        <is>
+          <t>Layer 1-User</t>
+        </is>
+      </c>
+      <c r="AB41" s="3" t="inlineStr">
+        <is>
+          <t>L1  Support</t>
+        </is>
+      </c>
+      <c r="AC41" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="AD41" s="3" t="inlineStr"/>
+      <c r="AE41" s="3" t="inlineStr">
+        <is>
+          <t>near Balkumari temple and Lumbini Kaja Ghar chowmein and chart House, Balkumari, Lalitpur, Bagmati,</t>
+        </is>
+      </c>
+      <c r="AF41" s="3" t="inlineStr">
+        <is>
+          <t>krissna333@gmail.com</t>
+        </is>
+      </c>
+      <c r="AG41" s="3" t="inlineStr">
+        <is>
+          <t>Video content is Buffering</t>
+        </is>
+      </c>
+      <c r="AH41" s="3" t="inlineStr"/>
+      <c r="AI41" s="3" t="inlineStr">
+        <is>
+          <t>08:58 hour</t>
+        </is>
+      </c>
+      <c r="AJ41" s="3" t="inlineStr"/>
+      <c r="AK41" s="3" t="inlineStr"/>
+      <c r="AL41" s="3" t="inlineStr">
+        <is>
+          <t>Puja Khadka</t>
+        </is>
+      </c>
+      <c r="AM41" s="3" t="inlineStr">
+        <is>
+          <t>Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="AN41" s="3" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AO41" s="3" t="inlineStr">
+        <is>
+          <t>CDB626</t>
+        </is>
+      </c>
+      <c r="AP41" s="3" t="inlineStr">
+        <is>
+          <t>85.33733</t>
+        </is>
+      </c>
+      <c r="AQ41" s="3" t="inlineStr"/>
+      <c r="AR41" s="3" t="inlineStr">
+        <is>
+          <t>Case : SLOW ISSUE   has been updated by Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="AS41" s="3" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="AT41" s="3" t="inlineStr">
+        <is>
+          <t>22h 58m</t>
+        </is>
+      </c>
+      <c r="AU41" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Completed)</t>
+        </is>
+      </c>
+      <c r="AV41" s="3" t="inlineStr">
+        <is>
+          <t>Case : SLOW ISSUE   has been updated by Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="AW41" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="3" t="inlineStr">
+        <is>
+          <t>Ajit Shrestha</t>
+        </is>
+      </c>
+      <c r="B42" s="3" t="inlineStr">
+        <is>
+          <t>23 Sep 2026 4:35 PM</t>
+        </is>
+      </c>
+      <c r="C42" s="3" t="inlineStr">
+        <is>
+          <t>KK1e4rFHODw22QGqrKXwiw==</t>
+        </is>
+      </c>
+      <c r="D42" s="3" t="inlineStr">
+        <is>
+          <t>Ajit Shrestha</t>
+        </is>
+      </c>
+      <c r="E42" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F42" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G42" s="3" t="inlineStr"/>
+      <c r="H42" s="3" t="inlineStr">
+        <is>
+          <t>Case : Wifi 6 Router   has been updated by Ajit Shrestha</t>
+        </is>
+      </c>
+      <c r="I42" s="3" t="inlineStr">
+        <is>
+          <t>Wifi 6 Router</t>
+        </is>
+      </c>
+      <c r="J42" s="3" t="inlineStr">
+        <is>
+          <t>TKT1343427</t>
+        </is>
+      </c>
+      <c r="K42" s="3" t="inlineStr">
+        <is>
+          <t>Aryan Tibrewal</t>
+        </is>
+      </c>
+      <c r="L42" s="3" t="inlineStr">
+        <is>
+          <t>Closed</t>
+        </is>
+      </c>
+      <c r="M42" s="3" t="inlineStr">
+        <is>
+          <t>Phone</t>
+        </is>
+      </c>
+      <c r="N42" s="3" t="inlineStr">
+        <is>
+          <t>Aryan Tibrewal</t>
+        </is>
+      </c>
+      <c r="O42" s="3" t="inlineStr">
+        <is>
+          <t>9851320259</t>
+        </is>
+      </c>
+      <c r="P42" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="Q42" s="3" t="inlineStr"/>
+      <c r="R42" s="3" t="inlineStr">
+        <is>
+          <t>23 Sep 2026 10:12:54 AM</t>
+        </is>
+      </c>
+      <c r="S42" s="3" t="inlineStr"/>
+      <c r="T42" s="3" t="inlineStr"/>
+      <c r="U42" s="3" t="inlineStr">
+        <is>
+          <t>9851320259</t>
+        </is>
+      </c>
+      <c r="V42" s="3" t="inlineStr">
+        <is>
+          <t>23 Sep 2026 10:12:54 AM</t>
+        </is>
+      </c>
+      <c r="W42" s="3" t="inlineStr">
+        <is>
+          <t>23 Sep 2026 04:35:13 PM</t>
+        </is>
+      </c>
+      <c r="X42" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Y42" s="3" t="inlineStr">
+        <is>
+          <t>27.69314</t>
+        </is>
+      </c>
+      <c r="Z42" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="AA42" s="3" t="inlineStr">
+        <is>
+          <t>Layer 1-</t>
+        </is>
+      </c>
+      <c r="AB42" s="3" t="inlineStr">
+        <is>
+          <t>Laxman Koirala</t>
+        </is>
+      </c>
+      <c r="AC42" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="AD42" s="3" t="inlineStr"/>
+      <c r="AE42" s="3" t="inlineStr">
+        <is>
+          <t>Near to Nepal Electricity Authority Kuleswor Distribution Center, Kuleshwor , Kathmadnu, Bagmati, Ce</t>
+        </is>
+      </c>
+      <c r="AF42" s="3" t="inlineStr">
+        <is>
+          <t>tibrewalaryan4@gmail.com</t>
+        </is>
+      </c>
+      <c r="AG42" s="3" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="AH42" s="3" t="inlineStr"/>
+      <c r="AI42" s="3" t="inlineStr">
+        <is>
+          <t>06:22 hour</t>
+        </is>
+      </c>
+      <c r="AJ42" s="3" t="inlineStr"/>
+      <c r="AK42" s="3" t="inlineStr"/>
+      <c r="AL42" s="3" t="inlineStr">
+        <is>
+          <t>Seeta Magar</t>
+        </is>
+      </c>
+      <c r="AM42" s="3" t="inlineStr">
+        <is>
+          <t>Ajit Shrestha</t>
+        </is>
+      </c>
+      <c r="AN42" s="3" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AO42" s="3" t="inlineStr">
+        <is>
+          <t>3,14</t>
+        </is>
+      </c>
+      <c r="AP42" s="3" t="inlineStr">
+        <is>
+          <t>85.2963</t>
+        </is>
+      </c>
+      <c r="AQ42" s="3" t="inlineStr"/>
+      <c r="AR42" s="3" t="inlineStr">
+        <is>
+          <t>Case : Wifi 6 Router   has been updated by Ajit Shrestha</t>
+        </is>
+      </c>
+      <c r="AS42" s="3" t="inlineStr">
+        <is>
+          <t>6h 22m</t>
+        </is>
+      </c>
+      <c r="AT42" s="3" t="inlineStr">
+        <is>
+          <t>6h 22m</t>
+        </is>
+      </c>
+      <c r="AU42" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Closed)</t>
+        </is>
+      </c>
+      <c r="AV42" s="3" t="inlineStr">
+        <is>
+          <t>Case : Wifi 6 Router   has been updated by Ajit Shrestha</t>
+        </is>
+      </c>
+      <c r="AW42" s="3" t="inlineStr">
+        <is>
+          <t>WiFi 6 Upgrade</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="3" t="inlineStr">
+        <is>
+          <t>Ajit Shrestha</t>
+        </is>
+      </c>
+      <c r="B43" s="3" t="inlineStr">
+        <is>
+          <t>23 Sep 2026 4:34 PM</t>
+        </is>
+      </c>
+      <c r="C43" s="3" t="inlineStr">
+        <is>
+          <t>KK1e4rFHODw22QGqrKXwiw==</t>
+        </is>
+      </c>
+      <c r="D43" s="3" t="inlineStr">
+        <is>
+          <t>Ajit Shrestha</t>
+        </is>
+      </c>
+      <c r="E43" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F43" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G43" s="3" t="inlineStr"/>
+      <c r="H43" s="3" t="inlineStr">
+        <is>
+          <t>Case : Wifi 6 Router   has been updated by Ajit Shrestha</t>
+        </is>
+      </c>
+      <c r="I43" s="3" t="inlineStr">
+        <is>
+          <t>Wifi 6 Router</t>
+        </is>
+      </c>
+      <c r="J43" s="3" t="inlineStr">
+        <is>
+          <t>TKT1343427</t>
+        </is>
+      </c>
+      <c r="K43" s="3" t="inlineStr">
+        <is>
+          <t>Aryan Tibrewal</t>
+        </is>
+      </c>
+      <c r="L43" s="3" t="inlineStr">
+        <is>
+          <t>Closed</t>
+        </is>
+      </c>
+      <c r="M43" s="3" t="inlineStr">
+        <is>
+          <t>Phone</t>
+        </is>
+      </c>
+      <c r="N43" s="3" t="inlineStr">
+        <is>
+          <t>Aryan Tibrewal</t>
+        </is>
+      </c>
+      <c r="O43" s="3" t="inlineStr">
+        <is>
+          <t>9851320259</t>
+        </is>
+      </c>
+      <c r="P43" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="Q43" s="3" t="inlineStr"/>
+      <c r="R43" s="3" t="inlineStr">
+        <is>
+          <t>23 Sep 2026 10:12:54 AM</t>
+        </is>
+      </c>
+      <c r="S43" s="3" t="inlineStr"/>
+      <c r="T43" s="3" t="inlineStr"/>
+      <c r="U43" s="3" t="inlineStr">
+        <is>
+          <t>9851320259</t>
+        </is>
+      </c>
+      <c r="V43" s="3" t="inlineStr">
+        <is>
+          <t>23 Sep 2026 10:12:54 AM</t>
+        </is>
+      </c>
+      <c r="W43" s="3" t="inlineStr">
+        <is>
+          <t>23 Sep 2026 04:35:13 PM</t>
+        </is>
+      </c>
+      <c r="X43" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Y43" s="3" t="inlineStr">
+        <is>
+          <t>27.69314</t>
+        </is>
+      </c>
+      <c r="Z43" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="AA43" s="3" t="inlineStr">
+        <is>
+          <t>Layer 1-</t>
+        </is>
+      </c>
+      <c r="AB43" s="3" t="inlineStr">
+        <is>
+          <t>Laxman Koirala</t>
+        </is>
+      </c>
+      <c r="AC43" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="AD43" s="3" t="inlineStr"/>
+      <c r="AE43" s="3" t="inlineStr">
+        <is>
+          <t>Near to Nepal Electricity Authority Kuleswor Distribution Center, Kuleshwor , Kathmadnu, Bagmati, Ce</t>
+        </is>
+      </c>
+      <c r="AF43" s="3" t="inlineStr">
+        <is>
+          <t>tibrewalaryan4@gmail.com</t>
+        </is>
+      </c>
+      <c r="AG43" s="3" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="AH43" s="3" t="inlineStr"/>
+      <c r="AI43" s="3" t="inlineStr">
+        <is>
+          <t>06:22 hour</t>
+        </is>
+      </c>
+      <c r="AJ43" s="3" t="inlineStr"/>
+      <c r="AK43" s="3" t="inlineStr"/>
+      <c r="AL43" s="3" t="inlineStr">
+        <is>
+          <t>Seeta Magar</t>
+        </is>
+      </c>
+      <c r="AM43" s="3" t="inlineStr">
+        <is>
+          <t>Ajit Shrestha</t>
+        </is>
+      </c>
+      <c r="AN43" s="3" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AO43" s="3" t="inlineStr">
+        <is>
+          <t>3,14</t>
+        </is>
+      </c>
+      <c r="AP43" s="3" t="inlineStr">
+        <is>
+          <t>85.2963</t>
+        </is>
+      </c>
+      <c r="AQ43" s="3" t="inlineStr"/>
+      <c r="AR43" s="3" t="inlineStr">
+        <is>
+          <t>Case : Wifi 6 Router   has been updated by Ajit Shrestha</t>
+        </is>
+      </c>
+      <c r="AS43" s="3" t="inlineStr">
+        <is>
+          <t>6h 22m</t>
+        </is>
+      </c>
+      <c r="AT43" s="3" t="inlineStr">
+        <is>
+          <t>6h 22m</t>
+        </is>
+      </c>
+      <c r="AU43" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Closed)</t>
+        </is>
+      </c>
+      <c r="AV43" s="3" t="inlineStr">
+        <is>
+          <t>Case : Wifi 6 Router   has been updated by Ajit Shrestha</t>
+        </is>
+      </c>
+      <c r="AW43" s="3" t="inlineStr">
+        <is>
+          <t>WiFi 6 Upgrade</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="3" t="inlineStr">
+        <is>
+          <t>Sabin Giri</t>
+        </is>
+      </c>
+      <c r="B44" s="3" t="inlineStr">
+        <is>
+          <t>23 Sep 2026 4:46 PM</t>
+        </is>
+      </c>
+      <c r="C44" s="3" t="inlineStr">
+        <is>
+          <t>WGnmUJF06LTlUriJ5DeDBQ==</t>
+        </is>
+      </c>
+      <c r="D44" s="3" t="inlineStr">
+        <is>
+          <t>Sabin Giri</t>
+        </is>
+      </c>
+      <c r="E44" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F44" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G44" s="3" t="inlineStr"/>
+      <c r="H44" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi 6  has been updated by Sabin Giri</t>
+        </is>
+      </c>
+      <c r="I44" s="3" t="inlineStr">
+        <is>
+          <t>wifi 6</t>
+        </is>
+      </c>
+      <c r="J44" s="3" t="inlineStr">
+        <is>
+          <t>TKT1343577</t>
+        </is>
+      </c>
+      <c r="K44" s="3" t="inlineStr">
+        <is>
+          <t>Sujan Ghising</t>
+        </is>
+      </c>
+      <c r="L44" s="3" t="inlineStr">
+        <is>
+          <t>Reopen</t>
+        </is>
+      </c>
+      <c r="M44" s="3" t="inlineStr">
+        <is>
+          <t>Phone</t>
+        </is>
+      </c>
+      <c r="N44" s="3" t="inlineStr">
+        <is>
+          <t>Sujan Ghising</t>
+        </is>
+      </c>
+      <c r="O44" s="3" t="inlineStr">
+        <is>
+          <t>9863524625</t>
+        </is>
+      </c>
+      <c r="P44" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="Q44" s="3" t="inlineStr"/>
+      <c r="R44" s="3" t="inlineStr">
+        <is>
+          <t>23 Sep 2026 04:47:49 PM</t>
+        </is>
+      </c>
+      <c r="S44" s="3" t="inlineStr"/>
+      <c r="T44" s="3" t="inlineStr"/>
+      <c r="U44" s="3" t="inlineStr">
+        <is>
+          <t>9863524625</t>
+        </is>
+      </c>
+      <c r="V44" s="3" t="inlineStr">
+        <is>
+          <t>23 Sep 2026 11:28:38 AM</t>
+        </is>
+      </c>
+      <c r="W44" s="3" t="inlineStr">
+        <is>
+          <t>23 Sep 2026 04:46:00 PM</t>
+        </is>
+      </c>
+      <c r="X44" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Y44" s="3" t="inlineStr">
+        <is>
+          <t>27.73786</t>
+        </is>
+      </c>
+      <c r="Z44" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="AA44" s="3" t="inlineStr">
+        <is>
+          <t>Layer 1-User</t>
+        </is>
+      </c>
+      <c r="AB44" s="3" t="inlineStr">
+        <is>
+          <t>L1  Support</t>
+        </is>
+      </c>
+      <c r="AC44" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="AD44" s="3" t="inlineStr"/>
+      <c r="AE44" s="3" t="inlineStr">
+        <is>
+          <t>Kathmandu Gokarneshwor Jorpati nward no:5 near Nepal Telecome Office , Bagmati, Central, Nepal</t>
+        </is>
+      </c>
+      <c r="AF44" s="3" t="inlineStr">
+        <is>
+          <t>mokatnniru496@gmail.com</t>
+        </is>
+      </c>
+      <c r="AG44" s="3" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="AH44" s="3" t="inlineStr"/>
+      <c r="AI44" s="3" t="inlineStr"/>
+      <c r="AJ44" s="3" t="inlineStr"/>
+      <c r="AK44" s="3" t="inlineStr"/>
+      <c r="AL44" s="3" t="inlineStr">
+        <is>
+          <t>Monika Chaudhary</t>
+        </is>
+      </c>
+      <c r="AM44" s="3" t="inlineStr">
+        <is>
+          <t>Sabin Giri</t>
+        </is>
+      </c>
+      <c r="AN44" s="3" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AO44" s="3" t="inlineStr">
+        <is>
+          <t>L62-8</t>
+        </is>
+      </c>
+      <c r="AP44" s="3" t="inlineStr">
+        <is>
+          <t>85.36657</t>
+        </is>
+      </c>
+      <c r="AQ44" s="3" t="inlineStr"/>
+      <c r="AR44" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi 6  has been updated by Sabin Giri</t>
+        </is>
+      </c>
+      <c r="AS44" s="3" t="inlineStr">
+        <is>
+          <t>Negative Time</t>
+        </is>
+      </c>
+      <c r="AT44" s="3" t="inlineStr">
+        <is>
+          <t>5h 17m</t>
+        </is>
+      </c>
+      <c r="AU44" s="3" t="inlineStr">
+        <is>
+          <t>Other / In Progress (Reopen)</t>
+        </is>
+      </c>
+      <c r="AV44" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi 6  has been updated by Sabin Giri</t>
+        </is>
+      </c>
+      <c r="AW44" s="3" t="inlineStr">
+        <is>
+          <t>WiFi 6 Upgrade</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="3" t="inlineStr">
+        <is>
+          <t>Rajesh Maharjan</t>
+        </is>
+      </c>
+      <c r="B45" s="3" t="inlineStr">
+        <is>
+          <t>23 Sep 2026 4:34 PM</t>
+        </is>
+      </c>
+      <c r="C45" s="3" t="inlineStr">
+        <is>
+          <t>/Oi+2zlne73U37ZA62PktA==</t>
+        </is>
+      </c>
+      <c r="D45" s="3" t="inlineStr">
+        <is>
+          <t>Rajesh Maharjan</t>
+        </is>
+      </c>
+      <c r="E45" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F45" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G45" s="3" t="inlineStr"/>
+      <c r="H45" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi 6 upgrade  has been updated by Rajesh Maharjan</t>
+        </is>
+      </c>
+      <c r="I45" s="3" t="inlineStr">
+        <is>
+          <t>wifi 6 upgrade</t>
+        </is>
+      </c>
+      <c r="J45" s="3" t="inlineStr">
+        <is>
+          <t>TKT1342270</t>
+        </is>
+      </c>
+      <c r="K45" s="3" t="inlineStr">
+        <is>
+          <t>Ayush Shakya</t>
+        </is>
+      </c>
+      <c r="L45" s="3" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="M45" s="3" t="inlineStr">
+        <is>
+          <t>Self Care</t>
+        </is>
+      </c>
+      <c r="N45" s="3" t="inlineStr">
+        <is>
+          <t>Ayush Shakya</t>
+        </is>
+      </c>
+      <c r="O45" s="3" t="inlineStr">
+        <is>
+          <t>9813326072</t>
+        </is>
+      </c>
+      <c r="P45" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="Q45" s="3" t="inlineStr"/>
+      <c r="R45" s="3" t="inlineStr">
+        <is>
+          <t>23 Sep 2026 04:34:58 PM</t>
+        </is>
+      </c>
+      <c r="S45" s="3" t="inlineStr"/>
+      <c r="T45" s="3" t="inlineStr"/>
+      <c r="U45" s="3" t="inlineStr">
+        <is>
+          <t>9813326072</t>
+        </is>
+      </c>
+      <c r="V45" s="3" t="inlineStr">
+        <is>
+          <t>22 Sep 2026 11:39:34 AM</t>
+        </is>
+      </c>
+      <c r="W45" s="3" t="inlineStr">
+        <is>
+          <t>23 Sep 2026 04:34:58 PM</t>
+        </is>
+      </c>
+      <c r="X45" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Y45" s="3" t="inlineStr">
+        <is>
+          <t>27.6751</t>
+        </is>
+      </c>
+      <c r="Z45" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="AA45" s="3" t="inlineStr">
+        <is>
+          <t>Layer 1-User</t>
+        </is>
+      </c>
+      <c r="AB45" s="3" t="inlineStr">
+        <is>
+          <t>L1  Support</t>
+        </is>
+      </c>
+      <c r="AC45" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="AD45" s="3" t="inlineStr"/>
+      <c r="AE45" s="3" t="inlineStr">
+        <is>
+          <t>Pulchwok Back Side of S.P. Petrol Pump,Lalitpur, Bagmati, Nepal, Nepal</t>
+        </is>
+      </c>
+      <c r="AF45" s="3" t="inlineStr">
+        <is>
+          <t>ayushshakya327@gmail.com</t>
+        </is>
+      </c>
+      <c r="AG45" s="3" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="AH45" s="3" t="inlineStr"/>
+      <c r="AI45" s="3" t="inlineStr">
+        <is>
+          <t>14:55 hour</t>
+        </is>
+      </c>
+      <c r="AJ45" s="3" t="inlineStr"/>
+      <c r="AK45" s="3" t="inlineStr"/>
+      <c r="AL45" s="3" t="inlineStr">
+        <is>
+          <t>Sabina K.C</t>
+        </is>
+      </c>
+      <c r="AM45" s="3" t="inlineStr">
+        <is>
+          <t>Rajesh Maharjan</t>
+        </is>
+      </c>
+      <c r="AN45" s="3" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AO45" s="3" t="inlineStr">
+        <is>
+          <t>3,1</t>
+        </is>
+      </c>
+      <c r="AP45" s="3" t="inlineStr">
+        <is>
+          <t>85.31538</t>
+        </is>
+      </c>
+      <c r="AQ45" s="3" t="inlineStr"/>
+      <c r="AR45" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi 6 upgrade  has been updated by Rajesh Maharjan</t>
+        </is>
+      </c>
+      <c r="AS45" s="3" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="AT45" s="3" t="inlineStr">
+        <is>
+          <t>1d 4h 55m</t>
+        </is>
+      </c>
+      <c r="AU45" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Completed)</t>
+        </is>
+      </c>
+      <c r="AV45" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi 6 upgrade  has been updated by Rajesh Maharjan</t>
+        </is>
+      </c>
+      <c r="AW45" s="3" t="inlineStr">
+        <is>
+          <t>WiFi 6 Upgrade</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -7825,7 +9087,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M57"/>
+  <dimension ref="A1:M62"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="45" customWidth="1" min="1" max="1"/>
@@ -7834,7 +9096,7 @@
     <col width="40" customWidth="1" min="4" max="4"/>
     <col width="19" customWidth="1" min="5" max="5"/>
     <col width="25" customWidth="1" min="6" max="6"/>
-    <col width="35" customWidth="1" min="7" max="7"/>
+    <col width="45" customWidth="1" min="7" max="7"/>
     <col width="45" customWidth="1" min="8" max="8"/>
     <col width="27" customWidth="1" min="9" max="9"/>
     <col width="27" customWidth="1" min="10" max="10"/>
@@ -7862,7 +9124,7 @@
         </is>
       </c>
       <c r="B2" s="3" t="n">
-        <v>38</v>
+        <v>44</v>
       </c>
     </row>
     <row r="3">
@@ -7872,7 +9134,7 @@
         </is>
       </c>
       <c r="B3" s="5" t="n">
-        <v>27</v>
+        <v>32</v>
       </c>
     </row>
     <row r="4">
@@ -7883,7 +9145,7 @@
       </c>
       <c r="B4" s="3" t="inlineStr">
         <is>
-          <t>71.1%</t>
+          <t>72.7%</t>
         </is>
       </c>
     </row>
@@ -7895,7 +9157,7 @@
       </c>
       <c r="B5" s="5" t="inlineStr">
         <is>
-          <t>5h 51m</t>
+          <t>5h 20m</t>
         </is>
       </c>
     </row>
@@ -7907,7 +9169,7 @@
       </c>
       <c r="B6" s="3" t="inlineStr">
         <is>
-          <t>20h 1m</t>
+          <t>19h 1m</t>
         </is>
       </c>
     </row>
@@ -7948,14 +9210,14 @@
         </is>
       </c>
       <c r="B10" s="3" t="n">
+        <v>27</v>
+      </c>
+      <c r="C10" s="3" t="n">
         <v>22</v>
       </c>
-      <c r="C10" s="3" t="n">
-        <v>18</v>
-      </c>
       <c r="D10" s="3" t="inlineStr">
         <is>
-          <t>81.8%</t>
+          <t>81.5%</t>
         </is>
       </c>
     </row>
@@ -8020,14 +9282,14 @@
         </is>
       </c>
       <c r="B14" s="3" t="n">
+        <v>4</v>
+      </c>
+      <c r="C14" s="3" t="n">
         <v>3</v>
       </c>
-      <c r="C14" s="3" t="n">
-        <v>2</v>
-      </c>
       <c r="D14" s="3" t="inlineStr">
         <is>
-          <t>66.7%</t>
+          <t>75.0%</t>
         </is>
       </c>
     </row>
@@ -8115,10 +9377,10 @@
         </is>
       </c>
       <c r="C20" s="3" t="n">
+        <v>25</v>
+      </c>
+      <c r="D20" s="3" t="n">
         <v>20</v>
-      </c>
-      <c r="D20" s="3" t="n">
-        <v>16</v>
       </c>
       <c r="E20" s="3" t="inlineStr">
         <is>
@@ -8253,14 +9515,14 @@
         </is>
       </c>
       <c r="C26" s="3" t="n">
+        <v>4</v>
+      </c>
+      <c r="D26" s="3" t="n">
         <v>3</v>
       </c>
-      <c r="D26" s="3" t="n">
-        <v>2</v>
-      </c>
       <c r="E26" s="3" t="inlineStr">
         <is>
-          <t>66.7%</t>
+          <t>75.0%</t>
         </is>
       </c>
     </row>
@@ -10163,6 +11425,341 @@
         </is>
       </c>
     </row>
+    <row r="58">
+      <c r="A58" s="3" t="inlineStr">
+        <is>
+          <t>TKT1343717</t>
+        </is>
+      </c>
+      <c r="B58" s="3" t="inlineStr">
+        <is>
+          <t>Jagaran Media Center</t>
+        </is>
+      </c>
+      <c r="C58" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="D58" s="3" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="E58" s="3" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="F58" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Completed)</t>
+        </is>
+      </c>
+      <c r="G58" s="3" t="inlineStr">
+        <is>
+          <t>Case : WIFI6 Router Upgrade   has been updated by Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="H58" s="3" t="inlineStr">
+        <is>
+          <t>Case : WIFI6 Router Upgrade   has been updated by Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="I58" s="3" t="inlineStr">
+        <is>
+          <t>23 Sep 2026 04:42:34 PM</t>
+        </is>
+      </c>
+      <c r="J58" s="3" t="inlineStr">
+        <is>
+          <t>23 Sep 2026 12:59:27 PM</t>
+        </is>
+      </c>
+      <c r="K58" s="3" t="inlineStr">
+        <is>
+          <t>23 Sep 2026 04:42:34 PM</t>
+        </is>
+      </c>
+      <c r="L58" s="3" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="M58" s="3" t="inlineStr">
+        <is>
+          <t>3h 43m</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" s="5" t="inlineStr">
+        <is>
+          <t>TKT1342843</t>
+        </is>
+      </c>
+      <c r="B59" s="5" t="inlineStr">
+        <is>
+          <t>Krishna Prasad Paudel</t>
+        </is>
+      </c>
+      <c r="C59" s="5" t="inlineStr">
+        <is>
+          <t>Slow Internet Connection</t>
+        </is>
+      </c>
+      <c r="D59" s="5" t="inlineStr">
+        <is>
+          <t>Video content is Buffering</t>
+        </is>
+      </c>
+      <c r="E59" s="5" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="F59" s="5" t="inlineStr">
+        <is>
+          <t>Completed (Completed)</t>
+        </is>
+      </c>
+      <c r="G59" s="5" t="inlineStr">
+        <is>
+          <t>Case : SLOW ISSUE   has been updated by Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="H59" s="5" t="inlineStr">
+        <is>
+          <t>Case : SLOW ISSUE   has been updated by Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="I59" s="5" t="inlineStr">
+        <is>
+          <t>23 Sep 2026 04:36:44 PM</t>
+        </is>
+      </c>
+      <c r="J59" s="5" t="inlineStr">
+        <is>
+          <t>22 Sep 2026 05:38:25 PM</t>
+        </is>
+      </c>
+      <c r="K59" s="5" t="inlineStr">
+        <is>
+          <t>23 Sep 2026 04:36:44 PM</t>
+        </is>
+      </c>
+      <c r="L59" s="5" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="M59" s="5" t="inlineStr">
+        <is>
+          <t>22h 58m</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" s="3" t="inlineStr">
+        <is>
+          <t>TKT1343427</t>
+        </is>
+      </c>
+      <c r="B60" s="3" t="inlineStr">
+        <is>
+          <t>Aryan Tibrewal</t>
+        </is>
+      </c>
+      <c r="C60" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="D60" s="3" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="E60" s="3" t="inlineStr">
+        <is>
+          <t>Closed</t>
+        </is>
+      </c>
+      <c r="F60" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Closed)</t>
+        </is>
+      </c>
+      <c r="G60" s="3" t="inlineStr">
+        <is>
+          <t>Case : Wifi 6 Router   has been updated by Ajit Shrestha</t>
+        </is>
+      </c>
+      <c r="H60" s="3" t="inlineStr">
+        <is>
+          <t>Case : Wifi 6 Router   has been updated by Ajit Shrestha</t>
+        </is>
+      </c>
+      <c r="I60" s="3" t="inlineStr">
+        <is>
+          <t>23 Sep 2026 10:12:54 AM</t>
+        </is>
+      </c>
+      <c r="J60" s="3" t="inlineStr">
+        <is>
+          <t>23 Sep 2026 10:12:54 AM</t>
+        </is>
+      </c>
+      <c r="K60" s="3" t="inlineStr">
+        <is>
+          <t>23 Sep 2026 04:35:13 PM</t>
+        </is>
+      </c>
+      <c r="L60" s="3" t="inlineStr">
+        <is>
+          <t>6h 22m</t>
+        </is>
+      </c>
+      <c r="M60" s="3" t="inlineStr">
+        <is>
+          <t>6h 22m</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" s="5" t="inlineStr">
+        <is>
+          <t>TKT1343427</t>
+        </is>
+      </c>
+      <c r="B61" s="5" t="inlineStr">
+        <is>
+          <t>Aryan Tibrewal</t>
+        </is>
+      </c>
+      <c r="C61" s="5" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="D61" s="5" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="E61" s="5" t="inlineStr">
+        <is>
+          <t>Closed</t>
+        </is>
+      </c>
+      <c r="F61" s="5" t="inlineStr">
+        <is>
+          <t>Completed (Closed)</t>
+        </is>
+      </c>
+      <c r="G61" s="5" t="inlineStr">
+        <is>
+          <t>Case : Wifi 6 Router   has been updated by Ajit Shrestha</t>
+        </is>
+      </c>
+      <c r="H61" s="5" t="inlineStr">
+        <is>
+          <t>Case : Wifi 6 Router   has been updated by Ajit Shrestha</t>
+        </is>
+      </c>
+      <c r="I61" s="5" t="inlineStr">
+        <is>
+          <t>23 Sep 2026 10:12:54 AM</t>
+        </is>
+      </c>
+      <c r="J61" s="5" t="inlineStr">
+        <is>
+          <t>23 Sep 2026 10:12:54 AM</t>
+        </is>
+      </c>
+      <c r="K61" s="5" t="inlineStr">
+        <is>
+          <t>23 Sep 2026 04:35:13 PM</t>
+        </is>
+      </c>
+      <c r="L61" s="5" t="inlineStr">
+        <is>
+          <t>6h 22m</t>
+        </is>
+      </c>
+      <c r="M61" s="5" t="inlineStr">
+        <is>
+          <t>6h 22m</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" s="3" t="inlineStr">
+        <is>
+          <t>TKT1342270</t>
+        </is>
+      </c>
+      <c r="B62" s="3" t="inlineStr">
+        <is>
+          <t>Ayush Shakya</t>
+        </is>
+      </c>
+      <c r="C62" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="D62" s="3" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="E62" s="3" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="F62" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Completed)</t>
+        </is>
+      </c>
+      <c r="G62" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi 6 upgrade  has been updated by Rajesh Maharjan</t>
+        </is>
+      </c>
+      <c r="H62" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi 6 upgrade  has been updated by Rajesh Maharjan</t>
+        </is>
+      </c>
+      <c r="I62" s="3" t="inlineStr">
+        <is>
+          <t>23 Sep 2026 04:34:58 PM</t>
+        </is>
+      </c>
+      <c r="J62" s="3" t="inlineStr">
+        <is>
+          <t>22 Sep 2026 11:39:34 AM</t>
+        </is>
+      </c>
+      <c r="K62" s="3" t="inlineStr">
+        <is>
+          <t>23 Sep 2026 04:34:58 PM</t>
+        </is>
+      </c>
+      <c r="L62" s="3" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="M62" s="3" t="inlineStr">
+        <is>
+          <t>1d 4h 55m</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/audit_report_ALL_TEAM_23_Sep_2026.xlsx
+++ b/audit_report_ALL_TEAM_23_Sep_2026.xlsx
@@ -483,7 +483,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AW45"/>
+  <dimension ref="A1:AW49"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="23" customWidth="1" min="1" max="1"/>
@@ -7881,10 +7881,8 @@
           <t>Jagaran Media Center</t>
         </is>
       </c>
-      <c r="O40" s="3" t="inlineStr">
-        <is>
-          <t>9841022343</t>
-        </is>
+      <c r="O40" s="3" t="n">
+        <v>9841022343</v>
       </c>
       <c r="P40" s="3" t="inlineStr">
         <is>
@@ -7919,10 +7917,8 @@
           <t>Active</t>
         </is>
       </c>
-      <c r="Y40" s="3" t="inlineStr">
-        <is>
-          <t>27.694641</t>
-        </is>
+      <c r="Y40" s="3" t="n">
+        <v>27.694641</v>
       </c>
       <c r="Z40" s="3" t="inlineStr">
         <is>
@@ -7978,25 +7974,21 @@
           <t>Chandramani Tharu</t>
         </is>
       </c>
-      <c r="AN40" s="3" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
+      <c r="AN40" s="3" t="n">
+        <v>6</v>
       </c>
       <c r="AO40" s="3" t="inlineStr">
         <is>
           <t>L56-3</t>
         </is>
       </c>
-      <c r="AP40" s="3" t="inlineStr">
-        <is>
-          <t>85.330157</t>
-        </is>
+      <c r="AP40" s="3" t="n">
+        <v>85.330157</v>
       </c>
       <c r="AQ40" s="3" t="inlineStr"/>
       <c r="AR40" s="3" t="inlineStr">
         <is>
-          <t>Case : WIFI6 Router Upgrade   has been updated by Chandramani Tharu</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="AS40" s="3" t="inlineStr">
@@ -8092,10 +8084,8 @@
           <t>Krishna Prasad Paudel</t>
         </is>
       </c>
-      <c r="O41" s="3" t="inlineStr">
-        <is>
-          <t>9849481434</t>
-        </is>
+      <c r="O41" s="3" t="n">
+        <v>9849481434</v>
       </c>
       <c r="P41" s="3" t="inlineStr">
         <is>
@@ -8130,10 +8120,8 @@
           <t>Active</t>
         </is>
       </c>
-      <c r="Y41" s="3" t="inlineStr">
-        <is>
-          <t>27.67106</t>
-        </is>
+      <c r="Y41" s="3" t="n">
+        <v>27.67106</v>
       </c>
       <c r="Z41" s="3" t="inlineStr">
         <is>
@@ -8189,25 +8177,21 @@
           <t>Shashikant Chaudhary</t>
         </is>
       </c>
-      <c r="AN41" s="3" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
+      <c r="AN41" s="3" t="n">
+        <v>6</v>
       </c>
       <c r="AO41" s="3" t="inlineStr">
         <is>
           <t>CDB626</t>
         </is>
       </c>
-      <c r="AP41" s="3" t="inlineStr">
-        <is>
-          <t>85.33733</t>
-        </is>
+      <c r="AP41" s="3" t="n">
+        <v>85.33732999999999</v>
       </c>
       <c r="AQ41" s="3" t="inlineStr"/>
       <c r="AR41" s="3" t="inlineStr">
         <is>
-          <t>Case : SLOW ISSUE   has been updated by Shashikant Chaudhary</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="AS41" s="3" t="inlineStr">
@@ -8303,10 +8287,8 @@
           <t>Aryan Tibrewal</t>
         </is>
       </c>
-      <c r="O42" s="3" t="inlineStr">
-        <is>
-          <t>9851320259</t>
-        </is>
+      <c r="O42" s="3" t="n">
+        <v>9851320259</v>
       </c>
       <c r="P42" s="3" t="inlineStr">
         <is>
@@ -8341,10 +8323,8 @@
           <t>Active</t>
         </is>
       </c>
-      <c r="Y42" s="3" t="inlineStr">
-        <is>
-          <t>27.69314</t>
-        </is>
+      <c r="Y42" s="3" t="n">
+        <v>27.69314</v>
       </c>
       <c r="Z42" s="3" t="inlineStr">
         <is>
@@ -8400,25 +8380,21 @@
           <t>Ajit Shrestha</t>
         </is>
       </c>
-      <c r="AN42" s="3" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
+      <c r="AN42" s="3" t="n">
+        <v>4</v>
       </c>
       <c r="AO42" s="3" t="inlineStr">
         <is>
           <t>3,14</t>
         </is>
       </c>
-      <c r="AP42" s="3" t="inlineStr">
-        <is>
-          <t>85.2963</t>
-        </is>
+      <c r="AP42" s="3" t="n">
+        <v>85.2963</v>
       </c>
       <c r="AQ42" s="3" t="inlineStr"/>
       <c r="AR42" s="3" t="inlineStr">
         <is>
-          <t>Case : Wifi 6 Router   has been updated by Ajit Shrestha</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="AS42" s="3" t="inlineStr">
@@ -8514,10 +8490,8 @@
           <t>Aryan Tibrewal</t>
         </is>
       </c>
-      <c r="O43" s="3" t="inlineStr">
-        <is>
-          <t>9851320259</t>
-        </is>
+      <c r="O43" s="3" t="n">
+        <v>9851320259</v>
       </c>
       <c r="P43" s="3" t="inlineStr">
         <is>
@@ -8552,10 +8526,8 @@
           <t>Active</t>
         </is>
       </c>
-      <c r="Y43" s="3" t="inlineStr">
-        <is>
-          <t>27.69314</t>
-        </is>
+      <c r="Y43" s="3" t="n">
+        <v>27.69314</v>
       </c>
       <c r="Z43" s="3" t="inlineStr">
         <is>
@@ -8611,25 +8583,21 @@
           <t>Ajit Shrestha</t>
         </is>
       </c>
-      <c r="AN43" s="3" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
+      <c r="AN43" s="3" t="n">
+        <v>4</v>
       </c>
       <c r="AO43" s="3" t="inlineStr">
         <is>
           <t>3,14</t>
         </is>
       </c>
-      <c r="AP43" s="3" t="inlineStr">
-        <is>
-          <t>85.2963</t>
-        </is>
+      <c r="AP43" s="3" t="n">
+        <v>85.2963</v>
       </c>
       <c r="AQ43" s="3" t="inlineStr"/>
       <c r="AR43" s="3" t="inlineStr">
         <is>
-          <t>Case : Wifi 6 Router   has been updated by Ajit Shrestha</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="AS43" s="3" t="inlineStr">
@@ -8725,10 +8693,8 @@
           <t>Sujan Ghising</t>
         </is>
       </c>
-      <c r="O44" s="3" t="inlineStr">
-        <is>
-          <t>9863524625</t>
-        </is>
+      <c r="O44" s="3" t="n">
+        <v>9863524625</v>
       </c>
       <c r="P44" s="3" t="inlineStr">
         <is>
@@ -8763,10 +8729,8 @@
           <t>Active</t>
         </is>
       </c>
-      <c r="Y44" s="3" t="inlineStr">
-        <is>
-          <t>27.73786</t>
-        </is>
+      <c r="Y44" s="3" t="n">
+        <v>27.73786</v>
       </c>
       <c r="Z44" s="3" t="inlineStr">
         <is>
@@ -8818,25 +8782,21 @@
           <t>Sabin Giri</t>
         </is>
       </c>
-      <c r="AN44" s="3" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
+      <c r="AN44" s="3" t="n">
+        <v>6</v>
       </c>
       <c r="AO44" s="3" t="inlineStr">
         <is>
           <t>L62-8</t>
         </is>
       </c>
-      <c r="AP44" s="3" t="inlineStr">
-        <is>
-          <t>85.36657</t>
-        </is>
+      <c r="AP44" s="3" t="n">
+        <v>85.36657</v>
       </c>
       <c r="AQ44" s="3" t="inlineStr"/>
       <c r="AR44" s="3" t="inlineStr">
         <is>
-          <t>Case : wifi 6  has been updated by Sabin Giri</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="AS44" s="3" t="inlineStr">
@@ -8932,10 +8892,8 @@
           <t>Ayush Shakya</t>
         </is>
       </c>
-      <c r="O45" s="3" t="inlineStr">
-        <is>
-          <t>9813326072</t>
-        </is>
+      <c r="O45" s="3" t="n">
+        <v>9813326072</v>
       </c>
       <c r="P45" s="3" t="inlineStr">
         <is>
@@ -8970,10 +8928,8 @@
           <t>Active</t>
         </is>
       </c>
-      <c r="Y45" s="3" t="inlineStr">
-        <is>
-          <t>27.6751</t>
-        </is>
+      <c r="Y45" s="3" t="n">
+        <v>27.6751</v>
       </c>
       <c r="Z45" s="3" t="inlineStr">
         <is>
@@ -9029,48 +8985,880 @@
           <t>Rajesh Maharjan</t>
         </is>
       </c>
-      <c r="AN45" s="3" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
+      <c r="AN45" s="3" t="n">
+        <v>4</v>
       </c>
       <c r="AO45" s="3" t="inlineStr">
         <is>
           <t>3,1</t>
         </is>
       </c>
-      <c r="AP45" s="3" t="inlineStr">
-        <is>
-          <t>85.31538</t>
-        </is>
+      <c r="AP45" s="3" t="n">
+        <v>85.31538</v>
       </c>
       <c r="AQ45" s="3" t="inlineStr"/>
       <c r="AR45" s="3" t="inlineStr">
         <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="AS45" s="3" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="AT45" s="3" t="inlineStr">
+        <is>
+          <t>1d 4h 55m</t>
+        </is>
+      </c>
+      <c r="AU45" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Completed)</t>
+        </is>
+      </c>
+      <c r="AV45" s="3" t="inlineStr">
+        <is>
           <t>Case : wifi 6 upgrade  has been updated by Rajesh Maharjan</t>
         </is>
       </c>
-      <c r="AS45" s="3" t="inlineStr">
+      <c r="AW45" s="3" t="inlineStr">
+        <is>
+          <t>WiFi 6 Upgrade</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="3" t="inlineStr">
+        <is>
+          <t>Sabin Giri</t>
+        </is>
+      </c>
+      <c r="B46" s="3" t="inlineStr">
+        <is>
+          <t>23 Sep 2026 4:48 PM</t>
+        </is>
+      </c>
+      <c r="C46" s="3" t="inlineStr">
+        <is>
+          <t>WGnmUJF06LTlUriJ5DeDBQ==</t>
+        </is>
+      </c>
+      <c r="D46" s="3" t="inlineStr">
+        <is>
+          <t>Sabin Giri</t>
+        </is>
+      </c>
+      <c r="E46" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F46" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G46" s="3" t="inlineStr"/>
+      <c r="H46" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi 6  has been updated by Sabin Giri</t>
+        </is>
+      </c>
+      <c r="I46" s="3" t="inlineStr">
+        <is>
+          <t>wifi 6</t>
+        </is>
+      </c>
+      <c r="J46" s="3" t="inlineStr">
+        <is>
+          <t>TKT1343577</t>
+        </is>
+      </c>
+      <c r="K46" s="3" t="inlineStr">
+        <is>
+          <t>Sujan Ghising</t>
+        </is>
+      </c>
+      <c r="L46" s="3" t="inlineStr">
+        <is>
+          <t>Reopen</t>
+        </is>
+      </c>
+      <c r="M46" s="3" t="inlineStr">
+        <is>
+          <t>Phone</t>
+        </is>
+      </c>
+      <c r="N46" s="3" t="inlineStr">
+        <is>
+          <t>Sujan Ghising</t>
+        </is>
+      </c>
+      <c r="O46" s="3" t="inlineStr">
+        <is>
+          <t>9863524625</t>
+        </is>
+      </c>
+      <c r="P46" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="Q46" s="3" t="inlineStr"/>
+      <c r="R46" s="3" t="inlineStr">
+        <is>
+          <t>23 Sep 2026 04:56:52 PM</t>
+        </is>
+      </c>
+      <c r="S46" s="3" t="inlineStr"/>
+      <c r="T46" s="3" t="inlineStr"/>
+      <c r="U46" s="3" t="inlineStr">
+        <is>
+          <t>9863524625</t>
+        </is>
+      </c>
+      <c r="V46" s="3" t="inlineStr">
+        <is>
+          <t>23 Sep 2026 11:28:38 AM</t>
+        </is>
+      </c>
+      <c r="W46" s="3" t="inlineStr">
+        <is>
+          <t>23 Sep 2026 04:56:52 PM</t>
+        </is>
+      </c>
+      <c r="X46" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Y46" s="3" t="inlineStr">
+        <is>
+          <t>27.73786</t>
+        </is>
+      </c>
+      <c r="Z46" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="AA46" s="3" t="inlineStr">
+        <is>
+          <t>Layer 1-User</t>
+        </is>
+      </c>
+      <c r="AB46" s="3" t="inlineStr">
+        <is>
+          <t>Hari Rijal</t>
+        </is>
+      </c>
+      <c r="AC46" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="AD46" s="3" t="inlineStr"/>
+      <c r="AE46" s="3" t="inlineStr">
+        <is>
+          <t>Kathmandu Gokarneshwor Jorpati nward no:5 near Nepal Telecome Office , Bagmati, Central, Nepal</t>
+        </is>
+      </c>
+      <c r="AF46" s="3" t="inlineStr">
+        <is>
+          <t>mokatnniru496@gmail.com</t>
+        </is>
+      </c>
+      <c r="AG46" s="3" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="AH46" s="3" t="inlineStr"/>
+      <c r="AI46" s="3" t="inlineStr"/>
+      <c r="AJ46" s="3" t="inlineStr"/>
+      <c r="AK46" s="3" t="inlineStr"/>
+      <c r="AL46" s="3" t="inlineStr">
+        <is>
+          <t>Monika Chaudhary</t>
+        </is>
+      </c>
+      <c r="AM46" s="3" t="inlineStr">
+        <is>
+          <t>MS TICKET  HANDLER</t>
+        </is>
+      </c>
+      <c r="AN46" s="3" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AO46" s="3" t="inlineStr">
+        <is>
+          <t>L62-8</t>
+        </is>
+      </c>
+      <c r="AP46" s="3" t="inlineStr">
+        <is>
+          <t>85.36657</t>
+        </is>
+      </c>
+      <c r="AQ46" s="3" t="inlineStr"/>
+      <c r="AR46" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi 6  has been updated by Sabin Giri</t>
+        </is>
+      </c>
+      <c r="AS46" s="3" t="inlineStr">
         <is>
           <t>0m</t>
         </is>
       </c>
-      <c r="AT45" s="3" t="inlineStr">
-        <is>
-          <t>1d 4h 55m</t>
-        </is>
-      </c>
-      <c r="AU45" s="3" t="inlineStr">
-        <is>
-          <t>Completed (Completed)</t>
-        </is>
-      </c>
-      <c r="AV45" s="3" t="inlineStr">
-        <is>
-          <t>Case : wifi 6 upgrade  has been updated by Rajesh Maharjan</t>
-        </is>
-      </c>
-      <c r="AW45" s="3" t="inlineStr">
+      <c r="AT46" s="3" t="inlineStr">
+        <is>
+          <t>5h 28m</t>
+        </is>
+      </c>
+      <c r="AU46" s="3" t="inlineStr">
+        <is>
+          <t>Other / In Progress (Reopen)</t>
+        </is>
+      </c>
+      <c r="AV46" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi 6  has been updated by Sabin Giri</t>
+        </is>
+      </c>
+      <c r="AW46" s="3" t="inlineStr">
+        <is>
+          <t>WiFi 6 Upgrade</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="3" t="inlineStr">
+        <is>
+          <t>Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="B47" s="3" t="inlineStr">
+        <is>
+          <t>23 Sep 2026 4:40 PM</t>
+        </is>
+      </c>
+      <c r="C47" s="3" t="inlineStr">
+        <is>
+          <t>Zg1bIUI+iSmQ1fi360NaxA==</t>
+        </is>
+      </c>
+      <c r="D47" s="3" t="inlineStr">
+        <is>
+          <t>Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="E47" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F47" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G47" s="3" t="inlineStr"/>
+      <c r="H47" s="3" t="inlineStr">
+        <is>
+          <t>Case : SETUP BOX FAULTY   has been updated by Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="I47" s="3" t="inlineStr">
+        <is>
+          <t>SETUP BOX FAULTY</t>
+        </is>
+      </c>
+      <c r="J47" s="3" t="inlineStr">
+        <is>
+          <t>TKT1342776</t>
+        </is>
+      </c>
+      <c r="K47" s="3" t="inlineStr">
+        <is>
+          <t>Bimala Thapa</t>
+        </is>
+      </c>
+      <c r="L47" s="3" t="inlineStr">
+        <is>
+          <t>Closed</t>
+        </is>
+      </c>
+      <c r="M47" s="3" t="inlineStr">
+        <is>
+          <t>Phone</t>
+        </is>
+      </c>
+      <c r="N47" s="3" t="inlineStr">
+        <is>
+          <t>Bimala Thapa</t>
+        </is>
+      </c>
+      <c r="O47" s="3" t="inlineStr">
+        <is>
+          <t>9861032606</t>
+        </is>
+      </c>
+      <c r="P47" s="3" t="inlineStr">
+        <is>
+          <t>Hardware Damage / Malfunction</t>
+        </is>
+      </c>
+      <c r="Q47" s="3" t="inlineStr"/>
+      <c r="R47" s="3" t="inlineStr">
+        <is>
+          <t>22 Sep 2026 05:21:05 PM</t>
+        </is>
+      </c>
+      <c r="S47" s="3" t="inlineStr"/>
+      <c r="T47" s="3" t="inlineStr"/>
+      <c r="U47" s="3" t="inlineStr">
+        <is>
+          <t>9861032606</t>
+        </is>
+      </c>
+      <c r="V47" s="3" t="inlineStr">
+        <is>
+          <t>22 Sep 2026 04:56:20 PM</t>
+        </is>
+      </c>
+      <c r="W47" s="3" t="inlineStr">
+        <is>
+          <t>23 Sep 2026 04:40:21 PM</t>
+        </is>
+      </c>
+      <c r="X47" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Y47" s="3" t="inlineStr">
+        <is>
+          <t>27.682479</t>
+        </is>
+      </c>
+      <c r="Z47" s="3" t="inlineStr">
+        <is>
+          <t>Hardware Damage / Malfunction</t>
+        </is>
+      </c>
+      <c r="AA47" s="3" t="inlineStr">
+        <is>
+          <t>Layer 1-</t>
+        </is>
+      </c>
+      <c r="AB47" s="3" t="inlineStr">
+        <is>
+          <t>Laxman Koirala</t>
+        </is>
+      </c>
+      <c r="AC47" s="3" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="AD47" s="3" t="inlineStr"/>
+      <c r="AE47" s="3" t="inlineStr">
+        <is>
+          <t>Chandragiri ,Naikap ward no:15,panchakanya marga,near Munal Chowk Club, Bagmati, Central, Nepal</t>
+        </is>
+      </c>
+      <c r="AF47" s="3" t="inlineStr">
+        <is>
+          <t>prabeshroka90@gmail.com</t>
+        </is>
+      </c>
+      <c r="AG47" s="3" t="inlineStr">
+        <is>
+          <t>IPTV STB box Damage Issue</t>
+        </is>
+      </c>
+      <c r="AH47" s="3" t="inlineStr"/>
+      <c r="AI47" s="3" t="inlineStr">
+        <is>
+          <t>09:43 hour</t>
+        </is>
+      </c>
+      <c r="AJ47" s="3" t="inlineStr"/>
+      <c r="AK47" s="3" t="inlineStr"/>
+      <c r="AL47" s="3" t="inlineStr">
+        <is>
+          <t>Prajwal Adhikari</t>
+        </is>
+      </c>
+      <c r="AM47" s="3" t="inlineStr">
+        <is>
+          <t>Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="AN47" s="3" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AO47" s="3" t="inlineStr">
+        <is>
+          <t>CDB568</t>
+        </is>
+      </c>
+      <c r="AP47" s="3" t="inlineStr">
+        <is>
+          <t>85.266186</t>
+        </is>
+      </c>
+      <c r="AQ47" s="3" t="inlineStr"/>
+      <c r="AR47" s="3" t="inlineStr">
+        <is>
+          <t>Case : SETUP BOX FAULTY   has been updated by Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="AS47" s="3" t="inlineStr">
+        <is>
+          <t>23h 19m</t>
+        </is>
+      </c>
+      <c r="AT47" s="3" t="inlineStr">
+        <is>
+          <t>23h 44m</t>
+        </is>
+      </c>
+      <c r="AU47" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Closed)</t>
+        </is>
+      </c>
+      <c r="AV47" s="3" t="inlineStr">
+        <is>
+          <t>Case : SETUP BOX FAULTY   has been updated by Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="AW47" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="3" t="inlineStr">
+        <is>
+          <t>Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="B48" s="3" t="inlineStr">
+        <is>
+          <t>23 Sep 2026 4:39 PM</t>
+        </is>
+      </c>
+      <c r="C48" s="3" t="inlineStr">
+        <is>
+          <t>Zg1bIUI+iSmQ1fi360NaxA==</t>
+        </is>
+      </c>
+      <c r="D48" s="3" t="inlineStr">
+        <is>
+          <t>Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="E48" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F48" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G48" s="3" t="inlineStr"/>
+      <c r="H48" s="3" t="inlineStr">
+        <is>
+          <t>Case : SETUP BOX FAULTY   has been updated by Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="I48" s="3" t="inlineStr">
+        <is>
+          <t>SETUP BOX FAULTY</t>
+        </is>
+      </c>
+      <c r="J48" s="3" t="inlineStr">
+        <is>
+          <t>TKT1342776</t>
+        </is>
+      </c>
+      <c r="K48" s="3" t="inlineStr">
+        <is>
+          <t>Bimala Thapa</t>
+        </is>
+      </c>
+      <c r="L48" s="3" t="inlineStr">
+        <is>
+          <t>Closed</t>
+        </is>
+      </c>
+      <c r="M48" s="3" t="inlineStr">
+        <is>
+          <t>Phone</t>
+        </is>
+      </c>
+      <c r="N48" s="3" t="inlineStr">
+        <is>
+          <t>Bimala Thapa</t>
+        </is>
+      </c>
+      <c r="O48" s="3" t="inlineStr">
+        <is>
+          <t>9861032606</t>
+        </is>
+      </c>
+      <c r="P48" s="3" t="inlineStr">
+        <is>
+          <t>Hardware Damage / Malfunction</t>
+        </is>
+      </c>
+      <c r="Q48" s="3" t="inlineStr"/>
+      <c r="R48" s="3" t="inlineStr">
+        <is>
+          <t>22 Sep 2026 05:21:05 PM</t>
+        </is>
+      </c>
+      <c r="S48" s="3" t="inlineStr"/>
+      <c r="T48" s="3" t="inlineStr"/>
+      <c r="U48" s="3" t="inlineStr">
+        <is>
+          <t>9861032606</t>
+        </is>
+      </c>
+      <c r="V48" s="3" t="inlineStr">
+        <is>
+          <t>22 Sep 2026 04:56:20 PM</t>
+        </is>
+      </c>
+      <c r="W48" s="3" t="inlineStr">
+        <is>
+          <t>23 Sep 2026 04:40:21 PM</t>
+        </is>
+      </c>
+      <c r="X48" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Y48" s="3" t="inlineStr">
+        <is>
+          <t>27.682479</t>
+        </is>
+      </c>
+      <c r="Z48" s="3" t="inlineStr">
+        <is>
+          <t>Hardware Damage / Malfunction</t>
+        </is>
+      </c>
+      <c r="AA48" s="3" t="inlineStr">
+        <is>
+          <t>Layer 1-</t>
+        </is>
+      </c>
+      <c r="AB48" s="3" t="inlineStr">
+        <is>
+          <t>Laxman Koirala</t>
+        </is>
+      </c>
+      <c r="AC48" s="3" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="AD48" s="3" t="inlineStr"/>
+      <c r="AE48" s="3" t="inlineStr">
+        <is>
+          <t>Chandragiri ,Naikap ward no:15,panchakanya marga,near Munal Chowk Club, Bagmati, Central, Nepal</t>
+        </is>
+      </c>
+      <c r="AF48" s="3" t="inlineStr">
+        <is>
+          <t>prabeshroka90@gmail.com</t>
+        </is>
+      </c>
+      <c r="AG48" s="3" t="inlineStr">
+        <is>
+          <t>IPTV STB box Damage Issue</t>
+        </is>
+      </c>
+      <c r="AH48" s="3" t="inlineStr"/>
+      <c r="AI48" s="3" t="inlineStr">
+        <is>
+          <t>09:43 hour</t>
+        </is>
+      </c>
+      <c r="AJ48" s="3" t="inlineStr"/>
+      <c r="AK48" s="3" t="inlineStr"/>
+      <c r="AL48" s="3" t="inlineStr">
+        <is>
+          <t>Prajwal Adhikari</t>
+        </is>
+      </c>
+      <c r="AM48" s="3" t="inlineStr">
+        <is>
+          <t>Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="AN48" s="3" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AO48" s="3" t="inlineStr">
+        <is>
+          <t>CDB568</t>
+        </is>
+      </c>
+      <c r="AP48" s="3" t="inlineStr">
+        <is>
+          <t>85.266186</t>
+        </is>
+      </c>
+      <c r="AQ48" s="3" t="inlineStr"/>
+      <c r="AR48" s="3" t="inlineStr">
+        <is>
+          <t>Case : SETUP BOX FAULTY   has been updated by Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="AS48" s="3" t="inlineStr">
+        <is>
+          <t>23h 19m</t>
+        </is>
+      </c>
+      <c r="AT48" s="3" t="inlineStr">
+        <is>
+          <t>23h 44m</t>
+        </is>
+      </c>
+      <c r="AU48" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Closed)</t>
+        </is>
+      </c>
+      <c r="AV48" s="3" t="inlineStr">
+        <is>
+          <t>Case : SETUP BOX FAULTY   has been updated by Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="AW48" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="3" t="inlineStr">
+        <is>
+          <t>Ajit Shrestha</t>
+        </is>
+      </c>
+      <c r="B49" s="3" t="inlineStr">
+        <is>
+          <t>23 Sep 2026 4:56 PM</t>
+        </is>
+      </c>
+      <c r="C49" s="3" t="inlineStr">
+        <is>
+          <t>KK1e4rFHODw22QGqrKXwiw==</t>
+        </is>
+      </c>
+      <c r="D49" s="3" t="inlineStr">
+        <is>
+          <t>Ajit Shrestha</t>
+        </is>
+      </c>
+      <c r="E49" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F49" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G49" s="3" t="inlineStr"/>
+      <c r="H49" s="3" t="inlineStr">
+        <is>
+          <t>Case : Wifi 6 router exchange   has been updated by Ajit Shrestha</t>
+        </is>
+      </c>
+      <c r="I49" s="3" t="inlineStr">
+        <is>
+          <t>Wifi 6 router exchange</t>
+        </is>
+      </c>
+      <c r="J49" s="3" t="inlineStr">
+        <is>
+          <t>TKT1343676</t>
+        </is>
+      </c>
+      <c r="K49" s="3" t="inlineStr">
+        <is>
+          <t>Ajay Khakurel</t>
+        </is>
+      </c>
+      <c r="L49" s="3" t="inlineStr">
+        <is>
+          <t>Closed</t>
+        </is>
+      </c>
+      <c r="M49" s="3" t="inlineStr">
+        <is>
+          <t>Phone</t>
+        </is>
+      </c>
+      <c r="N49" s="3" t="inlineStr">
+        <is>
+          <t>Ajay Khakurel</t>
+        </is>
+      </c>
+      <c r="O49" s="3" t="inlineStr">
+        <is>
+          <t>9840567809</t>
+        </is>
+      </c>
+      <c r="P49" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="Q49" s="3" t="inlineStr"/>
+      <c r="R49" s="3" t="inlineStr">
+        <is>
+          <t>23 Sep 2026 12:26:51 PM</t>
+        </is>
+      </c>
+      <c r="S49" s="3" t="inlineStr"/>
+      <c r="T49" s="3" t="inlineStr"/>
+      <c r="U49" s="3" t="inlineStr">
+        <is>
+          <t>9840567809</t>
+        </is>
+      </c>
+      <c r="V49" s="3" t="inlineStr">
+        <is>
+          <t>23 Sep 2026 12:26:51 PM</t>
+        </is>
+      </c>
+      <c r="W49" s="3" t="inlineStr">
+        <is>
+          <t>23 Sep 2026 04:56:51 PM</t>
+        </is>
+      </c>
+      <c r="X49" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Y49" s="3" t="inlineStr">
+        <is>
+          <t>27.69252</t>
+        </is>
+      </c>
+      <c r="Z49" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="AA49" s="3" t="inlineStr">
+        <is>
+          <t>Layer 1-</t>
+        </is>
+      </c>
+      <c r="AB49" s="3" t="inlineStr">
+        <is>
+          <t>Laxman Koirala</t>
+        </is>
+      </c>
+      <c r="AC49" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="AD49" s="3" t="inlineStr"/>
+      <c r="AE49" s="3" t="inlineStr">
+        <is>
+          <t>kuleshwor, Kathmandu, Bagmati, Central, Nepal, Kathmandu, Nepal, Nepal</t>
+        </is>
+      </c>
+      <c r="AF49" s="3" t="inlineStr"/>
+      <c r="AG49" s="3" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="AH49" s="3" t="inlineStr"/>
+      <c r="AI49" s="3" t="inlineStr">
+        <is>
+          <t>04:30 hour</t>
+        </is>
+      </c>
+      <c r="AJ49" s="3" t="inlineStr"/>
+      <c r="AK49" s="3" t="inlineStr"/>
+      <c r="AL49" s="3" t="inlineStr">
+        <is>
+          <t>Anisha Khadka</t>
+        </is>
+      </c>
+      <c r="AM49" s="3" t="inlineStr">
+        <is>
+          <t>Ajit Shrestha</t>
+        </is>
+      </c>
+      <c r="AN49" s="3" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AO49" s="3" t="inlineStr">
+        <is>
+          <t>CDB338</t>
+        </is>
+      </c>
+      <c r="AP49" s="3" t="inlineStr">
+        <is>
+          <t>85.29843</t>
+        </is>
+      </c>
+      <c r="AQ49" s="3" t="inlineStr"/>
+      <c r="AR49" s="3" t="inlineStr">
+        <is>
+          <t>Case : Wifi 6 router exchange   has been updated by Ajit Shrestha</t>
+        </is>
+      </c>
+      <c r="AS49" s="3" t="inlineStr">
+        <is>
+          <t>4h 30m</t>
+        </is>
+      </c>
+      <c r="AT49" s="3" t="inlineStr">
+        <is>
+          <t>4h 30m</t>
+        </is>
+      </c>
+      <c r="AU49" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Closed)</t>
+        </is>
+      </c>
+      <c r="AV49" s="3" t="inlineStr">
+        <is>
+          <t>Case : Wifi 6 router exchange   has been updated by Ajit Shrestha</t>
+        </is>
+      </c>
+      <c r="AW49" s="3" t="inlineStr">
         <is>
           <t>WiFi 6 Upgrade</t>
         </is>
@@ -9087,7 +9875,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M62"/>
+  <dimension ref="A1:M65"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="45" customWidth="1" min="1" max="1"/>
@@ -9124,7 +9912,7 @@
         </is>
       </c>
       <c r="B2" s="3" t="n">
-        <v>44</v>
+        <v>48</v>
       </c>
     </row>
     <row r="3">
@@ -9134,7 +9922,7 @@
         </is>
       </c>
       <c r="B3" s="5" t="n">
-        <v>32</v>
+        <v>35</v>
       </c>
     </row>
     <row r="4">
@@ -9145,7 +9933,7 @@
       </c>
       <c r="B4" s="3" t="inlineStr">
         <is>
-          <t>72.7%</t>
+          <t>72.9%</t>
         </is>
       </c>
     </row>
@@ -9157,7 +9945,7 @@
       </c>
       <c r="B5" s="5" t="inlineStr">
         <is>
-          <t>5h 20m</t>
+          <t>6h 20m</t>
         </is>
       </c>
     </row>
@@ -9169,7 +9957,7 @@
       </c>
       <c r="B6" s="3" t="inlineStr">
         <is>
-          <t>19h 1m</t>
+          <t>18h 52m</t>
         </is>
       </c>
     </row>
@@ -9210,14 +9998,14 @@
         </is>
       </c>
       <c r="B10" s="3" t="n">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="C10" s="3" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="D10" s="3" t="inlineStr">
         <is>
-          <t>81.5%</t>
+          <t>79.3%</t>
         </is>
       </c>
     </row>
@@ -9228,10 +10016,10 @@
         </is>
       </c>
       <c r="B11" s="5" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="C11" s="5" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="D11" s="5" t="inlineStr">
         <is>
@@ -9377,14 +10165,14 @@
         </is>
       </c>
       <c r="C20" s="3" t="n">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="D20" s="3" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="E20" s="3" t="inlineStr">
         <is>
-          <t>80.0%</t>
+          <t>77.8%</t>
         </is>
       </c>
     </row>
@@ -9423,10 +10211,10 @@
         </is>
       </c>
       <c r="C22" s="3" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="D22" s="3" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="E22" s="3" t="inlineStr">
         <is>
@@ -11458,7 +12246,7 @@
       </c>
       <c r="G58" s="3" t="inlineStr">
         <is>
-          <t>Case : WIFI6 Router Upgrade   has been updated by Chandramani Tharu</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="H58" s="3" t="inlineStr">
@@ -11525,7 +12313,7 @@
       </c>
       <c r="G59" s="5" t="inlineStr">
         <is>
-          <t>Case : SLOW ISSUE   has been updated by Shashikant Chaudhary</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="H59" s="5" t="inlineStr">
@@ -11592,7 +12380,7 @@
       </c>
       <c r="G60" s="3" t="inlineStr">
         <is>
-          <t>Case : Wifi 6 Router   has been updated by Ajit Shrestha</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="H60" s="3" t="inlineStr">
@@ -11659,7 +12447,7 @@
       </c>
       <c r="G61" s="5" t="inlineStr">
         <is>
-          <t>Case : Wifi 6 Router   has been updated by Ajit Shrestha</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="H61" s="5" t="inlineStr">
@@ -11726,14 +12514,14 @@
       </c>
       <c r="G62" s="3" t="inlineStr">
         <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="H62" s="3" t="inlineStr">
+        <is>
           <t>Case : wifi 6 upgrade  has been updated by Rajesh Maharjan</t>
         </is>
       </c>
-      <c r="H62" s="3" t="inlineStr">
-        <is>
-          <t>Case : wifi 6 upgrade  has been updated by Rajesh Maharjan</t>
-        </is>
-      </c>
       <c r="I62" s="3" t="inlineStr">
         <is>
           <t>23 Sep 2026 04:34:58 PM</t>
@@ -11757,6 +12545,207 @@
       <c r="M62" s="3" t="inlineStr">
         <is>
           <t>1d 4h 55m</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" s="5" t="inlineStr">
+        <is>
+          <t>TKT1342776</t>
+        </is>
+      </c>
+      <c r="B63" s="5" t="inlineStr">
+        <is>
+          <t>Bimala Thapa</t>
+        </is>
+      </c>
+      <c r="C63" s="5" t="inlineStr">
+        <is>
+          <t>Hardware Damage / Malfunction</t>
+        </is>
+      </c>
+      <c r="D63" s="5" t="inlineStr">
+        <is>
+          <t>IPTV STB box Damage Issue</t>
+        </is>
+      </c>
+      <c r="E63" s="5" t="inlineStr">
+        <is>
+          <t>Closed</t>
+        </is>
+      </c>
+      <c r="F63" s="5" t="inlineStr">
+        <is>
+          <t>Completed (Closed)</t>
+        </is>
+      </c>
+      <c r="G63" s="5" t="inlineStr">
+        <is>
+          <t>Case : SETUP BOX FAULTY   has been updated by Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="H63" s="5" t="inlineStr">
+        <is>
+          <t>Case : SETUP BOX FAULTY   has been updated by Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="I63" s="5" t="inlineStr">
+        <is>
+          <t>22 Sep 2026 05:21:05 PM</t>
+        </is>
+      </c>
+      <c r="J63" s="5" t="inlineStr">
+        <is>
+          <t>22 Sep 2026 04:56:20 PM</t>
+        </is>
+      </c>
+      <c r="K63" s="5" t="inlineStr">
+        <is>
+          <t>23 Sep 2026 04:40:21 PM</t>
+        </is>
+      </c>
+      <c r="L63" s="5" t="inlineStr">
+        <is>
+          <t>23h 19m</t>
+        </is>
+      </c>
+      <c r="M63" s="5" t="inlineStr">
+        <is>
+          <t>23h 44m</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" s="3" t="inlineStr">
+        <is>
+          <t>TKT1342776</t>
+        </is>
+      </c>
+      <c r="B64" s="3" t="inlineStr">
+        <is>
+          <t>Bimala Thapa</t>
+        </is>
+      </c>
+      <c r="C64" s="3" t="inlineStr">
+        <is>
+          <t>Hardware Damage / Malfunction</t>
+        </is>
+      </c>
+      <c r="D64" s="3" t="inlineStr">
+        <is>
+          <t>IPTV STB box Damage Issue</t>
+        </is>
+      </c>
+      <c r="E64" s="3" t="inlineStr">
+        <is>
+          <t>Closed</t>
+        </is>
+      </c>
+      <c r="F64" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Closed)</t>
+        </is>
+      </c>
+      <c r="G64" s="3" t="inlineStr">
+        <is>
+          <t>Case : SETUP BOX FAULTY   has been updated by Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="H64" s="3" t="inlineStr">
+        <is>
+          <t>Case : SETUP BOX FAULTY   has been updated by Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="I64" s="3" t="inlineStr">
+        <is>
+          <t>22 Sep 2026 05:21:05 PM</t>
+        </is>
+      </c>
+      <c r="J64" s="3" t="inlineStr">
+        <is>
+          <t>22 Sep 2026 04:56:20 PM</t>
+        </is>
+      </c>
+      <c r="K64" s="3" t="inlineStr">
+        <is>
+          <t>23 Sep 2026 04:40:21 PM</t>
+        </is>
+      </c>
+      <c r="L64" s="3" t="inlineStr">
+        <is>
+          <t>23h 19m</t>
+        </is>
+      </c>
+      <c r="M64" s="3" t="inlineStr">
+        <is>
+          <t>23h 44m</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" s="5" t="inlineStr">
+        <is>
+          <t>TKT1343676</t>
+        </is>
+      </c>
+      <c r="B65" s="5" t="inlineStr">
+        <is>
+          <t>Ajay Khakurel</t>
+        </is>
+      </c>
+      <c r="C65" s="5" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="D65" s="5" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="E65" s="5" t="inlineStr">
+        <is>
+          <t>Closed</t>
+        </is>
+      </c>
+      <c r="F65" s="5" t="inlineStr">
+        <is>
+          <t>Completed (Closed)</t>
+        </is>
+      </c>
+      <c r="G65" s="5" t="inlineStr">
+        <is>
+          <t>Case : Wifi 6 router exchange   has been updated by Ajit Shrestha</t>
+        </is>
+      </c>
+      <c r="H65" s="5" t="inlineStr">
+        <is>
+          <t>Case : Wifi 6 router exchange   has been updated by Ajit Shrestha</t>
+        </is>
+      </c>
+      <c r="I65" s="5" t="inlineStr">
+        <is>
+          <t>23 Sep 2026 12:26:51 PM</t>
+        </is>
+      </c>
+      <c r="J65" s="5" t="inlineStr">
+        <is>
+          <t>23 Sep 2026 12:26:51 PM</t>
+        </is>
+      </c>
+      <c r="K65" s="5" t="inlineStr">
+        <is>
+          <t>23 Sep 2026 04:56:51 PM</t>
+        </is>
+      </c>
+      <c r="L65" s="5" t="inlineStr">
+        <is>
+          <t>4h 30m</t>
+        </is>
+      </c>
+      <c r="M65" s="5" t="inlineStr">
+        <is>
+          <t>4h 30m</t>
         </is>
       </c>
     </row>

--- a/audit_report_ALL_TEAM_23_Sep_2026.xlsx
+++ b/audit_report_ALL_TEAM_23_Sep_2026.xlsx
@@ -483,7 +483,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AW49"/>
+  <dimension ref="A1:AW51"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="23" customWidth="1" min="1" max="1"/>
@@ -496,10 +496,10 @@
     <col width="40" customWidth="1" min="8" max="8"/>
     <col width="29" customWidth="1" min="9" max="9"/>
     <col width="16" customWidth="1" min="10" max="10"/>
-    <col width="31" customWidth="1" min="11" max="11"/>
+    <col width="40" customWidth="1" min="11" max="11"/>
     <col width="12" customWidth="1" min="12" max="12"/>
     <col width="14" customWidth="1" min="13" max="13"/>
-    <col width="31" customWidth="1" min="14" max="14"/>
+    <col width="40" customWidth="1" min="14" max="14"/>
     <col width="13" customWidth="1" min="15" max="15"/>
     <col width="32" customWidth="1" min="16" max="16"/>
     <col width="19" customWidth="1" min="17" max="17"/>
@@ -9095,10 +9095,8 @@
           <t>Sujan Ghising</t>
         </is>
       </c>
-      <c r="O46" s="3" t="inlineStr">
-        <is>
-          <t>9863524625</t>
-        </is>
+      <c r="O46" s="3" t="n">
+        <v>9863524625</v>
       </c>
       <c r="P46" s="3" t="inlineStr">
         <is>
@@ -9133,10 +9131,8 @@
           <t>Active</t>
         </is>
       </c>
-      <c r="Y46" s="3" t="inlineStr">
-        <is>
-          <t>27.73786</t>
-        </is>
+      <c r="Y46" s="3" t="n">
+        <v>27.73786</v>
       </c>
       <c r="Z46" s="3" t="inlineStr">
         <is>
@@ -9188,25 +9184,21 @@
           <t>MS TICKET  HANDLER</t>
         </is>
       </c>
-      <c r="AN46" s="3" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
+      <c r="AN46" s="3" t="n">
+        <v>6</v>
       </c>
       <c r="AO46" s="3" t="inlineStr">
         <is>
           <t>L62-8</t>
         </is>
       </c>
-      <c r="AP46" s="3" t="inlineStr">
-        <is>
-          <t>85.36657</t>
-        </is>
+      <c r="AP46" s="3" t="n">
+        <v>85.36657</v>
       </c>
       <c r="AQ46" s="3" t="inlineStr"/>
       <c r="AR46" s="3" t="inlineStr">
         <is>
-          <t>Case : wifi 6  has been updated by Sabin Giri</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="AS46" s="3" t="inlineStr">
@@ -9302,10 +9294,8 @@
           <t>Bimala Thapa</t>
         </is>
       </c>
-      <c r="O47" s="3" t="inlineStr">
-        <is>
-          <t>9861032606</t>
-        </is>
+      <c r="O47" s="3" t="n">
+        <v>9861032606</v>
       </c>
       <c r="P47" s="3" t="inlineStr">
         <is>
@@ -9340,10 +9330,8 @@
           <t>Active</t>
         </is>
       </c>
-      <c r="Y47" s="3" t="inlineStr">
-        <is>
-          <t>27.682479</t>
-        </is>
+      <c r="Y47" s="3" t="n">
+        <v>27.682479</v>
       </c>
       <c r="Z47" s="3" t="inlineStr">
         <is>
@@ -9399,25 +9387,21 @@
           <t>Sunil Chaudhary</t>
         </is>
       </c>
-      <c r="AN47" s="3" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
+      <c r="AN47" s="3" t="n">
+        <v>6</v>
       </c>
       <c r="AO47" s="3" t="inlineStr">
         <is>
           <t>CDB568</t>
         </is>
       </c>
-      <c r="AP47" s="3" t="inlineStr">
-        <is>
-          <t>85.266186</t>
-        </is>
+      <c r="AP47" s="3" t="n">
+        <v>85.266186</v>
       </c>
       <c r="AQ47" s="3" t="inlineStr"/>
       <c r="AR47" s="3" t="inlineStr">
         <is>
-          <t>Case : SETUP BOX FAULTY   has been updated by Sunil Chaudhary</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="AS47" s="3" t="inlineStr">
@@ -9513,10 +9497,8 @@
           <t>Bimala Thapa</t>
         </is>
       </c>
-      <c r="O48" s="3" t="inlineStr">
-        <is>
-          <t>9861032606</t>
-        </is>
+      <c r="O48" s="3" t="n">
+        <v>9861032606</v>
       </c>
       <c r="P48" s="3" t="inlineStr">
         <is>
@@ -9551,10 +9533,8 @@
           <t>Active</t>
         </is>
       </c>
-      <c r="Y48" s="3" t="inlineStr">
-        <is>
-          <t>27.682479</t>
-        </is>
+      <c r="Y48" s="3" t="n">
+        <v>27.682479</v>
       </c>
       <c r="Z48" s="3" t="inlineStr">
         <is>
@@ -9610,25 +9590,21 @@
           <t>Sunil Chaudhary</t>
         </is>
       </c>
-      <c r="AN48" s="3" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
+      <c r="AN48" s="3" t="n">
+        <v>6</v>
       </c>
       <c r="AO48" s="3" t="inlineStr">
         <is>
           <t>CDB568</t>
         </is>
       </c>
-      <c r="AP48" s="3" t="inlineStr">
-        <is>
-          <t>85.266186</t>
-        </is>
+      <c r="AP48" s="3" t="n">
+        <v>85.266186</v>
       </c>
       <c r="AQ48" s="3" t="inlineStr"/>
       <c r="AR48" s="3" t="inlineStr">
         <is>
-          <t>Case : SETUP BOX FAULTY   has been updated by Sunil Chaudhary</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="AS48" s="3" t="inlineStr">
@@ -9724,10 +9700,8 @@
           <t>Ajay Khakurel</t>
         </is>
       </c>
-      <c r="O49" s="3" t="inlineStr">
-        <is>
-          <t>9840567809</t>
-        </is>
+      <c r="O49" s="3" t="n">
+        <v>9840567809</v>
       </c>
       <c r="P49" s="3" t="inlineStr">
         <is>
@@ -9762,10 +9736,8 @@
           <t>Active</t>
         </is>
       </c>
-      <c r="Y49" s="3" t="inlineStr">
-        <is>
-          <t>27.69252</t>
-        </is>
+      <c r="Y49" s="3" t="n">
+        <v>27.69252</v>
       </c>
       <c r="Z49" s="3" t="inlineStr">
         <is>
@@ -9817,48 +9789,466 @@
           <t>Ajit Shrestha</t>
         </is>
       </c>
-      <c r="AN49" s="3" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
+      <c r="AN49" s="3" t="n">
+        <v>6</v>
       </c>
       <c r="AO49" s="3" t="inlineStr">
         <is>
           <t>CDB338</t>
         </is>
       </c>
-      <c r="AP49" s="3" t="inlineStr">
-        <is>
-          <t>85.29843</t>
-        </is>
+      <c r="AP49" s="3" t="n">
+        <v>85.29843</v>
       </c>
       <c r="AQ49" s="3" t="inlineStr"/>
       <c r="AR49" s="3" t="inlineStr">
         <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="AS49" s="3" t="inlineStr">
+        <is>
+          <t>4h 30m</t>
+        </is>
+      </c>
+      <c r="AT49" s="3" t="inlineStr">
+        <is>
+          <t>4h 30m</t>
+        </is>
+      </c>
+      <c r="AU49" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Closed)</t>
+        </is>
+      </c>
+      <c r="AV49" s="3" t="inlineStr">
+        <is>
           <t>Case : Wifi 6 router exchange   has been updated by Ajit Shrestha</t>
         </is>
       </c>
-      <c r="AS49" s="3" t="inlineStr">
-        <is>
-          <t>4h 30m</t>
-        </is>
-      </c>
-      <c r="AT49" s="3" t="inlineStr">
-        <is>
-          <t>4h 30m</t>
-        </is>
-      </c>
-      <c r="AU49" s="3" t="inlineStr">
+      <c r="AW49" s="3" t="inlineStr">
+        <is>
+          <t>WiFi 6 Upgrade</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="3" t="inlineStr">
+        <is>
+          <t>Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="B50" s="3" t="inlineStr">
+        <is>
+          <t>23 Sep 2026 5:15 PM</t>
+        </is>
+      </c>
+      <c r="C50" s="3" t="inlineStr">
+        <is>
+          <t>Zg1bIUI+iSmQ1fi360NaxA==</t>
+        </is>
+      </c>
+      <c r="D50" s="3" t="inlineStr">
+        <is>
+          <t>Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="E50" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F50" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G50" s="3" t="inlineStr"/>
+      <c r="H50" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi 6  has been updated by Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="I50" s="3" t="inlineStr">
+        <is>
+          <t>wifi 6</t>
+        </is>
+      </c>
+      <c r="J50" s="3" t="inlineStr">
+        <is>
+          <t>TKT1343738</t>
+        </is>
+      </c>
+      <c r="K50" s="3" t="inlineStr">
+        <is>
+          <t>CT Rental and Event Management Pvt Ltd</t>
+        </is>
+      </c>
+      <c r="L50" s="3" t="inlineStr">
+        <is>
+          <t>Closed</t>
+        </is>
+      </c>
+      <c r="M50" s="3" t="inlineStr">
+        <is>
+          <t>Phone</t>
+        </is>
+      </c>
+      <c r="N50" s="3" t="inlineStr">
+        <is>
+          <t>CT Rental and Event Management Pvt Ltd</t>
+        </is>
+      </c>
+      <c r="O50" s="3" t="inlineStr">
+        <is>
+          <t>9851318537</t>
+        </is>
+      </c>
+      <c r="P50" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="Q50" s="3" t="inlineStr"/>
+      <c r="R50" s="3" t="inlineStr">
+        <is>
+          <t>23 Sep 2026 01:21:11 PM</t>
+        </is>
+      </c>
+      <c r="S50" s="3" t="inlineStr"/>
+      <c r="T50" s="3" t="inlineStr"/>
+      <c r="U50" s="3" t="inlineStr">
+        <is>
+          <t>9851318537</t>
+        </is>
+      </c>
+      <c r="V50" s="3" t="inlineStr">
+        <is>
+          <t>23 Sep 2026 01:16:34 PM</t>
+        </is>
+      </c>
+      <c r="W50" s="3" t="inlineStr">
+        <is>
+          <t>23 Sep 2026 05:15:07 PM</t>
+        </is>
+      </c>
+      <c r="X50" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Y50" s="3" t="inlineStr">
+        <is>
+          <t>27.69617</t>
+        </is>
+      </c>
+      <c r="Z50" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="AA50" s="3" t="inlineStr">
+        <is>
+          <t>Layer 1-</t>
+        </is>
+      </c>
+      <c r="AB50" s="3" t="inlineStr">
+        <is>
+          <t>Laxman Koirala</t>
+        </is>
+      </c>
+      <c r="AC50" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="AD50" s="3" t="inlineStr"/>
+      <c r="AE50" s="3" t="inlineStr">
+        <is>
+          <t>Munal club tinthana, Bagmati, Nepal, Nepal</t>
+        </is>
+      </c>
+      <c r="AF50" s="3" t="inlineStr">
+        <is>
+          <t>amal.hsenag421@gmail.com</t>
+        </is>
+      </c>
+      <c r="AG50" s="3" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="AH50" s="3" t="inlineStr"/>
+      <c r="AI50" s="3" t="inlineStr">
+        <is>
+          <t>03:58 hour</t>
+        </is>
+      </c>
+      <c r="AJ50" s="3" t="inlineStr"/>
+      <c r="AK50" s="3" t="inlineStr"/>
+      <c r="AL50" s="3" t="inlineStr">
+        <is>
+          <t>Joshna Shrestha</t>
+        </is>
+      </c>
+      <c r="AM50" s="3" t="inlineStr">
+        <is>
+          <t>Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="AN50" s="3" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AO50" s="3" t="inlineStr">
+        <is>
+          <t>4,4</t>
+        </is>
+      </c>
+      <c r="AP50" s="3" t="inlineStr">
+        <is>
+          <t>85.2928</t>
+        </is>
+      </c>
+      <c r="AQ50" s="3" t="inlineStr"/>
+      <c r="AR50" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi 6  has been updated by Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="AS50" s="3" t="inlineStr">
+        <is>
+          <t>3h 53m</t>
+        </is>
+      </c>
+      <c r="AT50" s="3" t="inlineStr">
+        <is>
+          <t>3h 58m</t>
+        </is>
+      </c>
+      <c r="AU50" s="3" t="inlineStr">
         <is>
           <t>Completed (Closed)</t>
         </is>
       </c>
-      <c r="AV49" s="3" t="inlineStr">
-        <is>
-          <t>Case : Wifi 6 router exchange   has been updated by Ajit Shrestha</t>
-        </is>
-      </c>
-      <c r="AW49" s="3" t="inlineStr">
+      <c r="AV50" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi 6  has been updated by Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="AW50" s="3" t="inlineStr">
+        <is>
+          <t>WiFi 6 Upgrade</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="3" t="inlineStr">
+        <is>
+          <t>Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="B51" s="3" t="inlineStr">
+        <is>
+          <t>23 Sep 2026 5:14 PM</t>
+        </is>
+      </c>
+      <c r="C51" s="3" t="inlineStr">
+        <is>
+          <t>Zg1bIUI+iSmQ1fi360NaxA==</t>
+        </is>
+      </c>
+      <c r="D51" s="3" t="inlineStr">
+        <is>
+          <t>Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="E51" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F51" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G51" s="3" t="inlineStr"/>
+      <c r="H51" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi 6  has been updated by Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="I51" s="3" t="inlineStr">
+        <is>
+          <t>wifi 6</t>
+        </is>
+      </c>
+      <c r="J51" s="3" t="inlineStr">
+        <is>
+          <t>TKT1343738</t>
+        </is>
+      </c>
+      <c r="K51" s="3" t="inlineStr">
+        <is>
+          <t>CT Rental and Event Management Pvt Ltd</t>
+        </is>
+      </c>
+      <c r="L51" s="3" t="inlineStr">
+        <is>
+          <t>Closed</t>
+        </is>
+      </c>
+      <c r="M51" s="3" t="inlineStr">
+        <is>
+          <t>Phone</t>
+        </is>
+      </c>
+      <c r="N51" s="3" t="inlineStr">
+        <is>
+          <t>CT Rental and Event Management Pvt Ltd</t>
+        </is>
+      </c>
+      <c r="O51" s="3" t="inlineStr">
+        <is>
+          <t>9851318537</t>
+        </is>
+      </c>
+      <c r="P51" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="Q51" s="3" t="inlineStr"/>
+      <c r="R51" s="3" t="inlineStr">
+        <is>
+          <t>23 Sep 2026 01:21:11 PM</t>
+        </is>
+      </c>
+      <c r="S51" s="3" t="inlineStr"/>
+      <c r="T51" s="3" t="inlineStr"/>
+      <c r="U51" s="3" t="inlineStr">
+        <is>
+          <t>9851318537</t>
+        </is>
+      </c>
+      <c r="V51" s="3" t="inlineStr">
+        <is>
+          <t>23 Sep 2026 01:16:34 PM</t>
+        </is>
+      </c>
+      <c r="W51" s="3" t="inlineStr">
+        <is>
+          <t>23 Sep 2026 05:15:07 PM</t>
+        </is>
+      </c>
+      <c r="X51" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Y51" s="3" t="inlineStr">
+        <is>
+          <t>27.69617</t>
+        </is>
+      </c>
+      <c r="Z51" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="AA51" s="3" t="inlineStr">
+        <is>
+          <t>Layer 1-</t>
+        </is>
+      </c>
+      <c r="AB51" s="3" t="inlineStr">
+        <is>
+          <t>Laxman Koirala</t>
+        </is>
+      </c>
+      <c r="AC51" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="AD51" s="3" t="inlineStr"/>
+      <c r="AE51" s="3" t="inlineStr">
+        <is>
+          <t>Munal club tinthana, Bagmati, Nepal, Nepal</t>
+        </is>
+      </c>
+      <c r="AF51" s="3" t="inlineStr">
+        <is>
+          <t>amal.hsenag421@gmail.com</t>
+        </is>
+      </c>
+      <c r="AG51" s="3" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="AH51" s="3" t="inlineStr"/>
+      <c r="AI51" s="3" t="inlineStr">
+        <is>
+          <t>03:58 hour</t>
+        </is>
+      </c>
+      <c r="AJ51" s="3" t="inlineStr"/>
+      <c r="AK51" s="3" t="inlineStr"/>
+      <c r="AL51" s="3" t="inlineStr">
+        <is>
+          <t>Joshna Shrestha</t>
+        </is>
+      </c>
+      <c r="AM51" s="3" t="inlineStr">
+        <is>
+          <t>Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="AN51" s="3" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AO51" s="3" t="inlineStr">
+        <is>
+          <t>4,4</t>
+        </is>
+      </c>
+      <c r="AP51" s="3" t="inlineStr">
+        <is>
+          <t>85.2928</t>
+        </is>
+      </c>
+      <c r="AQ51" s="3" t="inlineStr"/>
+      <c r="AR51" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi 6  has been updated by Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="AS51" s="3" t="inlineStr">
+        <is>
+          <t>3h 53m</t>
+        </is>
+      </c>
+      <c r="AT51" s="3" t="inlineStr">
+        <is>
+          <t>3h 58m</t>
+        </is>
+      </c>
+      <c r="AU51" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Closed)</t>
+        </is>
+      </c>
+      <c r="AV51" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi 6  has been updated by Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="AW51" s="3" t="inlineStr">
         <is>
           <t>WiFi 6 Upgrade</t>
         </is>
@@ -9875,11 +10265,11 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M65"/>
+  <dimension ref="A1:M67"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="45" customWidth="1" min="1" max="1"/>
-    <col width="40" customWidth="1" min="2" max="2"/>
+    <col width="42" customWidth="1" min="2" max="2"/>
     <col width="33" customWidth="1" min="3" max="3"/>
     <col width="40" customWidth="1" min="4" max="4"/>
     <col width="19" customWidth="1" min="5" max="5"/>
@@ -9912,7 +10302,7 @@
         </is>
       </c>
       <c r="B2" s="3" t="n">
-        <v>48</v>
+        <v>50</v>
       </c>
     </row>
     <row r="3">
@@ -9922,7 +10312,7 @@
         </is>
       </c>
       <c r="B3" s="5" t="n">
-        <v>35</v>
+        <v>37</v>
       </c>
     </row>
     <row r="4">
@@ -9933,7 +10323,7 @@
       </c>
       <c r="B4" s="3" t="inlineStr">
         <is>
-          <t>72.9%</t>
+          <t>74.0%</t>
         </is>
       </c>
     </row>
@@ -9945,7 +10335,7 @@
       </c>
       <c r="B5" s="5" t="inlineStr">
         <is>
-          <t>6h 20m</t>
+          <t>6h 12m</t>
         </is>
       </c>
     </row>
@@ -9957,7 +10347,7 @@
       </c>
       <c r="B6" s="3" t="inlineStr">
         <is>
-          <t>18h 52m</t>
+          <t>18h 4m</t>
         </is>
       </c>
     </row>
@@ -9998,14 +10388,14 @@
         </is>
       </c>
       <c r="B10" s="3" t="n">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="C10" s="3" t="n">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="D10" s="3" t="inlineStr">
         <is>
-          <t>79.3%</t>
+          <t>80.6%</t>
         </is>
       </c>
     </row>
@@ -10165,14 +10555,14 @@
         </is>
       </c>
       <c r="C20" s="3" t="n">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="D20" s="3" t="n">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="E20" s="3" t="inlineStr">
         <is>
-          <t>77.8%</t>
+          <t>79.3%</t>
         </is>
       </c>
     </row>
@@ -12581,7 +12971,7 @@
       </c>
       <c r="G63" s="5" t="inlineStr">
         <is>
-          <t>Case : SETUP BOX FAULTY   has been updated by Sunil Chaudhary</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="H63" s="5" t="inlineStr">
@@ -12648,7 +13038,7 @@
       </c>
       <c r="G64" s="3" t="inlineStr">
         <is>
-          <t>Case : SETUP BOX FAULTY   has been updated by Sunil Chaudhary</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="H64" s="3" t="inlineStr">
@@ -12715,14 +13105,14 @@
       </c>
       <c r="G65" s="5" t="inlineStr">
         <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="H65" s="5" t="inlineStr">
+        <is>
           <t>Case : Wifi 6 router exchange   has been updated by Ajit Shrestha</t>
         </is>
       </c>
-      <c r="H65" s="5" t="inlineStr">
-        <is>
-          <t>Case : Wifi 6 router exchange   has been updated by Ajit Shrestha</t>
-        </is>
-      </c>
       <c r="I65" s="5" t="inlineStr">
         <is>
           <t>23 Sep 2026 12:26:51 PM</t>
@@ -12746,6 +13136,140 @@
       <c r="M65" s="5" t="inlineStr">
         <is>
           <t>4h 30m</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" s="3" t="inlineStr">
+        <is>
+          <t>TKT1343738</t>
+        </is>
+      </c>
+      <c r="B66" s="3" t="inlineStr">
+        <is>
+          <t>CT Rental and Event Management Pvt Ltd</t>
+        </is>
+      </c>
+      <c r="C66" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="D66" s="3" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="E66" s="3" t="inlineStr">
+        <is>
+          <t>Closed</t>
+        </is>
+      </c>
+      <c r="F66" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Closed)</t>
+        </is>
+      </c>
+      <c r="G66" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi 6  has been updated by Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="H66" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi 6  has been updated by Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="I66" s="3" t="inlineStr">
+        <is>
+          <t>23 Sep 2026 01:21:11 PM</t>
+        </is>
+      </c>
+      <c r="J66" s="3" t="inlineStr">
+        <is>
+          <t>23 Sep 2026 01:16:34 PM</t>
+        </is>
+      </c>
+      <c r="K66" s="3" t="inlineStr">
+        <is>
+          <t>23 Sep 2026 05:15:07 PM</t>
+        </is>
+      </c>
+      <c r="L66" s="3" t="inlineStr">
+        <is>
+          <t>3h 53m</t>
+        </is>
+      </c>
+      <c r="M66" s="3" t="inlineStr">
+        <is>
+          <t>3h 58m</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" s="5" t="inlineStr">
+        <is>
+          <t>TKT1343738</t>
+        </is>
+      </c>
+      <c r="B67" s="5" t="inlineStr">
+        <is>
+          <t>CT Rental and Event Management Pvt Ltd</t>
+        </is>
+      </c>
+      <c r="C67" s="5" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="D67" s="5" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="E67" s="5" t="inlineStr">
+        <is>
+          <t>Closed</t>
+        </is>
+      </c>
+      <c r="F67" s="5" t="inlineStr">
+        <is>
+          <t>Completed (Closed)</t>
+        </is>
+      </c>
+      <c r="G67" s="5" t="inlineStr">
+        <is>
+          <t>Case : wifi 6  has been updated by Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="H67" s="5" t="inlineStr">
+        <is>
+          <t>Case : wifi 6  has been updated by Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="I67" s="5" t="inlineStr">
+        <is>
+          <t>23 Sep 2026 01:21:11 PM</t>
+        </is>
+      </c>
+      <c r="J67" s="5" t="inlineStr">
+        <is>
+          <t>23 Sep 2026 01:16:34 PM</t>
+        </is>
+      </c>
+      <c r="K67" s="5" t="inlineStr">
+        <is>
+          <t>23 Sep 2026 05:15:07 PM</t>
+        </is>
+      </c>
+      <c r="L67" s="5" t="inlineStr">
+        <is>
+          <t>3h 53m</t>
+        </is>
+      </c>
+      <c r="M67" s="5" t="inlineStr">
+        <is>
+          <t>3h 58m</t>
         </is>
       </c>
     </row>

--- a/audit_report_ALL_TEAM_23_Sep_2026.xlsx
+++ b/audit_report_ALL_TEAM_23_Sep_2026.xlsx
@@ -529,7 +529,7 @@
     <col width="27" customWidth="1" min="41" max="41"/>
     <col width="12" customWidth="1" min="42" max="42"/>
     <col width="17" customWidth="1" min="43" max="43"/>
-    <col width="40" customWidth="1" min="44" max="44"/>
+    <col width="34" customWidth="1" min="44" max="44"/>
     <col width="34" customWidth="1" min="45" max="45"/>
     <col width="33" customWidth="1" min="46" max="46"/>
     <col width="32" customWidth="1" min="47" max="47"/>
@@ -9899,10 +9899,8 @@
           <t>CT Rental and Event Management Pvt Ltd</t>
         </is>
       </c>
-      <c r="O50" s="3" t="inlineStr">
-        <is>
-          <t>9851318537</t>
-        </is>
+      <c r="O50" s="3" t="n">
+        <v>9851318537</v>
       </c>
       <c r="P50" s="3" t="inlineStr">
         <is>
@@ -9937,10 +9935,8 @@
           <t>Active</t>
         </is>
       </c>
-      <c r="Y50" s="3" t="inlineStr">
-        <is>
-          <t>27.69617</t>
-        </is>
+      <c r="Y50" s="3" t="n">
+        <v>27.69617</v>
       </c>
       <c r="Z50" s="3" t="inlineStr">
         <is>
@@ -9996,25 +9992,21 @@
           <t>Sunil Chaudhary</t>
         </is>
       </c>
-      <c r="AN50" s="3" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
+      <c r="AN50" s="3" t="n">
+        <v>4</v>
       </c>
       <c r="AO50" s="3" t="inlineStr">
         <is>
           <t>4,4</t>
         </is>
       </c>
-      <c r="AP50" s="3" t="inlineStr">
-        <is>
-          <t>85.2928</t>
-        </is>
+      <c r="AP50" s="3" t="n">
+        <v>85.2928</v>
       </c>
       <c r="AQ50" s="3" t="inlineStr"/>
       <c r="AR50" s="3" t="inlineStr">
         <is>
-          <t>Case : wifi 6  has been updated by Sunil Chaudhary</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="AS50" s="3" t="inlineStr">
@@ -10110,10 +10102,8 @@
           <t>CT Rental and Event Management Pvt Ltd</t>
         </is>
       </c>
-      <c r="O51" s="3" t="inlineStr">
-        <is>
-          <t>9851318537</t>
-        </is>
+      <c r="O51" s="3" t="n">
+        <v>9851318537</v>
       </c>
       <c r="P51" s="3" t="inlineStr">
         <is>
@@ -10148,10 +10138,8 @@
           <t>Active</t>
         </is>
       </c>
-      <c r="Y51" s="3" t="inlineStr">
-        <is>
-          <t>27.69617</t>
-        </is>
+      <c r="Y51" s="3" t="n">
+        <v>27.69617</v>
       </c>
       <c r="Z51" s="3" t="inlineStr">
         <is>
@@ -10207,25 +10195,21 @@
           <t>Sunil Chaudhary</t>
         </is>
       </c>
-      <c r="AN51" s="3" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
+      <c r="AN51" s="3" t="n">
+        <v>4</v>
       </c>
       <c r="AO51" s="3" t="inlineStr">
         <is>
           <t>4,4</t>
         </is>
       </c>
-      <c r="AP51" s="3" t="inlineStr">
-        <is>
-          <t>85.2928</t>
-        </is>
+      <c r="AP51" s="3" t="n">
+        <v>85.2928</v>
       </c>
       <c r="AQ51" s="3" t="inlineStr"/>
       <c r="AR51" s="3" t="inlineStr">
         <is>
-          <t>Case : wifi 6  has been updated by Sunil Chaudhary</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="AS51" s="3" t="inlineStr">
@@ -10274,7 +10258,7 @@
     <col width="40" customWidth="1" min="4" max="4"/>
     <col width="19" customWidth="1" min="5" max="5"/>
     <col width="25" customWidth="1" min="6" max="6"/>
-    <col width="45" customWidth="1" min="7" max="7"/>
+    <col width="35" customWidth="1" min="7" max="7"/>
     <col width="45" customWidth="1" min="8" max="8"/>
     <col width="27" customWidth="1" min="9" max="9"/>
     <col width="27" customWidth="1" min="10" max="10"/>
@@ -13172,7 +13156,7 @@
       </c>
       <c r="G66" s="3" t="inlineStr">
         <is>
-          <t>Case : wifi 6  has been updated by Sunil Chaudhary</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="H66" s="3" t="inlineStr">
@@ -13239,7 +13223,7 @@
       </c>
       <c r="G67" s="5" t="inlineStr">
         <is>
-          <t>Case : wifi 6  has been updated by Sunil Chaudhary</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="H67" s="5" t="inlineStr">

--- a/audit_report_ALL_TEAM_23_Sep_2026.xlsx
+++ b/audit_report_ALL_TEAM_23_Sep_2026.xlsx
@@ -483,7 +483,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AW51"/>
+  <dimension ref="A1:AW53"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="23" customWidth="1" min="1" max="1"/>
@@ -529,7 +529,7 @@
     <col width="27" customWidth="1" min="41" max="41"/>
     <col width="12" customWidth="1" min="42" max="42"/>
     <col width="17" customWidth="1" min="43" max="43"/>
-    <col width="34" customWidth="1" min="44" max="44"/>
+    <col width="40" customWidth="1" min="44" max="44"/>
     <col width="34" customWidth="1" min="45" max="45"/>
     <col width="33" customWidth="1" min="46" max="46"/>
     <col width="32" customWidth="1" min="47" max="47"/>
@@ -10238,6 +10238,320 @@
         </is>
       </c>
     </row>
+    <row r="52">
+      <c r="A52" s="3" t="inlineStr">
+        <is>
+          <t>Rajesh Maharjan</t>
+        </is>
+      </c>
+      <c r="B52" s="3" t="inlineStr">
+        <is>
+          <t>23 Sep 2026 5:18 PM</t>
+        </is>
+      </c>
+      <c r="C52" s="3" t="inlineStr">
+        <is>
+          <t>/Oi+2zlne73U37ZA62PktA==</t>
+        </is>
+      </c>
+      <c r="D52" s="3" t="inlineStr">
+        <is>
+          <t>Rajesh Maharjan</t>
+        </is>
+      </c>
+      <c r="E52" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F52" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G52" s="3" t="inlineStr"/>
+      <c r="H52" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi 6  has been updated by Rajesh Maharjan</t>
+        </is>
+      </c>
+      <c r="I52" s="3" t="inlineStr"/>
+      <c r="J52" s="3" t="inlineStr"/>
+      <c r="K52" s="3" t="inlineStr"/>
+      <c r="L52" s="3" t="inlineStr"/>
+      <c r="M52" s="3" t="inlineStr"/>
+      <c r="N52" s="3" t="inlineStr"/>
+      <c r="O52" s="3" t="inlineStr"/>
+      <c r="P52" s="3" t="inlineStr"/>
+      <c r="Q52" s="3" t="inlineStr"/>
+      <c r="R52" s="3" t="inlineStr"/>
+      <c r="S52" s="3" t="inlineStr"/>
+      <c r="T52" s="3" t="inlineStr"/>
+      <c r="U52" s="3" t="inlineStr"/>
+      <c r="V52" s="3" t="inlineStr"/>
+      <c r="W52" s="3" t="inlineStr"/>
+      <c r="X52" s="3" t="inlineStr"/>
+      <c r="Y52" s="3" t="inlineStr"/>
+      <c r="Z52" s="3" t="inlineStr"/>
+      <c r="AA52" s="3" t="inlineStr"/>
+      <c r="AB52" s="3" t="inlineStr"/>
+      <c r="AC52" s="3" t="inlineStr"/>
+      <c r="AD52" s="3" t="inlineStr"/>
+      <c r="AE52" s="3" t="inlineStr"/>
+      <c r="AF52" s="3" t="inlineStr"/>
+      <c r="AG52" s="3" t="inlineStr"/>
+      <c r="AH52" s="3" t="inlineStr"/>
+      <c r="AI52" s="3" t="inlineStr"/>
+      <c r="AJ52" s="3" t="inlineStr"/>
+      <c r="AK52" s="3" t="inlineStr"/>
+      <c r="AL52" s="3" t="inlineStr"/>
+      <c r="AM52" s="3" t="inlineStr"/>
+      <c r="AN52" s="3" t="inlineStr"/>
+      <c r="AO52" s="3" t="inlineStr"/>
+      <c r="AP52" s="3" t="inlineStr"/>
+      <c r="AQ52" s="3" t="inlineStr"/>
+      <c r="AR52" s="3" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="AS52" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="AT52" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="AU52" s="3" t="inlineStr">
+        <is>
+          <t>Other / In Progress (nan)</t>
+        </is>
+      </c>
+      <c r="AV52" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi 6  has been updated by Rajesh Maharjan</t>
+        </is>
+      </c>
+      <c r="AW52" s="3" t="inlineStr">
+        <is>
+          <t>WiFi 6 Upgrade</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="3" t="inlineStr">
+        <is>
+          <t>Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="B53" s="3" t="inlineStr">
+        <is>
+          <t>23 Sep 2026 5:32 PM</t>
+        </is>
+      </c>
+      <c r="C53" s="3" t="inlineStr">
+        <is>
+          <t>atwz5SElGeKMz8qxsp3b6c34SBAfIMR+</t>
+        </is>
+      </c>
+      <c r="D53" s="3" t="inlineStr">
+        <is>
+          <t>Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="E53" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F53" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G53" s="3" t="inlineStr"/>
+      <c r="H53" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi 6  has been updated by Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="I53" s="3" t="inlineStr">
+        <is>
+          <t>wifi 6</t>
+        </is>
+      </c>
+      <c r="J53" s="3" t="inlineStr">
+        <is>
+          <t>TKT1343449</t>
+        </is>
+      </c>
+      <c r="K53" s="3" t="inlineStr">
+        <is>
+          <t>Kirti Kiran Joshi</t>
+        </is>
+      </c>
+      <c r="L53" s="3" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="M53" s="3" t="inlineStr">
+        <is>
+          <t>Phone</t>
+        </is>
+      </c>
+      <c r="N53" s="3" t="inlineStr">
+        <is>
+          <t>Kirti Kiran Joshi</t>
+        </is>
+      </c>
+      <c r="O53" s="3" t="inlineStr">
+        <is>
+          <t>9741673311</t>
+        </is>
+      </c>
+      <c r="P53" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="Q53" s="3" t="inlineStr"/>
+      <c r="R53" s="3" t="inlineStr">
+        <is>
+          <t>23 Sep 2026 05:32:18 PM</t>
+        </is>
+      </c>
+      <c r="S53" s="3" t="inlineStr"/>
+      <c r="T53" s="3" t="inlineStr"/>
+      <c r="U53" s="3" t="inlineStr">
+        <is>
+          <t>9841229694</t>
+        </is>
+      </c>
+      <c r="V53" s="3" t="inlineStr">
+        <is>
+          <t>23 Sep 2026 10:26:05 AM</t>
+        </is>
+      </c>
+      <c r="W53" s="3" t="inlineStr">
+        <is>
+          <t>23 Sep 2026 05:32:18 PM</t>
+        </is>
+      </c>
+      <c r="X53" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Y53" s="3" t="inlineStr">
+        <is>
+          <t>27.68406</t>
+        </is>
+      </c>
+      <c r="Z53" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="AA53" s="3" t="inlineStr">
+        <is>
+          <t>Layer 1-User</t>
+        </is>
+      </c>
+      <c r="AB53" s="3" t="inlineStr">
+        <is>
+          <t>L1  Support</t>
+        </is>
+      </c>
+      <c r="AC53" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="AD53" s="3" t="inlineStr"/>
+      <c r="AE53" s="3" t="inlineStr">
+        <is>
+          <t>, Bagmati, Central, Nepal</t>
+        </is>
+      </c>
+      <c r="AF53" s="3" t="inlineStr">
+        <is>
+          <t>kirtikirtanj@gmail.com</t>
+        </is>
+      </c>
+      <c r="AG53" s="3" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="AH53" s="3" t="inlineStr"/>
+      <c r="AI53" s="3" t="inlineStr">
+        <is>
+          <t>07:06 hour</t>
+        </is>
+      </c>
+      <c r="AJ53" s="3" t="inlineStr"/>
+      <c r="AK53" s="3" t="inlineStr"/>
+      <c r="AL53" s="3" t="inlineStr">
+        <is>
+          <t>Monika Chaudhary</t>
+        </is>
+      </c>
+      <c r="AM53" s="3" t="inlineStr">
+        <is>
+          <t>Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="AN53" s="3" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AO53" s="3" t="inlineStr">
+        <is>
+          <t>2,12</t>
+        </is>
+      </c>
+      <c r="AP53" s="3" t="inlineStr">
+        <is>
+          <t>85.32381</t>
+        </is>
+      </c>
+      <c r="AQ53" s="3" t="inlineStr"/>
+      <c r="AR53" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi 6  has been updated by Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="AS53" s="3" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="AT53" s="3" t="inlineStr">
+        <is>
+          <t>7h 6m</t>
+        </is>
+      </c>
+      <c r="AU53" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Completed)</t>
+        </is>
+      </c>
+      <c r="AV53" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi 6  has been updated by Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="AW53" s="3" t="inlineStr">
+        <is>
+          <t>WiFi 6 Upgrade</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -10249,7 +10563,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M67"/>
+  <dimension ref="A1:M68"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="45" customWidth="1" min="1" max="1"/>
@@ -10258,7 +10572,7 @@
     <col width="40" customWidth="1" min="4" max="4"/>
     <col width="19" customWidth="1" min="5" max="5"/>
     <col width="25" customWidth="1" min="6" max="6"/>
-    <col width="35" customWidth="1" min="7" max="7"/>
+    <col width="45" customWidth="1" min="7" max="7"/>
     <col width="45" customWidth="1" min="8" max="8"/>
     <col width="27" customWidth="1" min="9" max="9"/>
     <col width="27" customWidth="1" min="10" max="10"/>
@@ -10286,7 +10600,7 @@
         </is>
       </c>
       <c r="B2" s="3" t="n">
-        <v>50</v>
+        <v>52</v>
       </c>
     </row>
     <row r="3">
@@ -10296,7 +10610,7 @@
         </is>
       </c>
       <c r="B3" s="5" t="n">
-        <v>37</v>
+        <v>38</v>
       </c>
     </row>
     <row r="4">
@@ -10307,7 +10621,7 @@
       </c>
       <c r="B4" s="3" t="inlineStr">
         <is>
-          <t>74.0%</t>
+          <t>73.1%</t>
         </is>
       </c>
     </row>
@@ -10319,7 +10633,7 @@
       </c>
       <c r="B5" s="5" t="inlineStr">
         <is>
-          <t>6h 12m</t>
+          <t>6h 3m</t>
         </is>
       </c>
     </row>
@@ -10331,7 +10645,7 @@
       </c>
       <c r="B6" s="3" t="inlineStr">
         <is>
-          <t>18h 4m</t>
+          <t>17h 47m</t>
         </is>
       </c>
     </row>
@@ -10372,14 +10686,14 @@
         </is>
       </c>
       <c r="B10" s="3" t="n">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="C10" s="3" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="D10" s="3" t="inlineStr">
         <is>
-          <t>80.6%</t>
+          <t>81.2%</t>
         </is>
       </c>
     </row>
@@ -10539,14 +10853,14 @@
         </is>
       </c>
       <c r="C20" s="3" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="D20" s="3" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="E20" s="3" t="inlineStr">
         <is>
-          <t>79.3%</t>
+          <t>80.0%</t>
         </is>
       </c>
     </row>
@@ -13257,6 +13571,73 @@
         </is>
       </c>
     </row>
+    <row r="68">
+      <c r="A68" s="3" t="inlineStr">
+        <is>
+          <t>TKT1343449</t>
+        </is>
+      </c>
+      <c r="B68" s="3" t="inlineStr">
+        <is>
+          <t>Kirti Kiran Joshi</t>
+        </is>
+      </c>
+      <c r="C68" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="D68" s="3" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="E68" s="3" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="F68" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Completed)</t>
+        </is>
+      </c>
+      <c r="G68" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi 6  has been updated by Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="H68" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi 6  has been updated by Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="I68" s="3" t="inlineStr">
+        <is>
+          <t>23 Sep 2026 05:32:18 PM</t>
+        </is>
+      </c>
+      <c r="J68" s="3" t="inlineStr">
+        <is>
+          <t>23 Sep 2026 10:26:05 AM</t>
+        </is>
+      </c>
+      <c r="K68" s="3" t="inlineStr">
+        <is>
+          <t>23 Sep 2026 05:32:18 PM</t>
+        </is>
+      </c>
+      <c r="L68" s="3" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="M68" s="3" t="inlineStr">
+        <is>
+          <t>7h 6m</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/audit_report_ALL_TEAM_23_Sep_2026.xlsx
+++ b/audit_report_ALL_TEAM_23_Sep_2026.xlsx
@@ -529,7 +529,7 @@
     <col width="27" customWidth="1" min="41" max="41"/>
     <col width="12" customWidth="1" min="42" max="42"/>
     <col width="17" customWidth="1" min="43" max="43"/>
-    <col width="40" customWidth="1" min="44" max="44"/>
+    <col width="34" customWidth="1" min="44" max="44"/>
     <col width="34" customWidth="1" min="45" max="45"/>
     <col width="33" customWidth="1" min="46" max="46"/>
     <col width="32" customWidth="1" min="47" max="47"/>
@@ -10408,10 +10408,8 @@
           <t>Kirti Kiran Joshi</t>
         </is>
       </c>
-      <c r="O53" s="3" t="inlineStr">
-        <is>
-          <t>9741673311</t>
-        </is>
+      <c r="O53" s="3" t="n">
+        <v>9741673311</v>
       </c>
       <c r="P53" s="3" t="inlineStr">
         <is>
@@ -10446,10 +10444,8 @@
           <t>Active</t>
         </is>
       </c>
-      <c r="Y53" s="3" t="inlineStr">
-        <is>
-          <t>27.68406</t>
-        </is>
+      <c r="Y53" s="3" t="n">
+        <v>27.68406</v>
       </c>
       <c r="Z53" s="3" t="inlineStr">
         <is>
@@ -10505,25 +10501,21 @@
           <t>Chandramani Tharu</t>
         </is>
       </c>
-      <c r="AN53" s="3" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
+      <c r="AN53" s="3" t="n">
+        <v>4</v>
       </c>
       <c r="AO53" s="3" t="inlineStr">
         <is>
           <t>2,12</t>
         </is>
       </c>
-      <c r="AP53" s="3" t="inlineStr">
-        <is>
-          <t>85.32381</t>
-        </is>
+      <c r="AP53" s="3" t="n">
+        <v>85.32380999999999</v>
       </c>
       <c r="AQ53" s="3" t="inlineStr"/>
       <c r="AR53" s="3" t="inlineStr">
         <is>
-          <t>Case : wifi 6  has been updated by Chandramani Tharu</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="AS53" s="3" t="inlineStr">
@@ -10572,7 +10564,7 @@
     <col width="40" customWidth="1" min="4" max="4"/>
     <col width="19" customWidth="1" min="5" max="5"/>
     <col width="25" customWidth="1" min="6" max="6"/>
-    <col width="45" customWidth="1" min="7" max="7"/>
+    <col width="35" customWidth="1" min="7" max="7"/>
     <col width="45" customWidth="1" min="8" max="8"/>
     <col width="27" customWidth="1" min="9" max="9"/>
     <col width="27" customWidth="1" min="10" max="10"/>
@@ -13604,7 +13596,7 @@
       </c>
       <c r="G68" s="3" t="inlineStr">
         <is>
-          <t>Case : wifi 6  has been updated by Chandramani Tharu</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="H68" s="3" t="inlineStr">

--- a/audit_report_ALL_TEAM_23_Sep_2026.xlsx
+++ b/audit_report_ALL_TEAM_23_Sep_2026.xlsx
@@ -483,7 +483,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AW53"/>
+  <dimension ref="A1:AW55"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="23" customWidth="1" min="1" max="1"/>
@@ -497,7 +497,7 @@
     <col width="29" customWidth="1" min="9" max="9"/>
     <col width="16" customWidth="1" min="10" max="10"/>
     <col width="40" customWidth="1" min="11" max="11"/>
-    <col width="12" customWidth="1" min="12" max="12"/>
+    <col width="14" customWidth="1" min="12" max="12"/>
     <col width="14" customWidth="1" min="13" max="13"/>
     <col width="40" customWidth="1" min="14" max="14"/>
     <col width="13" customWidth="1" min="15" max="15"/>
@@ -529,10 +529,10 @@
     <col width="27" customWidth="1" min="41" max="41"/>
     <col width="12" customWidth="1" min="42" max="42"/>
     <col width="17" customWidth="1" min="43" max="43"/>
-    <col width="34" customWidth="1" min="44" max="44"/>
+    <col width="40" customWidth="1" min="44" max="44"/>
     <col width="34" customWidth="1" min="45" max="45"/>
     <col width="33" customWidth="1" min="46" max="46"/>
-    <col width="32" customWidth="1" min="47" max="47"/>
+    <col width="36" customWidth="1" min="47" max="47"/>
     <col width="40" customWidth="1" min="48" max="48"/>
     <col width="25" customWidth="1" min="49" max="49"/>
   </cols>
@@ -10544,6 +10544,420 @@
         </is>
       </c>
     </row>
+    <row r="54">
+      <c r="A54" s="3" t="inlineStr">
+        <is>
+          <t>Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="B54" s="3" t="inlineStr">
+        <is>
+          <t>23 Sep 2026 6:13 PM</t>
+        </is>
+      </c>
+      <c r="C54" s="3" t="inlineStr">
+        <is>
+          <t>Zg1bIUI+iSmQ1fi360NaxA==</t>
+        </is>
+      </c>
+      <c r="D54" s="3" t="inlineStr">
+        <is>
+          <t>Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="E54" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F54" s="3" t="inlineStr">
+        <is>
+          <t>View</t>
+        </is>
+      </c>
+      <c r="G54" s="3" t="inlineStr">
+        <is>
+          <t>203.9.211.200</t>
+        </is>
+      </c>
+      <c r="H54" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi 6 upgrade  has been viewed by Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="I54" s="3" t="inlineStr">
+        <is>
+          <t>wifi 6 upgrade</t>
+        </is>
+      </c>
+      <c r="J54" s="3" t="inlineStr">
+        <is>
+          <t>TKT1341465</t>
+        </is>
+      </c>
+      <c r="K54" s="3" t="inlineStr">
+        <is>
+          <t>samrat shrestha</t>
+        </is>
+      </c>
+      <c r="L54" s="3" t="inlineStr">
+        <is>
+          <t>On Hold</t>
+        </is>
+      </c>
+      <c r="M54" s="3" t="inlineStr">
+        <is>
+          <t>Self Care</t>
+        </is>
+      </c>
+      <c r="N54" s="3" t="inlineStr">
+        <is>
+          <t>samrat shrestha</t>
+        </is>
+      </c>
+      <c r="O54" s="3" t="inlineStr">
+        <is>
+          <t>9820084508</t>
+        </is>
+      </c>
+      <c r="P54" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="Q54" s="3" t="inlineStr"/>
+      <c r="R54" s="3" t="inlineStr">
+        <is>
+          <t>23 Sep 2026 10:23:23 AM</t>
+        </is>
+      </c>
+      <c r="S54" s="3" t="inlineStr"/>
+      <c r="T54" s="3" t="inlineStr"/>
+      <c r="U54" s="3" t="inlineStr">
+        <is>
+          <t>KLK9813561196</t>
+        </is>
+      </c>
+      <c r="V54" s="3" t="inlineStr">
+        <is>
+          <t>21 Sep 2026 03:17:02 PM</t>
+        </is>
+      </c>
+      <c r="W54" s="3" t="inlineStr">
+        <is>
+          <t>23 Sep 2026 01:57:44 PM</t>
+        </is>
+      </c>
+      <c r="X54" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Y54" s="3" t="inlineStr"/>
+      <c r="Z54" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="AA54" s="3" t="inlineStr">
+        <is>
+          <t>Layer 1-User</t>
+        </is>
+      </c>
+      <c r="AB54" s="3" t="inlineStr">
+        <is>
+          <t>Laxman Koirala</t>
+        </is>
+      </c>
+      <c r="AC54" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="AD54" s="3" t="inlineStr"/>
+      <c r="AE54" s="3" t="inlineStr">
+        <is>
+          <t>Dhumbakhel Youth Club - Youth club P852+7J3 ??????? ????? Kathmandu 44600, Bagmati, Nepal, Nepal</t>
+        </is>
+      </c>
+      <c r="AF54" s="3" t="inlineStr">
+        <is>
+          <t>samshrestha080@gmail.com</t>
+        </is>
+      </c>
+      <c r="AG54" s="3" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="AH54" s="3" t="inlineStr"/>
+      <c r="AI54" s="3" t="inlineStr"/>
+      <c r="AJ54" s="3" t="inlineStr"/>
+      <c r="AK54" s="3" t="inlineStr"/>
+      <c r="AL54" s="3" t="inlineStr">
+        <is>
+          <t>Sabina K.C</t>
+        </is>
+      </c>
+      <c r="AM54" s="3" t="inlineStr">
+        <is>
+          <t>Ajit Shrestha</t>
+        </is>
+      </c>
+      <c r="AN54" s="3" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AO54" s="3" t="inlineStr">
+        <is>
+          <t>CDB348</t>
+        </is>
+      </c>
+      <c r="AP54" s="3" t="inlineStr"/>
+      <c r="AQ54" s="3" t="inlineStr"/>
+      <c r="AR54" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi 6 upgrade  has been viewed by Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="AS54" s="3" t="inlineStr">
+        <is>
+          <t>3h 34m</t>
+        </is>
+      </c>
+      <c r="AT54" s="3" t="inlineStr">
+        <is>
+          <t>1d 22h 40m</t>
+        </is>
+      </c>
+      <c r="AU54" s="3" t="inlineStr">
+        <is>
+          <t>Other / In Progress (On Hold)</t>
+        </is>
+      </c>
+      <c r="AV54" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi 6 upgrade  has been viewed by Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="AW54" s="3" t="inlineStr">
+        <is>
+          <t>WiFi 6 Upgrade</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="3" t="inlineStr">
+        <is>
+          <t>Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="B55" s="3" t="inlineStr">
+        <is>
+          <t>23 Sep 2026 5:25 PM</t>
+        </is>
+      </c>
+      <c r="C55" s="3" t="inlineStr">
+        <is>
+          <t>Zg1bIUI+iSmQ1fi360NaxA==</t>
+        </is>
+      </c>
+      <c r="D55" s="3" t="inlineStr">
+        <is>
+          <t>Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="E55" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F55" s="3" t="inlineStr">
+        <is>
+          <t>View</t>
+        </is>
+      </c>
+      <c r="G55" s="3" t="inlineStr">
+        <is>
+          <t>49.126.220.221</t>
+        </is>
+      </c>
+      <c r="H55" s="3" t="inlineStr">
+        <is>
+          <t>Case : iptv issue   has been viewed by Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="I55" s="3" t="inlineStr">
+        <is>
+          <t>iptv issue</t>
+        </is>
+      </c>
+      <c r="J55" s="3" t="inlineStr">
+        <is>
+          <t>TKT1342919</t>
+        </is>
+      </c>
+      <c r="K55" s="3" t="inlineStr">
+        <is>
+          <t>Mission shrestha</t>
+        </is>
+      </c>
+      <c r="L55" s="3" t="inlineStr">
+        <is>
+          <t>In Progress</t>
+        </is>
+      </c>
+      <c r="M55" s="3" t="inlineStr">
+        <is>
+          <t>Phone</t>
+        </is>
+      </c>
+      <c r="N55" s="3" t="inlineStr">
+        <is>
+          <t>Mission shrestha</t>
+        </is>
+      </c>
+      <c r="O55" s="3" t="inlineStr">
+        <is>
+          <t>9840344764</t>
+        </is>
+      </c>
+      <c r="P55" s="3" t="inlineStr">
+        <is>
+          <t>IPTV Related Issues</t>
+        </is>
+      </c>
+      <c r="Q55" s="3" t="inlineStr"/>
+      <c r="R55" s="3" t="inlineStr">
+        <is>
+          <t>22 Sep 2026 08:03:48 PM</t>
+        </is>
+      </c>
+      <c r="S55" s="3" t="inlineStr"/>
+      <c r="T55" s="3" t="inlineStr"/>
+      <c r="U55" s="3" t="inlineStr">
+        <is>
+          <t>9880368739</t>
+        </is>
+      </c>
+      <c r="V55" s="3" t="inlineStr">
+        <is>
+          <t>22 Sep 2026 06:54:03 PM</t>
+        </is>
+      </c>
+      <c r="W55" s="3" t="inlineStr">
+        <is>
+          <t>22 Sep 2026 08:03:48 PM</t>
+        </is>
+      </c>
+      <c r="X55" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Y55" s="3" t="inlineStr">
+        <is>
+          <t>27.69903</t>
+        </is>
+      </c>
+      <c r="Z55" s="3" t="inlineStr">
+        <is>
+          <t>IPTV Related Issues</t>
+        </is>
+      </c>
+      <c r="AA55" s="3" t="inlineStr">
+        <is>
+          <t>Layer 1-User</t>
+        </is>
+      </c>
+      <c r="AB55" s="3" t="inlineStr">
+        <is>
+          <t>Laxman Koirala</t>
+        </is>
+      </c>
+      <c r="AC55" s="3" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="AD55" s="3" t="inlineStr"/>
+      <c r="AE55" s="3" t="inlineStr">
+        <is>
+          <t>Near Dahachok, Bagmati, Nepal, Nepal</t>
+        </is>
+      </c>
+      <c r="AF55" s="3" t="inlineStr">
+        <is>
+          <t>9880368739@gmail.com</t>
+        </is>
+      </c>
+      <c r="AG55" s="3" t="inlineStr">
+        <is>
+          <t>SKYCOM-No internet connection on STB</t>
+        </is>
+      </c>
+      <c r="AH55" s="3" t="inlineStr"/>
+      <c r="AI55" s="3" t="inlineStr"/>
+      <c r="AJ55" s="3" t="inlineStr"/>
+      <c r="AK55" s="3" t="inlineStr"/>
+      <c r="AL55" s="3" t="inlineStr">
+        <is>
+          <t>Anusha Adhikari</t>
+        </is>
+      </c>
+      <c r="AM55" s="3" t="inlineStr">
+        <is>
+          <t>Bishal Karki</t>
+        </is>
+      </c>
+      <c r="AN55" s="3" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AO55" s="3" t="inlineStr">
+        <is>
+          <t>1,7</t>
+        </is>
+      </c>
+      <c r="AP55" s="3" t="inlineStr">
+        <is>
+          <t>85.24414</t>
+        </is>
+      </c>
+      <c r="AQ55" s="3" t="inlineStr"/>
+      <c r="AR55" s="3" t="inlineStr">
+        <is>
+          <t>Case : iptv issue   has been viewed by Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="AS55" s="3" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="AT55" s="3" t="inlineStr">
+        <is>
+          <t>1h 9m</t>
+        </is>
+      </c>
+      <c r="AU55" s="3" t="inlineStr">
+        <is>
+          <t>Other / In Progress (In Progress)</t>
+        </is>
+      </c>
+      <c r="AV55" s="3" t="inlineStr">
+        <is>
+          <t>Case : iptv issue   has been viewed by Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="AW55" s="3" t="inlineStr">
+        <is>
+          <t>IPTV Issue</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -10555,7 +10969,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M68"/>
+  <dimension ref="A1:M69"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="45" customWidth="1" min="1" max="1"/>
@@ -10592,7 +11006,7 @@
         </is>
       </c>
       <c r="B2" s="3" t="n">
-        <v>52</v>
+        <v>54</v>
       </c>
     </row>
     <row r="3">
@@ -10613,7 +11027,7 @@
       </c>
       <c r="B4" s="3" t="inlineStr">
         <is>
-          <t>73.1%</t>
+          <t>70.4%</t>
         </is>
       </c>
     </row>
@@ -10678,14 +11092,14 @@
         </is>
       </c>
       <c r="B10" s="3" t="n">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="C10" s="3" t="n">
         <v>26</v>
       </c>
       <c r="D10" s="3" t="inlineStr">
         <is>
-          <t>81.2%</t>
+          <t>78.8%</t>
         </is>
       </c>
     </row>
@@ -10714,14 +11128,14 @@
         </is>
       </c>
       <c r="B12" s="3" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C12" s="3" t="n">
         <v>2</v>
       </c>
       <c r="D12" s="3" t="inlineStr">
         <is>
-          <t>100.0%</t>
+          <t>66.7%</t>
         </is>
       </c>
     </row>
@@ -10845,14 +11259,14 @@
         </is>
       </c>
       <c r="C20" s="3" t="n">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="D20" s="3" t="n">
         <v>24</v>
       </c>
       <c r="E20" s="3" t="inlineStr">
         <is>
-          <t>80.0%</t>
+          <t>77.4%</t>
         </is>
       </c>
     </row>
@@ -10951,215 +11365,171 @@
     <row r="25">
       <c r="A25" s="5" t="inlineStr">
         <is>
-          <t>No Internet Connection</t>
+          <t>IPTV Related Issues</t>
         </is>
       </c>
       <c r="B25" s="5" t="inlineStr">
         <is>
-          <t>Configuration Issue</t>
+          <t>SKYCOM-No internet connection on STB</t>
         </is>
       </c>
       <c r="C25" s="5" t="n">
         <v>1</v>
       </c>
       <c r="D25" s="5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E25" s="5" t="inlineStr">
         <is>
-          <t>100.0%</t>
+          <t>0.0%</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="3" t="inlineStr">
         <is>
-          <t>Slow Internet Connection</t>
+          <t>No Internet Connection</t>
         </is>
       </c>
       <c r="B26" s="3" t="inlineStr">
         <is>
-          <t>Video content is Buffering</t>
+          <t>Configuration Issue</t>
         </is>
       </c>
       <c r="C26" s="3" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="D26" s="3" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E26" s="3" t="inlineStr">
         <is>
-          <t>75.0%</t>
+          <t>100.0%</t>
         </is>
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="5" t="inlineStr"/>
-      <c r="B27" s="5" t="inlineStr"/>
+      <c r="A27" s="5" t="inlineStr">
+        <is>
+          <t>Slow Internet Connection</t>
+        </is>
+      </c>
+      <c r="B27" s="5" t="inlineStr">
+        <is>
+          <t>Video content is Buffering</t>
+        </is>
+      </c>
       <c r="C27" s="5" t="n">
+        <v>4</v>
+      </c>
+      <c r="D27" s="5" t="n">
+        <v>3</v>
+      </c>
+      <c r="E27" s="5" t="inlineStr">
+        <is>
+          <t>75.0%</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="3" t="inlineStr"/>
+      <c r="B28" s="3" t="inlineStr"/>
+      <c r="C28" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="D27" s="5" t="n">
+      <c r="D28" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="E27" s="5" t="inlineStr">
+      <c r="E28" s="3" t="inlineStr">
         <is>
           <t>nan%</t>
         </is>
       </c>
     </row>
-    <row r="28"/>
-    <row r="29">
-      <c r="A29" s="6" t="inlineStr">
+    <row r="29"/>
+    <row r="30">
+      <c r="A30" s="6" t="inlineStr">
         <is>
           <t>Detailed Solved / Handled Tickets List</t>
-        </is>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" s="4" t="inlineStr">
-        <is>
-          <t>Ticket Number</t>
-        </is>
-      </c>
-      <c r="B30" s="4" t="inlineStr">
-        <is>
-          <t>Account Name</t>
-        </is>
-      </c>
-      <c r="C30" s="4" t="inlineStr">
-        <is>
-          <t>Category</t>
-        </is>
-      </c>
-      <c r="D30" s="4" t="inlineStr">
-        <is>
-          <t>Sub Category</t>
-        </is>
-      </c>
-      <c r="E30" s="4" t="inlineStr">
-        <is>
-          <t>Status</t>
-        </is>
-      </c>
-      <c r="F30" s="4" t="inlineStr">
-        <is>
-          <t>Resolution Type</t>
-        </is>
-      </c>
-      <c r="G30" s="4" t="inlineStr">
-        <is>
-          <t>Employee Remark / Solution Note</t>
-        </is>
-      </c>
-      <c r="H30" s="4" t="inlineStr">
-        <is>
-          <t>Action / Transfer Remark</t>
-        </is>
-      </c>
-      <c r="I30" s="4" t="inlineStr">
-        <is>
-          <t>Assigned Date</t>
-        </is>
-      </c>
-      <c r="J30" s="4" t="inlineStr">
-        <is>
-          <t>Created Date</t>
-        </is>
-      </c>
-      <c r="K30" s="4" t="inlineStr">
-        <is>
-          <t>Last Modified Date</t>
-        </is>
-      </c>
-      <c r="L30" s="4" t="inlineStr">
-        <is>
-          <t>Resolution Time (From Assigned)</t>
-        </is>
-      </c>
-      <c r="M30" s="4" t="inlineStr">
-        <is>
-          <t>Resolution Time (From Created)</t>
         </is>
       </c>
     </row>
     <row r="31">
-      <c r="A31" s="5" t="inlineStr">
-        <is>
-          <t>TKT1342514</t>
-        </is>
-      </c>
-      <c r="B31" s="5" t="inlineStr">
-        <is>
-          <t>Bijay Carlos Rana</t>
-        </is>
-      </c>
-      <c r="C31" s="5" t="inlineStr">
-        <is>
-          <t>General / Other Issues</t>
-        </is>
-      </c>
-      <c r="D31" s="5" t="inlineStr">
-        <is>
-          <t>Router Upgrade  Wi-Fi 6</t>
-        </is>
-      </c>
-      <c r="E31" s="5" t="inlineStr">
-        <is>
-          <t>Completed</t>
-        </is>
-      </c>
-      <c r="F31" s="5" t="inlineStr">
-        <is>
-          <t>Completed (Completed)</t>
-        </is>
-      </c>
-      <c r="G31" s="5" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
-      <c r="H31" s="5" t="inlineStr">
-        <is>
-          <t>Case : WIFI 6  has been updated by Rajesh Maharjan</t>
-        </is>
-      </c>
-      <c r="I31" s="5" t="inlineStr">
-        <is>
-          <t>23 Sep 2026 11:16:05 AM</t>
-        </is>
-      </c>
-      <c r="J31" s="5" t="inlineStr">
-        <is>
-          <t>22 Sep 2026 02:29:16 PM</t>
-        </is>
-      </c>
-      <c r="K31" s="5" t="inlineStr">
-        <is>
-          <t>23 Sep 2026 11:16:05 AM</t>
-        </is>
-      </c>
-      <c r="L31" s="5" t="inlineStr">
-        <is>
-          <t>0m</t>
-        </is>
-      </c>
-      <c r="M31" s="5" t="inlineStr">
-        <is>
-          <t>20h 46m</t>
+      <c r="A31" s="4" t="inlineStr">
+        <is>
+          <t>Ticket Number</t>
+        </is>
+      </c>
+      <c r="B31" s="4" t="inlineStr">
+        <is>
+          <t>Account Name</t>
+        </is>
+      </c>
+      <c r="C31" s="4" t="inlineStr">
+        <is>
+          <t>Category</t>
+        </is>
+      </c>
+      <c r="D31" s="4" t="inlineStr">
+        <is>
+          <t>Sub Category</t>
+        </is>
+      </c>
+      <c r="E31" s="4" t="inlineStr">
+        <is>
+          <t>Status</t>
+        </is>
+      </c>
+      <c r="F31" s="4" t="inlineStr">
+        <is>
+          <t>Resolution Type</t>
+        </is>
+      </c>
+      <c r="G31" s="4" t="inlineStr">
+        <is>
+          <t>Employee Remark / Solution Note</t>
+        </is>
+      </c>
+      <c r="H31" s="4" t="inlineStr">
+        <is>
+          <t>Action / Transfer Remark</t>
+        </is>
+      </c>
+      <c r="I31" s="4" t="inlineStr">
+        <is>
+          <t>Assigned Date</t>
+        </is>
+      </c>
+      <c r="J31" s="4" t="inlineStr">
+        <is>
+          <t>Created Date</t>
+        </is>
+      </c>
+      <c r="K31" s="4" t="inlineStr">
+        <is>
+          <t>Last Modified Date</t>
+        </is>
+      </c>
+      <c r="L31" s="4" t="inlineStr">
+        <is>
+          <t>Resolution Time (From Assigned)</t>
+        </is>
+      </c>
+      <c r="M31" s="4" t="inlineStr">
+        <is>
+          <t>Resolution Time (From Created)</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="3" t="inlineStr">
         <is>
-          <t>TKT1343394</t>
+          <t>TKT1342514</t>
         </is>
       </c>
       <c r="B32" s="3" t="inlineStr">
         <is>
-          <t>Kaizen Business consultant</t>
+          <t>Bijay Carlos Rana</t>
         </is>
       </c>
       <c r="C32" s="3" t="inlineStr">
@@ -11189,22 +11559,22 @@
       </c>
       <c r="H32" s="3" t="inlineStr">
         <is>
-          <t>Case : wifi 6 router  has been updated by Sabin Giri</t>
+          <t>Case : WIFI 6  has been updated by Rajesh Maharjan</t>
         </is>
       </c>
       <c r="I32" s="3" t="inlineStr">
         <is>
-          <t>23 Sep 2026 12:31:18 PM</t>
+          <t>23 Sep 2026 11:16:05 AM</t>
         </is>
       </c>
       <c r="J32" s="3" t="inlineStr">
         <is>
-          <t>23 Sep 2026 09:53:33 AM</t>
+          <t>22 Sep 2026 02:29:16 PM</t>
         </is>
       </c>
       <c r="K32" s="3" t="inlineStr">
         <is>
-          <t>23 Sep 2026 12:31:18 PM</t>
+          <t>23 Sep 2026 11:16:05 AM</t>
         </is>
       </c>
       <c r="L32" s="3" t="inlineStr">
@@ -11214,19 +11584,19 @@
       </c>
       <c r="M32" s="3" t="inlineStr">
         <is>
-          <t>2h 37m</t>
+          <t>20h 46m</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="5" t="inlineStr">
         <is>
-          <t>TKT1343122</t>
+          <t>TKT1343394</t>
         </is>
       </c>
       <c r="B33" s="5" t="inlineStr">
         <is>
-          <t>Rajesh Shahi</t>
+          <t>Kaizen Business consultant</t>
         </is>
       </c>
       <c r="C33" s="5" t="inlineStr">
@@ -11256,22 +11626,22 @@
       </c>
       <c r="H33" s="5" t="inlineStr">
         <is>
-          <t>Case : wifi 6  has been updated by Shashikant Chaudhary</t>
+          <t>Case : wifi 6 router  has been updated by Sabin Giri</t>
         </is>
       </c>
       <c r="I33" s="5" t="inlineStr">
         <is>
-          <t>23 Sep 2026 12:37:13 PM</t>
+          <t>23 Sep 2026 12:31:18 PM</t>
         </is>
       </c>
       <c r="J33" s="5" t="inlineStr">
         <is>
-          <t>22 Sep 2026 09:56:18 PM</t>
+          <t>23 Sep 2026 09:53:33 AM</t>
         </is>
       </c>
       <c r="K33" s="5" t="inlineStr">
         <is>
-          <t>23 Sep 2026 12:37:13 PM</t>
+          <t>23 Sep 2026 12:31:18 PM</t>
         </is>
       </c>
       <c r="L33" s="5" t="inlineStr">
@@ -11281,19 +11651,19 @@
       </c>
       <c r="M33" s="5" t="inlineStr">
         <is>
-          <t>14h 40m</t>
+          <t>2h 37m</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="3" t="inlineStr">
         <is>
-          <t>TKT1343670</t>
+          <t>TKT1343122</t>
         </is>
       </c>
       <c r="B34" s="3" t="inlineStr">
         <is>
-          <t>Suman Shah</t>
+          <t>Rajesh Shahi</t>
         </is>
       </c>
       <c r="C34" s="3" t="inlineStr">
@@ -11303,7 +11673,7 @@
       </c>
       <c r="D34" s="3" t="inlineStr">
         <is>
-          <t>Router Upgrade Dual Band</t>
+          <t>Router Upgrade  Wi-Fi 6</t>
         </is>
       </c>
       <c r="E34" s="3" t="inlineStr">
@@ -11323,22 +11693,22 @@
       </c>
       <c r="H34" s="3" t="inlineStr">
         <is>
-          <t>Case : router change  has been updated by Shashikant Chaudhary</t>
+          <t>Case : wifi 6  has been updated by Shashikant Chaudhary</t>
         </is>
       </c>
       <c r="I34" s="3" t="inlineStr">
         <is>
-          <t>23 Sep 2026 12:59:40 PM</t>
+          <t>23 Sep 2026 12:37:13 PM</t>
         </is>
       </c>
       <c r="J34" s="3" t="inlineStr">
         <is>
-          <t>23 Sep 2026 12:23:42 PM</t>
+          <t>22 Sep 2026 09:56:18 PM</t>
         </is>
       </c>
       <c r="K34" s="3" t="inlineStr">
         <is>
-          <t>23 Sep 2026 12:59:40 PM</t>
+          <t>23 Sep 2026 12:37:13 PM</t>
         </is>
       </c>
       <c r="L34" s="3" t="inlineStr">
@@ -11348,39 +11718,39 @@
       </c>
       <c r="M34" s="3" t="inlineStr">
         <is>
-          <t>35m</t>
+          <t>14h 40m</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="5" t="inlineStr">
         <is>
-          <t>TKT1342524</t>
+          <t>TKT1343670</t>
         </is>
       </c>
       <c r="B35" s="5" t="inlineStr">
         <is>
-          <t>Nakul Bhandari</t>
+          <t>Suman Shah</t>
         </is>
       </c>
       <c r="C35" s="5" t="inlineStr">
         <is>
-          <t>No Internet Connection</t>
+          <t>General / Other Issues</t>
         </is>
       </c>
       <c r="D35" s="5" t="inlineStr">
         <is>
-          <t>Configuration Issue</t>
+          <t>Router Upgrade Dual Band</t>
         </is>
       </c>
       <c r="E35" s="5" t="inlineStr">
         <is>
-          <t>Closed</t>
+          <t>Completed</t>
         </is>
       </c>
       <c r="F35" s="5" t="inlineStr">
         <is>
-          <t>Completed (Closed)</t>
+          <t>Completed (Completed)</t>
         </is>
       </c>
       <c r="G35" s="5" t="inlineStr">
@@ -11390,64 +11760,64 @@
       </c>
       <c r="H35" s="5" t="inlineStr">
         <is>
-          <t>Case : CONFINGURE ISSUE  has been updated by Ajit Shrestha</t>
+          <t>Case : router change  has been updated by Shashikant Chaudhary</t>
         </is>
       </c>
       <c r="I35" s="5" t="inlineStr">
         <is>
-          <t>22 Sep 2026 02:52:24 PM</t>
+          <t>23 Sep 2026 12:59:40 PM</t>
         </is>
       </c>
       <c r="J35" s="5" t="inlineStr">
         <is>
-          <t>22 Sep 2026 02:35:30 PM</t>
+          <t>23 Sep 2026 12:23:42 PM</t>
         </is>
       </c>
       <c r="K35" s="5" t="inlineStr">
         <is>
-          <t>23 Sep 2026 12:57:31 PM</t>
+          <t>23 Sep 2026 12:59:40 PM</t>
         </is>
       </c>
       <c r="L35" s="5" t="inlineStr">
         <is>
-          <t>22h 5m</t>
+          <t>0m</t>
         </is>
       </c>
       <c r="M35" s="5" t="inlineStr">
         <is>
-          <t>22h 22m</t>
+          <t>35m</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="3" t="inlineStr">
         <is>
-          <t>TKT1342923</t>
+          <t>TKT1342524</t>
         </is>
       </c>
       <c r="B36" s="3" t="inlineStr">
         <is>
-          <t>Maan maya poon</t>
+          <t>Nakul Bhandari</t>
         </is>
       </c>
       <c r="C36" s="3" t="inlineStr">
         <is>
-          <t>General / Other Issues</t>
+          <t>No Internet Connection</t>
         </is>
       </c>
       <c r="D36" s="3" t="inlineStr">
         <is>
-          <t>Router Upgrade  Wi-Fi 6</t>
+          <t>Configuration Issue</t>
         </is>
       </c>
       <c r="E36" s="3" t="inlineStr">
         <is>
-          <t>Completed</t>
+          <t>Closed</t>
         </is>
       </c>
       <c r="F36" s="3" t="inlineStr">
         <is>
-          <t>Completed (Completed)</t>
+          <t>Completed (Closed)</t>
         </is>
       </c>
       <c r="G36" s="3" t="inlineStr">
@@ -11457,44 +11827,44 @@
       </c>
       <c r="H36" s="3" t="inlineStr">
         <is>
-          <t>Case : For upgradation to wifi6   has been updated by Sabin Giri</t>
+          <t>Case : CONFINGURE ISSUE  has been updated by Ajit Shrestha</t>
         </is>
       </c>
       <c r="I36" s="3" t="inlineStr">
         <is>
-          <t>23 Sep 2026 01:01:06 PM</t>
+          <t>22 Sep 2026 02:52:24 PM</t>
         </is>
       </c>
       <c r="J36" s="3" t="inlineStr">
         <is>
-          <t>22 Sep 2026 06:58:31 PM</t>
+          <t>22 Sep 2026 02:35:30 PM</t>
         </is>
       </c>
       <c r="K36" s="3" t="inlineStr">
         <is>
-          <t>23 Sep 2026 01:01:06 PM</t>
+          <t>23 Sep 2026 12:57:31 PM</t>
         </is>
       </c>
       <c r="L36" s="3" t="inlineStr">
         <is>
-          <t>0m</t>
+          <t>22h 5m</t>
         </is>
       </c>
       <c r="M36" s="3" t="inlineStr">
         <is>
-          <t>18h 2m</t>
+          <t>22h 22m</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="5" t="inlineStr">
         <is>
-          <t>TKT1343451</t>
+          <t>TKT1342923</t>
         </is>
       </c>
       <c r="B37" s="5" t="inlineStr">
         <is>
-          <t>Sabin Maharjan</t>
+          <t>Maan maya poon</t>
         </is>
       </c>
       <c r="C37" s="5" t="inlineStr">
@@ -11524,22 +11894,22 @@
       </c>
       <c r="H37" s="5" t="inlineStr">
         <is>
-          <t>Case : Wifi 6  has been updated by Sabin Giri</t>
+          <t>Case : For upgradation to wifi6   has been updated by Sabin Giri</t>
         </is>
       </c>
       <c r="I37" s="5" t="inlineStr">
         <is>
-          <t>23 Sep 2026 01:17:39 PM</t>
+          <t>23 Sep 2026 01:01:06 PM</t>
         </is>
       </c>
       <c r="J37" s="5" t="inlineStr">
         <is>
-          <t>23 Sep 2026 10:26:34 AM</t>
+          <t>22 Sep 2026 06:58:31 PM</t>
         </is>
       </c>
       <c r="K37" s="5" t="inlineStr">
         <is>
-          <t>23 Sep 2026 01:17:39 PM</t>
+          <t>23 Sep 2026 01:01:06 PM</t>
         </is>
       </c>
       <c r="L37" s="5" t="inlineStr">
@@ -11549,29 +11919,29 @@
       </c>
       <c r="M37" s="5" t="inlineStr">
         <is>
-          <t>2h 51m</t>
+          <t>18h 2m</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="3" t="inlineStr">
         <is>
-          <t>TKT1343062</t>
+          <t>TKT1343451</t>
         </is>
       </c>
       <c r="B38" s="3" t="inlineStr">
         <is>
-          <t>Sabin Magar</t>
+          <t>Sabin Maharjan</t>
         </is>
       </c>
       <c r="C38" s="3" t="inlineStr">
         <is>
-          <t>Hardware Damage / Malfunction</t>
+          <t>General / Other Issues</t>
         </is>
       </c>
       <c r="D38" s="3" t="inlineStr">
         <is>
-          <t>IPTV STB box Damage Issue</t>
+          <t>Router Upgrade  Wi-Fi 6</t>
         </is>
       </c>
       <c r="E38" s="3" t="inlineStr">
@@ -11591,22 +11961,22 @@
       </c>
       <c r="H38" s="3" t="inlineStr">
         <is>
-          <t>Case : IP TV not Working   has been updated by Ajit Shrestha</t>
+          <t>Case : Wifi 6  has been updated by Sabin Giri</t>
         </is>
       </c>
       <c r="I38" s="3" t="inlineStr">
         <is>
-          <t>23 Sep 2026 01:16:47 PM</t>
+          <t>23 Sep 2026 01:17:39 PM</t>
         </is>
       </c>
       <c r="J38" s="3" t="inlineStr">
         <is>
-          <t>22 Sep 2026 08:56:52 PM</t>
+          <t>23 Sep 2026 10:26:34 AM</t>
         </is>
       </c>
       <c r="K38" s="3" t="inlineStr">
         <is>
-          <t>23 Sep 2026 01:16:47 PM</t>
+          <t>23 Sep 2026 01:17:39 PM</t>
         </is>
       </c>
       <c r="L38" s="3" t="inlineStr">
@@ -11616,39 +11986,39 @@
       </c>
       <c r="M38" s="3" t="inlineStr">
         <is>
-          <t>16h 19m</t>
+          <t>2h 51m</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="5" t="inlineStr">
         <is>
-          <t>TKT1341347</t>
+          <t>TKT1343062</t>
         </is>
       </c>
       <c r="B39" s="5" t="inlineStr">
         <is>
-          <t>Siddhartha Model School</t>
+          <t>Sabin Magar</t>
         </is>
       </c>
       <c r="C39" s="5" t="inlineStr">
         <is>
-          <t>General / Other Issues</t>
+          <t>Hardware Damage / Malfunction</t>
         </is>
       </c>
       <c r="D39" s="5" t="inlineStr">
         <is>
-          <t>Router Upgrade  Wi-Fi 6</t>
+          <t>IPTV STB box Damage Issue</t>
         </is>
       </c>
       <c r="E39" s="5" t="inlineStr">
         <is>
-          <t>Closed</t>
+          <t>Completed</t>
         </is>
       </c>
       <c r="F39" s="5" t="inlineStr">
         <is>
-          <t>Completed (Closed)</t>
+          <t>Completed (Completed)</t>
         </is>
       </c>
       <c r="G39" s="5" t="inlineStr">
@@ -11658,44 +12028,44 @@
       </c>
       <c r="H39" s="5" t="inlineStr">
         <is>
-          <t>Case : wifi 6  has been updated by Sunil Chaudhary</t>
+          <t>Case : IP TV not Working   has been updated by Ajit Shrestha</t>
         </is>
       </c>
       <c r="I39" s="5" t="inlineStr">
         <is>
-          <t>21 Sep 2026 01:35:47 PM</t>
+          <t>23 Sep 2026 01:16:47 PM</t>
         </is>
       </c>
       <c r="J39" s="5" t="inlineStr">
         <is>
-          <t>21 Sep 2026 01:35:47 PM</t>
+          <t>22 Sep 2026 08:56:52 PM</t>
         </is>
       </c>
       <c r="K39" s="5" t="inlineStr">
         <is>
-          <t>23 Sep 2026 01:22:44 PM</t>
+          <t>23 Sep 2026 01:16:47 PM</t>
         </is>
       </c>
       <c r="L39" s="5" t="inlineStr">
         <is>
-          <t>1d 23h 46m</t>
+          <t>0m</t>
         </is>
       </c>
       <c r="M39" s="5" t="inlineStr">
         <is>
-          <t>1d 23h 46m</t>
+          <t>16h 19m</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="3" t="inlineStr">
         <is>
-          <t>TKT1342867</t>
+          <t>TKT1341347</t>
         </is>
       </c>
       <c r="B40" s="3" t="inlineStr">
         <is>
-          <t>Punit Kumar Barnawal</t>
+          <t>Siddhartha Model School</t>
         </is>
       </c>
       <c r="C40" s="3" t="inlineStr">
@@ -11710,12 +12080,12 @@
       </c>
       <c r="E40" s="3" t="inlineStr">
         <is>
-          <t>Completed</t>
+          <t>Closed</t>
         </is>
       </c>
       <c r="F40" s="3" t="inlineStr">
         <is>
-          <t>Completed (Completed)</t>
+          <t>Completed (Closed)</t>
         </is>
       </c>
       <c r="G40" s="3" t="inlineStr">
@@ -11725,54 +12095,54 @@
       </c>
       <c r="H40" s="3" t="inlineStr">
         <is>
-          <t>Case : Wifi 6  has been updated by Shashikant Chaudhary</t>
+          <t>Case : wifi 6  has been updated by Sunil Chaudhary</t>
         </is>
       </c>
       <c r="I40" s="3" t="inlineStr">
         <is>
-          <t>23 Sep 2026 01:48:42 PM</t>
+          <t>21 Sep 2026 01:35:47 PM</t>
         </is>
       </c>
       <c r="J40" s="3" t="inlineStr">
         <is>
-          <t>22 Sep 2026 06:02:29 PM</t>
+          <t>21 Sep 2026 01:35:47 PM</t>
         </is>
       </c>
       <c r="K40" s="3" t="inlineStr">
         <is>
-          <t>23 Sep 2026 01:48:42 PM</t>
+          <t>23 Sep 2026 01:22:44 PM</t>
         </is>
       </c>
       <c r="L40" s="3" t="inlineStr">
         <is>
-          <t>0m</t>
+          <t>1d 23h 46m</t>
         </is>
       </c>
       <c r="M40" s="3" t="inlineStr">
         <is>
-          <t>19h 46m</t>
+          <t>1d 23h 46m</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="5" t="inlineStr">
         <is>
-          <t>TKT1343135</t>
+          <t>TKT1342867</t>
         </is>
       </c>
       <c r="B41" s="5" t="inlineStr">
         <is>
-          <t>Ashish Shahbadi</t>
+          <t>Punit Kumar Barnawal</t>
         </is>
       </c>
       <c r="C41" s="5" t="inlineStr">
         <is>
-          <t>Hardware Damage / Malfunction</t>
+          <t>General / Other Issues</t>
         </is>
       </c>
       <c r="D41" s="5" t="inlineStr">
         <is>
-          <t>Router Damage Issue</t>
+          <t>Router Upgrade  Wi-Fi 6</t>
         </is>
       </c>
       <c r="E41" s="5" t="inlineStr">
@@ -11792,22 +12162,22 @@
       </c>
       <c r="H41" s="5" t="inlineStr">
         <is>
-          <t>Case : 5g not working   has been updated by Rajesh Maharjan</t>
+          <t>Case : Wifi 6  has been updated by Shashikant Chaudhary</t>
         </is>
       </c>
       <c r="I41" s="5" t="inlineStr">
         <is>
-          <t>23 Sep 2026 01:51:51 PM</t>
+          <t>23 Sep 2026 01:48:42 PM</t>
         </is>
       </c>
       <c r="J41" s="5" t="inlineStr">
         <is>
-          <t>22 Sep 2026 10:20:07 PM</t>
+          <t>22 Sep 2026 06:02:29 PM</t>
         </is>
       </c>
       <c r="K41" s="5" t="inlineStr">
         <is>
-          <t>23 Sep 2026 01:51:51 PM</t>
+          <t>23 Sep 2026 01:48:42 PM</t>
         </is>
       </c>
       <c r="L41" s="5" t="inlineStr">
@@ -11817,29 +12187,29 @@
       </c>
       <c r="M41" s="5" t="inlineStr">
         <is>
-          <t>15h 31m</t>
+          <t>19h 46m</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="3" t="inlineStr">
         <is>
-          <t>TKT1343287</t>
+          <t>TKT1343135</t>
         </is>
       </c>
       <c r="B42" s="3" t="inlineStr">
         <is>
-          <t>Anup Chaudhary</t>
+          <t>Ashish Shahbadi</t>
         </is>
       </c>
       <c r="C42" s="3" t="inlineStr">
         <is>
-          <t>General / Other Issues</t>
+          <t>Hardware Damage / Malfunction</t>
         </is>
       </c>
       <c r="D42" s="3" t="inlineStr">
         <is>
-          <t>Router Upgrade  Wi-Fi 6</t>
+          <t>Router Damage Issue</t>
         </is>
       </c>
       <c r="E42" s="3" t="inlineStr">
@@ -11859,22 +12229,22 @@
       </c>
       <c r="H42" s="3" t="inlineStr">
         <is>
-          <t>Case : wifi 6  has been updated by Sabin Giri</t>
+          <t>Case : 5g not working   has been updated by Rajesh Maharjan</t>
         </is>
       </c>
       <c r="I42" s="3" t="inlineStr">
         <is>
-          <t>23 Sep 2026 02:03:32 PM</t>
+          <t>23 Sep 2026 01:51:51 PM</t>
         </is>
       </c>
       <c r="J42" s="3" t="inlineStr">
         <is>
-          <t>23 Sep 2026 08:37:17 AM</t>
+          <t>22 Sep 2026 10:20:07 PM</t>
         </is>
       </c>
       <c r="K42" s="3" t="inlineStr">
         <is>
-          <t>23 Sep 2026 02:03:32 PM</t>
+          <t>23 Sep 2026 01:51:51 PM</t>
         </is>
       </c>
       <c r="L42" s="3" t="inlineStr">
@@ -11884,39 +12254,39 @@
       </c>
       <c r="M42" s="3" t="inlineStr">
         <is>
-          <t>5h 26m</t>
+          <t>15h 31m</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="5" t="inlineStr">
         <is>
-          <t>TKT1342988</t>
+          <t>TKT1343287</t>
         </is>
       </c>
       <c r="B43" s="5" t="inlineStr">
         <is>
-          <t>Kushal Neupane</t>
+          <t>Anup Chaudhary</t>
         </is>
       </c>
       <c r="C43" s="5" t="inlineStr">
         <is>
-          <t>Hardware Damage / Malfunction</t>
+          <t>General / Other Issues</t>
         </is>
       </c>
       <c r="D43" s="5" t="inlineStr">
         <is>
-          <t>IPTV STB box Damage Issue</t>
+          <t>Router Upgrade  Wi-Fi 6</t>
         </is>
       </c>
       <c r="E43" s="5" t="inlineStr">
         <is>
-          <t>Closed</t>
+          <t>Completed</t>
         </is>
       </c>
       <c r="F43" s="5" t="inlineStr">
         <is>
-          <t>Completed (Closed)</t>
+          <t>Completed (Completed)</t>
         </is>
       </c>
       <c r="G43" s="5" t="inlineStr">
@@ -11926,32 +12296,32 @@
       </c>
       <c r="H43" s="5" t="inlineStr">
         <is>
-          <t>Case : stb faulty  has been updated by Sunil Chaudhary</t>
+          <t>Case : wifi 6  has been updated by Sabin Giri</t>
         </is>
       </c>
       <c r="I43" s="5" t="inlineStr">
         <is>
-          <t>22 Sep 2026 08:27:54 PM</t>
+          <t>23 Sep 2026 02:03:32 PM</t>
         </is>
       </c>
       <c r="J43" s="5" t="inlineStr">
         <is>
-          <t>22 Sep 2026 07:49:31 PM</t>
+          <t>23 Sep 2026 08:37:17 AM</t>
         </is>
       </c>
       <c r="K43" s="5" t="inlineStr">
         <is>
-          <t>23 Sep 2026 02:16:10 PM</t>
+          <t>23 Sep 2026 02:03:32 PM</t>
         </is>
       </c>
       <c r="L43" s="5" t="inlineStr">
         <is>
-          <t>17h 48m</t>
+          <t>0m</t>
         </is>
       </c>
       <c r="M43" s="5" t="inlineStr">
         <is>
-          <t>18h 26m</t>
+          <t>5h 26m</t>
         </is>
       </c>
     </row>
@@ -12025,32 +12395,32 @@
     <row r="45">
       <c r="A45" s="5" t="inlineStr">
         <is>
-          <t>TKT1340081</t>
+          <t>TKT1342988</t>
         </is>
       </c>
       <c r="B45" s="5" t="inlineStr">
         <is>
-          <t>Anjan Khadka</t>
+          <t>Kushal Neupane</t>
         </is>
       </c>
       <c r="C45" s="5" t="inlineStr">
         <is>
-          <t>General / Other Issues</t>
+          <t>Hardware Damage / Malfunction</t>
         </is>
       </c>
       <c r="D45" s="5" t="inlineStr">
         <is>
-          <t>Query For Secondary Router /Repeater</t>
+          <t>IPTV STB box Damage Issue</t>
         </is>
       </c>
       <c r="E45" s="5" t="inlineStr">
         <is>
-          <t>Completed</t>
+          <t>Closed</t>
         </is>
       </c>
       <c r="F45" s="5" t="inlineStr">
         <is>
-          <t>Completed (Completed)</t>
+          <t>Completed (Closed)</t>
         </is>
       </c>
       <c r="G45" s="5" t="inlineStr">
@@ -12060,54 +12430,54 @@
       </c>
       <c r="H45" s="5" t="inlineStr">
         <is>
-          <t>Case : Secondary Router Connetion   has been updated by Chandramani Tharu</t>
+          <t>Case : stb faulty  has been updated by Sunil Chaudhary</t>
         </is>
       </c>
       <c r="I45" s="5" t="inlineStr">
         <is>
-          <t>23 Sep 2026 02:23:04 PM</t>
+          <t>22 Sep 2026 08:27:54 PM</t>
         </is>
       </c>
       <c r="J45" s="5" t="inlineStr">
         <is>
-          <t>20 Sep 2026 02:38:36 PM</t>
+          <t>22 Sep 2026 07:49:31 PM</t>
         </is>
       </c>
       <c r="K45" s="5" t="inlineStr">
         <is>
-          <t>23 Sep 2026 02:23:04 PM</t>
+          <t>23 Sep 2026 02:16:10 PM</t>
         </is>
       </c>
       <c r="L45" s="5" t="inlineStr">
         <is>
-          <t>0m</t>
+          <t>17h 48m</t>
         </is>
       </c>
       <c r="M45" s="5" t="inlineStr">
         <is>
-          <t>2d 23h 44m</t>
+          <t>18h 26m</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="3" t="inlineStr">
         <is>
-          <t>TKT1339133</t>
+          <t>TKT1340081</t>
         </is>
       </c>
       <c r="B46" s="3" t="inlineStr">
         <is>
-          <t>Chalachitra Chautari pvt.ltd</t>
+          <t>Anjan Khadka</t>
         </is>
       </c>
       <c r="C46" s="3" t="inlineStr">
         <is>
-          <t>Slow Internet Connection</t>
+          <t>General / Other Issues</t>
         </is>
       </c>
       <c r="D46" s="3" t="inlineStr">
         <is>
-          <t>Video content is Buffering</t>
+          <t>Query For Secondary Router /Repeater</t>
         </is>
       </c>
       <c r="E46" s="3" t="inlineStr">
@@ -12127,22 +12497,22 @@
       </c>
       <c r="H46" s="3" t="inlineStr">
         <is>
-          <t>Case : slow issue  has been updated by Chandramani Tharu</t>
+          <t>Case : Secondary Router Connetion   has been updated by Chandramani Tharu</t>
         </is>
       </c>
       <c r="I46" s="3" t="inlineStr">
         <is>
-          <t>23 Sep 2026 02:21:55 PM</t>
+          <t>23 Sep 2026 02:23:04 PM</t>
         </is>
       </c>
       <c r="J46" s="3" t="inlineStr">
         <is>
-          <t>19 Sep 2026 05:49:47 PM</t>
+          <t>20 Sep 2026 02:38:36 PM</t>
         </is>
       </c>
       <c r="K46" s="3" t="inlineStr">
         <is>
-          <t>23 Sep 2026 02:21:55 PM</t>
+          <t>23 Sep 2026 02:23:04 PM</t>
         </is>
       </c>
       <c r="L46" s="3" t="inlineStr">
@@ -12152,29 +12522,29 @@
       </c>
       <c r="M46" s="3" t="inlineStr">
         <is>
-          <t>3d 20h 32m</t>
+          <t>2d 23h 44m</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="5" t="inlineStr">
         <is>
-          <t>TKT1343230</t>
+          <t>TKT1339133</t>
         </is>
       </c>
       <c r="B47" s="5" t="inlineStr">
         <is>
-          <t>Bikesh Shrestha</t>
+          <t>Chalachitra Chautari pvt.ltd</t>
         </is>
       </c>
       <c r="C47" s="5" t="inlineStr">
         <is>
-          <t>General / Other Issues</t>
+          <t>Slow Internet Connection</t>
         </is>
       </c>
       <c r="D47" s="5" t="inlineStr">
         <is>
-          <t>Router Upgrade  Wi-Fi 6</t>
+          <t>Video content is Buffering</t>
         </is>
       </c>
       <c r="E47" s="5" t="inlineStr">
@@ -12194,22 +12564,22 @@
       </c>
       <c r="H47" s="5" t="inlineStr">
         <is>
-          <t>Case : wifi 6  has been updated by Sabin Giri</t>
+          <t>Case : slow issue  has been updated by Chandramani Tharu</t>
         </is>
       </c>
       <c r="I47" s="5" t="inlineStr">
         <is>
-          <t>23 Sep 2026 02:41:26 PM</t>
+          <t>23 Sep 2026 02:21:55 PM</t>
         </is>
       </c>
       <c r="J47" s="5" t="inlineStr">
         <is>
-          <t>23 Sep 2026 07:43:57 AM</t>
+          <t>19 Sep 2026 05:49:47 PM</t>
         </is>
       </c>
       <c r="K47" s="5" t="inlineStr">
         <is>
-          <t>23 Sep 2026 02:41:26 PM</t>
+          <t>23 Sep 2026 02:21:55 PM</t>
         </is>
       </c>
       <c r="L47" s="5" t="inlineStr">
@@ -12219,19 +12589,19 @@
       </c>
       <c r="M47" s="5" t="inlineStr">
         <is>
-          <t>6h 57m</t>
+          <t>3d 20h 32m</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="3" t="inlineStr">
         <is>
-          <t>TKT1342466</t>
+          <t>TKT1343230</t>
         </is>
       </c>
       <c r="B48" s="3" t="inlineStr">
         <is>
-          <t>Dharmesh Maharjan</t>
+          <t>Bikesh Shrestha</t>
         </is>
       </c>
       <c r="C48" s="3" t="inlineStr">
@@ -12261,22 +12631,22 @@
       </c>
       <c r="H48" s="3" t="inlineStr">
         <is>
-          <t>Case : Wi-Fi 6  has been updated by Chandramani Tharu</t>
+          <t>Case : wifi 6  has been updated by Sabin Giri</t>
         </is>
       </c>
       <c r="I48" s="3" t="inlineStr">
         <is>
-          <t>23 Sep 2026 02:53:32 PM</t>
+          <t>23 Sep 2026 02:41:26 PM</t>
         </is>
       </c>
       <c r="J48" s="3" t="inlineStr">
         <is>
-          <t>22 Sep 2026 01:51:09 PM</t>
+          <t>23 Sep 2026 07:43:57 AM</t>
         </is>
       </c>
       <c r="K48" s="3" t="inlineStr">
         <is>
-          <t>23 Sep 2026 02:53:32 PM</t>
+          <t>23 Sep 2026 02:41:26 PM</t>
         </is>
       </c>
       <c r="L48" s="3" t="inlineStr">
@@ -12286,39 +12656,39 @@
       </c>
       <c r="M48" s="3" t="inlineStr">
         <is>
-          <t>1d 1h 2m</t>
+          <t>6h 57m</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="5" t="inlineStr">
         <is>
-          <t>TKT1342232</t>
+          <t>TKT1342466</t>
         </is>
       </c>
       <c r="B49" s="5" t="inlineStr">
         <is>
-          <t>Dipendra khanal</t>
+          <t>Dharmesh Maharjan</t>
         </is>
       </c>
       <c r="C49" s="5" t="inlineStr">
         <is>
-          <t>IPTV Related Issues</t>
+          <t>General / Other Issues</t>
         </is>
       </c>
       <c r="D49" s="5" t="inlineStr">
         <is>
-          <t>SKYCOM-Audio &amp; Video Syn Issue</t>
+          <t>Router Upgrade  Wi-Fi 6</t>
         </is>
       </c>
       <c r="E49" s="5" t="inlineStr">
         <is>
-          <t>Closed</t>
+          <t>Completed</t>
         </is>
       </c>
       <c r="F49" s="5" t="inlineStr">
         <is>
-          <t>Completed (Closed)</t>
+          <t>Completed (Completed)</t>
         </is>
       </c>
       <c r="G49" s="5" t="inlineStr">
@@ -12328,32 +12698,32 @@
       </c>
       <c r="H49" s="5" t="inlineStr">
         <is>
-          <t>Case : IPTV  Isssue  has been updated by Sunil Chaudhary</t>
+          <t>Case : Wi-Fi 6  has been updated by Chandramani Tharu</t>
         </is>
       </c>
       <c r="I49" s="5" t="inlineStr">
         <is>
-          <t>22 Sep 2026 08:25:10 PM</t>
+          <t>23 Sep 2026 02:53:32 PM</t>
         </is>
       </c>
       <c r="J49" s="5" t="inlineStr">
         <is>
-          <t>22 Sep 2026 11:24:09 AM</t>
+          <t>22 Sep 2026 01:51:09 PM</t>
         </is>
       </c>
       <c r="K49" s="5" t="inlineStr">
         <is>
-          <t>23 Sep 2026 03:46:01 PM</t>
+          <t>23 Sep 2026 02:53:32 PM</t>
         </is>
       </c>
       <c r="L49" s="5" t="inlineStr">
         <is>
-          <t>19h 20m</t>
+          <t>0m</t>
         </is>
       </c>
       <c r="M49" s="5" t="inlineStr">
         <is>
-          <t>1d 4h 21m</t>
+          <t>1d 1h 2m</t>
         </is>
       </c>
     </row>
@@ -12427,32 +12797,32 @@
     <row r="51">
       <c r="A51" s="5" t="inlineStr">
         <is>
-          <t>TKT1343067</t>
+          <t>TKT1342232</t>
         </is>
       </c>
       <c r="B51" s="5" t="inlineStr">
         <is>
-          <t>Aaryan Kumar Jha</t>
+          <t>Dipendra khanal</t>
         </is>
       </c>
       <c r="C51" s="5" t="inlineStr">
         <is>
-          <t>General / Other Issues</t>
+          <t>IPTV Related Issues</t>
         </is>
       </c>
       <c r="D51" s="5" t="inlineStr">
         <is>
-          <t>Router Upgrade  Wi-Fi 6</t>
+          <t>SKYCOM-Audio &amp; Video Syn Issue</t>
         </is>
       </c>
       <c r="E51" s="5" t="inlineStr">
         <is>
-          <t>Completed</t>
+          <t>Closed</t>
         </is>
       </c>
       <c r="F51" s="5" t="inlineStr">
         <is>
-          <t>Completed (Completed)</t>
+          <t>Completed (Closed)</t>
         </is>
       </c>
       <c r="G51" s="5" t="inlineStr">
@@ -12462,44 +12832,44 @@
       </c>
       <c r="H51" s="5" t="inlineStr">
         <is>
-          <t>Case : For upgradation to wifi6   has been updated by Chandramani Tharu</t>
+          <t>Case : IPTV  Isssue  has been updated by Sunil Chaudhary</t>
         </is>
       </c>
       <c r="I51" s="5" t="inlineStr">
         <is>
-          <t>23 Sep 2026 03:21:49 PM</t>
+          <t>22 Sep 2026 08:25:10 PM</t>
         </is>
       </c>
       <c r="J51" s="5" t="inlineStr">
         <is>
-          <t>22 Sep 2026 08:58:59 PM</t>
+          <t>22 Sep 2026 11:24:09 AM</t>
         </is>
       </c>
       <c r="K51" s="5" t="inlineStr">
         <is>
-          <t>23 Sep 2026 03:21:49 PM</t>
+          <t>23 Sep 2026 03:46:01 PM</t>
         </is>
       </c>
       <c r="L51" s="5" t="inlineStr">
         <is>
-          <t>0m</t>
+          <t>19h 20m</t>
         </is>
       </c>
       <c r="M51" s="5" t="inlineStr">
         <is>
-          <t>18h 22m</t>
+          <t>1d 4h 21m</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="3" t="inlineStr">
         <is>
-          <t>TKT1343673</t>
+          <t>TKT1343067</t>
         </is>
       </c>
       <c r="B52" s="3" t="inlineStr">
         <is>
-          <t>Bello World Pvt.Ltd</t>
+          <t>Aaryan Kumar Jha</t>
         </is>
       </c>
       <c r="C52" s="3" t="inlineStr">
@@ -12529,22 +12899,22 @@
       </c>
       <c r="H52" s="3" t="inlineStr">
         <is>
-          <t>Case : WIFI 6  has been updated by Rajesh Maharjan</t>
+          <t>Case : For upgradation to wifi6   has been updated by Chandramani Tharu</t>
         </is>
       </c>
       <c r="I52" s="3" t="inlineStr">
         <is>
-          <t>23 Sep 2026 03:58:20 PM</t>
+          <t>23 Sep 2026 03:21:49 PM</t>
         </is>
       </c>
       <c r="J52" s="3" t="inlineStr">
         <is>
-          <t>23 Sep 2026 12:25:04 PM</t>
+          <t>22 Sep 2026 08:58:59 PM</t>
         </is>
       </c>
       <c r="K52" s="3" t="inlineStr">
         <is>
-          <t>23 Sep 2026 03:58:20 PM</t>
+          <t>23 Sep 2026 03:21:49 PM</t>
         </is>
       </c>
       <c r="L52" s="3" t="inlineStr">
@@ -12554,19 +12924,19 @@
       </c>
       <c r="M52" s="3" t="inlineStr">
         <is>
-          <t>3h 33m</t>
+          <t>18h 22m</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="5" t="inlineStr">
         <is>
-          <t>TKT1343460</t>
+          <t>TKT1343673</t>
         </is>
       </c>
       <c r="B53" s="5" t="inlineStr">
         <is>
-          <t>GPRS Mobile</t>
+          <t>Bello World Pvt.Ltd</t>
         </is>
       </c>
       <c r="C53" s="5" t="inlineStr">
@@ -12581,12 +12951,12 @@
       </c>
       <c r="E53" s="5" t="inlineStr">
         <is>
-          <t>Closed</t>
+          <t>Completed</t>
         </is>
       </c>
       <c r="F53" s="5" t="inlineStr">
         <is>
-          <t>Completed (Closed)</t>
+          <t>Completed (Completed)</t>
         </is>
       </c>
       <c r="G53" s="5" t="inlineStr">
@@ -12596,32 +12966,32 @@
       </c>
       <c r="H53" s="5" t="inlineStr">
         <is>
-          <t>Case : wifi 6  has been updated by Ajit Shrestha</t>
+          <t>Case : WIFI 6  has been updated by Rajesh Maharjan</t>
         </is>
       </c>
       <c r="I53" s="5" t="inlineStr">
         <is>
-          <t>23 Sep 2026 10:29:49 AM</t>
+          <t>23 Sep 2026 03:58:20 PM</t>
         </is>
       </c>
       <c r="J53" s="5" t="inlineStr">
         <is>
-          <t>23 Sep 2026 10:29:49 AM</t>
+          <t>23 Sep 2026 12:25:04 PM</t>
         </is>
       </c>
       <c r="K53" s="5" t="inlineStr">
         <is>
-          <t>23 Sep 2026 03:48:08 PM</t>
+          <t>23 Sep 2026 03:58:20 PM</t>
         </is>
       </c>
       <c r="L53" s="5" t="inlineStr">
         <is>
-          <t>5h 18m</t>
+          <t>0m</t>
         </is>
       </c>
       <c r="M53" s="5" t="inlineStr">
         <is>
-          <t>5h 18m</t>
+          <t>3h 33m</t>
         </is>
       </c>
     </row>
@@ -12695,12 +13065,12 @@
     <row r="55">
       <c r="A55" s="5" t="inlineStr">
         <is>
-          <t>TKT1343757</t>
+          <t>TKT1343460</t>
         </is>
       </c>
       <c r="B55" s="5" t="inlineStr">
         <is>
-          <t>Manish Poudel</t>
+          <t>GPRS Mobile</t>
         </is>
       </c>
       <c r="C55" s="5" t="inlineStr">
@@ -12715,12 +13085,12 @@
       </c>
       <c r="E55" s="5" t="inlineStr">
         <is>
-          <t>Completed</t>
+          <t>Closed</t>
         </is>
       </c>
       <c r="F55" s="5" t="inlineStr">
         <is>
-          <t>Completed (Completed)</t>
+          <t>Completed (Closed)</t>
         </is>
       </c>
       <c r="G55" s="5" t="inlineStr">
@@ -12730,44 +13100,44 @@
       </c>
       <c r="H55" s="5" t="inlineStr">
         <is>
-          <t>Case : wifi6  has been updated by Sabin Giri</t>
+          <t>Case : wifi 6  has been updated by Ajit Shrestha</t>
         </is>
       </c>
       <c r="I55" s="5" t="inlineStr">
         <is>
-          <t>23 Sep 2026 04:03:26 PM</t>
+          <t>23 Sep 2026 10:29:49 AM</t>
         </is>
       </c>
       <c r="J55" s="5" t="inlineStr">
         <is>
-          <t>23 Sep 2026 01:35:27 PM</t>
+          <t>23 Sep 2026 10:29:49 AM</t>
         </is>
       </c>
       <c r="K55" s="5" t="inlineStr">
         <is>
-          <t>23 Sep 2026 04:03:26 PM</t>
+          <t>23 Sep 2026 03:48:08 PM</t>
         </is>
       </c>
       <c r="L55" s="5" t="inlineStr">
         <is>
-          <t>0m</t>
+          <t>5h 18m</t>
         </is>
       </c>
       <c r="M55" s="5" t="inlineStr">
         <is>
-          <t>2h 27m</t>
+          <t>5h 18m</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="3" t="inlineStr">
         <is>
-          <t>TKT1343695</t>
+          <t>TKT1343757</t>
         </is>
       </c>
       <c r="B56" s="3" t="inlineStr">
         <is>
-          <t>Kabiraj Maharjan</t>
+          <t>Manish Poudel</t>
         </is>
       </c>
       <c r="C56" s="3" t="inlineStr">
@@ -12782,12 +13152,12 @@
       </c>
       <c r="E56" s="3" t="inlineStr">
         <is>
-          <t>Closed</t>
+          <t>Completed</t>
         </is>
       </c>
       <c r="F56" s="3" t="inlineStr">
         <is>
-          <t>Completed (Closed)</t>
+          <t>Completed (Completed)</t>
         </is>
       </c>
       <c r="G56" s="3" t="inlineStr">
@@ -12797,64 +13167,64 @@
       </c>
       <c r="H56" s="3" t="inlineStr">
         <is>
-          <t>Case : Wifi 6  has been updated by Sunil Chaudhary</t>
+          <t>Case : wifi6  has been updated by Sabin Giri</t>
         </is>
       </c>
       <c r="I56" s="3" t="inlineStr">
         <is>
-          <t>23 Sep 2026 12:45:30 PM</t>
+          <t>23 Sep 2026 04:03:26 PM</t>
         </is>
       </c>
       <c r="J56" s="3" t="inlineStr">
         <is>
-          <t>23 Sep 2026 12:45:30 PM</t>
+          <t>23 Sep 2026 01:35:27 PM</t>
         </is>
       </c>
       <c r="K56" s="3" t="inlineStr">
         <is>
-          <t>23 Sep 2026 04:15:46 PM</t>
+          <t>23 Sep 2026 04:03:26 PM</t>
         </is>
       </c>
       <c r="L56" s="3" t="inlineStr">
         <is>
-          <t>3h 30m</t>
+          <t>0m</t>
         </is>
       </c>
       <c r="M56" s="3" t="inlineStr">
         <is>
-          <t>3h 30m</t>
+          <t>2h 27m</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="5" t="inlineStr">
         <is>
-          <t>TKT1342535</t>
+          <t>TKT1343695</t>
         </is>
       </c>
       <c r="B57" s="5" t="inlineStr">
         <is>
-          <t>madan shahi</t>
+          <t>Kabiraj Maharjan</t>
         </is>
       </c>
       <c r="C57" s="5" t="inlineStr">
         <is>
-          <t>Slow Internet Connection</t>
+          <t>General / Other Issues</t>
         </is>
       </c>
       <c r="D57" s="5" t="inlineStr">
         <is>
-          <t>Video content is Buffering</t>
+          <t>Router Upgrade  Wi-Fi 6</t>
         </is>
       </c>
       <c r="E57" s="5" t="inlineStr">
         <is>
-          <t>Completed</t>
+          <t>Closed</t>
         </is>
       </c>
       <c r="F57" s="5" t="inlineStr">
         <is>
-          <t>Completed (Completed)</t>
+          <t>Completed (Closed)</t>
         </is>
       </c>
       <c r="G57" s="5" t="inlineStr">
@@ -12864,54 +13234,54 @@
       </c>
       <c r="H57" s="5" t="inlineStr">
         <is>
-          <t>Case : slow issue field visit  has been updated by Chandramani Tharu</t>
+          <t>Case : Wifi 6  has been updated by Sunil Chaudhary</t>
         </is>
       </c>
       <c r="I57" s="5" t="inlineStr">
         <is>
-          <t>23 Sep 2026 04:06:38 PM</t>
+          <t>23 Sep 2026 12:45:30 PM</t>
         </is>
       </c>
       <c r="J57" s="5" t="inlineStr">
         <is>
-          <t>22 Sep 2026 02:45:24 PM</t>
+          <t>23 Sep 2026 12:45:30 PM</t>
         </is>
       </c>
       <c r="K57" s="5" t="inlineStr">
         <is>
-          <t>23 Sep 2026 04:06:38 PM</t>
+          <t>23 Sep 2026 04:15:46 PM</t>
         </is>
       </c>
       <c r="L57" s="5" t="inlineStr">
         <is>
-          <t>0m</t>
+          <t>3h 30m</t>
         </is>
       </c>
       <c r="M57" s="5" t="inlineStr">
         <is>
-          <t>1d 1h 21m</t>
+          <t>3h 30m</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="3" t="inlineStr">
         <is>
-          <t>TKT1343717</t>
+          <t>TKT1342535</t>
         </is>
       </c>
       <c r="B58" s="3" t="inlineStr">
         <is>
-          <t>Jagaran Media Center</t>
+          <t>madan shahi</t>
         </is>
       </c>
       <c r="C58" s="3" t="inlineStr">
         <is>
-          <t>General / Other Issues</t>
+          <t>Slow Internet Connection</t>
         </is>
       </c>
       <c r="D58" s="3" t="inlineStr">
         <is>
-          <t>Router Upgrade  Wi-Fi 6</t>
+          <t>Video content is Buffering</t>
         </is>
       </c>
       <c r="E58" s="3" t="inlineStr">
@@ -12931,22 +13301,22 @@
       </c>
       <c r="H58" s="3" t="inlineStr">
         <is>
-          <t>Case : WIFI6 Router Upgrade   has been updated by Chandramani Tharu</t>
+          <t>Case : slow issue field visit  has been updated by Chandramani Tharu</t>
         </is>
       </c>
       <c r="I58" s="3" t="inlineStr">
         <is>
-          <t>23 Sep 2026 04:42:34 PM</t>
+          <t>23 Sep 2026 04:06:38 PM</t>
         </is>
       </c>
       <c r="J58" s="3" t="inlineStr">
         <is>
-          <t>23 Sep 2026 12:59:27 PM</t>
+          <t>22 Sep 2026 02:45:24 PM</t>
         </is>
       </c>
       <c r="K58" s="3" t="inlineStr">
         <is>
-          <t>23 Sep 2026 04:42:34 PM</t>
+          <t>23 Sep 2026 04:06:38 PM</t>
         </is>
       </c>
       <c r="L58" s="3" t="inlineStr">
@@ -12956,29 +13326,29 @@
       </c>
       <c r="M58" s="3" t="inlineStr">
         <is>
-          <t>3h 43m</t>
+          <t>1d 1h 21m</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="5" t="inlineStr">
         <is>
-          <t>TKT1342843</t>
+          <t>TKT1343717</t>
         </is>
       </c>
       <c r="B59" s="5" t="inlineStr">
         <is>
-          <t>Krishna Prasad Paudel</t>
+          <t>Jagaran Media Center</t>
         </is>
       </c>
       <c r="C59" s="5" t="inlineStr">
         <is>
-          <t>Slow Internet Connection</t>
+          <t>General / Other Issues</t>
         </is>
       </c>
       <c r="D59" s="5" t="inlineStr">
         <is>
-          <t>Video content is Buffering</t>
+          <t>Router Upgrade  Wi-Fi 6</t>
         </is>
       </c>
       <c r="E59" s="5" t="inlineStr">
@@ -12998,22 +13368,22 @@
       </c>
       <c r="H59" s="5" t="inlineStr">
         <is>
-          <t>Case : SLOW ISSUE   has been updated by Shashikant Chaudhary</t>
+          <t>Case : WIFI6 Router Upgrade   has been updated by Chandramani Tharu</t>
         </is>
       </c>
       <c r="I59" s="5" t="inlineStr">
         <is>
-          <t>23 Sep 2026 04:36:44 PM</t>
+          <t>23 Sep 2026 04:42:34 PM</t>
         </is>
       </c>
       <c r="J59" s="5" t="inlineStr">
         <is>
-          <t>22 Sep 2026 05:38:25 PM</t>
+          <t>23 Sep 2026 12:59:27 PM</t>
         </is>
       </c>
       <c r="K59" s="5" t="inlineStr">
         <is>
-          <t>23 Sep 2026 04:36:44 PM</t>
+          <t>23 Sep 2026 04:42:34 PM</t>
         </is>
       </c>
       <c r="L59" s="5" t="inlineStr">
@@ -13023,39 +13393,39 @@
       </c>
       <c r="M59" s="5" t="inlineStr">
         <is>
-          <t>22h 58m</t>
+          <t>3h 43m</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="3" t="inlineStr">
         <is>
-          <t>TKT1343427</t>
+          <t>TKT1342843</t>
         </is>
       </c>
       <c r="B60" s="3" t="inlineStr">
         <is>
-          <t>Aryan Tibrewal</t>
+          <t>Krishna Prasad Paudel</t>
         </is>
       </c>
       <c r="C60" s="3" t="inlineStr">
         <is>
-          <t>General / Other Issues</t>
+          <t>Slow Internet Connection</t>
         </is>
       </c>
       <c r="D60" s="3" t="inlineStr">
         <is>
-          <t>Router Upgrade  Wi-Fi 6</t>
+          <t>Video content is Buffering</t>
         </is>
       </c>
       <c r="E60" s="3" t="inlineStr">
         <is>
-          <t>Closed</t>
+          <t>Completed</t>
         </is>
       </c>
       <c r="F60" s="3" t="inlineStr">
         <is>
-          <t>Completed (Closed)</t>
+          <t>Completed (Completed)</t>
         </is>
       </c>
       <c r="G60" s="3" t="inlineStr">
@@ -13065,32 +13435,32 @@
       </c>
       <c r="H60" s="3" t="inlineStr">
         <is>
-          <t>Case : Wifi 6 Router   has been updated by Ajit Shrestha</t>
+          <t>Case : SLOW ISSUE   has been updated by Shashikant Chaudhary</t>
         </is>
       </c>
       <c r="I60" s="3" t="inlineStr">
         <is>
-          <t>23 Sep 2026 10:12:54 AM</t>
+          <t>23 Sep 2026 04:36:44 PM</t>
         </is>
       </c>
       <c r="J60" s="3" t="inlineStr">
         <is>
-          <t>23 Sep 2026 10:12:54 AM</t>
+          <t>22 Sep 2026 05:38:25 PM</t>
         </is>
       </c>
       <c r="K60" s="3" t="inlineStr">
         <is>
-          <t>23 Sep 2026 04:35:13 PM</t>
+          <t>23 Sep 2026 04:36:44 PM</t>
         </is>
       </c>
       <c r="L60" s="3" t="inlineStr">
         <is>
-          <t>6h 22m</t>
+          <t>0m</t>
         </is>
       </c>
       <c r="M60" s="3" t="inlineStr">
         <is>
-          <t>6h 22m</t>
+          <t>22h 58m</t>
         </is>
       </c>
     </row>
@@ -13164,12 +13534,12 @@
     <row r="62">
       <c r="A62" s="3" t="inlineStr">
         <is>
-          <t>TKT1342270</t>
+          <t>TKT1343427</t>
         </is>
       </c>
       <c r="B62" s="3" t="inlineStr">
         <is>
-          <t>Ayush Shakya</t>
+          <t>Aryan Tibrewal</t>
         </is>
       </c>
       <c r="C62" s="3" t="inlineStr">
@@ -13184,12 +13554,12 @@
       </c>
       <c r="E62" s="3" t="inlineStr">
         <is>
-          <t>Completed</t>
+          <t>Closed</t>
         </is>
       </c>
       <c r="F62" s="3" t="inlineStr">
         <is>
-          <t>Completed (Completed)</t>
+          <t>Completed (Closed)</t>
         </is>
       </c>
       <c r="G62" s="3" t="inlineStr">
@@ -13199,64 +13569,64 @@
       </c>
       <c r="H62" s="3" t="inlineStr">
         <is>
-          <t>Case : wifi 6 upgrade  has been updated by Rajesh Maharjan</t>
+          <t>Case : Wifi 6 Router   has been updated by Ajit Shrestha</t>
         </is>
       </c>
       <c r="I62" s="3" t="inlineStr">
         <is>
-          <t>23 Sep 2026 04:34:58 PM</t>
+          <t>23 Sep 2026 10:12:54 AM</t>
         </is>
       </c>
       <c r="J62" s="3" t="inlineStr">
         <is>
-          <t>22 Sep 2026 11:39:34 AM</t>
+          <t>23 Sep 2026 10:12:54 AM</t>
         </is>
       </c>
       <c r="K62" s="3" t="inlineStr">
         <is>
-          <t>23 Sep 2026 04:34:58 PM</t>
+          <t>23 Sep 2026 04:35:13 PM</t>
         </is>
       </c>
       <c r="L62" s="3" t="inlineStr">
         <is>
-          <t>0m</t>
+          <t>6h 22m</t>
         </is>
       </c>
       <c r="M62" s="3" t="inlineStr">
         <is>
-          <t>1d 4h 55m</t>
+          <t>6h 22m</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="5" t="inlineStr">
         <is>
-          <t>TKT1342776</t>
+          <t>TKT1342270</t>
         </is>
       </c>
       <c r="B63" s="5" t="inlineStr">
         <is>
-          <t>Bimala Thapa</t>
+          <t>Ayush Shakya</t>
         </is>
       </c>
       <c r="C63" s="5" t="inlineStr">
         <is>
-          <t>Hardware Damage / Malfunction</t>
+          <t>General / Other Issues</t>
         </is>
       </c>
       <c r="D63" s="5" t="inlineStr">
         <is>
-          <t>IPTV STB box Damage Issue</t>
+          <t>Router Upgrade  Wi-Fi 6</t>
         </is>
       </c>
       <c r="E63" s="5" t="inlineStr">
         <is>
-          <t>Closed</t>
+          <t>Completed</t>
         </is>
       </c>
       <c r="F63" s="5" t="inlineStr">
         <is>
-          <t>Completed (Closed)</t>
+          <t>Completed (Completed)</t>
         </is>
       </c>
       <c r="G63" s="5" t="inlineStr">
@@ -13266,32 +13636,32 @@
       </c>
       <c r="H63" s="5" t="inlineStr">
         <is>
-          <t>Case : SETUP BOX FAULTY   has been updated by Sunil Chaudhary</t>
+          <t>Case : wifi 6 upgrade  has been updated by Rajesh Maharjan</t>
         </is>
       </c>
       <c r="I63" s="5" t="inlineStr">
         <is>
-          <t>22 Sep 2026 05:21:05 PM</t>
+          <t>23 Sep 2026 04:34:58 PM</t>
         </is>
       </c>
       <c r="J63" s="5" t="inlineStr">
         <is>
-          <t>22 Sep 2026 04:56:20 PM</t>
+          <t>22 Sep 2026 11:39:34 AM</t>
         </is>
       </c>
       <c r="K63" s="5" t="inlineStr">
         <is>
-          <t>23 Sep 2026 04:40:21 PM</t>
+          <t>23 Sep 2026 04:34:58 PM</t>
         </is>
       </c>
       <c r="L63" s="5" t="inlineStr">
         <is>
-          <t>23h 19m</t>
+          <t>0m</t>
         </is>
       </c>
       <c r="M63" s="5" t="inlineStr">
         <is>
-          <t>23h 44m</t>
+          <t>1d 4h 55m</t>
         </is>
       </c>
     </row>
@@ -13365,22 +13735,22 @@
     <row r="65">
       <c r="A65" s="5" t="inlineStr">
         <is>
-          <t>TKT1343676</t>
+          <t>TKT1342776</t>
         </is>
       </c>
       <c r="B65" s="5" t="inlineStr">
         <is>
-          <t>Ajay Khakurel</t>
+          <t>Bimala Thapa</t>
         </is>
       </c>
       <c r="C65" s="5" t="inlineStr">
         <is>
-          <t>General / Other Issues</t>
+          <t>Hardware Damage / Malfunction</t>
         </is>
       </c>
       <c r="D65" s="5" t="inlineStr">
         <is>
-          <t>Router Upgrade  Wi-Fi 6</t>
+          <t>IPTV STB box Damage Issue</t>
         </is>
       </c>
       <c r="E65" s="5" t="inlineStr">
@@ -13400,44 +13770,44 @@
       </c>
       <c r="H65" s="5" t="inlineStr">
         <is>
-          <t>Case : Wifi 6 router exchange   has been updated by Ajit Shrestha</t>
+          <t>Case : SETUP BOX FAULTY   has been updated by Sunil Chaudhary</t>
         </is>
       </c>
       <c r="I65" s="5" t="inlineStr">
         <is>
-          <t>23 Sep 2026 12:26:51 PM</t>
+          <t>22 Sep 2026 05:21:05 PM</t>
         </is>
       </c>
       <c r="J65" s="5" t="inlineStr">
         <is>
-          <t>23 Sep 2026 12:26:51 PM</t>
+          <t>22 Sep 2026 04:56:20 PM</t>
         </is>
       </c>
       <c r="K65" s="5" t="inlineStr">
         <is>
-          <t>23 Sep 2026 04:56:51 PM</t>
+          <t>23 Sep 2026 04:40:21 PM</t>
         </is>
       </c>
       <c r="L65" s="5" t="inlineStr">
         <is>
-          <t>4h 30m</t>
+          <t>23h 19m</t>
         </is>
       </c>
       <c r="M65" s="5" t="inlineStr">
         <is>
-          <t>4h 30m</t>
+          <t>23h 44m</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="3" t="inlineStr">
         <is>
-          <t>TKT1343738</t>
+          <t>TKT1343676</t>
         </is>
       </c>
       <c r="B66" s="3" t="inlineStr">
         <is>
-          <t>CT Rental and Event Management Pvt Ltd</t>
+          <t>Ajay Khakurel</t>
         </is>
       </c>
       <c r="C66" s="3" t="inlineStr">
@@ -13467,32 +13837,32 @@
       </c>
       <c r="H66" s="3" t="inlineStr">
         <is>
-          <t>Case : wifi 6  has been updated by Sunil Chaudhary</t>
+          <t>Case : Wifi 6 router exchange   has been updated by Ajit Shrestha</t>
         </is>
       </c>
       <c r="I66" s="3" t="inlineStr">
         <is>
-          <t>23 Sep 2026 01:21:11 PM</t>
+          <t>23 Sep 2026 12:26:51 PM</t>
         </is>
       </c>
       <c r="J66" s="3" t="inlineStr">
         <is>
-          <t>23 Sep 2026 01:16:34 PM</t>
+          <t>23 Sep 2026 12:26:51 PM</t>
         </is>
       </c>
       <c r="K66" s="3" t="inlineStr">
         <is>
-          <t>23 Sep 2026 05:15:07 PM</t>
+          <t>23 Sep 2026 04:56:51 PM</t>
         </is>
       </c>
       <c r="L66" s="3" t="inlineStr">
         <is>
-          <t>3h 53m</t>
+          <t>4h 30m</t>
         </is>
       </c>
       <c r="M66" s="3" t="inlineStr">
         <is>
-          <t>3h 58m</t>
+          <t>4h 30m</t>
         </is>
       </c>
     </row>
@@ -13566,65 +13936,132 @@
     <row r="68">
       <c r="A68" s="3" t="inlineStr">
         <is>
+          <t>TKT1343738</t>
+        </is>
+      </c>
+      <c r="B68" s="3" t="inlineStr">
+        <is>
+          <t>CT Rental and Event Management Pvt Ltd</t>
+        </is>
+      </c>
+      <c r="C68" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="D68" s="3" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="E68" s="3" t="inlineStr">
+        <is>
+          <t>Closed</t>
+        </is>
+      </c>
+      <c r="F68" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Closed)</t>
+        </is>
+      </c>
+      <c r="G68" s="3" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="H68" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi 6  has been updated by Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="I68" s="3" t="inlineStr">
+        <is>
+          <t>23 Sep 2026 01:21:11 PM</t>
+        </is>
+      </c>
+      <c r="J68" s="3" t="inlineStr">
+        <is>
+          <t>23 Sep 2026 01:16:34 PM</t>
+        </is>
+      </c>
+      <c r="K68" s="3" t="inlineStr">
+        <is>
+          <t>23 Sep 2026 05:15:07 PM</t>
+        </is>
+      </c>
+      <c r="L68" s="3" t="inlineStr">
+        <is>
+          <t>3h 53m</t>
+        </is>
+      </c>
+      <c r="M68" s="3" t="inlineStr">
+        <is>
+          <t>3h 58m</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" s="5" t="inlineStr">
+        <is>
           <t>TKT1343449</t>
         </is>
       </c>
-      <c r="B68" s="3" t="inlineStr">
+      <c r="B69" s="5" t="inlineStr">
         <is>
           <t>Kirti Kiran Joshi</t>
         </is>
       </c>
-      <c r="C68" s="3" t="inlineStr">
+      <c r="C69" s="5" t="inlineStr">
         <is>
           <t>General / Other Issues</t>
         </is>
       </c>
-      <c r="D68" s="3" t="inlineStr">
+      <c r="D69" s="5" t="inlineStr">
         <is>
           <t>Router Upgrade  Wi-Fi 6</t>
         </is>
       </c>
-      <c r="E68" s="3" t="inlineStr">
+      <c r="E69" s="5" t="inlineStr">
         <is>
           <t>Completed</t>
         </is>
       </c>
-      <c r="F68" s="3" t="inlineStr">
+      <c r="F69" s="5" t="inlineStr">
         <is>
           <t>Completed (Completed)</t>
         </is>
       </c>
-      <c r="G68" s="3" t="inlineStr">
+      <c r="G69" s="5" t="inlineStr">
         <is>
           <t>nan</t>
         </is>
       </c>
-      <c r="H68" s="3" t="inlineStr">
+      <c r="H69" s="5" t="inlineStr">
         <is>
           <t>Case : wifi 6  has been updated by Chandramani Tharu</t>
         </is>
       </c>
-      <c r="I68" s="3" t="inlineStr">
+      <c r="I69" s="5" t="inlineStr">
         <is>
           <t>23 Sep 2026 05:32:18 PM</t>
         </is>
       </c>
-      <c r="J68" s="3" t="inlineStr">
+      <c r="J69" s="5" t="inlineStr">
         <is>
           <t>23 Sep 2026 10:26:05 AM</t>
         </is>
       </c>
-      <c r="K68" s="3" t="inlineStr">
+      <c r="K69" s="5" t="inlineStr">
         <is>
           <t>23 Sep 2026 05:32:18 PM</t>
         </is>
       </c>
-      <c r="L68" s="3" t="inlineStr">
+      <c r="L69" s="5" t="inlineStr">
         <is>
           <t>0m</t>
         </is>
       </c>
-      <c r="M68" s="3" t="inlineStr">
+      <c r="M69" s="5" t="inlineStr">
         <is>
           <t>7h 6m</t>
         </is>

--- a/audit_report_ALL_TEAM_23_Sep_2026.xlsx
+++ b/audit_report_ALL_TEAM_23_Sep_2026.xlsx
@@ -529,7 +529,7 @@
     <col width="27" customWidth="1" min="41" max="41"/>
     <col width="12" customWidth="1" min="42" max="42"/>
     <col width="17" customWidth="1" min="43" max="43"/>
-    <col width="40" customWidth="1" min="44" max="44"/>
+    <col width="34" customWidth="1" min="44" max="44"/>
     <col width="34" customWidth="1" min="45" max="45"/>
     <col width="33" customWidth="1" min="46" max="46"/>
     <col width="36" customWidth="1" min="47" max="47"/>
@@ -10615,10 +10615,8 @@
           <t>samrat shrestha</t>
         </is>
       </c>
-      <c r="O54" s="3" t="inlineStr">
-        <is>
-          <t>9820084508</t>
-        </is>
+      <c r="O54" s="3" t="n">
+        <v>9820084508</v>
       </c>
       <c r="P54" s="3" t="inlineStr">
         <is>
@@ -10704,10 +10702,8 @@
           <t>Ajit Shrestha</t>
         </is>
       </c>
-      <c r="AN54" s="3" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
+      <c r="AN54" s="3" t="n">
+        <v>6</v>
       </c>
       <c r="AO54" s="3" t="inlineStr">
         <is>
@@ -10718,7 +10714,7 @@
       <c r="AQ54" s="3" t="inlineStr"/>
       <c r="AR54" s="3" t="inlineStr">
         <is>
-          <t>Case : wifi 6 upgrade  has been viewed by Sunil Chaudhary</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="AS54" s="3" t="inlineStr">
@@ -10818,10 +10814,8 @@
           <t>Mission shrestha</t>
         </is>
       </c>
-      <c r="O55" s="3" t="inlineStr">
-        <is>
-          <t>9840344764</t>
-        </is>
+      <c r="O55" s="3" t="n">
+        <v>9840344764</v>
       </c>
       <c r="P55" s="3" t="inlineStr">
         <is>
@@ -10856,10 +10850,8 @@
           <t>Active</t>
         </is>
       </c>
-      <c r="Y55" s="3" t="inlineStr">
-        <is>
-          <t>27.69903</t>
-        </is>
+      <c r="Y55" s="3" t="n">
+        <v>27.69903</v>
       </c>
       <c r="Z55" s="3" t="inlineStr">
         <is>
@@ -10911,25 +10903,21 @@
           <t>Bishal Karki</t>
         </is>
       </c>
-      <c r="AN55" s="3" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
+      <c r="AN55" s="3" t="n">
+        <v>4</v>
       </c>
       <c r="AO55" s="3" t="inlineStr">
         <is>
           <t>1,7</t>
         </is>
       </c>
-      <c r="AP55" s="3" t="inlineStr">
-        <is>
-          <t>85.24414</t>
-        </is>
+      <c r="AP55" s="3" t="n">
+        <v>85.24414</v>
       </c>
       <c r="AQ55" s="3" t="inlineStr"/>
       <c r="AR55" s="3" t="inlineStr">
         <is>
-          <t>Case : iptv issue   has been viewed by Sunil Chaudhary</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="AS55" s="3" t="inlineStr">
